--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37FB8B5-E76D-43B3-8A6F-90835019DEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656BA3F6-89D7-41CB-8076-878DCD4A9330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
   <sheets>
     <sheet name="literature review" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="289">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -910,6 +910,27 @@
   </si>
   <si>
     <t>kind of</t>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9740968/</t>
+  </si>
+  <si>
+    <t>Early Detection and Control of the Next Epidemic Wave Using Health Communications: Development of an Artificial Intelligence-Based Tool and Its Validation on COVID-19 Data from the US</t>
+  </si>
+  <si>
+    <t>Social-Media</t>
+  </si>
+  <si>
+    <t>Check tweets, reddits, etc with LLM to see if frequency of symptoms is on the rise, then fit a GGM on top of it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use brandwatch or reddit </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Varicela</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{354077A2-E602-4D9A-90DA-98AD5E623913}">
-  <dimension ref="B1:Q26"/>
+  <dimension ref="B1:Q27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -1816,6 +1837,26 @@
       </c>
       <c r="F26" s="1" t="s">
         <v>230</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B27" s="1">
+        <v>24</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -1844,6 +1885,7 @@
     <hyperlink ref="E24" r:id="rId22" xr:uid="{EAAB6CA0-E60C-4CCA-9A60-6D6314C9AA39}"/>
     <hyperlink ref="E25" r:id="rId23" xr:uid="{4730B165-77B9-44CC-96F1-5D46B06A3B46}"/>
     <hyperlink ref="E26" r:id="rId24" xr:uid="{27F3ABE4-E9A8-4610-B13D-775FBB8CFAA5}"/>
+    <hyperlink ref="E27" r:id="rId25" xr:uid="{9C94BE50-1EBB-4A1E-992C-64AF15F3BEC8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2440,7 +2482,7 @@
         <v>145</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>244</v>
@@ -2780,7 +2822,7 @@
         <v>145</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.3">
@@ -2956,7 +2998,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2EA5AC-0586-4893-B88A-0F9AA6E9FD44}">
-  <dimension ref="B1:BE46"/>
+  <dimension ref="B1:BJ46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -2981,33 +3023,39 @@
     <col min="23" max="23" width="8.33203125" style="1" customWidth="1"/>
     <col min="24" max="24" width="10.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="2" style="20" customWidth="1"/>
-    <col min="26" max="26" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.109375" style="1" customWidth="1"/>
-    <col min="32" max="32" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="2" style="20" customWidth="1"/>
-    <col min="34" max="36" width="12.109375" style="1" customWidth="1"/>
-    <col min="37" max="37" width="2" style="20" customWidth="1"/>
-    <col min="38" max="40" width="12.109375" style="1" customWidth="1"/>
-    <col min="41" max="41" width="2" style="20" customWidth="1"/>
-    <col min="42" max="42" width="15.109375" style="1" customWidth="1"/>
-    <col min="43" max="45" width="8.88671875" style="1"/>
+    <col min="26" max="28" width="10.109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="2" style="20" customWidth="1"/>
+    <col min="30" max="30" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.109375" style="1" customWidth="1"/>
+    <col min="36" max="36" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.109375" style="1" customWidth="1"/>
+    <col min="38" max="38" width="2" style="20" customWidth="1"/>
+    <col min="39" max="41" width="12.109375" style="1" customWidth="1"/>
+    <col min="42" max="42" width="2" style="20" customWidth="1"/>
+    <col min="43" max="45" width="12.109375" style="1" customWidth="1"/>
     <col min="46" max="46" width="2" style="20" customWidth="1"/>
-    <col min="47" max="49" width="8.88671875" style="1"/>
-    <col min="50" max="50" width="2" style="20" customWidth="1"/>
-    <col min="51" max="51" width="11.88671875" style="1" customWidth="1"/>
-    <col min="52" max="55" width="8.88671875" style="1"/>
-    <col min="56" max="56" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="16384" width="8.88671875" style="1"/>
+    <col min="47" max="47" width="15.109375" style="1" customWidth="1"/>
+    <col min="48" max="50" width="8.88671875" style="1"/>
+    <col min="51" max="51" width="2" style="20" customWidth="1"/>
+    <col min="52" max="54" width="8.88671875" style="1"/>
+    <col min="55" max="55" width="2" style="20" customWidth="1"/>
+    <col min="56" max="56" width="11.88671875" style="1" customWidth="1"/>
+    <col min="57" max="60" width="8.88671875" style="1"/>
+    <col min="61" max="61" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:57" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:62" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="2" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="AC1" s="20" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="2" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
         <v>186</v>
       </c>
@@ -3026,27 +3074,30 @@
       </c>
       <c r="W2" s="19"/>
       <c r="Z2" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="AD2" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AH2" s="19" t="s">
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="19"/>
+      <c r="AM2" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="AL2" s="19" t="s">
+      <c r="AQ2" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="AP2" s="19" t="s">
+      <c r="AU2" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="AU2" s="19" t="s">
+      <c r="AZ2" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="AY2" s="19" t="s">
+      <c r="BD2" s="19" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
         <v>181</v>
       </c>
@@ -3065,25 +3116,28 @@
       <c r="Z4" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AH4" s="13" t="s">
+      <c r="AD4" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="AE4" s="13"/>
+      <c r="AF4" s="13"/>
+      <c r="AM4" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="AL4" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="AP4" s="13" t="s">
+      <c r="AQ4" s="13" t="s">
         <v>198</v>
       </c>
       <c r="AU4" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="AY4" s="13" t="s">
+      <c r="AZ4" s="13" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="6" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="BD4" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>166</v>
       </c>
@@ -3145,46 +3199,46 @@
         <v>166</v>
       </c>
       <c r="AA6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE6" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="AB6" s="9" t="s">
+      <c r="AF6" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="AC6" s="9" t="s">
+      <c r="AG6" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="AD6" s="9" t="s">
+      <c r="AH6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AE6" s="9" t="s">
+      <c r="AI6" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="AF6" s="9" t="s">
+      <c r="AJ6" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="AH6" s="9" t="s">
+      <c r="AK6" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="AM6" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="AI6" s="9" t="s">
+      <c r="AN6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AJ6" s="9" t="s">
+      <c r="AO6" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="AL6" s="9" t="s">
+      <c r="AQ6" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="AM6" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="AN6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="AP6" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="AQ6" s="9" t="s">
-        <v>134</v>
       </c>
       <c r="AR6" s="9" t="s">
         <v>187</v>
@@ -3196,32 +3250,44 @@
         <v>195</v>
       </c>
       <c r="AV6" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="AW6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AW6" s="9" t="s">
+      <c r="AX6" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="AY6" s="9" t="s">
+      <c r="AZ6" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="AZ6" s="9" t="s">
+      <c r="BA6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BB6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="BD6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="BE6" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="BA6" s="9" t="s">
+      <c r="BF6" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="BB6" s="9" t="s">
+      <c r="BG6" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="BC6" s="9" t="s">
+      <c r="BH6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="BD6" s="9" t="s">
+      <c r="BI6" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="BE6" s="9"/>
-    </row>
-    <row r="7" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="BJ6" s="9"/>
+    </row>
+    <row r="7" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>171</v>
       </c>
@@ -3284,94 +3350,107 @@
       <c r="Z7" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="AA7" s="14">
-        <f>+_xlfn.XLOOKUP($Z7,N$7:N$16,P$7:P$16)</f>
+      <c r="AA7" s="32">
+        <v>0.99995000000000001</v>
+      </c>
+      <c r="AB7" s="14">
+        <v>91507.114184000005</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE7" s="14">
+        <f>+_xlfn.XLOOKUP($AD7,N$7:N$16,P$7:P$16)</f>
         <v>15217290</v>
       </c>
-      <c r="AB7" s="14">
-        <f>+_xlfn.XLOOKUP($Z7,R$7:R$16,T$7:T$16)</f>
+      <c r="AF7" s="14">
+        <f>+_xlfn.XLOOKUP($AD7,R$7:R$16,T$7:T$16)</f>
         <v>13264390</v>
       </c>
-      <c r="AC7" s="14">
-        <f>+_xlfn.XLOOKUP($Z7,B$7:B$16,D$7:D$16)</f>
+      <c r="AG7" s="14">
+        <f>+_xlfn.XLOOKUP($AD7,B$7:B$16,D$7:D$16)</f>
         <v>12385875.99</v>
       </c>
-      <c r="AD7" s="14">
-        <f>+_xlfn.XLOOKUP($Z7,B$7:B$16,F$7:F$16)</f>
+      <c r="AH7" s="14">
+        <f>+_xlfn.XLOOKUP($AD7,B$7:B$16,F$7:F$16)</f>
         <v>1529515.1</v>
       </c>
-      <c r="AE7" s="14">
-        <f>+_xlfn.XLOOKUP($Z7,V$7:V$16,X$7:X$16)</f>
+      <c r="AI7" s="14">
+        <f>+_xlfn.XLOOKUP($AD7,V$7:V$16,X$7:X$16)</f>
         <v>15940.183487</v>
       </c>
-      <c r="AF7" s="14">
-        <f t="shared" ref="AF7:AF16" si="0">+_xlfn.XLOOKUP($Z7,I$7:I$16,K$7:K$16)</f>
+      <c r="AJ7" s="14">
+        <f t="shared" ref="AJ7:AJ16" si="0">+_xlfn.XLOOKUP($AD7,I$7:I$16,K$7:K$16)</f>
         <v>15681.4452</v>
       </c>
-      <c r="AH7" s="1" t="s">
+      <c r="AK7" s="14">
+        <f>+_xlfn.XLOOKUP(AD7,$Z$7:$Z$16,$AB$7:$AB$16)</f>
+        <v>91507.114184000005</v>
+      </c>
+      <c r="AM7" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AI7" s="12">
+      <c r="AN7" s="12">
         <v>0.94224399999999997</v>
       </c>
-      <c r="AJ7" s="14">
+      <c r="AO7" s="14">
         <v>4703.6260300000004</v>
       </c>
-      <c r="AL7" s="1" t="s">
+      <c r="AQ7" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AM7" s="12">
-        <v>0.91781400000000002</v>
-      </c>
-      <c r="AN7" s="14">
-        <v>5610.9171020000003</v>
-      </c>
-      <c r="AP7" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="AQ7" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="AR7" s="12">
-        <v>-0.25174930000000001</v>
+        <v>0.91772100000000001</v>
       </c>
       <c r="AS7" s="14">
-        <v>210875.2597</v>
+        <v>5614.0714690000004</v>
       </c>
       <c r="AU7" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AV7" s="24">
+      <c r="AV7" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AW7" s="12">
+        <v>-0.25174930000000001</v>
+      </c>
+      <c r="AX7" s="14">
+        <v>210875.2597</v>
+      </c>
+      <c r="AZ7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="BA7" s="24">
         <v>0.99999979999999999</v>
       </c>
-      <c r="AW7" s="26">
+      <c r="BB7" s="26">
         <v>91.979789999999994</v>
       </c>
-      <c r="AY7" s="1" t="s">
+      <c r="BD7" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AZ7" s="14">
-        <f>+_xlfn.XLOOKUP($AY7,$AH$7:$AH$9,$AJ$7:$AJ$9)</f>
+      <c r="BE7" s="14">
+        <f>+_xlfn.XLOOKUP($BD7,$AM$7:$AM$9,$AO$7:$AO$9)</f>
         <v>22520.654823000001</v>
       </c>
-      <c r="BA7" s="14">
-        <f>+_xlfn.XLOOKUP(AY7,$AL$7:$AL$9,$AN$7:$AN$9)</f>
-        <v>18974.986979000001</v>
-      </c>
-      <c r="BB7" s="14">
-        <f>+AS7</f>
+      <c r="BF7" s="14">
+        <f>+_xlfn.XLOOKUP(BD7,$AQ$7:$AQ$9,$AS$7:$AS$9)</f>
+        <v>16596.507481000001</v>
+      </c>
+      <c r="BG7" s="14">
+        <f>+AX7</f>
         <v>210875.2597</v>
       </c>
-      <c r="BC7" s="14">
-        <f>+AS8</f>
+      <c r="BH7" s="14">
+        <f>+AX8</f>
         <v>15764.5885</v>
       </c>
-      <c r="BD7" s="14">
-        <f>+AW7</f>
+      <c r="BI7" s="14">
+        <f>+BB7</f>
         <v>91.979789999999994</v>
       </c>
     </row>
-    <row r="8" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>172</v>
       </c>
@@ -3434,94 +3513,107 @@
       <c r="Z8" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="AA8" s="17">
-        <f t="shared" ref="AA8:AA16" si="3">+_xlfn.XLOOKUP($Z8,N$7:N$16,P$7:P$16)</f>
+      <c r="AA8" s="33">
+        <v>0.999973</v>
+      </c>
+      <c r="AB8" s="17">
+        <v>9120.9211990000003</v>
+      </c>
+      <c r="AD8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE8" s="17">
+        <f t="shared" ref="AE8:AE16" si="3">+_xlfn.XLOOKUP($AD8,N$7:N$16,P$7:P$16)</f>
         <v>1304208</v>
       </c>
-      <c r="AB8" s="17">
-        <f t="shared" ref="AB8:AB16" si="4">+_xlfn.XLOOKUP($Z8,R$7:R$16,T$7:T$16)</f>
+      <c r="AF8" s="17">
+        <f t="shared" ref="AF8:AF16" si="4">+_xlfn.XLOOKUP($AD8,R$7:R$16,T$7:T$16)</f>
         <v>518469</v>
       </c>
-      <c r="AC8" s="17">
-        <f t="shared" ref="AC8:AC16" si="5">+_xlfn.XLOOKUP($Z8,B$7:B$16,D$7:D$16)</f>
+      <c r="AG8" s="17">
+        <f t="shared" ref="AG8:AG16" si="5">+_xlfn.XLOOKUP($AD8,B$7:B$16,D$7:D$16)</f>
         <v>1864908.65</v>
       </c>
-      <c r="AD8" s="17">
-        <f t="shared" ref="AD8:AD16" si="6">+_xlfn.XLOOKUP($Z8,B$7:B$16,F$7:F$16)</f>
+      <c r="AH8" s="17">
+        <f t="shared" ref="AH8:AH16" si="6">+_xlfn.XLOOKUP($AD8,B$7:B$16,F$7:F$16)</f>
         <v>845419.62</v>
       </c>
-      <c r="AE8" s="17">
-        <f t="shared" ref="AE8:AE16" si="7">+_xlfn.XLOOKUP($Z8,V$7:V$16,X$7:X$16)</f>
+      <c r="AI8" s="17">
+        <f t="shared" ref="AI8:AI16" si="7">+_xlfn.XLOOKUP($AD8,V$7:V$16,X$7:X$16)</f>
         <v>1580.191648</v>
       </c>
-      <c r="AF8" s="17">
+      <c r="AJ8" s="17">
         <f t="shared" si="0"/>
         <v>1577.3933</v>
       </c>
-      <c r="AH8" s="6" t="s">
+      <c r="AK8" s="14">
+        <f t="shared" ref="AK8:AK16" si="8">+_xlfn.XLOOKUP(AD8,$Z$7:$Z$16,$AB$7:$AB$16)</f>
+        <v>9120.9211990000003</v>
+      </c>
+      <c r="AM8" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="AI8" s="18">
+      <c r="AN8" s="18">
         <v>0.98572300000000002</v>
       </c>
-      <c r="AJ8" s="17">
+      <c r="AO8" s="17">
         <v>22520.654823000001</v>
       </c>
-      <c r="AL8" s="6" t="s">
+      <c r="AQ8" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="AM8" s="18">
-        <v>0.98986499999999999</v>
-      </c>
-      <c r="AN8" s="17">
-        <v>18974.986979000001</v>
-      </c>
-      <c r="AP8" s="6" t="s">
+      <c r="AR8" s="18">
+        <v>0.99224599999999996</v>
+      </c>
+      <c r="AS8" s="17">
+        <v>16596.507481000001</v>
+      </c>
+      <c r="AU8" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="AQ8" s="6" t="s">
+      <c r="AV8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AR8" s="18">
+      <c r="AW8" s="18">
         <v>0.99300429999999995</v>
       </c>
-      <c r="AS8" s="17">
+      <c r="AX8" s="17">
         <v>15764.5885</v>
       </c>
-      <c r="AU8" s="6" t="s">
+      <c r="AZ8" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="AV8" s="25">
+      <c r="BA8" s="25">
         <v>0.99997420000000004</v>
       </c>
-      <c r="AW8" s="27">
+      <c r="BB8" s="27">
         <v>99.435940000000002</v>
       </c>
-      <c r="AY8" s="6" t="s">
+      <c r="BD8" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="AZ8" s="17">
-        <f t="shared" ref="AZ8:AZ9" si="8">+_xlfn.XLOOKUP(AY8,$AH$7:$AH$9,$AJ$7:$AJ$9)</f>
+      <c r="BE8" s="17">
+        <f t="shared" ref="BE8:BE9" si="9">+_xlfn.XLOOKUP(BD8,$AM$7:$AM$9,$AO$7:$AO$9)</f>
         <v>4703.6260300000004</v>
       </c>
-      <c r="BA8" s="17">
-        <f t="shared" ref="BA8:BA9" si="9">+_xlfn.XLOOKUP(AY8,$AL$7:$AL$9,$AN$7:$AN$9)</f>
-        <v>5610.9171020000003</v>
-      </c>
-      <c r="BB8" s="17">
-        <f>+AS9</f>
+      <c r="BF8" s="17">
+        <f t="shared" ref="BF8:BF9" si="10">+_xlfn.XLOOKUP(BD8,$AQ$7:$AQ$9,$AS$7:$AS$9)</f>
+        <v>5614.0714690000004</v>
+      </c>
+      <c r="BG8" s="17">
+        <f>+AX9</f>
         <v>1100.5509999999999</v>
       </c>
-      <c r="BC8" s="17">
-        <f>+AS10</f>
+      <c r="BH8" s="17">
+        <f>+AX10</f>
         <v>756.05920000000003</v>
       </c>
-      <c r="BD8" s="17">
-        <f t="shared" ref="BD8:BD9" si="10">+AW8</f>
+      <c r="BI8" s="17">
+        <f t="shared" ref="BI8:BI9" si="11">+BB8</f>
         <v>99.435940000000002</v>
       </c>
     </row>
-    <row r="9" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>173</v>
       </c>
@@ -3584,94 +3676,107 @@
       <c r="Z9" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="AA9" s="14">
+      <c r="AA9" s="32">
+        <v>0.99992800000000004</v>
+      </c>
+      <c r="AB9" s="14">
+        <v>20962.221375000001</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE9" s="14">
         <f t="shared" si="3"/>
         <v>3356209</v>
       </c>
-      <c r="AB9" s="14">
+      <c r="AF9" s="14">
         <f t="shared" si="4"/>
         <v>2617900</v>
       </c>
-      <c r="AC9" s="14">
+      <c r="AG9" s="14">
         <f t="shared" si="5"/>
         <v>177163.47</v>
       </c>
-      <c r="AD9" s="14">
+      <c r="AH9" s="14">
         <f t="shared" si="6"/>
         <v>170439.52</v>
       </c>
-      <c r="AE9" s="14">
+      <c r="AI9" s="14">
         <f t="shared" si="7"/>
         <v>2142.2691100000002</v>
       </c>
-      <c r="AF9" s="14">
+      <c r="AJ9" s="14">
         <f t="shared" si="0"/>
         <v>169850.0097</v>
       </c>
-      <c r="AH9" s="1" t="s">
+      <c r="AK9" s="14">
+        <f t="shared" si="8"/>
+        <v>20962.221375000001</v>
+      </c>
+      <c r="AM9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AI9" s="12">
+      <c r="AN9" s="12">
         <v>0.98843700000000001</v>
       </c>
-      <c r="AJ9" s="14">
+      <c r="AO9" s="14">
         <v>2148.462321</v>
       </c>
-      <c r="AL9" s="1" t="s">
+      <c r="AQ9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AM9" s="12">
-        <v>0.70254799999999995</v>
-      </c>
-      <c r="AN9" s="14">
-        <v>10896.633938999999</v>
-      </c>
-      <c r="AP9" s="1" t="s">
+      <c r="AR9" s="12">
+        <v>0.97706400000000004</v>
+      </c>
+      <c r="AS9" s="14">
+        <v>3025.804118</v>
+      </c>
+      <c r="AU9" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AQ9" s="1" t="s">
+      <c r="AV9" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="AR9" s="12">
+      <c r="AW9" s="12">
         <v>0.99683809999999995</v>
       </c>
-      <c r="AS9" s="14">
+      <c r="AX9" s="14">
         <v>1100.5509999999999</v>
       </c>
-      <c r="AU9" s="1" t="s">
+      <c r="AZ9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AV9" s="24">
+      <c r="BA9" s="24">
         <v>0.9999806</v>
       </c>
-      <c r="AW9" s="26">
+      <c r="BB9" s="26">
         <v>88.003110000000007</v>
       </c>
-      <c r="AY9" s="1" t="s">
+      <c r="BD9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AZ9" s="14">
-        <f t="shared" si="8"/>
+      <c r="BE9" s="14">
+        <f t="shared" si="9"/>
         <v>2148.462321</v>
       </c>
-      <c r="BA9" s="14">
-        <f t="shared" si="9"/>
-        <v>10896.633938999999</v>
-      </c>
-      <c r="BB9" s="14">
-        <f>+AS11</f>
+      <c r="BF9" s="14">
+        <f t="shared" si="10"/>
+        <v>3025.804118</v>
+      </c>
+      <c r="BG9" s="14">
+        <f>+AX11</f>
         <v>1976.5089</v>
       </c>
-      <c r="BC9" s="14">
-        <f>+AS12</f>
+      <c r="BH9" s="14">
+        <f>+AX12</f>
         <v>902.76419999999996</v>
       </c>
-      <c r="BD9" s="14">
-        <f t="shared" si="10"/>
+      <c r="BI9" s="14">
+        <f t="shared" si="11"/>
         <v>88.003110000000007</v>
       </c>
     </row>
-    <row r="10" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>191</v>
       </c>
@@ -3734,49 +3839,75 @@
       <c r="Z10" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="AA10" s="17">
+      <c r="AA10" s="33">
+        <v>0.99969300000000005</v>
+      </c>
+      <c r="AB10" s="17">
+        <v>4105.2196100000001</v>
+      </c>
+      <c r="AD10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AE10" s="17">
         <f t="shared" si="3"/>
         <v>305803.09999999998</v>
       </c>
-      <c r="AB10" s="17">
+      <c r="AF10" s="17">
         <f t="shared" si="4"/>
         <v>224458</v>
       </c>
-      <c r="AC10" s="17">
+      <c r="AG10" s="17">
         <f t="shared" si="5"/>
         <v>23648.33</v>
       </c>
-      <c r="AD10" s="17">
+      <c r="AH10" s="17">
         <f t="shared" si="6"/>
         <v>20252.46</v>
       </c>
-      <c r="AE10" s="17">
+      <c r="AI10" s="17">
         <f t="shared" si="7"/>
         <v>433.14919800000001</v>
       </c>
-      <c r="AF10" s="17">
+      <c r="AJ10" s="17">
         <f t="shared" si="0"/>
         <v>425.01549999999997</v>
       </c>
-      <c r="AI10" s="12"/>
-      <c r="AJ10" s="14"/>
-      <c r="AL10" s="14"/>
-      <c r="AM10" s="14"/>
-      <c r="AN10" s="14"/>
-      <c r="AP10" s="6" t="s">
+      <c r="AK10" s="14">
+        <f t="shared" si="8"/>
+        <v>4105.2196100000001</v>
+      </c>
+      <c r="AM10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AN10" s="18">
+        <v>0.98303399999999996</v>
+      </c>
+      <c r="AO10" s="17">
+        <v>53755.513460000002</v>
+      </c>
+      <c r="AQ10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AR10" s="18">
+        <v>0.99701899999999999</v>
+      </c>
+      <c r="AS10" s="17">
+        <v>22532.557326999999</v>
+      </c>
+      <c r="AU10" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="AQ10" s="6" t="s">
+      <c r="AV10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AR10" s="18">
+      <c r="AW10" s="18">
         <v>0.9985077</v>
       </c>
-      <c r="AS10" s="17">
+      <c r="AX10" s="17">
         <v>756.05920000000003</v>
       </c>
     </row>
-    <row r="11" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>175</v>
       </c>
@@ -3839,49 +3970,62 @@
       <c r="Z11" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="AA11" s="14">
+      <c r="AA11" s="32">
+        <v>0.99996600000000002</v>
+      </c>
+      <c r="AB11" s="14">
+        <v>81396.828680000006</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AE11" s="14">
         <f t="shared" si="3"/>
         <v>2287439</v>
       </c>
-      <c r="AB11" s="14">
+      <c r="AF11" s="14">
         <f t="shared" si="4"/>
         <v>1656545</v>
       </c>
-      <c r="AC11" s="14">
+      <c r="AG11" s="14">
         <f t="shared" si="5"/>
         <v>1367228.95</v>
       </c>
-      <c r="AD11" s="14">
+      <c r="AH11" s="14">
         <f t="shared" si="6"/>
         <v>1271179.51</v>
       </c>
-      <c r="AE11" s="14">
+      <c r="AI11" s="14">
         <f t="shared" si="7"/>
         <v>30356.430119000001</v>
       </c>
-      <c r="AF11" s="14">
+      <c r="AJ11" s="14">
         <f t="shared" si="0"/>
         <v>39575.911200000002</v>
       </c>
-      <c r="AI11" s="12"/>
-      <c r="AJ11" s="14"/>
-      <c r="AL11" s="14"/>
-      <c r="AM11" s="14"/>
-      <c r="AN11" s="14"/>
-      <c r="AP11" s="1" t="s">
+      <c r="AK11" s="14">
+        <f t="shared" si="8"/>
+        <v>81396.828680000006</v>
+      </c>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="14"/>
+      <c r="AQ11" s="14"/>
+      <c r="AR11" s="14"/>
+      <c r="AS11" s="14"/>
+      <c r="AU11" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AQ11" s="1" t="s">
+      <c r="AV11" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="AR11" s="12">
+      <c r="AW11" s="12">
         <v>0.99021340000000002</v>
       </c>
-      <c r="AS11" s="14">
+      <c r="AX11" s="14">
         <v>1976.5089</v>
       </c>
     </row>
-    <row r="12" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>176</v>
       </c>
@@ -3944,52 +4088,65 @@
       <c r="Z12" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="AA12" s="17">
+      <c r="AA12" s="33">
+        <v>0.99982899999999997</v>
+      </c>
+      <c r="AB12" s="17">
+        <v>118520.743653</v>
+      </c>
+      <c r="AD12" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE12" s="17">
         <f t="shared" si="3"/>
         <v>2800556</v>
       </c>
-      <c r="AB12" s="17">
+      <c r="AF12" s="17">
         <f t="shared" si="4"/>
         <v>1697944</v>
       </c>
-      <c r="AC12" s="17">
+      <c r="AG12" s="17">
         <f t="shared" si="5"/>
         <v>1102529.6399999999</v>
       </c>
-      <c r="AD12" s="17">
+      <c r="AH12" s="17">
         <f t="shared" si="6"/>
         <v>963692.8</v>
       </c>
-      <c r="AE12" s="17">
+      <c r="AI12" s="17">
         <f t="shared" si="7"/>
         <v>16474.693931999998</v>
       </c>
-      <c r="AF12" s="17">
+      <c r="AJ12" s="17">
         <f t="shared" si="0"/>
         <v>16566.6181</v>
       </c>
-      <c r="AI12" s="12"/>
-      <c r="AJ12" s="14"/>
-      <c r="AL12" s="14"/>
-      <c r="AM12" s="14"/>
-      <c r="AN12" s="14"/>
-      <c r="AP12" s="6" t="s">
+      <c r="AK12" s="14">
+        <f t="shared" si="8"/>
+        <v>118520.743653</v>
+      </c>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="14"/>
+      <c r="AQ12" s="14"/>
+      <c r="AR12" s="14"/>
+      <c r="AS12" s="14"/>
+      <c r="AU12" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="AQ12" s="6" t="s">
+      <c r="AV12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AR12" s="18">
+      <c r="AW12" s="18">
         <v>0.99795840000000002</v>
       </c>
-      <c r="AS12" s="17">
+      <c r="AX12" s="17">
         <v>902.76419999999996</v>
       </c>
-      <c r="AY12" s="19" t="s">
+      <c r="BD12" s="19" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>177</v>
       </c>
@@ -4052,38 +4209,63 @@
       <c r="Z13" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="AA13" s="14">
+      <c r="AA13" s="32">
+        <v>0.99989799999999995</v>
+      </c>
+      <c r="AB13" s="14">
+        <v>26091.076145999999</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE13" s="14">
         <f t="shared" si="3"/>
         <v>46909600</v>
       </c>
-      <c r="AB13" s="14">
+      <c r="AF13" s="14">
         <f t="shared" si="4"/>
         <v>2603995</v>
       </c>
-      <c r="AC13" s="14">
+      <c r="AG13" s="14">
         <f t="shared" si="5"/>
         <v>2513538.7400000002</v>
       </c>
-      <c r="AD13" s="14">
+      <c r="AH13" s="14">
         <f t="shared" si="6"/>
         <v>200928.3</v>
       </c>
-      <c r="AE13" s="14">
+      <c r="AI13" s="14">
         <f t="shared" si="7"/>
         <v>7591.1932999999999</v>
       </c>
-      <c r="AF13" s="14">
+      <c r="AJ13" s="14">
         <f t="shared" si="0"/>
         <v>24061.312300000001</v>
       </c>
-      <c r="AH13" s="14"/>
-      <c r="AI13" s="14"/>
-      <c r="AJ13" s="14"/>
-      <c r="AL13" s="14"/>
+      <c r="AK13" s="14">
+        <f t="shared" si="8"/>
+        <v>26091.076145999999</v>
+      </c>
       <c r="AM13" s="14"/>
       <c r="AN13" s="14"/>
-    </row>
-    <row r="14" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="AO13" s="14"/>
+      <c r="AQ13" s="14"/>
+      <c r="AR13" s="14"/>
+      <c r="AS13" s="14"/>
+      <c r="AU13" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="AV13" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AW13" s="12">
+        <v>0.99908359999999996</v>
+      </c>
+      <c r="AX13" s="14">
+        <v>12493.0429</v>
+      </c>
+    </row>
+    <row r="14" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>178</v>
       </c>
@@ -4146,41 +4328,66 @@
       <c r="Z14" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="AA14" s="17">
+      <c r="AA14" s="33">
+        <v>0.99961699999999998</v>
+      </c>
+      <c r="AB14" s="17">
+        <v>7011.0990389999997</v>
+      </c>
+      <c r="AD14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AE14" s="17">
         <f t="shared" si="3"/>
         <v>353453</v>
       </c>
-      <c r="AB14" s="17">
+      <c r="AF14" s="17">
         <f t="shared" si="4"/>
         <v>125949</v>
       </c>
-      <c r="AC14" s="17">
+      <c r="AG14" s="17">
         <f t="shared" si="5"/>
         <v>355071.95</v>
       </c>
-      <c r="AD14" s="17">
+      <c r="AH14" s="17">
         <f t="shared" si="6"/>
         <v>48038.9</v>
       </c>
-      <c r="AE14" s="17">
+      <c r="AI14" s="17">
         <f t="shared" si="7"/>
         <v>1140.2147070000001</v>
       </c>
-      <c r="AF14" s="17">
+      <c r="AJ14" s="17">
         <f t="shared" si="0"/>
         <v>1157.9239</v>
       </c>
-      <c r="AH14" s="14"/>
-      <c r="AI14" s="14"/>
-      <c r="AJ14" s="14"/>
-      <c r="AL14" s="14"/>
+      <c r="AK14" s="14">
+        <f t="shared" si="8"/>
+        <v>7011.0990389999997</v>
+      </c>
       <c r="AM14" s="14"/>
       <c r="AN14" s="14"/>
-      <c r="AY14" s="13" t="s">
+      <c r="AO14" s="14"/>
+      <c r="AQ14" s="14"/>
+      <c r="AR14" s="14"/>
+      <c r="AS14" s="14"/>
+      <c r="AU14" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AV14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AW14" s="18">
+        <v>0.99956429999999996</v>
+      </c>
+      <c r="AX14" s="17">
+        <v>8614.8230000000003</v>
+      </c>
+      <c r="BD14" s="13" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="15" spans="2:57" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>179</v>
       </c>
@@ -4243,38 +4450,51 @@
       <c r="Z15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="AA15" s="14">
+      <c r="AA15" s="32">
+        <v>0.99987199999999998</v>
+      </c>
+      <c r="AB15" s="14">
+        <v>412581.51297400001</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE15" s="14">
         <f t="shared" si="3"/>
         <v>30580360</v>
       </c>
-      <c r="AB15" s="14">
+      <c r="AF15" s="14">
         <f t="shared" si="4"/>
         <v>14859300</v>
       </c>
-      <c r="AC15" s="14">
+      <c r="AG15" s="14">
         <f t="shared" si="5"/>
         <v>35497296.340000004</v>
       </c>
-      <c r="AD15" s="14">
+      <c r="AH15" s="14">
         <f t="shared" si="6"/>
         <v>4077358.71</v>
       </c>
-      <c r="AE15" s="14">
+      <c r="AI15" s="14">
         <f t="shared" si="7"/>
         <v>47866.562242</v>
       </c>
-      <c r="AF15" s="14">
+      <c r="AJ15" s="14">
         <f t="shared" si="0"/>
         <v>55078.919900000001</v>
       </c>
-      <c r="AH15" s="14"/>
-      <c r="AI15" s="14"/>
-      <c r="AJ15" s="14"/>
-      <c r="AL15" s="14"/>
+      <c r="AK15" s="14">
+        <f t="shared" si="8"/>
+        <v>412581.51297400001</v>
+      </c>
       <c r="AM15" s="14"/>
       <c r="AN15" s="14"/>
-    </row>
-    <row r="16" spans="2:57" x14ac:dyDescent="0.3">
+      <c r="AO15" s="14"/>
+      <c r="AQ15" s="14"/>
+      <c r="AR15" s="14"/>
+      <c r="AS15" s="14"/>
+    </row>
+    <row r="16" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
         <v>180</v>
       </c>
@@ -4337,150 +4557,166 @@
       <c r="Z16" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="AA16" s="17">
+      <c r="AA16" s="33">
+        <v>0.99970099999999995</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>7087.1279500000001</v>
+      </c>
+      <c r="AD16" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE16" s="17">
         <f t="shared" si="3"/>
         <v>283382.09999999998</v>
       </c>
-      <c r="AB16" s="17">
+      <c r="AF16" s="17">
         <f t="shared" si="4"/>
         <v>73683.27</v>
       </c>
-      <c r="AC16" s="17">
+      <c r="AG16" s="17">
         <f t="shared" si="5"/>
         <v>62216.71</v>
       </c>
-      <c r="AD16" s="17">
+      <c r="AH16" s="17">
         <f t="shared" si="6"/>
         <v>55278.55</v>
       </c>
-      <c r="AE16" s="17">
+      <c r="AI16" s="17">
         <f t="shared" si="7"/>
         <v>829.90016600000001</v>
       </c>
-      <c r="AF16" s="17">
+      <c r="AJ16" s="17">
         <f t="shared" si="0"/>
         <v>55089.632700000002</v>
       </c>
-      <c r="AH16" s="14"/>
-      <c r="AI16" s="14"/>
-      <c r="AJ16" s="14"/>
-      <c r="AL16" s="14"/>
+      <c r="AK16" s="14">
+        <f t="shared" si="8"/>
+        <v>7087.1279500000001</v>
+      </c>
       <c r="AM16" s="14"/>
       <c r="AN16" s="14"/>
-      <c r="AY16" s="9" t="s">
+      <c r="AO16" s="14"/>
+      <c r="AQ16" s="14"/>
+      <c r="AR16" s="14"/>
+      <c r="AS16" s="14"/>
+      <c r="BD16" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="AZ16" s="9" t="s">
+      <c r="BE16" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="BA16" s="9" t="s">
+      <c r="BF16" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="BB16" s="9" t="s">
+      <c r="BG16" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="BC16" s="9" t="s">
+      <c r="BH16" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="BD16" s="9" t="s">
+      <c r="BI16" s="9" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="17" spans="2:56" x14ac:dyDescent="0.3">
-      <c r="AY17" s="1" t="s">
+    <row r="17" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="BD17" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AZ17" s="12">
-        <f>+_xlfn.XLOOKUP($AY17,$AH$7:$AH$9,$AI$7:$AI$9)</f>
+      <c r="BE17" s="12">
+        <f>+_xlfn.XLOOKUP($BD17,$AM$7:$AM$9,$AN$7:$AN$9)</f>
         <v>0.98572300000000002</v>
       </c>
-      <c r="BA17" s="12">
-        <f>+_xlfn.XLOOKUP(AY17,$AL$7:$AL$9,$AM$7:$AM$9)</f>
-        <v>0.98986499999999999</v>
-      </c>
-      <c r="BB17" s="12">
-        <f>+AR7</f>
+      <c r="BF17" s="12">
+        <f>+_xlfn.XLOOKUP(BD17,$AQ$7:$AQ$9,$AR$7:$AR$9)</f>
+        <v>0.99224599999999996</v>
+      </c>
+      <c r="BG17" s="12">
+        <f>+AW7</f>
         <v>-0.25174930000000001</v>
       </c>
-      <c r="BC17" s="12">
-        <f>+AR8</f>
+      <c r="BH17" s="12">
+        <f>+AW8</f>
         <v>0.99300429999999995</v>
       </c>
-      <c r="BD17" s="12">
-        <f>+AV7</f>
+      <c r="BI17" s="12">
+        <f>+BA7</f>
         <v>0.99999979999999999</v>
       </c>
     </row>
-    <row r="18" spans="2:56" x14ac:dyDescent="0.3">
-      <c r="AY18" s="6" t="s">
+    <row r="18" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="BD18" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="AZ18" s="18">
-        <f t="shared" ref="AZ18:AZ19" si="11">+_xlfn.XLOOKUP($AY18,$AH$7:$AH$9,$AI$7:$AI$9)</f>
+      <c r="BE18" s="18">
+        <f t="shared" ref="BE18:BE19" si="12">+_xlfn.XLOOKUP($BD18,$AM$7:$AM$9,$AN$7:$AN$9)</f>
         <v>0.94224399999999997</v>
       </c>
-      <c r="BA18" s="18">
-        <f t="shared" ref="BA18:BA19" si="12">+_xlfn.XLOOKUP(AY18,$AL$7:$AL$9,$AM$7:$AM$9)</f>
-        <v>0.91781400000000002</v>
-      </c>
-      <c r="BB18" s="18">
-        <f>+AR9</f>
+      <c r="BF18" s="18">
+        <f t="shared" ref="BF18:BF19" si="13">+_xlfn.XLOOKUP(BD18,$AQ$7:$AQ$9,$AR$7:$AR$9)</f>
+        <v>0.91772100000000001</v>
+      </c>
+      <c r="BG18" s="18">
+        <f>+AW9</f>
         <v>0.99683809999999995</v>
       </c>
-      <c r="BC18" s="18">
-        <f>+AR10</f>
+      <c r="BH18" s="18">
+        <f>+AW10</f>
         <v>0.9985077</v>
       </c>
-      <c r="BD18" s="18">
-        <f t="shared" ref="BD18:BD19" si="13">+AV8</f>
+      <c r="BI18" s="18">
+        <f t="shared" ref="BI18:BI19" si="14">+BA8</f>
         <v>0.99997420000000004</v>
       </c>
     </row>
-    <row r="19" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>183</v>
       </c>
       <c r="I19" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="R19" s="13" t="s">
         <v>183</v>
       </c>
       <c r="T19" s="21"/>
       <c r="V19" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="Z19" s="22"/>
-      <c r="AA19" s="22"/>
-      <c r="AB19" s="22"/>
-      <c r="AY19" s="1" t="s">
+      <c r="AD19" s="22"/>
+      <c r="AE19" s="22"/>
+      <c r="AF19" s="22"/>
+      <c r="BD19" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AZ19" s="12">
-        <f t="shared" si="11"/>
+      <c r="BE19" s="12">
+        <f t="shared" si="12"/>
         <v>0.98843700000000001</v>
       </c>
-      <c r="BA19" s="12">
-        <f t="shared" si="12"/>
-        <v>0.70254799999999995</v>
-      </c>
-      <c r="BB19" s="12">
-        <f>+AR11</f>
+      <c r="BF19" s="12">
+        <f t="shared" si="13"/>
+        <v>0.97706400000000004</v>
+      </c>
+      <c r="BG19" s="12">
+        <f>+AW11</f>
         <v>0.99021340000000002</v>
       </c>
-      <c r="BC19" s="12">
-        <f>+AR12</f>
+      <c r="BH19" s="12">
+        <f>+AW12</f>
         <v>0.99795840000000002</v>
       </c>
-      <c r="BD19" s="12">
-        <f t="shared" si="13"/>
+      <c r="BI19" s="12">
+        <f t="shared" si="14"/>
         <v>0.9999806</v>
       </c>
     </row>
-    <row r="20" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="T20" s="21"/>
-      <c r="Z20" s="23"/>
-      <c r="AA20" s="23"/>
-      <c r="AB20" s="23"/>
-    </row>
-    <row r="21" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B21" s="9" t="s">
         <v>166</v>
       </c>
@@ -4511,7 +4747,24 @@
       <c r="L21" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="T21" s="21"/>
+      <c r="N21" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="T21" s="9" t="s">
+        <v>188</v>
+      </c>
       <c r="V21" s="9" t="s">
         <v>166</v>
       </c>
@@ -4521,11 +4774,11 @@
       <c r="X21" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="Z21" s="23"/>
-      <c r="AA21" s="23"/>
-      <c r="AB21" s="23"/>
-    </row>
-    <row r="22" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+    </row>
+    <row r="22" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>171</v>
       </c>
@@ -4558,7 +4811,24 @@
         <f>+K22-_xlfn.XLOOKUP(I22,B$22:B$31,F$22:F$31)</f>
         <v>-812345.71199999994</v>
       </c>
-      <c r="T22" s="21"/>
+      <c r="N22" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O22" s="12">
+        <v>0.82512600000000003</v>
+      </c>
+      <c r="P22" s="14">
+        <v>5285818</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="S22" s="12">
+        <v>0.64468300000000001</v>
+      </c>
+      <c r="T22" s="14">
+        <v>7558374</v>
+      </c>
       <c r="V22" s="1" t="s">
         <v>171</v>
       </c>
@@ -4568,11 +4838,11 @@
       <c r="X22" s="14">
         <v>72886.599426000001</v>
       </c>
-      <c r="Z22" s="23"/>
-      <c r="AA22" s="23"/>
-      <c r="AB22" s="23"/>
-    </row>
-    <row r="23" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="14"/>
+    </row>
+    <row r="23" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>172</v>
       </c>
@@ -4589,7 +4859,7 @@
         <v>191678.16</v>
       </c>
       <c r="G23" s="6" t="str">
-        <f t="shared" ref="G23:G31" si="14">+IF(F23&lt;D23,"GGM","BM")</f>
+        <f t="shared" ref="G23:G31" si="15">+IF(F23&lt;D23,"GGM","BM")</f>
         <v>GGM</v>
       </c>
       <c r="I23" s="6" t="s">
@@ -4602,10 +4872,27 @@
         <v>7970.5929999999998</v>
       </c>
       <c r="L23" s="17">
-        <f t="shared" ref="L23:L31" si="15">+K23-_xlfn.XLOOKUP(I23,B$22:B$31,F$22:F$31)</f>
+        <f t="shared" ref="L23:L31" si="16">+K23-_xlfn.XLOOKUP(I23,B$22:B$31,F$22:F$31)</f>
         <v>-183707.56700000001</v>
       </c>
-      <c r="T23" s="21"/>
+      <c r="N23" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="O23" s="18">
+        <v>0.85929699999999998</v>
+      </c>
+      <c r="P23" s="17">
+        <v>655919.19999999995</v>
+      </c>
+      <c r="R23" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="S23" s="18">
+        <v>0.86842799999999998</v>
+      </c>
+      <c r="T23" s="17">
+        <v>634278.5</v>
+      </c>
       <c r="V23" s="6" t="s">
         <v>172</v>
       </c>
@@ -4615,17 +4902,17 @@
       <c r="X23" s="17">
         <v>8395.1301469999999</v>
       </c>
-      <c r="Z23" s="23"/>
-      <c r="AA23" s="23"/>
-      <c r="AB23" s="23"/>
-      <c r="AH23" s="28"/>
-      <c r="AI23" s="28"/>
-      <c r="AJ23" s="28"/>
-      <c r="AL23" s="28"/>
+      <c r="Z23" s="17"/>
+      <c r="AA23" s="17"/>
+      <c r="AB23" s="17"/>
       <c r="AM23" s="28"/>
       <c r="AN23" s="28"/>
-    </row>
-    <row r="24" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AO23" s="28"/>
+      <c r="AQ23" s="28"/>
+      <c r="AR23" s="28"/>
+      <c r="AS23" s="28"/>
+    </row>
+    <row r="24" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>173</v>
       </c>
@@ -4642,7 +4929,7 @@
         <v>170016.12</v>
       </c>
       <c r="G24" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -4655,10 +4942,27 @@
         <v>10259.941000000001</v>
       </c>
       <c r="L24" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-159756.179</v>
       </c>
-      <c r="T24" s="21"/>
+      <c r="N24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O24" s="12">
+        <v>0.91229700000000002</v>
+      </c>
+      <c r="P24" s="14">
+        <v>711743.3</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="S24" s="12">
+        <v>0.43064400000000003</v>
+      </c>
+      <c r="T24" s="14">
+        <v>1813809</v>
+      </c>
       <c r="V24" s="1" t="s">
         <v>173</v>
       </c>
@@ -4668,17 +4972,17 @@
       <c r="X24" s="14">
         <v>11331.678796</v>
       </c>
-      <c r="Z24" s="23"/>
-      <c r="AA24" s="23"/>
-      <c r="AB24" s="23"/>
-      <c r="AH24" s="28"/>
-      <c r="AI24" s="29"/>
-      <c r="AJ24" s="29"/>
-      <c r="AL24" s="29"/>
-      <c r="AM24" s="29"/>
+      <c r="Z24" s="14"/>
+      <c r="AA24" s="14"/>
+      <c r="AB24" s="14"/>
+      <c r="AM24" s="28"/>
       <c r="AN24" s="29"/>
-    </row>
-    <row r="25" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AO24" s="29"/>
+      <c r="AQ24" s="29"/>
+      <c r="AR24" s="29"/>
+      <c r="AS24" s="29"/>
+    </row>
+    <row r="25" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>174</v>
       </c>
@@ -4695,7 +4999,7 @@
         <v>20254.93</v>
       </c>
       <c r="G25" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I25" s="6" t="s">
@@ -4708,10 +5012,27 @@
         <v>2682.71</v>
       </c>
       <c r="L25" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-17572.22</v>
       </c>
-      <c r="T25" s="21"/>
+      <c r="N25" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="O25" s="18">
+        <v>0.81773499999999999</v>
+      </c>
+      <c r="P25" s="17">
+        <v>96842.15</v>
+      </c>
+      <c r="R25" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="S25" s="18">
+        <v>-0.70466200000000001</v>
+      </c>
+      <c r="T25" s="17">
+        <v>300031.3</v>
+      </c>
       <c r="V25" s="6" t="s">
         <v>191</v>
       </c>
@@ -4721,17 +5042,17 @@
       <c r="X25" s="17">
         <v>2856.3407999999999</v>
       </c>
-      <c r="Z25" s="23"/>
-      <c r="AA25" s="23"/>
-      <c r="AB25" s="23"/>
-      <c r="AH25" s="28"/>
-      <c r="AI25" s="29"/>
-      <c r="AJ25" s="29"/>
-      <c r="AL25" s="29"/>
-      <c r="AM25" s="29"/>
+      <c r="Z25" s="17"/>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="17"/>
+      <c r="AM25" s="28"/>
       <c r="AN25" s="29"/>
-    </row>
-    <row r="26" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AO25" s="29"/>
+      <c r="AQ25" s="29"/>
+      <c r="AR25" s="29"/>
+      <c r="AS25" s="29"/>
+    </row>
+    <row r="26" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>175</v>
       </c>
@@ -4748,7 +5069,7 @@
         <v>1270365.45</v>
       </c>
       <c r="G26" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -4761,10 +5082,27 @@
         <v>54571.813999999998</v>
       </c>
       <c r="L26" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1215793.6359999999</v>
       </c>
-      <c r="T26" s="21"/>
+      <c r="N26" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O26" s="12">
+        <v>0.98488399999999998</v>
+      </c>
+      <c r="P26" s="14">
+        <v>1726783</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="S26" s="12">
+        <v>0.98622900000000002</v>
+      </c>
+      <c r="T26" s="14">
+        <v>1646926</v>
+      </c>
       <c r="V26" s="1" t="s">
         <v>175</v>
       </c>
@@ -4774,17 +5112,17 @@
       <c r="X26" s="14">
         <v>59096.011952000001</v>
       </c>
-      <c r="Z26" s="23"/>
-      <c r="AA26" s="23"/>
-      <c r="AB26" s="23"/>
-      <c r="AH26" s="28"/>
-      <c r="AI26" s="29"/>
-      <c r="AJ26" s="29"/>
-      <c r="AL26" s="29"/>
-      <c r="AM26" s="29"/>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AM26" s="28"/>
       <c r="AN26" s="29"/>
-    </row>
-    <row r="27" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AO26" s="29"/>
+      <c r="AQ26" s="29"/>
+      <c r="AR26" s="29"/>
+      <c r="AS26" s="29"/>
+    </row>
+    <row r="27" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
         <v>176</v>
       </c>
@@ -4801,7 +5139,7 @@
         <v>962242.14</v>
       </c>
       <c r="G27" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -4814,10 +5152,27 @@
         <v>37554.368000000002</v>
       </c>
       <c r="L27" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-924687.772</v>
       </c>
-      <c r="T27" s="21"/>
+      <c r="N27" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="O27" s="18">
+        <v>0.94516</v>
+      </c>
+      <c r="P27" s="17">
+        <v>2120841</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="S27" s="18">
+        <v>0.94915899999999997</v>
+      </c>
+      <c r="T27" s="17">
+        <v>2056768</v>
+      </c>
       <c r="V27" s="6" t="s">
         <v>176</v>
       </c>
@@ -4827,11 +5182,11 @@
       <c r="X27" s="17">
         <v>40276.492481000001</v>
       </c>
-      <c r="Z27" s="23"/>
-      <c r="AA27" s="23"/>
-      <c r="AB27" s="23"/>
-    </row>
-    <row r="28" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="Z27" s="17"/>
+      <c r="AA27" s="17"/>
+      <c r="AB27" s="17"/>
+    </row>
+    <row r="28" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>177</v>
       </c>
@@ -4848,7 +5203,7 @@
         <v>177553.42</v>
       </c>
       <c r="G28" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -4861,10 +5216,27 @@
         <v>18001.951000000001</v>
       </c>
       <c r="L28" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-159551.46900000001</v>
       </c>
-      <c r="T28" s="21"/>
+      <c r="N28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="O28" s="12">
+        <v>0.84834900000000002</v>
+      </c>
+      <c r="P28" s="14">
+        <v>999266.5</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S28" s="12">
+        <v>-0.34762500000000002</v>
+      </c>
+      <c r="T28" s="14">
+        <v>2976087</v>
+      </c>
       <c r="V28" s="1" t="s">
         <v>177</v>
       </c>
@@ -4874,11 +5246,14 @@
       <c r="X28" s="14">
         <v>20204.683582000001</v>
       </c>
-      <c r="Z28" s="23"/>
-      <c r="AA28" s="23"/>
-      <c r="AB28" s="23"/>
-    </row>
-    <row r="29" spans="2:56" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AD28" s="23"/>
+      <c r="AE28" s="23"/>
+      <c r="AF28" s="23"/>
+    </row>
+    <row r="29" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
         <v>178</v>
       </c>
@@ -4895,7 +5270,7 @@
         <v>41689.589999999997</v>
       </c>
       <c r="G29" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I29" s="6" t="s">
@@ -4908,10 +5283,27 @@
         <v>2688.72</v>
       </c>
       <c r="L29" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-39000.869999999995</v>
       </c>
-      <c r="T29" s="21"/>
+      <c r="N29" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="O29" s="18">
+        <v>0.83975299999999997</v>
+      </c>
+      <c r="P29" s="17">
+        <v>140633.70000000001</v>
+      </c>
+      <c r="R29" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="S29" s="18">
+        <v>0.86644399999999999</v>
+      </c>
+      <c r="T29" s="17">
+        <v>128388.6</v>
+      </c>
       <c r="V29" s="6" t="s">
         <v>178</v>
       </c>
@@ -4921,11 +5313,14 @@
       <c r="X29" s="17">
         <v>2835.1556179999998</v>
       </c>
-      <c r="Z29" s="23"/>
-      <c r="AA29" s="23"/>
-      <c r="AB29" s="23"/>
-    </row>
-    <row r="30" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="Z29" s="17"/>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="17"/>
+      <c r="AD29" s="23"/>
+      <c r="AE29" s="23"/>
+      <c r="AF29" s="23"/>
+    </row>
+    <row r="30" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>179</v>
       </c>
@@ -4942,7 +5337,7 @@
         <v>55105.7</v>
       </c>
       <c r="G30" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -4955,8 +5350,26 @@
         <v>3653520.236</v>
       </c>
       <c r="L30" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-4.0000001899898052E-3</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="O30" s="12">
+        <v>0.83721299999999998</v>
+      </c>
+      <c r="P30" s="14">
+        <v>14749160</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S30" s="12">
+        <v>0.84466699999999995</v>
+      </c>
+      <c r="T30" s="14">
+        <v>14407510</v>
       </c>
       <c r="V30" s="1" t="s">
         <v>180</v>
@@ -4967,8 +5380,14 @@
       <c r="X30" s="14">
         <v>189197.220477</v>
       </c>
-    </row>
-    <row r="31" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="Z30" s="14"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+      <c r="AD30" s="23"/>
+      <c r="AE30" s="23"/>
+      <c r="AF30" s="23"/>
+    </row>
+    <row r="31" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>180</v>
       </c>
@@ -4985,7 +5404,7 @@
         <v>3653520.24</v>
       </c>
       <c r="G31" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I31" s="6" t="s">
@@ -4998,8 +5417,26 @@
         <v>2309.4769999999999</v>
       </c>
       <c r="L31" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-52796.222999999998</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="O31" s="18">
+        <v>0.94254700000000002</v>
+      </c>
+      <c r="P31" s="17">
+        <v>97667.94</v>
+      </c>
+      <c r="R31" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="S31" s="18">
+        <v>0.95194400000000001</v>
+      </c>
+      <c r="T31" s="17">
+        <v>89659.199999999997</v>
       </c>
       <c r="V31" s="6" t="s">
         <v>179</v>
@@ -5010,8 +5447,19 @@
       <c r="X31" s="17">
         <v>2423.543439</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z31" s="17"/>
+      <c r="AA31" s="17"/>
+      <c r="AB31" s="17"/>
+      <c r="AD31" s="23"/>
+      <c r="AE31" s="23"/>
+      <c r="AF31" s="23"/>
+    </row>
+    <row r="32" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AD32" s="23"/>
+      <c r="AE32" s="23"/>
+      <c r="AF32" s="23"/>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
         <v>184</v>
       </c>
@@ -5022,7 +5470,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B36" s="9" t="s">
         <v>166</v>
       </c>
@@ -5062,8 +5510,11 @@
       <c r="X36" s="9" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>171</v>
       </c>
@@ -5105,8 +5556,11 @@
       <c r="X37" s="14">
         <v>584602.6</v>
       </c>
-    </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z37" s="14"/>
+      <c r="AA37" s="14"/>
+      <c r="AB37" s="14"/>
+    </row>
+    <row r="38" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
         <v>172</v>
       </c>
@@ -5123,7 +5577,7 @@
         <v>211942.1</v>
       </c>
       <c r="G38" s="6" t="str">
-        <f t="shared" ref="G38:G46" si="16">+IF(F38&lt;D38,"GGM","BM")</f>
+        <f t="shared" ref="G38:G46" si="17">+IF(F38&lt;D38,"GGM","BM")</f>
         <v>GGM</v>
       </c>
       <c r="I38" s="6" t="s">
@@ -5136,7 +5590,7 @@
         <v>100789.75999999999</v>
       </c>
       <c r="L38" s="17">
-        <f t="shared" ref="L38:L46" si="17">+K38-_xlfn.XLOOKUP(I38,B$37:B$46,F$37:F$46)</f>
+        <f t="shared" ref="L38:L46" si="18">+K38-_xlfn.XLOOKUP(I38,B$37:B$46,F$37:F$46)</f>
         <v>-111152.34000000001</v>
       </c>
       <c r="V38" s="6" t="s">
@@ -5148,8 +5602,11 @@
       <c r="X38" s="17">
         <v>118904.3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17"/>
+      <c r="AB38" s="17"/>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>173</v>
       </c>
@@ -5166,7 +5623,7 @@
         <v>174775.12</v>
       </c>
       <c r="G39" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>GGM</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -5179,7 +5636,7 @@
         <v>120410.38</v>
       </c>
       <c r="L39" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-54364.739999999991</v>
       </c>
       <c r="V39" s="1" t="s">
@@ -5191,8 +5648,11 @@
       <c r="X39" s="14">
         <v>169254.2</v>
       </c>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z39" s="14"/>
+      <c r="AA39" s="14"/>
+      <c r="AB39" s="14"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
         <v>174</v>
       </c>
@@ -5209,7 +5669,7 @@
         <v>23030.65</v>
       </c>
       <c r="G40" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>GGM</v>
       </c>
       <c r="I40" s="6" t="s">
@@ -5222,7 +5682,7 @@
         <v>18214.75</v>
       </c>
       <c r="L40" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-4815.9000000000015</v>
       </c>
       <c r="V40" s="6" t="s">
@@ -5234,8 +5694,11 @@
       <c r="X40" s="17">
         <v>22240.09</v>
       </c>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z40" s="17"/>
+      <c r="AA40" s="17"/>
+      <c r="AB40" s="17"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>175</v>
       </c>
@@ -5252,7 +5715,7 @@
         <v>1236195.68</v>
       </c>
       <c r="G41" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>GGM</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -5265,7 +5728,7 @@
         <v>510440.15</v>
       </c>
       <c r="L41" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-725755.52999999991</v>
       </c>
       <c r="V41" s="1" t="s">
@@ -5277,8 +5740,11 @@
       <c r="X41" s="14">
         <v>755112.7</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z41" s="14"/>
+      <c r="AA41" s="14"/>
+      <c r="AB41" s="14"/>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
         <v>176</v>
       </c>
@@ -5295,7 +5761,7 @@
         <v>1098061.48</v>
       </c>
       <c r="G42" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>GGM</v>
       </c>
       <c r="I42" s="6" t="s">
@@ -5308,7 +5774,7 @@
         <v>631028.31999999995</v>
       </c>
       <c r="L42" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-467033.16000000003</v>
       </c>
       <c r="V42" s="6" t="s">
@@ -5320,8 +5786,11 @@
       <c r="X42" s="17">
         <v>787945.7</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z42" s="17"/>
+      <c r="AA42" s="17"/>
+      <c r="AB42" s="17"/>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>177</v>
       </c>
@@ -5338,7 +5807,7 @@
         <v>198641.06</v>
       </c>
       <c r="G43" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>GGM</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -5351,7 +5820,7 @@
         <v>126978.78</v>
       </c>
       <c r="L43" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-71662.28</v>
       </c>
       <c r="V43" s="1" t="s">
@@ -5363,8 +5832,11 @@
       <c r="X43" s="14">
         <v>172431</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z43" s="14"/>
+      <c r="AA43" s="14"/>
+      <c r="AB43" s="14"/>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="s">
         <v>178</v>
       </c>
@@ -5381,7 +5853,7 @@
         <v>46165.85</v>
       </c>
       <c r="G44" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>GGM</v>
       </c>
       <c r="I44" s="6" t="s">
@@ -5394,7 +5866,7 @@
         <v>29197.63</v>
       </c>
       <c r="L44" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-16968.219999999998</v>
       </c>
       <c r="V44" s="6" t="s">
@@ -5406,8 +5878,11 @@
       <c r="X44" s="17">
         <v>33780.839999999997</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z44" s="17"/>
+      <c r="AA44" s="17"/>
+      <c r="AB44" s="17"/>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>179</v>
       </c>
@@ -5424,7 +5899,7 @@
         <v>53945.74</v>
       </c>
       <c r="G45" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>GGM</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -5437,7 +5912,7 @@
         <v>4077694.45</v>
       </c>
       <c r="L45" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="V45" s="1" t="s">
@@ -5449,8 +5924,11 @@
       <c r="X45" s="14">
         <v>3069392</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Z45" s="14"/>
+      <c r="AA45" s="14"/>
+      <c r="AB45" s="14"/>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5467,7 +5945,7 @@
         <v>4077694.45</v>
       </c>
       <c r="G46" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>GGM</v>
       </c>
       <c r="I46" s="6" t="s">
@@ -5480,7 +5958,7 @@
         <v>30806.880000000001</v>
       </c>
       <c r="L46" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-23138.859999999997</v>
       </c>
       <c r="V46" s="6" t="s">
@@ -5492,9 +5970,12 @@
       <c r="X46" s="17">
         <v>41331.65</v>
       </c>
+      <c r="Z46" s="17"/>
+      <c r="AA46" s="17"/>
+      <c r="AB46" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA7:AF16">
+  <conditionalFormatting sqref="AE7:AK16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5506,8 +5987,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH13:AJ16 AL13:AN16 AA7:AF16">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="AM13:AO16 AQ13:AS16 AE7:AK16">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656BA3F6-89D7-41CB-8076-878DCD4A9330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC48FEEB-F891-4126-929C-AEDC64A082A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="289">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -943,7 +943,7 @@
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1022,12 +1022,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -1099,7 +1093,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1125,19 +1119,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -1738,7 +1729,7 @@
       <c r="E19" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="Q19" s="31"/>
+      <c r="Q19" s="30"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
@@ -1823,7 +1814,7 @@
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B26" s="30">
+      <c r="B26" s="29">
         <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2558,7 +2549,7 @@
       <c r="D20" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="Q20" s="31" t="s">
+      <c r="Q20" s="30" t="s">
         <v>266</v>
       </c>
       <c r="R20" s="1" t="s">
@@ -3341,7 +3332,7 @@
       <c r="V7" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="W7" s="32">
+      <c r="W7" s="31">
         <v>0.99999800000000005</v>
       </c>
       <c r="X7" s="14">
@@ -3350,7 +3341,7 @@
       <c r="Z7" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="AA7" s="32">
+      <c r="AA7" s="31">
         <v>0.99995000000000001</v>
       </c>
       <c r="AB7" s="14">
@@ -3420,10 +3411,10 @@
       <c r="AZ7" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="BA7" s="24">
+      <c r="BA7" s="23">
         <v>0.99999979999999999</v>
       </c>
-      <c r="BB7" s="26">
+      <c r="BB7" s="25">
         <v>91.979789999999994</v>
       </c>
       <c r="BD7" s="1" t="s">
@@ -3504,7 +3495,7 @@
       <c r="V8" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="W8" s="33">
+      <c r="W8" s="32">
         <v>0.99999899999999997</v>
       </c>
       <c r="X8" s="17">
@@ -3513,7 +3504,7 @@
       <c r="Z8" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="AA8" s="33">
+      <c r="AA8" s="32">
         <v>0.999973</v>
       </c>
       <c r="AB8" s="17">
@@ -3583,10 +3574,10 @@
       <c r="AZ8" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="BA8" s="25">
+      <c r="BA8" s="24">
         <v>0.99997420000000004</v>
       </c>
-      <c r="BB8" s="27">
+      <c r="BB8" s="26">
         <v>99.435940000000002</v>
       </c>
       <c r="BD8" s="6" t="s">
@@ -3667,7 +3658,7 @@
       <c r="V9" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="W9" s="32">
+      <c r="W9" s="31">
         <v>0.99999899999999997</v>
       </c>
       <c r="X9" s="14">
@@ -3676,7 +3667,7 @@
       <c r="Z9" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="AA9" s="32">
+      <c r="AA9" s="31">
         <v>0.99992800000000004</v>
       </c>
       <c r="AB9" s="14">
@@ -3746,10 +3737,10 @@
       <c r="AZ9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="BA9" s="24">
+      <c r="BA9" s="23">
         <v>0.9999806</v>
       </c>
-      <c r="BB9" s="26">
+      <c r="BB9" s="25">
         <v>88.003110000000007</v>
       </c>
       <c r="BD9" s="1" t="s">
@@ -3830,7 +3821,7 @@
       <c r="V10" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="W10" s="33">
+      <c r="W10" s="32">
         <v>0.99999700000000002</v>
       </c>
       <c r="X10" s="17">
@@ -3839,7 +3830,7 @@
       <c r="Z10" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="AA10" s="33">
+      <c r="AA10" s="32">
         <v>0.99969300000000005</v>
       </c>
       <c r="AB10" s="17">
@@ -3961,7 +3952,7 @@
       <c r="V11" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="W11" s="32">
+      <c r="W11" s="31">
         <v>0.99999499999999997</v>
       </c>
       <c r="X11" s="14">
@@ -3970,7 +3961,7 @@
       <c r="Z11" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="AA11" s="32">
+      <c r="AA11" s="31">
         <v>0.99996600000000002</v>
       </c>
       <c r="AB11" s="14">
@@ -4079,7 +4070,7 @@
       <c r="V12" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="W12" s="33">
+      <c r="W12" s="32">
         <v>0.99999700000000002</v>
       </c>
       <c r="X12" s="17">
@@ -4088,7 +4079,7 @@
       <c r="Z12" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="AA12" s="33">
+      <c r="AA12" s="32">
         <v>0.99982899999999997</v>
       </c>
       <c r="AB12" s="17">
@@ -4200,7 +4191,7 @@
       <c r="V13" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="W13" s="32">
+      <c r="W13" s="31">
         <v>0.99999099999999996</v>
       </c>
       <c r="X13" s="14">
@@ -4209,7 +4200,7 @@
       <c r="Z13" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="AA13" s="32">
+      <c r="AA13" s="31">
         <v>0.99989799999999995</v>
       </c>
       <c r="AB13" s="14">
@@ -4319,7 +4310,7 @@
       <c r="V14" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="W14" s="33">
+      <c r="W14" s="32">
         <v>0.99999000000000005</v>
       </c>
       <c r="X14" s="17">
@@ -4328,7 +4319,7 @@
       <c r="Z14" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="AA14" s="33">
+      <c r="AA14" s="32">
         <v>0.99961699999999998</v>
       </c>
       <c r="AB14" s="17">
@@ -4441,7 +4432,7 @@
       <c r="V15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="W15" s="32">
+      <c r="W15" s="31">
         <v>0.99999800000000005</v>
       </c>
       <c r="X15" s="14">
@@ -4450,7 +4441,7 @@
       <c r="Z15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="AA15" s="32">
+      <c r="AA15" s="31">
         <v>0.99987199999999998</v>
       </c>
       <c r="AB15" s="14">
@@ -4548,7 +4539,7 @@
       <c r="V16" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="W16" s="33">
+      <c r="W16" s="32">
         <v>0.999996</v>
       </c>
       <c r="X16" s="17">
@@ -4557,7 +4548,7 @@
       <c r="Z16" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="AA16" s="33">
+      <c r="AA16" s="32">
         <v>0.99970099999999995</v>
       </c>
       <c r="AB16" s="17">
@@ -4686,9 +4677,14 @@
       <c r="V19" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="AD19" s="22"/>
-      <c r="AE19" s="22"/>
-      <c r="AF19" s="22"/>
+      <c r="Z19" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="AD19" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="13"/>
       <c r="BD19" s="1" t="s">
         <v>201</v>
       </c>
@@ -4774,9 +4770,39 @@
       <c r="X21" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="Z21" s="13"/>
-      <c r="AA21" s="13"/>
-      <c r="AB21" s="13"/>
+      <c r="Z21" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA21" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB21" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD21" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE21" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF21" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG21" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="AH21" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI21" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="AJ21" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="AK21" s="9" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="22" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
@@ -4832,15 +4858,52 @@
       <c r="V22" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="W22" s="32">
+      <c r="W22" s="31">
         <v>0.99996799999999997</v>
       </c>
       <c r="X22" s="14">
         <v>72886.599426000001</v>
       </c>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
+      <c r="Z22" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA22" s="31">
+        <v>0.998919</v>
+      </c>
+      <c r="AB22" s="14">
+        <v>424624.7</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE22" s="14">
+        <f>+_xlfn.XLOOKUP($AD22,N$22:N$31,P$22:P$31)</f>
+        <v>5285818</v>
+      </c>
+      <c r="AF22" s="14">
+        <f>+_xlfn.XLOOKUP($AD22,R$22:R$31,T$22:T$31)</f>
+        <v>7558374</v>
+      </c>
+      <c r="AG22" s="14">
+        <f>+_xlfn.XLOOKUP($AD22,B$22:B$31,D$22:D$31)</f>
+        <v>1072993.76</v>
+      </c>
+      <c r="AH22" s="14">
+        <f>+_xlfn.XLOOKUP($AD22,B$22:B$31,F$22:F$31)</f>
+        <v>879227.23</v>
+      </c>
+      <c r="AI22" s="14">
+        <f>+_xlfn.XLOOKUP($AD22,V$22:V$31,X$22:X$31)</f>
+        <v>72886.599426000001</v>
+      </c>
+      <c r="AJ22" s="14">
+        <f>+_xlfn.XLOOKUP($AD22,I$22:I$31,K$22:K$31)</f>
+        <v>66881.517999999996</v>
+      </c>
+      <c r="AK22" s="14">
+        <f>+_xlfn.XLOOKUP(AD22,$Z$22:$Z$31,$AB$22:$AB$31)</f>
+        <v>424624.7</v>
+      </c>
     </row>
     <row r="23" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
@@ -4896,21 +4959,58 @@
       <c r="V23" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="W23" s="33">
+      <c r="W23" s="32">
         <v>0.999977</v>
       </c>
       <c r="X23" s="17">
         <v>8395.1301469999999</v>
       </c>
-      <c r="Z23" s="17"/>
-      <c r="AA23" s="17"/>
-      <c r="AB23" s="17"/>
-      <c r="AM23" s="28"/>
-      <c r="AN23" s="28"/>
-      <c r="AO23" s="28"/>
-      <c r="AQ23" s="28"/>
-      <c r="AR23" s="28"/>
-      <c r="AS23" s="28"/>
+      <c r="Z23" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA23" s="32">
+        <v>0.99666699999999997</v>
+      </c>
+      <c r="AB23" s="17">
+        <v>101494.2</v>
+      </c>
+      <c r="AD23" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE23" s="14">
+        <f t="shared" ref="AE23:AE31" si="17">+_xlfn.XLOOKUP($AD23,N$22:N$31,P$22:P$31)</f>
+        <v>655919.19999999995</v>
+      </c>
+      <c r="AF23" s="14">
+        <f t="shared" ref="AF23:AF31" si="18">+_xlfn.XLOOKUP($AD23,R$22:R$31,T$22:T$31)</f>
+        <v>634278.5</v>
+      </c>
+      <c r="AG23" s="14">
+        <f t="shared" ref="AG23:AG31" si="19">+_xlfn.XLOOKUP($AD23,B$22:B$31,D$22:D$31)</f>
+        <v>215298.15</v>
+      </c>
+      <c r="AH23" s="14">
+        <f t="shared" ref="AH23:AH31" si="20">+_xlfn.XLOOKUP($AD23,B$22:B$31,F$22:F$31)</f>
+        <v>191678.16</v>
+      </c>
+      <c r="AI23" s="14">
+        <f t="shared" ref="AI23:AI31" si="21">+_xlfn.XLOOKUP($AD23,V$22:V$31,X$22:X$31)</f>
+        <v>8395.1301469999999</v>
+      </c>
+      <c r="AJ23" s="14">
+        <f t="shared" ref="AJ23:AJ31" si="22">+_xlfn.XLOOKUP($AD23,I$22:I$31,K$22:K$31)</f>
+        <v>7970.5929999999998</v>
+      </c>
+      <c r="AK23" s="14">
+        <f t="shared" ref="AK23:AK31" si="23">+_xlfn.XLOOKUP(AD23,$Z$22:$Z$31,$AB$22:$AB$31)</f>
+        <v>101494.2</v>
+      </c>
+      <c r="AM23" s="27"/>
+      <c r="AN23" s="27"/>
+      <c r="AO23" s="27"/>
+      <c r="AQ23" s="27"/>
+      <c r="AR23" s="27"/>
+      <c r="AS23" s="27"/>
     </row>
     <row r="24" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
@@ -4966,25 +5066,62 @@
       <c r="V24" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="W24" s="32">
+      <c r="W24" s="31">
         <v>0.99997899999999995</v>
       </c>
       <c r="X24" s="14">
         <v>11331.678796</v>
       </c>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AM24" s="28"/>
-      <c r="AN24" s="29"/>
-      <c r="AO24" s="29"/>
-      <c r="AQ24" s="29"/>
-      <c r="AR24" s="29"/>
-      <c r="AS24" s="29"/>
+      <c r="Z24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA24" s="31">
+        <v>0.99987199999999998</v>
+      </c>
+      <c r="AB24" s="14">
+        <v>27934.33</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE24" s="14">
+        <f t="shared" si="17"/>
+        <v>711743.3</v>
+      </c>
+      <c r="AF24" s="14">
+        <f t="shared" si="18"/>
+        <v>1813809</v>
+      </c>
+      <c r="AG24" s="14">
+        <f t="shared" si="19"/>
+        <v>176803.48</v>
+      </c>
+      <c r="AH24" s="14">
+        <f t="shared" si="20"/>
+        <v>170016.12</v>
+      </c>
+      <c r="AI24" s="14">
+        <f t="shared" si="21"/>
+        <v>11331.678796</v>
+      </c>
+      <c r="AJ24" s="14">
+        <f t="shared" si="22"/>
+        <v>10259.941000000001</v>
+      </c>
+      <c r="AK24" s="14">
+        <f t="shared" si="23"/>
+        <v>27934.33</v>
+      </c>
+      <c r="AM24" s="27"/>
+      <c r="AN24" s="28"/>
+      <c r="AO24" s="28"/>
+      <c r="AQ24" s="28"/>
+      <c r="AR24" s="28"/>
+      <c r="AS24" s="28"/>
     </row>
     <row r="25" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="C25" s="16">
         <v>0.98980849999999998</v>
@@ -5003,7 +5140,7 @@
         <v>GGM</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="J25" s="18">
         <v>0.99986940000000002</v>
@@ -5036,21 +5173,58 @@
       <c r="V25" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="W25" s="33">
+      <c r="W25" s="32">
         <v>0.99985199999999996</v>
       </c>
       <c r="X25" s="17">
         <v>2856.3407999999999</v>
       </c>
-      <c r="Z25" s="17"/>
-      <c r="AA25" s="17"/>
-      <c r="AB25" s="17"/>
-      <c r="AM25" s="28"/>
-      <c r="AN25" s="29"/>
-      <c r="AO25" s="29"/>
-      <c r="AQ25" s="29"/>
-      <c r="AR25" s="29"/>
-      <c r="AS25" s="29"/>
+      <c r="Z25" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA25" s="32">
+        <v>0.99764399999999998</v>
+      </c>
+      <c r="AB25" s="17">
+        <v>11391.69</v>
+      </c>
+      <c r="AD25" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AE25" s="14">
+        <f t="shared" si="17"/>
+        <v>96842.15</v>
+      </c>
+      <c r="AF25" s="14">
+        <f t="shared" si="18"/>
+        <v>300031.3</v>
+      </c>
+      <c r="AG25" s="14">
+        <f t="shared" si="19"/>
+        <v>23695.26</v>
+      </c>
+      <c r="AH25" s="14">
+        <f t="shared" si="20"/>
+        <v>20254.93</v>
+      </c>
+      <c r="AI25" s="14">
+        <f t="shared" si="21"/>
+        <v>2856.3407999999999</v>
+      </c>
+      <c r="AJ25" s="14">
+        <f t="shared" si="22"/>
+        <v>2682.71</v>
+      </c>
+      <c r="AK25" s="14">
+        <f t="shared" si="23"/>
+        <v>11391.69</v>
+      </c>
+      <c r="AM25" s="27"/>
+      <c r="AN25" s="28"/>
+      <c r="AO25" s="28"/>
+      <c r="AQ25" s="28"/>
+      <c r="AR25" s="28"/>
+      <c r="AS25" s="28"/>
     </row>
     <row r="26" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
@@ -5106,21 +5280,58 @@
       <c r="V26" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="W26" s="32">
+      <c r="W26" s="31">
         <v>0.99998200000000004</v>
       </c>
       <c r="X26" s="14">
         <v>59096.011952000001</v>
       </c>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="14"/>
-      <c r="AB26" s="14"/>
-      <c r="AM26" s="28"/>
-      <c r="AN26" s="29"/>
-      <c r="AO26" s="29"/>
-      <c r="AQ26" s="29"/>
-      <c r="AR26" s="29"/>
-      <c r="AS26" s="29"/>
+      <c r="Z26" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA26" s="31">
+        <v>0.99986600000000003</v>
+      </c>
+      <c r="AB26" s="14">
+        <v>162463.20000000001</v>
+      </c>
+      <c r="AD26" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AE26" s="14">
+        <f t="shared" si="17"/>
+        <v>1726783</v>
+      </c>
+      <c r="AF26" s="14">
+        <f t="shared" si="18"/>
+        <v>1646926</v>
+      </c>
+      <c r="AG26" s="14">
+        <f t="shared" si="19"/>
+        <v>1370516.61</v>
+      </c>
+      <c r="AH26" s="14">
+        <f t="shared" si="20"/>
+        <v>1270365.45</v>
+      </c>
+      <c r="AI26" s="14">
+        <f t="shared" si="21"/>
+        <v>59096.011952000001</v>
+      </c>
+      <c r="AJ26" s="14">
+        <f t="shared" si="22"/>
+        <v>54571.813999999998</v>
+      </c>
+      <c r="AK26" s="14">
+        <f t="shared" si="23"/>
+        <v>162463.20000000001</v>
+      </c>
+      <c r="AM26" s="27"/>
+      <c r="AN26" s="28"/>
+      <c r="AO26" s="28"/>
+      <c r="AQ26" s="28"/>
+      <c r="AR26" s="28"/>
+      <c r="AS26" s="28"/>
     </row>
     <row r="27" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
@@ -5176,17 +5387,54 @@
       <c r="V27" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="W27" s="33">
+      <c r="W27" s="32">
         <v>0.99997999999999998</v>
       </c>
       <c r="X27" s="17">
         <v>40276.492481000001</v>
       </c>
-      <c r="Z27" s="17"/>
-      <c r="AA27" s="17"/>
-      <c r="AB27" s="17"/>
-    </row>
-    <row r="28" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="Z27" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA27" s="32">
+        <v>0.99753099999999995</v>
+      </c>
+      <c r="AB27" s="17">
+        <v>453190.5</v>
+      </c>
+      <c r="AD27" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE27" s="14">
+        <f t="shared" si="17"/>
+        <v>2120841</v>
+      </c>
+      <c r="AF27" s="14">
+        <f t="shared" si="18"/>
+        <v>2056768</v>
+      </c>
+      <c r="AG27" s="14">
+        <f t="shared" si="19"/>
+        <v>1102885.5</v>
+      </c>
+      <c r="AH27" s="14">
+        <f t="shared" si="20"/>
+        <v>962242.14</v>
+      </c>
+      <c r="AI27" s="14">
+        <f t="shared" si="21"/>
+        <v>40276.492481000001</v>
+      </c>
+      <c r="AJ27" s="14">
+        <f t="shared" si="22"/>
+        <v>37554.368000000002</v>
+      </c>
+      <c r="AK27" s="14">
+        <f t="shared" si="23"/>
+        <v>453190.5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>177</v>
       </c>
@@ -5240,20 +5488,54 @@
       <c r="V28" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="W28" s="32">
+      <c r="W28" s="31">
         <v>0.99994000000000005</v>
       </c>
       <c r="X28" s="14">
         <v>20204.683582000001</v>
       </c>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-      <c r="AB28" s="14"/>
-      <c r="AD28" s="23"/>
-      <c r="AE28" s="23"/>
-      <c r="AF28" s="23"/>
-    </row>
-    <row r="29" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="Z28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA28" s="31">
+        <v>0.99860599999999999</v>
+      </c>
+      <c r="AB28" s="14">
+        <v>97029.98</v>
+      </c>
+      <c r="AD28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE28" s="14">
+        <f t="shared" si="17"/>
+        <v>999266.5</v>
+      </c>
+      <c r="AF28" s="14">
+        <f t="shared" si="18"/>
+        <v>2976087</v>
+      </c>
+      <c r="AG28" s="14">
+        <f t="shared" si="19"/>
+        <v>212970.27</v>
+      </c>
+      <c r="AH28" s="14">
+        <f t="shared" si="20"/>
+        <v>177553.42</v>
+      </c>
+      <c r="AI28" s="14">
+        <f t="shared" si="21"/>
+        <v>20204.683582000001</v>
+      </c>
+      <c r="AJ28" s="14">
+        <f t="shared" si="22"/>
+        <v>18001.951000000001</v>
+      </c>
+      <c r="AK28" s="14">
+        <f t="shared" si="23"/>
+        <v>97029.98</v>
+      </c>
+    </row>
+    <row r="29" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
         <v>178</v>
       </c>
@@ -5307,20 +5589,54 @@
       <c r="V29" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="W29" s="33">
+      <c r="W29" s="32">
         <v>0.99993799999999999</v>
       </c>
       <c r="X29" s="17">
         <v>2835.1556179999998</v>
       </c>
-      <c r="Z29" s="17"/>
-      <c r="AA29" s="17"/>
-      <c r="AB29" s="17"/>
-      <c r="AD29" s="23"/>
-      <c r="AE29" s="23"/>
-      <c r="AF29" s="23"/>
-    </row>
-    <row r="30" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="Z29" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AA29" s="32">
+        <v>0.99784799999999996</v>
+      </c>
+      <c r="AB29" s="17">
+        <v>16657.2</v>
+      </c>
+      <c r="AD29" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AE29" s="14">
+        <f t="shared" si="17"/>
+        <v>140633.70000000001</v>
+      </c>
+      <c r="AF29" s="14">
+        <f t="shared" si="18"/>
+        <v>128388.6</v>
+      </c>
+      <c r="AG29" s="14">
+        <f t="shared" si="19"/>
+        <v>47981.11</v>
+      </c>
+      <c r="AH29" s="14">
+        <f t="shared" si="20"/>
+        <v>41689.589999999997</v>
+      </c>
+      <c r="AI29" s="14">
+        <f t="shared" si="21"/>
+        <v>2835.1556179999998</v>
+      </c>
+      <c r="AJ29" s="14">
+        <f t="shared" si="22"/>
+        <v>2688.72</v>
+      </c>
+      <c r="AK29" s="14">
+        <f t="shared" si="23"/>
+        <v>16657.2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>179</v>
       </c>
@@ -5374,20 +5690,54 @@
       <c r="V30" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="W30" s="32">
+      <c r="W30" s="31">
         <v>0.999973</v>
       </c>
       <c r="X30" s="14">
         <v>189197.220477</v>
       </c>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
-      <c r="AB30" s="14"/>
-      <c r="AD30" s="23"/>
-      <c r="AE30" s="23"/>
-      <c r="AF30" s="23"/>
-    </row>
-    <row r="31" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="Z30" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA30" s="31">
+        <v>0.99802000000000002</v>
+      </c>
+      <c r="AB30" s="14">
+        <v>1626782</v>
+      </c>
+      <c r="AD30" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE30" s="14">
+        <f t="shared" si="17"/>
+        <v>14749160</v>
+      </c>
+      <c r="AF30" s="14">
+        <f t="shared" si="18"/>
+        <v>14407510</v>
+      </c>
+      <c r="AG30" s="14">
+        <f t="shared" si="19"/>
+        <v>4160546.94</v>
+      </c>
+      <c r="AH30" s="14">
+        <f t="shared" si="20"/>
+        <v>3653520.24</v>
+      </c>
+      <c r="AI30" s="14">
+        <f t="shared" si="21"/>
+        <v>189197.220477</v>
+      </c>
+      <c r="AJ30" s="14">
+        <f t="shared" si="22"/>
+        <v>3653520.236</v>
+      </c>
+      <c r="AK30" s="14">
+        <f t="shared" si="23"/>
+        <v>1626782</v>
+      </c>
+    </row>
+    <row r="31" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>180</v>
       </c>
@@ -5441,25 +5791,59 @@
       <c r="V31" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="W31" s="33">
+      <c r="W31" s="32">
         <v>0.99996499999999999</v>
       </c>
       <c r="X31" s="17">
         <v>2423.543439</v>
       </c>
-      <c r="Z31" s="17"/>
-      <c r="AA31" s="17"/>
-      <c r="AB31" s="17"/>
-      <c r="AD31" s="23"/>
-      <c r="AE31" s="23"/>
-      <c r="AF31" s="23"/>
+      <c r="Z31" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AA31" s="32">
+        <v>0.98897800000000002</v>
+      </c>
+      <c r="AB31" s="17">
+        <v>43128.99</v>
+      </c>
+      <c r="AD31" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE31" s="14">
+        <f t="shared" si="17"/>
+        <v>97667.94</v>
+      </c>
+      <c r="AF31" s="14">
+        <f t="shared" si="18"/>
+        <v>89659.199999999997</v>
+      </c>
+      <c r="AG31" s="14">
+        <f t="shared" si="19"/>
+        <v>62031.38</v>
+      </c>
+      <c r="AH31" s="14">
+        <f t="shared" si="20"/>
+        <v>55105.7</v>
+      </c>
+      <c r="AI31" s="14">
+        <f t="shared" si="21"/>
+        <v>2423.543439</v>
+      </c>
+      <c r="AJ31" s="14">
+        <f t="shared" si="22"/>
+        <v>2309.4769999999999</v>
+      </c>
+      <c r="AK31" s="14">
+        <f t="shared" si="23"/>
+        <v>43128.99</v>
+      </c>
     </row>
     <row r="32" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="AD32" s="23"/>
-      <c r="AE32" s="23"/>
-      <c r="AF32" s="23"/>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="AD32" s="22"/>
+      <c r="AE32" s="22"/>
+      <c r="AF32" s="22"/>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
         <v>184</v>
       </c>
@@ -5470,7 +5854,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="2:28" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B36" s="9" t="s">
         <v>166</v>
       </c>
@@ -5510,11 +5894,8 @@
       <c r="X36" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="Z36" s="13"/>
-      <c r="AA36" s="13"/>
-      <c r="AB36" s="13"/>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>171</v>
       </c>
@@ -5550,17 +5931,14 @@
       <c r="V37" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="W37" s="32">
+      <c r="W37" s="31">
         <v>0.99801799999999996</v>
       </c>
       <c r="X37" s="14">
         <v>584602.6</v>
       </c>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-    </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
         <v>172</v>
       </c>
@@ -5577,7 +5955,7 @@
         <v>211942.1</v>
       </c>
       <c r="G38" s="6" t="str">
-        <f t="shared" ref="G38:G46" si="17">+IF(F38&lt;D38,"GGM","BM")</f>
+        <f t="shared" ref="G38:G46" si="24">+IF(F38&lt;D38,"GGM","BM")</f>
         <v>GGM</v>
       </c>
       <c r="I38" s="6" t="s">
@@ -5590,23 +5968,20 @@
         <v>100789.75999999999</v>
       </c>
       <c r="L38" s="17">
-        <f t="shared" ref="L38:L46" si="18">+K38-_xlfn.XLOOKUP(I38,B$37:B$46,F$37:F$46)</f>
+        <f t="shared" ref="L38:L46" si="25">+K38-_xlfn.XLOOKUP(I38,B$37:B$46,F$37:F$46)</f>
         <v>-111152.34000000001</v>
       </c>
       <c r="V38" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="W38" s="33">
+      <c r="W38" s="32">
         <v>0.99567000000000005</v>
       </c>
       <c r="X38" s="17">
         <v>118904.3</v>
       </c>
-      <c r="Z38" s="17"/>
-      <c r="AA38" s="17"/>
-      <c r="AB38" s="17"/>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>173</v>
       </c>
@@ -5623,7 +5998,7 @@
         <v>174775.12</v>
       </c>
       <c r="G39" s="1" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -5636,23 +6011,20 @@
         <v>120410.38</v>
       </c>
       <c r="L39" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>-54364.739999999991</v>
       </c>
       <c r="V39" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="W39" s="32">
+      <c r="W39" s="31">
         <v>0.99534699999999998</v>
       </c>
       <c r="X39" s="14">
         <v>169254.2</v>
       </c>
-      <c r="Z39" s="14"/>
-      <c r="AA39" s="14"/>
-      <c r="AB39" s="14"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
         <v>174</v>
       </c>
@@ -5669,7 +6041,7 @@
         <v>23030.65</v>
       </c>
       <c r="G40" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I40" s="6" t="s">
@@ -5682,23 +6054,20 @@
         <v>18214.75</v>
       </c>
       <c r="L40" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>-4815.9000000000015</v>
       </c>
       <c r="V40" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="W40" s="33">
+      <c r="W40" s="32">
         <v>0.99124800000000002</v>
       </c>
       <c r="X40" s="17">
         <v>22240.09</v>
       </c>
-      <c r="Z40" s="17"/>
-      <c r="AA40" s="17"/>
-      <c r="AB40" s="17"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>175</v>
       </c>
@@ -5715,7 +6084,7 @@
         <v>1236195.68</v>
       </c>
       <c r="G41" s="1" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -5728,23 +6097,20 @@
         <v>510440.15</v>
       </c>
       <c r="L41" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>-725755.52999999991</v>
       </c>
       <c r="V41" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="W41" s="32">
+      <c r="W41" s="31">
         <v>0.99727699999999997</v>
       </c>
       <c r="X41" s="14">
         <v>755112.7</v>
       </c>
-      <c r="Z41" s="14"/>
-      <c r="AA41" s="14"/>
-      <c r="AB41" s="14"/>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
         <v>176</v>
       </c>
@@ -5761,7 +6127,7 @@
         <v>1098061.48</v>
       </c>
       <c r="G42" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I42" s="6" t="s">
@@ -5774,23 +6140,20 @@
         <v>631028.31999999995</v>
       </c>
       <c r="L42" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>-467033.16000000003</v>
       </c>
       <c r="V42" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="W42" s="33">
+      <c r="W42" s="32">
         <v>0.99294800000000005</v>
       </c>
       <c r="X42" s="17">
         <v>787945.7</v>
       </c>
-      <c r="Z42" s="17"/>
-      <c r="AA42" s="17"/>
-      <c r="AB42" s="17"/>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>177</v>
       </c>
@@ -5807,7 +6170,7 @@
         <v>198641.06</v>
       </c>
       <c r="G43" s="1" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -5820,23 +6183,20 @@
         <v>126978.78</v>
       </c>
       <c r="L43" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>-71662.28</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="W43" s="32">
+      <c r="W43" s="31">
         <v>0.99575800000000003</v>
       </c>
       <c r="X43" s="14">
         <v>172431</v>
       </c>
-      <c r="Z43" s="14"/>
-      <c r="AA43" s="14"/>
-      <c r="AB43" s="14"/>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="s">
         <v>178</v>
       </c>
@@ -5853,7 +6213,7 @@
         <v>46165.85</v>
       </c>
       <c r="G44" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I44" s="6" t="s">
@@ -5866,23 +6226,20 @@
         <v>29197.63</v>
       </c>
       <c r="L44" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>-16968.219999999998</v>
       </c>
       <c r="V44" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="W44" s="33">
+      <c r="W44" s="32">
         <v>0.99148400000000003</v>
       </c>
       <c r="X44" s="17">
         <v>33780.839999999997</v>
       </c>
-      <c r="Z44" s="17"/>
-      <c r="AA44" s="17"/>
-      <c r="AB44" s="17"/>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>179</v>
       </c>
@@ -5899,7 +6256,7 @@
         <v>53945.74</v>
       </c>
       <c r="G45" s="1" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -5912,23 +6269,20 @@
         <v>4077694.45</v>
       </c>
       <c r="L45" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V45" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="W45" s="32">
+      <c r="W45" s="31">
         <v>0.993228</v>
       </c>
       <c r="X45" s="14">
         <v>3069392</v>
       </c>
-      <c r="Z45" s="14"/>
-      <c r="AA45" s="14"/>
-      <c r="AB45" s="14"/>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B46" s="6" t="s">
         <v>180</v>
       </c>
@@ -5945,7 +6299,7 @@
         <v>4077694.45</v>
       </c>
       <c r="G46" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I46" s="6" t="s">
@@ -5958,24 +6312,45 @@
         <v>30806.880000000001</v>
       </c>
       <c r="L46" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>-23138.859999999997</v>
       </c>
       <c r="V46" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="W46" s="33">
+      <c r="W46" s="32">
         <v>0.99019000000000001</v>
       </c>
       <c r="X46" s="17">
         <v>41331.65</v>
       </c>
-      <c r="Z46" s="17"/>
-      <c r="AA46" s="17"/>
-      <c r="AB46" s="17"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="AE7:AK16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM13:AO16 AQ13:AS16 AE7:AK16">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE22:AK31">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5987,8 +6362,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM13:AO16 AQ13:AS16 AE7:AK16">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="AE22:AK31">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6319,7 +6694,7 @@
       <c r="B40" s="1">
         <v>37</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C40" s="29" t="s">
         <v>280</v>
       </c>
     </row>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC48FEEB-F891-4126-929C-AEDC64A082A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC0E92A-92C9-4E3F-8BE9-F4C0DC8654B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
   <sheets>
     <sheet name="literature review" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,10 @@
     <sheet name="sources" sheetId="4" r:id="rId4"/>
     <sheet name="modelling" sheetId="6" r:id="rId5"/>
     <sheet name="results" sheetId="8" r:id="rId6"/>
-    <sheet name="Ideas" sheetId="5" r:id="rId7"/>
-    <sheet name="pytrends_categories" sheetId="9" r:id="rId8"/>
-    <sheet name="help" sheetId="7" r:id="rId9"/>
+    <sheet name="results_train_test" sheetId="10" r:id="rId7"/>
+    <sheet name="Ideas" sheetId="5" r:id="rId8"/>
+    <sheet name="pytrends_categories" sheetId="9" r:id="rId9"/>
+    <sheet name="help" sheetId="7" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="295">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -931,6 +932,24 @@
   </si>
   <si>
     <t>Varicela</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>EPIDEMICS</t>
+  </si>
+  <si>
+    <t>COVID</t>
+  </si>
+  <si>
+    <t>BM &amp; GGM</t>
+  </si>
+  <si>
+    <t>GGM Refined</t>
+  </si>
+  <si>
+    <t>Chicungunya</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1058,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1070,6 +1089,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1093,7 +1130,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1135,6 +1172,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1882,6 +1924,40 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5625718-4007-43A2-8FA5-6282944FC450}">
+  <dimension ref="B1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CEB97B9-116F-4382-A8CC-FDBD6D42603B}">
   <dimension ref="B1:B9"/>
@@ -2989,7 +3065,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2EA5AC-0586-4893-B88A-0F9AA6E9FD44}">
-  <dimension ref="B1:BJ46"/>
+  <dimension ref="B1:BR46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -3023,22 +3099,26 @@
     <col min="36" max="36" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="12.109375" style="1" customWidth="1"/>
     <col min="38" max="38" width="2" style="20" customWidth="1"/>
-    <col min="39" max="41" width="12.109375" style="1" customWidth="1"/>
-    <col min="42" max="42" width="2" style="20" customWidth="1"/>
-    <col min="43" max="45" width="12.109375" style="1" customWidth="1"/>
-    <col min="46" max="46" width="2" style="20" customWidth="1"/>
-    <col min="47" max="47" width="15.109375" style="1" customWidth="1"/>
-    <col min="48" max="50" width="8.88671875" style="1"/>
+    <col min="39" max="39" width="15.109375" style="1" customWidth="1"/>
+    <col min="40" max="42" width="8.88671875" style="1"/>
+    <col min="43" max="43" width="2" style="20" customWidth="1"/>
+    <col min="44" max="46" width="8.88671875" style="1"/>
+    <col min="47" max="47" width="2" style="20" customWidth="1"/>
+    <col min="48" max="50" width="12.109375" style="1" customWidth="1"/>
     <col min="51" max="51" width="2" style="20" customWidth="1"/>
-    <col min="52" max="54" width="8.88671875" style="1"/>
+    <col min="52" max="54" width="12.109375" style="1" customWidth="1"/>
     <col min="55" max="55" width="2" style="20" customWidth="1"/>
-    <col min="56" max="56" width="11.88671875" style="1" customWidth="1"/>
-    <col min="57" max="60" width="8.88671875" style="1"/>
-    <col min="61" max="61" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="16384" width="8.88671875" style="1"/>
+    <col min="56" max="58" width="12.109375" style="1" customWidth="1"/>
+    <col min="59" max="59" width="2" style="20" customWidth="1"/>
+    <col min="60" max="62" width="12.109375" style="1" customWidth="1"/>
+    <col min="63" max="63" width="2" style="20" customWidth="1"/>
+    <col min="64" max="64" width="11.88671875" style="1" customWidth="1"/>
+    <col min="65" max="68" width="8.88671875" style="1"/>
+    <col min="69" max="69" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:62" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:70" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
         <v>165</v>
       </c>
@@ -3046,7 +3126,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="2" spans="2:62" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
         <v>186</v>
       </c>
@@ -3073,22 +3153,28 @@
       <c r="AE2" s="19"/>
       <c r="AF2" s="19"/>
       <c r="AM2" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="AR2" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="AV2" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="AQ2" s="19" t="s">
+      <c r="AZ2" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="AU2" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="AZ2" s="19" t="s">
-        <v>200</v>
-      </c>
       <c r="BD2" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="BH2" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="BL2" s="19" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="2:62" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
         <v>181</v>
       </c>
@@ -3115,10 +3201,10 @@
       <c r="AM4" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="AQ4" s="13" t="s">
+      <c r="AR4" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="AU4" s="13" t="s">
+      <c r="AV4" s="13" t="s">
         <v>198</v>
       </c>
       <c r="AZ4" s="13" t="s">
@@ -3127,8 +3213,14 @@
       <c r="BD4" s="13" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="6" spans="2:62" x14ac:dyDescent="0.3">
+      <c r="BH4" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="BL4" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>166</v>
       </c>
@@ -3223,25 +3315,25 @@
         <v>195</v>
       </c>
       <c r="AN6" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="AO6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AO6" s="9" t="s">
+      <c r="AP6" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="AQ6" s="9" t="s">
+      <c r="AR6" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="AR6" s="9" t="s">
+      <c r="AS6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AS6" s="9" t="s">
+      <c r="AT6" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="AU6" s="9" t="s">
+      <c r="AV6" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="AV6" s="9" t="s">
-        <v>134</v>
       </c>
       <c r="AW6" s="9" t="s">
         <v>187</v>
@@ -3262,23 +3354,41 @@
         <v>195</v>
       </c>
       <c r="BE6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BF6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="BH6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="BI6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BJ6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="BL6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="BM6" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="BF6" s="9" t="s">
+      <c r="BN6" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="BG6" s="9" t="s">
+      <c r="BO6" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="BH6" s="9" t="s">
+      <c r="BP6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="BI6" s="9" t="s">
+      <c r="BQ6" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="BJ6" s="9"/>
-    </row>
-    <row r="7" spans="2:62" x14ac:dyDescent="0.3">
+      <c r="BR6" s="9"/>
+    </row>
+    <row r="7" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>171</v>
       </c>
@@ -3379,69 +3489,87 @@
         <v>91507.114184000005</v>
       </c>
       <c r="AM7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AO7" s="12">
+        <v>-0.25174930000000001</v>
+      </c>
+      <c r="AP7" s="14">
+        <v>210875.2597</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="AS7" s="23">
+        <v>0.99999979999999999</v>
+      </c>
+      <c r="AT7" s="25">
+        <v>91.979789999999994</v>
+      </c>
+      <c r="AV7" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AN7" s="12">
+      <c r="AW7" s="12">
         <v>0.94224399999999997</v>
       </c>
-      <c r="AO7" s="14">
+      <c r="AX7" s="14">
         <v>4703.6260300000004</v>
       </c>
-      <c r="AQ7" s="1" t="s">
+      <c r="AZ7" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AR7" s="12">
+      <c r="BA7" s="12">
         <v>0.91772100000000001</v>
       </c>
-      <c r="AS7" s="14">
+      <c r="BB7" s="14">
         <v>5614.0714690000004</v>
       </c>
-      <c r="AU7" s="1" t="s">
+      <c r="BD7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="BE7" s="12">
+        <v>0.91772100000000001</v>
+      </c>
+      <c r="BF7" s="14">
+        <v>5614.0714690000004</v>
+      </c>
+      <c r="BH7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="BI7" s="12">
+        <v>0.91772100000000001</v>
+      </c>
+      <c r="BJ7" s="14">
+        <v>5614.0714690000004</v>
+      </c>
+      <c r="BL7" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AV7" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AW7" s="12">
-        <v>-0.25174930000000001</v>
-      </c>
-      <c r="AX7" s="14">
+      <c r="BM7" s="14">
+        <f>+_xlfn.XLOOKUP($BL7,$AV$7:$AV$9,$AX$7:$AX$9)</f>
+        <v>22520.654823000001</v>
+      </c>
+      <c r="BN7" s="14">
+        <f>+_xlfn.XLOOKUP(BL7,$AZ$7:$AZ$9,$BB$7:$BB$9)</f>
+        <v>16596.507481000001</v>
+      </c>
+      <c r="BO7" s="14">
+        <f>+AP7</f>
         <v>210875.2597</v>
       </c>
-      <c r="AZ7" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="BA7" s="23">
-        <v>0.99999979999999999</v>
-      </c>
-      <c r="BB7" s="25">
+      <c r="BP7" s="14">
+        <f>+AP8</f>
+        <v>15764.5885</v>
+      </c>
+      <c r="BQ7" s="14">
+        <f>+AT7</f>
         <v>91.979789999999994</v>
       </c>
-      <c r="BD7" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="BE7" s="14">
-        <f>+_xlfn.XLOOKUP($BD7,$AM$7:$AM$9,$AO$7:$AO$9)</f>
-        <v>22520.654823000001</v>
-      </c>
-      <c r="BF7" s="14">
-        <f>+_xlfn.XLOOKUP(BD7,$AQ$7:$AQ$9,$AS$7:$AS$9)</f>
-        <v>16596.507481000001</v>
-      </c>
-      <c r="BG7" s="14">
-        <f>+AX7</f>
-        <v>210875.2597</v>
-      </c>
-      <c r="BH7" s="14">
-        <f>+AX8</f>
-        <v>15764.5885</v>
-      </c>
-      <c r="BI7" s="14">
-        <f>+BB7</f>
-        <v>91.979789999999994</v>
-      </c>
-    </row>
-    <row r="8" spans="2:62" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>172</v>
       </c>
@@ -3513,27 +3641,27 @@
       <c r="AD8" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="AE8" s="17">
+      <c r="AE8" s="14">
         <f t="shared" ref="AE8:AE16" si="3">+_xlfn.XLOOKUP($AD8,N$7:N$16,P$7:P$16)</f>
         <v>1304208</v>
       </c>
-      <c r="AF8" s="17">
+      <c r="AF8" s="14">
         <f t="shared" ref="AF8:AF16" si="4">+_xlfn.XLOOKUP($AD8,R$7:R$16,T$7:T$16)</f>
         <v>518469</v>
       </c>
-      <c r="AG8" s="17">
+      <c r="AG8" s="14">
         <f t="shared" ref="AG8:AG16" si="5">+_xlfn.XLOOKUP($AD8,B$7:B$16,D$7:D$16)</f>
         <v>1864908.65</v>
       </c>
-      <c r="AH8" s="17">
+      <c r="AH8" s="14">
         <f t="shared" ref="AH8:AH16" si="6">+_xlfn.XLOOKUP($AD8,B$7:B$16,F$7:F$16)</f>
         <v>845419.62</v>
       </c>
-      <c r="AI8" s="17">
+      <c r="AI8" s="14">
         <f t="shared" ref="AI8:AI16" si="7">+_xlfn.XLOOKUP($AD8,V$7:V$16,X$7:X$16)</f>
         <v>1580.191648</v>
       </c>
-      <c r="AJ8" s="17">
+      <c r="AJ8" s="14">
         <f t="shared" si="0"/>
         <v>1577.3933</v>
       </c>
@@ -3544,67 +3672,85 @@
       <c r="AM8" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="AN8" s="18">
+      <c r="AN8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO8" s="18">
+        <v>0.99300429999999995</v>
+      </c>
+      <c r="AP8" s="17">
+        <v>15764.5885</v>
+      </c>
+      <c r="AR8" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AS8" s="24">
+        <v>0.99997420000000004</v>
+      </c>
+      <c r="AT8" s="26">
+        <v>99.435940000000002</v>
+      </c>
+      <c r="AV8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AW8" s="18">
         <v>0.98572300000000002</v>
       </c>
-      <c r="AO8" s="17">
+      <c r="AX8" s="17">
         <v>22520.654823000001</v>
       </c>
-      <c r="AQ8" s="6" t="s">
+      <c r="AZ8" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="AR8" s="18">
+      <c r="BA8" s="18">
         <v>0.99224599999999996</v>
       </c>
-      <c r="AS8" s="17">
+      <c r="BB8" s="17">
         <v>16596.507481000001</v>
       </c>
-      <c r="AU8" s="6" t="s">
+      <c r="BD8" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="AV8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW8" s="18">
-        <v>0.99300429999999995</v>
-      </c>
-      <c r="AX8" s="17">
-        <v>15764.5885</v>
-      </c>
-      <c r="AZ8" s="6" t="s">
+      <c r="BE8" s="18">
+        <v>0.99224599999999996</v>
+      </c>
+      <c r="BF8" s="17">
+        <v>16596.507481000001</v>
+      </c>
+      <c r="BH8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="BI8" s="18">
+        <v>0.99224599999999996</v>
+      </c>
+      <c r="BJ8" s="17">
+        <v>16596.507481000001</v>
+      </c>
+      <c r="BL8" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="BA8" s="24">
-        <v>0.99997420000000004</v>
-      </c>
-      <c r="BB8" s="26">
+      <c r="BM8" s="17">
+        <f t="shared" ref="BM8:BM9" si="9">+_xlfn.XLOOKUP(BL8,$AV$7:$AV$9,$AX$7:$AX$9)</f>
+        <v>4703.6260300000004</v>
+      </c>
+      <c r="BN8" s="17">
+        <f t="shared" ref="BN8:BN9" si="10">+_xlfn.XLOOKUP(BL8,$AZ$7:$AZ$9,$BB$7:$BB$9)</f>
+        <v>5614.0714690000004</v>
+      </c>
+      <c r="BO8" s="17">
+        <f>+AP9</f>
+        <v>1100.5509999999999</v>
+      </c>
+      <c r="BP8" s="17">
+        <f>+AP10</f>
+        <v>756.05920000000003</v>
+      </c>
+      <c r="BQ8" s="17">
+        <f>+AT8</f>
         <v>99.435940000000002</v>
       </c>
-      <c r="BD8" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="BE8" s="17">
-        <f t="shared" ref="BE8:BE9" si="9">+_xlfn.XLOOKUP(BD8,$AM$7:$AM$9,$AO$7:$AO$9)</f>
-        <v>4703.6260300000004</v>
-      </c>
-      <c r="BF8" s="17">
-        <f t="shared" ref="BF8:BF9" si="10">+_xlfn.XLOOKUP(BD8,$AQ$7:$AQ$9,$AS$7:$AS$9)</f>
-        <v>5614.0714690000004</v>
-      </c>
-      <c r="BG8" s="17">
-        <f>+AX9</f>
-        <v>1100.5509999999999</v>
-      </c>
-      <c r="BH8" s="17">
-        <f>+AX10</f>
-        <v>756.05920000000003</v>
-      </c>
-      <c r="BI8" s="17">
-        <f t="shared" ref="BI8:BI9" si="11">+BB8</f>
-        <v>99.435940000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="2:62" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>173</v>
       </c>
@@ -3705,69 +3851,87 @@
         <v>20962.221375000001</v>
       </c>
       <c r="AM9" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AO9" s="12">
+        <v>0.99683809999999995</v>
+      </c>
+      <c r="AP9" s="14">
+        <v>1100.5509999999999</v>
+      </c>
+      <c r="AR9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AN9" s="12">
+      <c r="AS9" s="23">
+        <v>0.9999806</v>
+      </c>
+      <c r="AT9" s="25">
+        <v>88.003110000000007</v>
+      </c>
+      <c r="AV9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AW9" s="12">
         <v>0.98843700000000001</v>
       </c>
-      <c r="AO9" s="14">
+      <c r="AX9" s="14">
         <v>2148.462321</v>
-      </c>
-      <c r="AQ9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR9" s="12">
-        <v>0.97706400000000004</v>
-      </c>
-      <c r="AS9" s="14">
-        <v>3025.804118</v>
-      </c>
-      <c r="AU9" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="AV9" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AW9" s="12">
-        <v>0.99683809999999995</v>
-      </c>
-      <c r="AX9" s="14">
-        <v>1100.5509999999999</v>
       </c>
       <c r="AZ9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="BA9" s="23">
-        <v>0.9999806</v>
-      </c>
-      <c r="BB9" s="25">
-        <v>88.003110000000007</v>
+      <c r="BA9" s="12">
+        <v>0.97706400000000004</v>
+      </c>
+      <c r="BB9" s="14">
+        <v>3025.804118</v>
       </c>
       <c r="BD9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="BE9" s="14">
+      <c r="BE9" s="12">
+        <v>0.97706400000000004</v>
+      </c>
+      <c r="BF9" s="14">
+        <v>3025.804118</v>
+      </c>
+      <c r="BH9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BI9" s="12">
+        <v>0.97706400000000004</v>
+      </c>
+      <c r="BJ9" s="14">
+        <v>3025.804118</v>
+      </c>
+      <c r="BL9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BM9" s="14">
         <f t="shared" si="9"/>
         <v>2148.462321</v>
       </c>
-      <c r="BF9" s="14">
+      <c r="BN9" s="14">
         <f t="shared" si="10"/>
         <v>3025.804118</v>
       </c>
-      <c r="BG9" s="14">
-        <f>+AX11</f>
+      <c r="BO9" s="14">
+        <f>+AP11</f>
         <v>1976.5089</v>
       </c>
-      <c r="BH9" s="14">
-        <f>+AX12</f>
+      <c r="BP9" s="14">
+        <f>+AP12</f>
         <v>902.76419999999996</v>
       </c>
-      <c r="BI9" s="14">
-        <f t="shared" si="11"/>
+      <c r="BQ9" s="14">
+        <f>+AT9</f>
         <v>88.003110000000007</v>
       </c>
     </row>
-    <row r="10" spans="2:62" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>191</v>
       </c>
@@ -3839,27 +4003,27 @@
       <c r="AD10" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="AE10" s="17">
+      <c r="AE10" s="14">
         <f t="shared" si="3"/>
         <v>305803.09999999998</v>
       </c>
-      <c r="AF10" s="17">
+      <c r="AF10" s="14">
         <f t="shared" si="4"/>
         <v>224458</v>
       </c>
-      <c r="AG10" s="17">
+      <c r="AG10" s="14">
         <f t="shared" si="5"/>
         <v>23648.33</v>
       </c>
-      <c r="AH10" s="17">
+      <c r="AH10" s="14">
         <f t="shared" si="6"/>
         <v>20252.46</v>
       </c>
-      <c r="AI10" s="17">
+      <c r="AI10" s="14">
         <f t="shared" si="7"/>
         <v>433.14919800000001</v>
       </c>
-      <c r="AJ10" s="17">
+      <c r="AJ10" s="14">
         <f t="shared" si="0"/>
         <v>425.01549999999997</v>
       </c>
@@ -3868,37 +4032,55 @@
         <v>4105.2196100000001</v>
       </c>
       <c r="AM10" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AN10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO10" s="18">
+        <v>0.9985077</v>
+      </c>
+      <c r="AP10" s="17">
+        <v>756.05920000000003</v>
+      </c>
+      <c r="AV10" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AN10" s="18">
+      <c r="AW10" s="18">
         <v>0.98303399999999996</v>
       </c>
-      <c r="AO10" s="17">
+      <c r="AX10" s="17">
         <v>53755.513460000002</v>
       </c>
-      <c r="AQ10" s="6" t="s">
+      <c r="AZ10" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AR10" s="18">
+      <c r="BA10" s="18">
         <v>0.99701899999999999</v>
       </c>
-      <c r="AS10" s="17">
+      <c r="BB10" s="17">
         <v>22532.557326999999</v>
       </c>
-      <c r="AU10" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="AV10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW10" s="18">
-        <v>0.9985077</v>
-      </c>
-      <c r="AX10" s="17">
-        <v>756.05920000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="2:62" x14ac:dyDescent="0.3">
+      <c r="BD10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="BE10" s="18">
+        <v>0.99701899999999999</v>
+      </c>
+      <c r="BF10" s="17">
+        <v>22532.557326999999</v>
+      </c>
+      <c r="BH10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="BI10" s="18">
+        <v>0.99701899999999999</v>
+      </c>
+      <c r="BJ10" s="17">
+        <v>22532.557326999999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>175</v>
       </c>
@@ -3998,25 +4180,31 @@
         <f t="shared" si="8"/>
         <v>81396.828680000006</v>
       </c>
-      <c r="AN11" s="12"/>
-      <c r="AO11" s="14"/>
-      <c r="AQ11" s="14"/>
-      <c r="AR11" s="14"/>
-      <c r="AS11" s="14"/>
-      <c r="AU11" s="1" t="s">
+      <c r="AM11" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AV11" s="1" t="s">
+      <c r="AN11" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="AW11" s="12">
+      <c r="AO11" s="12">
         <v>0.99021340000000002</v>
       </c>
-      <c r="AX11" s="14">
+      <c r="AP11" s="14">
         <v>1976.5089</v>
       </c>
-    </row>
-    <row r="12" spans="2:62" x14ac:dyDescent="0.3">
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="14"/>
+      <c r="AZ11" s="14"/>
+      <c r="BA11" s="14"/>
+      <c r="BB11" s="14"/>
+      <c r="BD11" s="14"/>
+      <c r="BE11" s="14"/>
+      <c r="BF11" s="14"/>
+      <c r="BH11" s="14"/>
+      <c r="BI11" s="14"/>
+      <c r="BJ11" s="14"/>
+    </row>
+    <row r="12" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>176</v>
       </c>
@@ -4088,27 +4276,27 @@
       <c r="AD12" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="AE12" s="17">
+      <c r="AE12" s="14">
         <f t="shared" si="3"/>
         <v>2800556</v>
       </c>
-      <c r="AF12" s="17">
+      <c r="AF12" s="14">
         <f t="shared" si="4"/>
         <v>1697944</v>
       </c>
-      <c r="AG12" s="17">
+      <c r="AG12" s="14">
         <f t="shared" si="5"/>
         <v>1102529.6399999999</v>
       </c>
-      <c r="AH12" s="17">
+      <c r="AH12" s="14">
         <f t="shared" si="6"/>
         <v>963692.8</v>
       </c>
-      <c r="AI12" s="17">
+      <c r="AI12" s="14">
         <f t="shared" si="7"/>
         <v>16474.693931999998</v>
       </c>
-      <c r="AJ12" s="17">
+      <c r="AJ12" s="14">
         <f t="shared" si="0"/>
         <v>16566.6181</v>
       </c>
@@ -4116,28 +4304,34 @@
         <f t="shared" si="8"/>
         <v>118520.743653</v>
       </c>
-      <c r="AN12" s="12"/>
-      <c r="AO12" s="14"/>
-      <c r="AQ12" s="14"/>
-      <c r="AR12" s="14"/>
-      <c r="AS12" s="14"/>
-      <c r="AU12" s="6" t="s">
+      <c r="AM12" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="AV12" s="6" t="s">
+      <c r="AN12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AW12" s="18">
+      <c r="AO12" s="18">
         <v>0.99795840000000002</v>
       </c>
-      <c r="AX12" s="17">
+      <c r="AP12" s="17">
         <v>902.76419999999996</v>
       </c>
-      <c r="BD12" s="19" t="s">
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="14"/>
+      <c r="AZ12" s="14"/>
+      <c r="BA12" s="14"/>
+      <c r="BB12" s="14"/>
+      <c r="BD12" s="14"/>
+      <c r="BE12" s="14"/>
+      <c r="BF12" s="14"/>
+      <c r="BH12" s="14"/>
+      <c r="BI12" s="14"/>
+      <c r="BJ12" s="14"/>
+      <c r="BL12" s="19" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="2:62" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>177</v>
       </c>
@@ -4237,26 +4431,32 @@
         <f t="shared" si="8"/>
         <v>26091.076145999999</v>
       </c>
-      <c r="AM13" s="14"/>
-      <c r="AN13" s="14"/>
-      <c r="AO13" s="14"/>
-      <c r="AQ13" s="14"/>
-      <c r="AR13" s="14"/>
-      <c r="AS13" s="14"/>
-      <c r="AU13" s="1" t="s">
+      <c r="AM13" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="AV13" s="1" t="s">
+      <c r="AN13" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="AW13" s="12">
+      <c r="AO13" s="12">
         <v>0.99908359999999996</v>
       </c>
-      <c r="AX13" s="14">
+      <c r="AP13" s="14">
         <v>12493.0429</v>
       </c>
-    </row>
-    <row r="14" spans="2:62" x14ac:dyDescent="0.3">
+      <c r="AV13" s="14"/>
+      <c r="AW13" s="14"/>
+      <c r="AX13" s="14"/>
+      <c r="AZ13" s="14"/>
+      <c r="BA13" s="14"/>
+      <c r="BB13" s="14"/>
+      <c r="BD13" s="14"/>
+      <c r="BE13" s="14"/>
+      <c r="BF13" s="14"/>
+      <c r="BH13" s="14"/>
+      <c r="BI13" s="14"/>
+      <c r="BJ13" s="14"/>
+    </row>
+    <row r="14" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>178</v>
       </c>
@@ -4328,27 +4528,27 @@
       <c r="AD14" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="AE14" s="17">
+      <c r="AE14" s="14">
         <f t="shared" si="3"/>
         <v>353453</v>
       </c>
-      <c r="AF14" s="17">
+      <c r="AF14" s="14">
         <f t="shared" si="4"/>
         <v>125949</v>
       </c>
-      <c r="AG14" s="17">
+      <c r="AG14" s="14">
         <f t="shared" si="5"/>
         <v>355071.95</v>
       </c>
-      <c r="AH14" s="17">
+      <c r="AH14" s="14">
         <f t="shared" si="6"/>
         <v>48038.9</v>
       </c>
-      <c r="AI14" s="17">
+      <c r="AI14" s="14">
         <f t="shared" si="7"/>
         <v>1140.2147070000001</v>
       </c>
-      <c r="AJ14" s="17">
+      <c r="AJ14" s="14">
         <f t="shared" si="0"/>
         <v>1157.9239</v>
       </c>
@@ -4356,29 +4556,35 @@
         <f t="shared" si="8"/>
         <v>7011.0990389999997</v>
       </c>
-      <c r="AM14" s="14"/>
-      <c r="AN14" s="14"/>
-      <c r="AO14" s="14"/>
-      <c r="AQ14" s="14"/>
-      <c r="AR14" s="14"/>
-      <c r="AS14" s="14"/>
-      <c r="AU14" s="6" t="s">
+      <c r="AM14" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AV14" s="6" t="s">
+      <c r="AN14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AW14" s="18">
+      <c r="AO14" s="18">
         <v>0.99956429999999996</v>
       </c>
-      <c r="AX14" s="17">
+      <c r="AP14" s="17">
         <v>8614.8230000000003</v>
       </c>
-      <c r="BD14" s="13" t="s">
+      <c r="AV14" s="14"/>
+      <c r="AW14" s="14"/>
+      <c r="AX14" s="14"/>
+      <c r="AZ14" s="14"/>
+      <c r="BA14" s="14"/>
+      <c r="BB14" s="14"/>
+      <c r="BD14" s="14"/>
+      <c r="BE14" s="14"/>
+      <c r="BF14" s="14"/>
+      <c r="BH14" s="14"/>
+      <c r="BI14" s="14"/>
+      <c r="BJ14" s="14"/>
+      <c r="BL14" s="13" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="15" spans="2:62" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>179</v>
       </c>
@@ -4478,14 +4684,20 @@
         <f t="shared" si="8"/>
         <v>412581.51297400001</v>
       </c>
-      <c r="AM15" s="14"/>
-      <c r="AN15" s="14"/>
-      <c r="AO15" s="14"/>
-      <c r="AQ15" s="14"/>
-      <c r="AR15" s="14"/>
-      <c r="AS15" s="14"/>
-    </row>
-    <row r="16" spans="2:62" x14ac:dyDescent="0.3">
+      <c r="AV15" s="14"/>
+      <c r="AW15" s="14"/>
+      <c r="AX15" s="14"/>
+      <c r="AZ15" s="14"/>
+      <c r="BA15" s="14"/>
+      <c r="BB15" s="14"/>
+      <c r="BD15" s="14"/>
+      <c r="BE15" s="14"/>
+      <c r="BF15" s="14"/>
+      <c r="BH15" s="14"/>
+      <c r="BI15" s="14"/>
+      <c r="BJ15" s="14"/>
+    </row>
+    <row r="16" spans="2:70" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
         <v>180</v>
       </c>
@@ -4557,27 +4769,27 @@
       <c r="AD16" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="AE16" s="17">
+      <c r="AE16" s="14">
         <f t="shared" si="3"/>
         <v>283382.09999999998</v>
       </c>
-      <c r="AF16" s="17">
+      <c r="AF16" s="14">
         <f t="shared" si="4"/>
         <v>73683.27</v>
       </c>
-      <c r="AG16" s="17">
+      <c r="AG16" s="14">
         <f t="shared" si="5"/>
         <v>62216.71</v>
       </c>
-      <c r="AH16" s="17">
+      <c r="AH16" s="14">
         <f t="shared" si="6"/>
         <v>55278.55</v>
       </c>
-      <c r="AI16" s="17">
+      <c r="AI16" s="14">
         <f t="shared" si="7"/>
         <v>829.90016600000001</v>
       </c>
-      <c r="AJ16" s="17">
+      <c r="AJ16" s="14">
         <f t="shared" si="0"/>
         <v>55089.632700000002</v>
       </c>
@@ -4585,82 +4797,88 @@
         <f t="shared" si="8"/>
         <v>7087.1279500000001</v>
       </c>
-      <c r="AM16" s="14"/>
-      <c r="AN16" s="14"/>
-      <c r="AO16" s="14"/>
-      <c r="AQ16" s="14"/>
-      <c r="AR16" s="14"/>
-      <c r="AS16" s="14"/>
-      <c r="BD16" s="9" t="s">
+      <c r="AV16" s="14"/>
+      <c r="AW16" s="14"/>
+      <c r="AX16" s="14"/>
+      <c r="AZ16" s="14"/>
+      <c r="BA16" s="14"/>
+      <c r="BB16" s="14"/>
+      <c r="BD16" s="14"/>
+      <c r="BE16" s="14"/>
+      <c r="BF16" s="14"/>
+      <c r="BH16" s="14"/>
+      <c r="BI16" s="14"/>
+      <c r="BJ16" s="14"/>
+      <c r="BL16" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="BE16" s="9" t="s">
+      <c r="BM16" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="BF16" s="9" t="s">
+      <c r="BN16" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="BG16" s="9" t="s">
+      <c r="BO16" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="BH16" s="9" t="s">
+      <c r="BP16" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="BI16" s="9" t="s">
+      <c r="BQ16" s="9" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="17" spans="2:61" x14ac:dyDescent="0.3">
-      <c r="BD17" s="1" t="s">
+    <row r="17" spans="2:69" x14ac:dyDescent="0.3">
+      <c r="BL17" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="BE17" s="12">
-        <f>+_xlfn.XLOOKUP($BD17,$AM$7:$AM$9,$AN$7:$AN$9)</f>
+      <c r="BM17" s="12">
+        <f>+_xlfn.XLOOKUP($BL17,$AV$7:$AV$9,$AW$7:$AW$9)</f>
         <v>0.98572300000000002</v>
       </c>
-      <c r="BF17" s="12">
-        <f>+_xlfn.XLOOKUP(BD17,$AQ$7:$AQ$9,$AR$7:$AR$9)</f>
+      <c r="BN17" s="12">
+        <f>+_xlfn.XLOOKUP(BL17,$AZ$7:$AZ$9,$BA$7:$BA$9)</f>
         <v>0.99224599999999996</v>
       </c>
-      <c r="BG17" s="12">
-        <f>+AW7</f>
+      <c r="BO17" s="12">
+        <f>+AO7</f>
         <v>-0.25174930000000001</v>
       </c>
-      <c r="BH17" s="12">
-        <f>+AW8</f>
+      <c r="BP17" s="12">
+        <f>+AO8</f>
         <v>0.99300429999999995</v>
       </c>
-      <c r="BI17" s="12">
-        <f>+BA7</f>
+      <c r="BQ17" s="12">
+        <f>+AS7</f>
         <v>0.99999979999999999</v>
       </c>
     </row>
-    <row r="18" spans="2:61" x14ac:dyDescent="0.3">
-      <c r="BD18" s="6" t="s">
+    <row r="18" spans="2:69" x14ac:dyDescent="0.3">
+      <c r="BL18" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="BE18" s="18">
-        <f t="shared" ref="BE18:BE19" si="12">+_xlfn.XLOOKUP($BD18,$AM$7:$AM$9,$AN$7:$AN$9)</f>
+      <c r="BM18" s="18">
+        <f>+_xlfn.XLOOKUP($BL18,$AV$7:$AV$9,$AW$7:$AW$9)</f>
         <v>0.94224399999999997</v>
       </c>
-      <c r="BF18" s="18">
-        <f t="shared" ref="BF18:BF19" si="13">+_xlfn.XLOOKUP(BD18,$AQ$7:$AQ$9,$AR$7:$AR$9)</f>
+      <c r="BN18" s="18">
+        <f t="shared" ref="BN18:BN19" si="11">+_xlfn.XLOOKUP(BL18,$AZ$7:$AZ$9,$BA$7:$BA$9)</f>
         <v>0.91772100000000001</v>
       </c>
-      <c r="BG18" s="18">
-        <f>+AW9</f>
+      <c r="BO18" s="18">
+        <f>+AO9</f>
         <v>0.99683809999999995</v>
       </c>
-      <c r="BH18" s="18">
-        <f>+AW10</f>
+      <c r="BP18" s="18">
+        <f>+AO10</f>
         <v>0.9985077</v>
       </c>
-      <c r="BI18" s="18">
-        <f t="shared" ref="BI18:BI19" si="14">+BA8</f>
+      <c r="BQ18" s="18">
+        <f>+AS8</f>
         <v>0.99997420000000004</v>
       </c>
     </row>
-    <row r="19" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>183</v>
       </c>
@@ -4685,34 +4903,34 @@
       </c>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
-      <c r="BD19" s="1" t="s">
+      <c r="BL19" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="BE19" s="12">
-        <f t="shared" si="12"/>
+      <c r="BM19" s="12">
+        <f>+_xlfn.XLOOKUP($BL19,$AV$7:$AV$9,$AW$7:$AW$9)</f>
         <v>0.98843700000000001</v>
       </c>
-      <c r="BF19" s="12">
-        <f t="shared" si="13"/>
+      <c r="BN19" s="12">
+        <f t="shared" si="11"/>
         <v>0.97706400000000004</v>
       </c>
-      <c r="BG19" s="12">
-        <f>+AW11</f>
+      <c r="BO19" s="12">
+        <f>+AO11</f>
         <v>0.99021340000000002</v>
       </c>
-      <c r="BH19" s="12">
-        <f>+AW12</f>
+      <c r="BP19" s="12">
+        <f>+AO12</f>
         <v>0.99795840000000002</v>
       </c>
-      <c r="BI19" s="12">
-        <f t="shared" si="14"/>
+      <c r="BQ19" s="12">
+        <f>+AS9</f>
         <v>0.9999806</v>
       </c>
     </row>
-    <row r="20" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
       <c r="T20" s="21"/>
     </row>
-    <row r="21" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:69" x14ac:dyDescent="0.3">
       <c r="B21" s="9" t="s">
         <v>166</v>
       </c>
@@ -4804,7 +5022,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="22" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:69" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>171</v>
       </c>
@@ -4905,7 +5123,7 @@
         <v>424624.7</v>
       </c>
     </row>
-    <row r="23" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>172</v>
       </c>
@@ -4922,7 +5140,7 @@
         <v>191678.16</v>
       </c>
       <c r="G23" s="6" t="str">
-        <f t="shared" ref="G23:G31" si="15">+IF(F23&lt;D23,"GGM","BM")</f>
+        <f t="shared" ref="G23:G31" si="12">+IF(F23&lt;D23,"GGM","BM")</f>
         <v>GGM</v>
       </c>
       <c r="I23" s="6" t="s">
@@ -4935,7 +5153,7 @@
         <v>7970.5929999999998</v>
       </c>
       <c r="L23" s="17">
-        <f t="shared" ref="L23:L31" si="16">+K23-_xlfn.XLOOKUP(I23,B$22:B$31,F$22:F$31)</f>
+        <f t="shared" ref="L23:L31" si="13">+K23-_xlfn.XLOOKUP(I23,B$22:B$31,F$22:F$31)</f>
         <v>-183707.56700000001</v>
       </c>
       <c r="N23" s="6" t="s">
@@ -4978,41 +5196,47 @@
         <v>172</v>
       </c>
       <c r="AE23" s="14">
-        <f t="shared" ref="AE23:AE31" si="17">+_xlfn.XLOOKUP($AD23,N$22:N$31,P$22:P$31)</f>
+        <f t="shared" ref="AE23:AE31" si="14">+_xlfn.XLOOKUP($AD23,N$22:N$31,P$22:P$31)</f>
         <v>655919.19999999995</v>
       </c>
       <c r="AF23" s="14">
-        <f t="shared" ref="AF23:AF31" si="18">+_xlfn.XLOOKUP($AD23,R$22:R$31,T$22:T$31)</f>
+        <f t="shared" ref="AF23:AF31" si="15">+_xlfn.XLOOKUP($AD23,R$22:R$31,T$22:T$31)</f>
         <v>634278.5</v>
       </c>
       <c r="AG23" s="14">
-        <f t="shared" ref="AG23:AG31" si="19">+_xlfn.XLOOKUP($AD23,B$22:B$31,D$22:D$31)</f>
+        <f t="shared" ref="AG23:AG31" si="16">+_xlfn.XLOOKUP($AD23,B$22:B$31,D$22:D$31)</f>
         <v>215298.15</v>
       </c>
       <c r="AH23" s="14">
-        <f t="shared" ref="AH23:AH31" si="20">+_xlfn.XLOOKUP($AD23,B$22:B$31,F$22:F$31)</f>
+        <f t="shared" ref="AH23:AH31" si="17">+_xlfn.XLOOKUP($AD23,B$22:B$31,F$22:F$31)</f>
         <v>191678.16</v>
       </c>
       <c r="AI23" s="14">
-        <f t="shared" ref="AI23:AI31" si="21">+_xlfn.XLOOKUP($AD23,V$22:V$31,X$22:X$31)</f>
+        <f t="shared" ref="AI23:AI31" si="18">+_xlfn.XLOOKUP($AD23,V$22:V$31,X$22:X$31)</f>
         <v>8395.1301469999999</v>
       </c>
       <c r="AJ23" s="14">
-        <f t="shared" ref="AJ23:AJ31" si="22">+_xlfn.XLOOKUP($AD23,I$22:I$31,K$22:K$31)</f>
+        <f t="shared" ref="AJ23:AJ31" si="19">+_xlfn.XLOOKUP($AD23,I$22:I$31,K$22:K$31)</f>
         <v>7970.5929999999998</v>
       </c>
       <c r="AK23" s="14">
-        <f t="shared" ref="AK23:AK31" si="23">+_xlfn.XLOOKUP(AD23,$Z$22:$Z$31,$AB$22:$AB$31)</f>
+        <f t="shared" ref="AK23:AK31" si="20">+_xlfn.XLOOKUP(AD23,$Z$22:$Z$31,$AB$22:$AB$31)</f>
         <v>101494.2</v>
       </c>
-      <c r="AM23" s="27"/>
-      <c r="AN23" s="27"/>
-      <c r="AO23" s="27"/>
-      <c r="AQ23" s="27"/>
-      <c r="AR23" s="27"/>
-      <c r="AS23" s="27"/>
-    </row>
-    <row r="24" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AV23" s="27"/>
+      <c r="AW23" s="27"/>
+      <c r="AX23" s="27"/>
+      <c r="AZ23" s="27"/>
+      <c r="BA23" s="27"/>
+      <c r="BB23" s="27"/>
+      <c r="BD23" s="27"/>
+      <c r="BE23" s="27"/>
+      <c r="BF23" s="27"/>
+      <c r="BH23" s="27"/>
+      <c r="BI23" s="27"/>
+      <c r="BJ23" s="27"/>
+    </row>
+    <row r="24" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>173</v>
       </c>
@@ -5029,7 +5253,7 @@
         <v>170016.12</v>
       </c>
       <c r="G24" s="1" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>GGM</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -5042,7 +5266,7 @@
         <v>10259.941000000001</v>
       </c>
       <c r="L24" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>-159756.179</v>
       </c>
       <c r="N24" s="1" t="s">
@@ -5085,41 +5309,47 @@
         <v>173</v>
       </c>
       <c r="AE24" s="14">
+        <f t="shared" si="14"/>
+        <v>711743.3</v>
+      </c>
+      <c r="AF24" s="14">
+        <f t="shared" si="15"/>
+        <v>1813809</v>
+      </c>
+      <c r="AG24" s="14">
+        <f t="shared" si="16"/>
+        <v>176803.48</v>
+      </c>
+      <c r="AH24" s="14">
         <f t="shared" si="17"/>
-        <v>711743.3</v>
-      </c>
-      <c r="AF24" s="14">
+        <v>170016.12</v>
+      </c>
+      <c r="AI24" s="14">
         <f t="shared" si="18"/>
-        <v>1813809</v>
-      </c>
-      <c r="AG24" s="14">
+        <v>11331.678796</v>
+      </c>
+      <c r="AJ24" s="14">
         <f t="shared" si="19"/>
-        <v>176803.48</v>
-      </c>
-      <c r="AH24" s="14">
+        <v>10259.941000000001</v>
+      </c>
+      <c r="AK24" s="14">
         <f t="shared" si="20"/>
-        <v>170016.12</v>
-      </c>
-      <c r="AI24" s="14">
-        <f t="shared" si="21"/>
-        <v>11331.678796</v>
-      </c>
-      <c r="AJ24" s="14">
-        <f t="shared" si="22"/>
-        <v>10259.941000000001</v>
-      </c>
-      <c r="AK24" s="14">
-        <f t="shared" si="23"/>
         <v>27934.33</v>
       </c>
-      <c r="AM24" s="27"/>
-      <c r="AN24" s="28"/>
-      <c r="AO24" s="28"/>
-      <c r="AQ24" s="28"/>
-      <c r="AR24" s="28"/>
-      <c r="AS24" s="28"/>
-    </row>
-    <row r="25" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AV24" s="27"/>
+      <c r="AW24" s="28"/>
+      <c r="AX24" s="28"/>
+      <c r="AZ24" s="28"/>
+      <c r="BA24" s="28"/>
+      <c r="BB24" s="28"/>
+      <c r="BD24" s="28"/>
+      <c r="BE24" s="28"/>
+      <c r="BF24" s="28"/>
+      <c r="BH24" s="28"/>
+      <c r="BI24" s="28"/>
+      <c r="BJ24" s="28"/>
+    </row>
+    <row r="25" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>191</v>
       </c>
@@ -5136,7 +5366,7 @@
         <v>20254.93</v>
       </c>
       <c r="G25" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>GGM</v>
       </c>
       <c r="I25" s="6" t="s">
@@ -5149,7 +5379,7 @@
         <v>2682.71</v>
       </c>
       <c r="L25" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>-17572.22</v>
       </c>
       <c r="N25" s="6" t="s">
@@ -5192,41 +5422,47 @@
         <v>191</v>
       </c>
       <c r="AE25" s="14">
+        <f t="shared" si="14"/>
+        <v>96842.15</v>
+      </c>
+      <c r="AF25" s="14">
+        <f t="shared" si="15"/>
+        <v>300031.3</v>
+      </c>
+      <c r="AG25" s="14">
+        <f t="shared" si="16"/>
+        <v>23695.26</v>
+      </c>
+      <c r="AH25" s="14">
         <f t="shared" si="17"/>
-        <v>96842.15</v>
-      </c>
-      <c r="AF25" s="14">
+        <v>20254.93</v>
+      </c>
+      <c r="AI25" s="14">
         <f t="shared" si="18"/>
-        <v>300031.3</v>
-      </c>
-      <c r="AG25" s="14">
+        <v>2856.3407999999999</v>
+      </c>
+      <c r="AJ25" s="14">
         <f t="shared" si="19"/>
-        <v>23695.26</v>
-      </c>
-      <c r="AH25" s="14">
+        <v>2682.71</v>
+      </c>
+      <c r="AK25" s="14">
         <f t="shared" si="20"/>
-        <v>20254.93</v>
-      </c>
-      <c r="AI25" s="14">
-        <f t="shared" si="21"/>
-        <v>2856.3407999999999</v>
-      </c>
-      <c r="AJ25" s="14">
-        <f t="shared" si="22"/>
-        <v>2682.71</v>
-      </c>
-      <c r="AK25" s="14">
-        <f t="shared" si="23"/>
         <v>11391.69</v>
       </c>
-      <c r="AM25" s="27"/>
-      <c r="AN25" s="28"/>
-      <c r="AO25" s="28"/>
-      <c r="AQ25" s="28"/>
-      <c r="AR25" s="28"/>
-      <c r="AS25" s="28"/>
-    </row>
-    <row r="26" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AV25" s="27"/>
+      <c r="AW25" s="28"/>
+      <c r="AX25" s="28"/>
+      <c r="AZ25" s="28"/>
+      <c r="BA25" s="28"/>
+      <c r="BB25" s="28"/>
+      <c r="BD25" s="28"/>
+      <c r="BE25" s="28"/>
+      <c r="BF25" s="28"/>
+      <c r="BH25" s="28"/>
+      <c r="BI25" s="28"/>
+      <c r="BJ25" s="28"/>
+    </row>
+    <row r="26" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>175</v>
       </c>
@@ -5243,7 +5479,7 @@
         <v>1270365.45</v>
       </c>
       <c r="G26" s="1" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>GGM</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -5256,7 +5492,7 @@
         <v>54571.813999999998</v>
       </c>
       <c r="L26" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>-1215793.6359999999</v>
       </c>
       <c r="N26" s="1" t="s">
@@ -5299,41 +5535,47 @@
         <v>175</v>
       </c>
       <c r="AE26" s="14">
+        <f t="shared" si="14"/>
+        <v>1726783</v>
+      </c>
+      <c r="AF26" s="14">
+        <f t="shared" si="15"/>
+        <v>1646926</v>
+      </c>
+      <c r="AG26" s="14">
+        <f t="shared" si="16"/>
+        <v>1370516.61</v>
+      </c>
+      <c r="AH26" s="14">
         <f t="shared" si="17"/>
-        <v>1726783</v>
-      </c>
-      <c r="AF26" s="14">
+        <v>1270365.45</v>
+      </c>
+      <c r="AI26" s="14">
         <f t="shared" si="18"/>
-        <v>1646926</v>
-      </c>
-      <c r="AG26" s="14">
+        <v>59096.011952000001</v>
+      </c>
+      <c r="AJ26" s="14">
         <f t="shared" si="19"/>
-        <v>1370516.61</v>
-      </c>
-      <c r="AH26" s="14">
+        <v>54571.813999999998</v>
+      </c>
+      <c r="AK26" s="14">
         <f t="shared" si="20"/>
-        <v>1270365.45</v>
-      </c>
-      <c r="AI26" s="14">
-        <f t="shared" si="21"/>
-        <v>59096.011952000001</v>
-      </c>
-      <c r="AJ26" s="14">
-        <f t="shared" si="22"/>
-        <v>54571.813999999998</v>
-      </c>
-      <c r="AK26" s="14">
-        <f t="shared" si="23"/>
         <v>162463.20000000001</v>
       </c>
-      <c r="AM26" s="27"/>
-      <c r="AN26" s="28"/>
-      <c r="AO26" s="28"/>
-      <c r="AQ26" s="28"/>
-      <c r="AR26" s="28"/>
-      <c r="AS26" s="28"/>
-    </row>
-    <row r="27" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="AV26" s="27"/>
+      <c r="AW26" s="28"/>
+      <c r="AX26" s="28"/>
+      <c r="AZ26" s="28"/>
+      <c r="BA26" s="28"/>
+      <c r="BB26" s="28"/>
+      <c r="BD26" s="28"/>
+      <c r="BE26" s="28"/>
+      <c r="BF26" s="28"/>
+      <c r="BH26" s="28"/>
+      <c r="BI26" s="28"/>
+      <c r="BJ26" s="28"/>
+    </row>
+    <row r="27" spans="2:69" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
         <v>176</v>
       </c>
@@ -5350,7 +5592,7 @@
         <v>962242.14</v>
       </c>
       <c r="G27" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>GGM</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -5363,7 +5605,7 @@
         <v>37554.368000000002</v>
       </c>
       <c r="L27" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>-924687.772</v>
       </c>
       <c r="N27" s="6" t="s">
@@ -5406,35 +5648,35 @@
         <v>176</v>
       </c>
       <c r="AE27" s="14">
+        <f t="shared" si="14"/>
+        <v>2120841</v>
+      </c>
+      <c r="AF27" s="14">
+        <f t="shared" si="15"/>
+        <v>2056768</v>
+      </c>
+      <c r="AG27" s="14">
+        <f t="shared" si="16"/>
+        <v>1102885.5</v>
+      </c>
+      <c r="AH27" s="14">
         <f t="shared" si="17"/>
-        <v>2120841</v>
-      </c>
-      <c r="AF27" s="14">
+        <v>962242.14</v>
+      </c>
+      <c r="AI27" s="14">
         <f t="shared" si="18"/>
-        <v>2056768</v>
-      </c>
-      <c r="AG27" s="14">
+        <v>40276.492481000001</v>
+      </c>
+      <c r="AJ27" s="14">
         <f t="shared" si="19"/>
-        <v>1102885.5</v>
-      </c>
-      <c r="AH27" s="14">
+        <v>37554.368000000002</v>
+      </c>
+      <c r="AK27" s="14">
         <f t="shared" si="20"/>
-        <v>962242.14</v>
-      </c>
-      <c r="AI27" s="14">
-        <f t="shared" si="21"/>
-        <v>40276.492481000001</v>
-      </c>
-      <c r="AJ27" s="14">
-        <f t="shared" si="22"/>
-        <v>37554.368000000002</v>
-      </c>
-      <c r="AK27" s="14">
-        <f t="shared" si="23"/>
         <v>453190.5</v>
       </c>
     </row>
-    <row r="28" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:69" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>177</v>
       </c>
@@ -5451,7 +5693,7 @@
         <v>177553.42</v>
       </c>
       <c r="G28" s="1" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>GGM</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -5464,7 +5706,7 @@
         <v>18001.951000000001</v>
       </c>
       <c r="L28" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>-159551.46900000001</v>
       </c>
       <c r="N28" s="1" t="s">
@@ -5507,35 +5749,35 @@
         <v>177</v>
       </c>
       <c r="AE28" s="14">
+        <f t="shared" si="14"/>
+        <v>999266.5</v>
+      </c>
+      <c r="AF28" s="14">
+        <f t="shared" si="15"/>
+        <v>2976087</v>
+      </c>
+      <c r="AG28" s="14">
+        <f t="shared" si="16"/>
+        <v>212970.27</v>
+      </c>
+      <c r="AH28" s="14">
         <f t="shared" si="17"/>
-        <v>999266.5</v>
-      </c>
-      <c r="AF28" s="14">
+        <v>177553.42</v>
+      </c>
+      <c r="AI28" s="14">
         <f t="shared" si="18"/>
-        <v>2976087</v>
-      </c>
-      <c r="AG28" s="14">
+        <v>20204.683582000001</v>
+      </c>
+      <c r="AJ28" s="14">
         <f t="shared" si="19"/>
-        <v>212970.27</v>
-      </c>
-      <c r="AH28" s="14">
+        <v>18001.951000000001</v>
+      </c>
+      <c r="AK28" s="14">
         <f t="shared" si="20"/>
-        <v>177553.42</v>
-      </c>
-      <c r="AI28" s="14">
-        <f t="shared" si="21"/>
-        <v>20204.683582000001</v>
-      </c>
-      <c r="AJ28" s="14">
-        <f t="shared" si="22"/>
-        <v>18001.951000000001</v>
-      </c>
-      <c r="AK28" s="14">
-        <f t="shared" si="23"/>
         <v>97029.98</v>
       </c>
     </row>
-    <row r="29" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:69" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
         <v>178</v>
       </c>
@@ -5552,7 +5794,7 @@
         <v>41689.589999999997</v>
       </c>
       <c r="G29" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>GGM</v>
       </c>
       <c r="I29" s="6" t="s">
@@ -5565,7 +5807,7 @@
         <v>2688.72</v>
       </c>
       <c r="L29" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>-39000.869999999995</v>
       </c>
       <c r="N29" s="6" t="s">
@@ -5608,35 +5850,35 @@
         <v>178</v>
       </c>
       <c r="AE29" s="14">
+        <f t="shared" si="14"/>
+        <v>140633.70000000001</v>
+      </c>
+      <c r="AF29" s="14">
+        <f t="shared" si="15"/>
+        <v>128388.6</v>
+      </c>
+      <c r="AG29" s="14">
+        <f t="shared" si="16"/>
+        <v>47981.11</v>
+      </c>
+      <c r="AH29" s="14">
         <f t="shared" si="17"/>
-        <v>140633.70000000001</v>
-      </c>
-      <c r="AF29" s="14">
+        <v>41689.589999999997</v>
+      </c>
+      <c r="AI29" s="14">
         <f t="shared" si="18"/>
-        <v>128388.6</v>
-      </c>
-      <c r="AG29" s="14">
+        <v>2835.1556179999998</v>
+      </c>
+      <c r="AJ29" s="14">
         <f t="shared" si="19"/>
-        <v>47981.11</v>
-      </c>
-      <c r="AH29" s="14">
+        <v>2688.72</v>
+      </c>
+      <c r="AK29" s="14">
         <f t="shared" si="20"/>
-        <v>41689.589999999997</v>
-      </c>
-      <c r="AI29" s="14">
-        <f t="shared" si="21"/>
-        <v>2835.1556179999998</v>
-      </c>
-      <c r="AJ29" s="14">
-        <f t="shared" si="22"/>
-        <v>2688.72</v>
-      </c>
-      <c r="AK29" s="14">
-        <f t="shared" si="23"/>
         <v>16657.2</v>
       </c>
     </row>
-    <row r="30" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:69" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>179</v>
       </c>
@@ -5653,7 +5895,7 @@
         <v>55105.7</v>
       </c>
       <c r="G30" s="1" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>GGM</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -5666,7 +5908,7 @@
         <v>3653520.236</v>
       </c>
       <c r="L30" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>-4.0000001899898052E-3</v>
       </c>
       <c r="N30" s="1" t="s">
@@ -5709,35 +5951,35 @@
         <v>180</v>
       </c>
       <c r="AE30" s="14">
+        <f t="shared" si="14"/>
+        <v>14749160</v>
+      </c>
+      <c r="AF30" s="14">
+        <f t="shared" si="15"/>
+        <v>14407510</v>
+      </c>
+      <c r="AG30" s="14">
+        <f t="shared" si="16"/>
+        <v>4160546.94</v>
+      </c>
+      <c r="AH30" s="14">
         <f t="shared" si="17"/>
-        <v>14749160</v>
-      </c>
-      <c r="AF30" s="14">
+        <v>3653520.24</v>
+      </c>
+      <c r="AI30" s="14">
         <f t="shared" si="18"/>
-        <v>14407510</v>
-      </c>
-      <c r="AG30" s="14">
+        <v>189197.220477</v>
+      </c>
+      <c r="AJ30" s="14">
         <f t="shared" si="19"/>
-        <v>4160546.94</v>
-      </c>
-      <c r="AH30" s="14">
+        <v>3653520.236</v>
+      </c>
+      <c r="AK30" s="14">
         <f t="shared" si="20"/>
-        <v>3653520.24</v>
-      </c>
-      <c r="AI30" s="14">
-        <f t="shared" si="21"/>
-        <v>189197.220477</v>
-      </c>
-      <c r="AJ30" s="14">
-        <f t="shared" si="22"/>
-        <v>3653520.236</v>
-      </c>
-      <c r="AK30" s="14">
-        <f t="shared" si="23"/>
         <v>1626782</v>
       </c>
     </row>
-    <row r="31" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:69" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>180</v>
       </c>
@@ -5754,7 +5996,7 @@
         <v>3653520.24</v>
       </c>
       <c r="G31" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>GGM</v>
       </c>
       <c r="I31" s="6" t="s">
@@ -5767,7 +6009,7 @@
         <v>2309.4769999999999</v>
       </c>
       <c r="L31" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>-52796.222999999998</v>
       </c>
       <c r="N31" s="6" t="s">
@@ -5810,35 +6052,35 @@
         <v>179</v>
       </c>
       <c r="AE31" s="14">
+        <f t="shared" si="14"/>
+        <v>97667.94</v>
+      </c>
+      <c r="AF31" s="14">
+        <f t="shared" si="15"/>
+        <v>89659.199999999997</v>
+      </c>
+      <c r="AG31" s="14">
+        <f t="shared" si="16"/>
+        <v>62031.38</v>
+      </c>
+      <c r="AH31" s="14">
         <f t="shared" si="17"/>
-        <v>97667.94</v>
-      </c>
-      <c r="AF31" s="14">
+        <v>55105.7</v>
+      </c>
+      <c r="AI31" s="14">
         <f t="shared" si="18"/>
-        <v>89659.199999999997</v>
-      </c>
-      <c r="AG31" s="14">
+        <v>2423.543439</v>
+      </c>
+      <c r="AJ31" s="14">
         <f t="shared" si="19"/>
-        <v>62031.38</v>
-      </c>
-      <c r="AH31" s="14">
+        <v>2309.4769999999999</v>
+      </c>
+      <c r="AK31" s="14">
         <f t="shared" si="20"/>
-        <v>55105.7</v>
-      </c>
-      <c r="AI31" s="14">
-        <f t="shared" si="21"/>
-        <v>2423.543439</v>
-      </c>
-      <c r="AJ31" s="14">
-        <f t="shared" si="22"/>
-        <v>2309.4769999999999</v>
-      </c>
-      <c r="AK31" s="14">
-        <f t="shared" si="23"/>
         <v>43128.99</v>
       </c>
     </row>
-    <row r="32" spans="2:61" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AD32" s="22"/>
       <c r="AE32" s="22"/>
       <c r="AF32" s="22"/>
@@ -5955,7 +6197,7 @@
         <v>211942.1</v>
       </c>
       <c r="G38" s="6" t="str">
-        <f t="shared" ref="G38:G46" si="24">+IF(F38&lt;D38,"GGM","BM")</f>
+        <f t="shared" ref="G38:G46" si="21">+IF(F38&lt;D38,"GGM","BM")</f>
         <v>GGM</v>
       </c>
       <c r="I38" s="6" t="s">
@@ -5968,7 +6210,7 @@
         <v>100789.75999999999</v>
       </c>
       <c r="L38" s="17">
-        <f t="shared" ref="L38:L46" si="25">+K38-_xlfn.XLOOKUP(I38,B$37:B$46,F$37:F$46)</f>
+        <f t="shared" ref="L38:L46" si="22">+K38-_xlfn.XLOOKUP(I38,B$37:B$46,F$37:F$46)</f>
         <v>-111152.34000000001</v>
       </c>
       <c r="V38" s="6" t="s">
@@ -5998,7 +6240,7 @@
         <v>174775.12</v>
       </c>
       <c r="G39" s="1" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>GGM</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -6011,7 +6253,7 @@
         <v>120410.38</v>
       </c>
       <c r="L39" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-54364.739999999991</v>
       </c>
       <c r="V39" s="1" t="s">
@@ -6041,7 +6283,7 @@
         <v>23030.65</v>
       </c>
       <c r="G40" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>GGM</v>
       </c>
       <c r="I40" s="6" t="s">
@@ -6054,7 +6296,7 @@
         <v>18214.75</v>
       </c>
       <c r="L40" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-4815.9000000000015</v>
       </c>
       <c r="V40" s="6" t="s">
@@ -6084,7 +6326,7 @@
         <v>1236195.68</v>
       </c>
       <c r="G41" s="1" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>GGM</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -6097,7 +6339,7 @@
         <v>510440.15</v>
       </c>
       <c r="L41" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-725755.52999999991</v>
       </c>
       <c r="V41" s="1" t="s">
@@ -6127,7 +6369,7 @@
         <v>1098061.48</v>
       </c>
       <c r="G42" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>GGM</v>
       </c>
       <c r="I42" s="6" t="s">
@@ -6140,7 +6382,7 @@
         <v>631028.31999999995</v>
       </c>
       <c r="L42" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-467033.16000000003</v>
       </c>
       <c r="V42" s="6" t="s">
@@ -6170,7 +6412,7 @@
         <v>198641.06</v>
       </c>
       <c r="G43" s="1" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>GGM</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -6183,7 +6425,7 @@
         <v>126978.78</v>
       </c>
       <c r="L43" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-71662.28</v>
       </c>
       <c r="V43" s="1" t="s">
@@ -6213,7 +6455,7 @@
         <v>46165.85</v>
       </c>
       <c r="G44" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>GGM</v>
       </c>
       <c r="I44" s="6" t="s">
@@ -6226,7 +6468,7 @@
         <v>29197.63</v>
       </c>
       <c r="L44" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-16968.219999999998</v>
       </c>
       <c r="V44" s="6" t="s">
@@ -6256,7 +6498,7 @@
         <v>53945.74</v>
       </c>
       <c r="G45" s="1" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>GGM</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -6269,7 +6511,7 @@
         <v>4077694.45</v>
       </c>
       <c r="L45" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="V45" s="1" t="s">
@@ -6299,7 +6541,7 @@
         <v>4077694.45</v>
       </c>
       <c r="G46" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>GGM</v>
       </c>
       <c r="I46" s="6" t="s">
@@ -6312,7 +6554,7 @@
         <v>30806.880000000001</v>
       </c>
       <c r="L46" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>-23138.859999999997</v>
       </c>
       <c r="V46" s="6" t="s">
@@ -6326,7 +6568,391 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AE7:AK16">
+  <conditionalFormatting sqref="AV13:AX16 AZ13:BB16 BD13:BF16 BH13:BJ16">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AE16">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF7:AF16">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG7:AG16">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH7:AH16">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI7:AI16">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AJ16">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK7:AK16">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AK7">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE8:AK8">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE9:AK9">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE10:AK10">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE11:AK11">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE12:AK12">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE13:AK13">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE14:AK14">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE15:AK15">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE16:AK16">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE22:AE31">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF22:AF31">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG22:AG31">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH22:AH31">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI22:AI31">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ22:AJ31">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK22:AK31">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE22:AK22">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE23:AK23">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE24:AK24">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE25:AK25">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE26:AK26">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE27:AK27">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE28:AK28">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE29:AK29">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6338,8 +6964,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM13:AO16 AQ13:AS16 AE7:AK16">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="AE30:AK30">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6350,20 +6976,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE22:AK31">
+  <conditionalFormatting sqref="AE31:AK31">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE22:AK31">
-    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6379,6 +6993,2495 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93B5247-589C-44F9-8D52-5DE81A7C1480}">
+  <dimension ref="B1:CE26"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="12.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="2" style="20" customWidth="1"/>
+    <col min="9" max="11" width="8.88671875" style="1"/>
+    <col min="12" max="12" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2" style="20" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="1"/>
+    <col min="15" max="15" width="11.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="2" style="20" customWidth="1"/>
+    <col min="18" max="18" width="8.88671875" style="1"/>
+    <col min="19" max="19" width="9" style="1" customWidth="1"/>
+    <col min="20" max="20" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="2" style="20" customWidth="1"/>
+    <col min="22" max="22" width="8.88671875" style="1"/>
+    <col min="23" max="23" width="11.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="20" customWidth="1"/>
+    <col min="26" max="28" width="10.109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="2" style="20" customWidth="1"/>
+    <col min="30" max="32" width="10.109375" style="1" customWidth="1"/>
+    <col min="33" max="33" width="2" style="20" customWidth="1"/>
+    <col min="34" max="34" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="38" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="9.109375" style="1" customWidth="1"/>
+    <col min="40" max="40" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="12.109375" style="1" customWidth="1"/>
+    <col min="43" max="43" width="2" style="36" customWidth="1"/>
+    <col min="44" max="44" width="2" style="35" customWidth="1"/>
+    <col min="45" max="45" width="2" style="36" customWidth="1"/>
+    <col min="46" max="46" width="15.109375" style="1" customWidth="1"/>
+    <col min="47" max="49" width="8.88671875" style="1"/>
+    <col min="50" max="50" width="2" style="20" customWidth="1"/>
+    <col min="51" max="53" width="8.88671875" style="1"/>
+    <col min="54" max="54" width="2" style="20" customWidth="1"/>
+    <col min="55" max="57" width="12.109375" style="1" customWidth="1"/>
+    <col min="58" max="58" width="2" style="20" customWidth="1"/>
+    <col min="59" max="61" width="12.109375" style="1" customWidth="1"/>
+    <col min="62" max="62" width="2" style="20" customWidth="1"/>
+    <col min="63" max="65" width="12.109375" style="1" customWidth="1"/>
+    <col min="66" max="66" width="2" style="20" customWidth="1"/>
+    <col min="67" max="69" width="12.109375" style="1" customWidth="1"/>
+    <col min="70" max="70" width="2" style="20" customWidth="1"/>
+    <col min="71" max="73" width="12.109375" style="1" customWidth="1"/>
+    <col min="74" max="74" width="2" style="20" customWidth="1"/>
+    <col min="75" max="75" width="11.88671875" style="1" customWidth="1"/>
+    <col min="76" max="77" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="78" max="79" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="84" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:83" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="AC1" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="AG1" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="AT1" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="AX1" s="20" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="2" spans="2:83" x14ac:dyDescent="0.3">
+      <c r="B2" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="R2" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="S2" s="19"/>
+      <c r="V2" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="W2" s="19"/>
+      <c r="Z2" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="AD2" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH2" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="19"/>
+      <c r="AT2" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="AY2" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="BC2" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="BG2" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="BK2" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="BO2" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="BS2" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="BW2" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="2:83" x14ac:dyDescent="0.3">
+      <c r="B3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="Z3" s="37"/>
+      <c r="AD3" s="37"/>
+      <c r="AT3" s="37"/>
+      <c r="AY3" s="37"/>
+      <c r="BC3" s="37"/>
+      <c r="BG3" s="37"/>
+      <c r="BK3" s="37"/>
+      <c r="BO3" s="37"/>
+      <c r="BS3" s="37"/>
+    </row>
+    <row r="4" spans="2:83" ht="16.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="T4" s="21"/>
+      <c r="V4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="AH4" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="AI4" s="13"/>
+      <c r="AJ4" s="13"/>
+      <c r="AT4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="AY4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="BC4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="BG4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="BK4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="BO4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="BS4" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="BW4" s="13" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5" spans="2:83" ht="16.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="T5" s="21"/>
+    </row>
+    <row r="6" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="V6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="W6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="AF6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="AH6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI6" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ6" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK6" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM6" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="AN6" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="AO6" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="AP6" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="AT6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="AU6" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="AW6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="AY6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="AZ6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BA6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="BC6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="BD6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BE6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="BG6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="BH6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BI6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="BK6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="BL6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BM6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="BO6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="BP6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BQ6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="BS6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="BT6" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="BU6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="BW6" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="BX6" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="BY6" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="BZ6" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="CA6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="CB6" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="CC6" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="CD6" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="CE6" s="9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="15">
+        <v>-0.88045949999999995</v>
+      </c>
+      <c r="D7" s="14">
+        <v>1457551.04</v>
+      </c>
+      <c r="E7" s="15">
+        <v>-18.720834199999999</v>
+      </c>
+      <c r="F7" s="14">
+        <v>4720135</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f>+IF(F7&lt;D7,"GGM","BM")</f>
+        <v>BM</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" s="33">
+        <v>-18.442921699999999</v>
+      </c>
+      <c r="K7" s="14">
+        <v>4686758.0999999996</v>
+      </c>
+      <c r="L7" s="14">
+        <f>+K7-F7</f>
+        <v>-33376.900000000373</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O7" s="33">
+        <v>-1167.2323490000001</v>
+      </c>
+      <c r="P7" s="14">
+        <v>35518040</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="S7" s="33">
+        <v>-1167.7180880000001</v>
+      </c>
+      <c r="T7" s="14">
+        <v>35525420</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="W7" s="33">
+        <v>-6.5581474999999996</v>
+      </c>
+      <c r="X7" s="14">
+        <v>2922129.51</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA7" s="33">
+        <v>-5.1333900000000003</v>
+      </c>
+      <c r="AB7" s="14">
+        <v>2632341</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE7" s="33">
+        <v>0.15242800000000001</v>
+      </c>
+      <c r="AF7" s="14">
+        <v>978543.1</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI7" s="14">
+        <f t="shared" ref="AI7:AI16" si="0">+_xlfn.XLOOKUP($AH7,N$7:N$16,P$7:P$16)</f>
+        <v>35518040</v>
+      </c>
+      <c r="AJ7" s="14">
+        <f t="shared" ref="AJ7:AJ16" si="1">+_xlfn.XLOOKUP($AH7,R$7:R$16,T$7:T$16)</f>
+        <v>35525420</v>
+      </c>
+      <c r="AK7" s="14">
+        <f t="shared" ref="AK7:AK16" si="2">+_xlfn.XLOOKUP($AH7,B$7:B$16,D$7:D$16)</f>
+        <v>1457551.04</v>
+      </c>
+      <c r="AL7" s="14">
+        <f t="shared" ref="AL7:AL16" si="3">+_xlfn.XLOOKUP($AH7,B$7:B$16,F$7:F$16)</f>
+        <v>4720135</v>
+      </c>
+      <c r="AM7" s="14">
+        <f t="shared" ref="AM7:AM16" si="4">+_xlfn.XLOOKUP($AH7,V$7:V$16,X$7:X$16)</f>
+        <v>2922129.51</v>
+      </c>
+      <c r="AN7" s="14">
+        <f t="shared" ref="AN7:AN16" si="5">+_xlfn.XLOOKUP($AH7,I$7:I$16,K$7:K$16)</f>
+        <v>4686758.0999999996</v>
+      </c>
+      <c r="AO7" s="14">
+        <f t="shared" ref="AO7:AO16" si="6">+_xlfn.XLOOKUP(AH7,$Z$7:$Z$16,$AB$7:$AB$16)</f>
+        <v>2632341</v>
+      </c>
+      <c r="AP7" s="14">
+        <f>+_xlfn.XLOOKUP(AH7,$AD$7:$AD$16,$AF$7:$AF$16)</f>
+        <v>978543.1</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="AU7" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AV7" s="12">
+        <v>-5.7474112999999996</v>
+      </c>
+      <c r="AW7" s="14">
+        <v>269246.39079999999</v>
+      </c>
+      <c r="AY7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="AZ7" s="15">
+        <v>-2.6609845999999999</v>
+      </c>
+      <c r="BA7" s="25">
+        <v>62.22701</v>
+      </c>
+      <c r="BC7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="BD7" s="33">
+        <v>-1556969</v>
+      </c>
+      <c r="BE7" s="14">
+        <v>40580.75</v>
+      </c>
+      <c r="BG7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="BH7" s="33">
+        <v>-1466067</v>
+      </c>
+      <c r="BI7" s="14">
+        <v>39378.31</v>
+      </c>
+      <c r="BK7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="BL7" s="33">
+        <v>0.45879575</v>
+      </c>
+      <c r="BM7" s="14">
+        <v>23.92548</v>
+      </c>
+      <c r="BO7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="BP7" s="33">
+        <v>-71.902986999999996</v>
+      </c>
+      <c r="BQ7" s="14">
+        <v>1366.269454</v>
+      </c>
+      <c r="BS7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="BT7" s="33">
+        <v>0.95831999999999995</v>
+      </c>
+      <c r="BU7" s="14">
+        <v>6.6396439999999997</v>
+      </c>
+      <c r="BW7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="BX7" s="14">
+        <f>+_xlfn.XLOOKUP($BW7,$BC$7:$BC$10,$BE$7:$BE$10)</f>
+        <v>517077.6</v>
+      </c>
+      <c r="BY7" s="14">
+        <f>+_xlfn.XLOOKUP(BW7,$BG$7:$BG$10,$BI$7:$BI$10)</f>
+        <v>510340.6</v>
+      </c>
+      <c r="BZ7" s="14">
+        <f>+AW7</f>
+        <v>269246.39079999999</v>
+      </c>
+      <c r="CA7" s="14">
+        <f>+AW8</f>
+        <v>367562.62449999998</v>
+      </c>
+      <c r="CB7" s="14">
+        <f>+_xlfn.XLOOKUP($BW7,$BK$7:$BK$10,$BM$7:$BM$10)</f>
+        <v>55606.478790000001</v>
+      </c>
+      <c r="CC7" s="14">
+        <f>+BA7</f>
+        <v>62.22701</v>
+      </c>
+      <c r="CD7" s="14">
+        <f>+_xlfn.XLOOKUP($BW7,$BO$7:$BO$10,$BQ$7:$BQ$10)</f>
+        <v>55867.376609999999</v>
+      </c>
+      <c r="CE7" s="14">
+        <f>+_xlfn.XLOOKUP($BW7,$BS$7:$BS$10,$BU$7:$BU$10)</f>
+        <v>34732.780121999996</v>
+      </c>
+    </row>
+    <row r="8" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="16">
+        <v>-28.473542599999998</v>
+      </c>
+      <c r="D8" s="17">
+        <v>1507384.69</v>
+      </c>
+      <c r="E8" s="16">
+        <v>-44.418825099999999</v>
+      </c>
+      <c r="F8" s="17">
+        <v>1871224.42</v>
+      </c>
+      <c r="G8" s="6" t="str">
+        <f t="shared" ref="G8:G16" si="7">+IF(F8&lt;D8,"GGM","BM")</f>
+        <v>BM</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="J8" s="34">
+        <v>-39.417364499999998</v>
+      </c>
+      <c r="K8" s="17">
+        <v>1765191.9</v>
+      </c>
+      <c r="L8" s="17">
+        <f t="shared" ref="L8:L16" si="8">+K8-F8</f>
+        <v>-106032.52000000002</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="O8" s="34">
+        <v>-342.44675999999998</v>
+      </c>
+      <c r="P8" s="17">
+        <v>4850543</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="S8" s="34">
+        <v>-342.43093699999997</v>
+      </c>
+      <c r="T8" s="17">
+        <v>4850431</v>
+      </c>
+      <c r="V8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="W8" s="34">
+        <v>-0.14459959999999999</v>
+      </c>
+      <c r="X8" s="17">
+        <v>297053.53000000003</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA8" s="34">
+        <v>-3.654674</v>
+      </c>
+      <c r="AB8" s="17">
+        <v>599035.5</v>
+      </c>
+      <c r="AD8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE8" s="34">
+        <v>0.90742500000000004</v>
+      </c>
+      <c r="AF8" s="17">
+        <v>84480.34</v>
+      </c>
+      <c r="AH8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI8" s="14">
+        <f t="shared" si="0"/>
+        <v>4850543</v>
+      </c>
+      <c r="AJ8" s="14">
+        <f t="shared" si="1"/>
+        <v>4850431</v>
+      </c>
+      <c r="AK8" s="14">
+        <f t="shared" si="2"/>
+        <v>1507384.69</v>
+      </c>
+      <c r="AL8" s="14">
+        <f t="shared" si="3"/>
+        <v>1871224.42</v>
+      </c>
+      <c r="AM8" s="14">
+        <f t="shared" si="4"/>
+        <v>297053.53000000003</v>
+      </c>
+      <c r="AN8" s="14">
+        <f t="shared" si="5"/>
+        <v>1765191.9</v>
+      </c>
+      <c r="AO8" s="14">
+        <f t="shared" si="6"/>
+        <v>599035.5</v>
+      </c>
+      <c r="AP8" s="14">
+        <f t="shared" ref="AP8:AP16" si="9">+_xlfn.XLOOKUP(AH8,$AD$7:$AD$16,$AF$7:$AF$16)</f>
+        <v>84480.34</v>
+      </c>
+      <c r="AT8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AU8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV8" s="18">
+        <v>-11.574771200000001</v>
+      </c>
+      <c r="AW8" s="17">
+        <v>367562.62449999998</v>
+      </c>
+      <c r="AY8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AZ8" s="16">
+        <v>0.59136739999999999</v>
+      </c>
+      <c r="BA8" s="26">
+        <v>33522.334649999997</v>
+      </c>
+      <c r="BC8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="BD8" s="34">
+        <v>-96.224559999999997</v>
+      </c>
+      <c r="BE8" s="17">
+        <v>517077.6</v>
+      </c>
+      <c r="BG8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="BH8" s="34">
+        <v>-93.707589999999996</v>
+      </c>
+      <c r="BI8" s="17">
+        <v>510340.6</v>
+      </c>
+      <c r="BK8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="BL8" s="34">
+        <v>-0.12438572000000001</v>
+      </c>
+      <c r="BM8" s="17">
+        <v>55606.478790000001</v>
+      </c>
+      <c r="BO8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="BP8" s="34">
+        <v>0.70949499999999999</v>
+      </c>
+      <c r="BQ8" s="17">
+        <v>55867.376609999999</v>
+      </c>
+      <c r="BS8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="BT8" s="34">
+        <v>0.56132400000000005</v>
+      </c>
+      <c r="BU8" s="17">
+        <v>34732.780121999996</v>
+      </c>
+      <c r="BW8" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="BX8" s="17">
+        <f t="shared" ref="BX8:BX10" si="10">+_xlfn.XLOOKUP($BW8,$BC$7:$BC$10,$BE$7:$BE$10)</f>
+        <v>40580.75</v>
+      </c>
+      <c r="BY8" s="17">
+        <f>+_xlfn.XLOOKUP(BW8,$BG$7:$BG$10,$BI$7:$BI$10)</f>
+        <v>39378.31</v>
+      </c>
+      <c r="BZ8" s="17">
+        <f>+AW9</f>
+        <v>1508.5369000000001</v>
+      </c>
+      <c r="CA8" s="17">
+        <f>+AW10</f>
+        <v>1273.9808</v>
+      </c>
+      <c r="CB8" s="17">
+        <f t="shared" ref="CB8:CB10" si="11">+_xlfn.XLOOKUP($BW8,$BK$7:$BK$10,$BM$7:$BM$10)</f>
+        <v>23.92548</v>
+      </c>
+      <c r="CC8" s="17">
+        <f>+BA8</f>
+        <v>33522.334649999997</v>
+      </c>
+      <c r="CD8" s="17">
+        <f t="shared" ref="CD8:CD10" si="12">+_xlfn.XLOOKUP($BW8,$BO$7:$BO$10,$BQ$7:$BQ$10)</f>
+        <v>1366.269454</v>
+      </c>
+      <c r="CE8" s="17">
+        <f t="shared" ref="CE8:CE10" si="13">+_xlfn.XLOOKUP($BW8,$BS$7:$BS$10,$BU$7:$BU$10)</f>
+        <v>6.6396439999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="15">
+        <v>-14.8750605</v>
+      </c>
+      <c r="D9" s="14">
+        <v>98817.08</v>
+      </c>
+      <c r="E9" s="15">
+        <v>-100.7885666</v>
+      </c>
+      <c r="F9" s="14">
+        <v>250221.03</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>BM</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J9" s="33">
+        <v>-101.5126727</v>
+      </c>
+      <c r="K9" s="14">
+        <v>251109.5</v>
+      </c>
+      <c r="L9" s="14">
+        <f>+K9-F9</f>
+        <v>888.47000000000116</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O9" s="33">
+        <v>-74322.225143000003</v>
+      </c>
+      <c r="P9" s="14">
+        <v>6319862</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="S9" s="33">
+        <v>-74373.441279000006</v>
+      </c>
+      <c r="T9" s="14">
+        <v>6322039</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="W9" s="33">
+        <v>-844.09909029999994</v>
+      </c>
+      <c r="X9" s="14">
+        <v>720988.16000000003</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA9" s="33">
+        <v>-527.98294699999997</v>
+      </c>
+      <c r="AB9" s="14">
+        <v>570420.5</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE9" s="33">
+        <v>0.85376200000000002</v>
+      </c>
+      <c r="AF9" s="14">
+        <v>9484.2870000000003</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AI9" s="14">
+        <f t="shared" si="0"/>
+        <v>6319862</v>
+      </c>
+      <c r="AJ9" s="14">
+        <f t="shared" si="1"/>
+        <v>6322039</v>
+      </c>
+      <c r="AK9" s="14">
+        <f t="shared" si="2"/>
+        <v>98817.08</v>
+      </c>
+      <c r="AL9" s="14">
+        <f t="shared" si="3"/>
+        <v>250221.03</v>
+      </c>
+      <c r="AM9" s="14">
+        <f t="shared" si="4"/>
+        <v>720988.16000000003</v>
+      </c>
+      <c r="AN9" s="14">
+        <f t="shared" si="5"/>
+        <v>251109.5</v>
+      </c>
+      <c r="AO9" s="14">
+        <f t="shared" si="6"/>
+        <v>570420.5</v>
+      </c>
+      <c r="AP9" s="14">
+        <f t="shared" si="9"/>
+        <v>9484.2870000000003</v>
+      </c>
+      <c r="AT9" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="AU9" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AV9" s="12">
+        <v>-87.875995500000002</v>
+      </c>
+      <c r="AW9" s="14">
+        <v>1508.5369000000001</v>
+      </c>
+      <c r="AY9" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="AZ9" s="15">
+        <v>-54.161358200000002</v>
+      </c>
+      <c r="BA9" s="25">
+        <v>326.82960000000003</v>
+      </c>
+      <c r="BC9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BD9" s="33">
+        <v>-1116797</v>
+      </c>
+      <c r="BE9" s="14">
+        <v>46504.1</v>
+      </c>
+      <c r="BG9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BH9" s="33">
+        <v>-1057560</v>
+      </c>
+      <c r="BI9" s="14">
+        <v>45253.96</v>
+      </c>
+      <c r="BK9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BL9" s="33">
+        <v>0.43556107999999999</v>
+      </c>
+      <c r="BM9" s="14">
+        <v>33.06073</v>
+      </c>
+      <c r="BO9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BP9" s="33">
+        <v>-16.475088</v>
+      </c>
+      <c r="BQ9" s="14">
+        <v>1129.176692</v>
+      </c>
+      <c r="BS9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BT9" s="33">
+        <v>-2.6274600000000001</v>
+      </c>
+      <c r="BU9" s="14">
+        <v>83.811807000000002</v>
+      </c>
+      <c r="BW9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="BX9" s="14">
+        <f t="shared" si="10"/>
+        <v>46504.1</v>
+      </c>
+      <c r="BY9" s="14">
+        <f>+_xlfn.XLOOKUP(BW10,$BG$7:$BG$10,$BI$7:$BI$10)</f>
+        <v>1090796</v>
+      </c>
+      <c r="BZ9" s="14">
+        <f>+AW11</f>
+        <v>2156.3809999999999</v>
+      </c>
+      <c r="CA9" s="14">
+        <f>+AW12</f>
+        <v>367.51769999999999</v>
+      </c>
+      <c r="CB9" s="14">
+        <f t="shared" si="11"/>
+        <v>33.06073</v>
+      </c>
+      <c r="CC9" s="14">
+        <f>+BA9</f>
+        <v>326.82960000000003</v>
+      </c>
+      <c r="CD9" s="14">
+        <f t="shared" si="12"/>
+        <v>1129.176692</v>
+      </c>
+      <c r="CE9" s="14">
+        <f t="shared" si="13"/>
+        <v>83.811807000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" s="16">
+        <v>-45.222719599999998</v>
+      </c>
+      <c r="D10" s="17">
+        <v>62347.05</v>
+      </c>
+      <c r="E10" s="16">
+        <v>-42.999206399999998</v>
+      </c>
+      <c r="F10" s="17">
+        <v>60828.99</v>
+      </c>
+      <c r="G10" s="6" t="str">
+        <f t="shared" si="7"/>
+        <v>GGM</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="J10" s="34">
+        <v>-36.981007400000003</v>
+      </c>
+      <c r="K10" s="17">
+        <v>56516</v>
+      </c>
+      <c r="L10" s="17">
+        <f t="shared" si="8"/>
+        <v>-4312.989999999998</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="O10" s="34">
+        <v>-5849.742776</v>
+      </c>
+      <c r="P10" s="17">
+        <v>648975</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="S10" s="34">
+        <v>-5872.4790750000002</v>
+      </c>
+      <c r="T10" s="17">
+        <v>650234.80000000005</v>
+      </c>
+      <c r="V10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="W10" s="34">
+        <v>-39.938344000000001</v>
+      </c>
+      <c r="X10" s="17">
+        <v>58675.03</v>
+      </c>
+      <c r="Z10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA10" s="34">
+        <v>-164.294004</v>
+      </c>
+      <c r="AB10" s="17">
+        <v>117900.8</v>
+      </c>
+      <c r="AD10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AE10" s="34">
+        <v>0.70942099999999997</v>
+      </c>
+      <c r="AF10" s="17">
+        <v>4943.3419999999996</v>
+      </c>
+      <c r="AH10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AI10" s="14">
+        <f t="shared" si="0"/>
+        <v>648975</v>
+      </c>
+      <c r="AJ10" s="14">
+        <f t="shared" si="1"/>
+        <v>650234.80000000005</v>
+      </c>
+      <c r="AK10" s="14">
+        <f t="shared" si="2"/>
+        <v>62347.05</v>
+      </c>
+      <c r="AL10" s="14">
+        <f t="shared" si="3"/>
+        <v>60828.99</v>
+      </c>
+      <c r="AM10" s="14">
+        <f t="shared" si="4"/>
+        <v>58675.03</v>
+      </c>
+      <c r="AN10" s="14">
+        <f t="shared" si="5"/>
+        <v>56516</v>
+      </c>
+      <c r="AO10" s="14">
+        <f t="shared" si="6"/>
+        <v>117900.8</v>
+      </c>
+      <c r="AP10" s="14">
+        <f t="shared" si="9"/>
+        <v>4943.3419999999996</v>
+      </c>
+      <c r="AT10" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AU10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV10" s="18">
+        <v>-62.386733300000003</v>
+      </c>
+      <c r="AW10" s="17">
+        <v>1273.9808</v>
+      </c>
+      <c r="AY10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AZ10" s="16">
+        <v>-7.8432873000000001</v>
+      </c>
+      <c r="BA10" s="26">
+        <v>63829.462</v>
+      </c>
+      <c r="BC10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="BD10" s="34">
+        <v>-2694.8380000000002</v>
+      </c>
+      <c r="BE10" s="17">
+        <v>1114452</v>
+      </c>
+      <c r="BG10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="BH10" s="34">
+        <v>-2581.6080000000002</v>
+      </c>
+      <c r="BI10" s="17">
+        <v>1090796</v>
+      </c>
+      <c r="BK10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="BL10" s="34">
+        <v>1.256618E-2</v>
+      </c>
+      <c r="BM10" s="17">
+        <v>21328.893110000001</v>
+      </c>
+      <c r="BO10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="BP10" s="34">
+        <v>-1.0690390000000001</v>
+      </c>
+      <c r="BQ10" s="17">
+        <v>197356.89684900001</v>
+      </c>
+      <c r="BS10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="BT10" s="34">
+        <v>0.74929500000000004</v>
+      </c>
+      <c r="BU10" s="17">
+        <v>10747.212681999999</v>
+      </c>
+      <c r="BW10" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="BX10" s="17">
+        <f t="shared" si="10"/>
+        <v>1114452</v>
+      </c>
+      <c r="BY10" s="17">
+        <f>+_xlfn.XLOOKUP(BW10,$BG$7:$BG$10,$BI$7:$BI$10)</f>
+        <v>1090796</v>
+      </c>
+      <c r="BZ10" s="17">
+        <f>+AW13</f>
+        <v>786390.35939999996</v>
+      </c>
+      <c r="CA10" s="17">
+        <f>+AW14</f>
+        <v>185228.0214</v>
+      </c>
+      <c r="CB10" s="17">
+        <f t="shared" si="11"/>
+        <v>21328.893110000001</v>
+      </c>
+      <c r="CC10" s="17">
+        <f>+BA10</f>
+        <v>63829.462</v>
+      </c>
+      <c r="CD10" s="17">
+        <f t="shared" si="12"/>
+        <v>197356.89684900001</v>
+      </c>
+      <c r="CE10" s="17">
+        <f t="shared" si="13"/>
+        <v>10747.212681999999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="15">
+        <v>-11.4324584</v>
+      </c>
+      <c r="D11" s="14">
+        <v>8599527.8300000001</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0.75520039999999999</v>
+      </c>
+      <c r="F11" s="14">
+        <v>1206705.8899999999</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>GGM</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" s="33">
+        <v>0.7672158</v>
+      </c>
+      <c r="K11" s="14">
+        <v>1176719.3</v>
+      </c>
+      <c r="L11" s="14">
+        <f t="shared" si="8"/>
+        <v>-29986.589999999851</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O11" s="33">
+        <v>-210.45065</v>
+      </c>
+      <c r="P11" s="14">
+        <v>35465050</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="S11" s="33">
+        <v>-210.44169099999999</v>
+      </c>
+      <c r="T11" s="14">
+        <v>35464300</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="W11" s="33">
+        <v>-10.440305199999999</v>
+      </c>
+      <c r="X11" s="14">
+        <v>8249258.3600000003</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA11" s="33">
+        <v>-22.354537000000001</v>
+      </c>
+      <c r="AB11" s="14">
+        <v>11786420</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AE11" s="33">
+        <v>0.96534200000000003</v>
+      </c>
+      <c r="AF11" s="14">
+        <v>454043.1</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AI11" s="14">
+        <f t="shared" si="0"/>
+        <v>35465050</v>
+      </c>
+      <c r="AJ11" s="14">
+        <f t="shared" si="1"/>
+        <v>35464300</v>
+      </c>
+      <c r="AK11" s="14">
+        <f t="shared" si="2"/>
+        <v>8599527.8300000001</v>
+      </c>
+      <c r="AL11" s="14">
+        <f t="shared" si="3"/>
+        <v>1206705.8899999999</v>
+      </c>
+      <c r="AM11" s="14">
+        <f t="shared" si="4"/>
+        <v>8249258.3600000003</v>
+      </c>
+      <c r="AN11" s="14">
+        <f t="shared" si="5"/>
+        <v>1176719.3</v>
+      </c>
+      <c r="AO11" s="14">
+        <f t="shared" si="6"/>
+        <v>11786420</v>
+      </c>
+      <c r="AP11" s="14">
+        <f t="shared" si="9"/>
+        <v>454043.1</v>
+      </c>
+      <c r="AT11" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="AU11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AV11" s="12">
+        <v>-62.730387200000003</v>
+      </c>
+      <c r="AW11" s="14">
+        <v>2156.3809999999999</v>
+      </c>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="14"/>
+      <c r="BG11" s="14"/>
+      <c r="BH11" s="14"/>
+      <c r="BI11" s="14"/>
+      <c r="BK11" s="14"/>
+      <c r="BL11" s="14"/>
+      <c r="BM11" s="14"/>
+      <c r="BO11" s="14"/>
+      <c r="BP11" s="14"/>
+      <c r="BQ11" s="14"/>
+      <c r="BS11" s="14"/>
+      <c r="BT11" s="14"/>
+      <c r="BU11" s="14"/>
+    </row>
+    <row r="12" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="16">
+        <v>-111.9174616</v>
+      </c>
+      <c r="D12" s="17">
+        <v>16238019.49</v>
+      </c>
+      <c r="E12" s="16">
+        <v>-17.482627300000001</v>
+      </c>
+      <c r="F12" s="17">
+        <v>6569530.8799999999</v>
+      </c>
+      <c r="G12" s="6" t="str">
+        <f t="shared" si="7"/>
+        <v>GGM</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="34">
+        <v>-11.824242099999999</v>
+      </c>
+      <c r="K12" s="17">
+        <v>5472280.5999999996</v>
+      </c>
+      <c r="L12" s="17">
+        <f t="shared" si="8"/>
+        <v>-1097250.2800000003</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="O12" s="34">
+        <v>-242.90492599999999</v>
+      </c>
+      <c r="P12" s="17">
+        <v>23865070</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="S12" s="34">
+        <v>-242.90095299999999</v>
+      </c>
+      <c r="T12" s="17">
+        <v>23864880</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="W12" s="34">
+        <v>0.73289349999999998</v>
+      </c>
+      <c r="X12" s="17">
+        <v>789759.22</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA12" s="34">
+        <v>-9.6180679999999992</v>
+      </c>
+      <c r="AB12" s="17">
+        <v>4979380</v>
+      </c>
+      <c r="AD12" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE12" s="34">
+        <v>-20.279411</v>
+      </c>
+      <c r="AF12" s="17">
+        <v>7049078</v>
+      </c>
+      <c r="AH12" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI12" s="14">
+        <f t="shared" si="0"/>
+        <v>23865070</v>
+      </c>
+      <c r="AJ12" s="14">
+        <f t="shared" si="1"/>
+        <v>23864880</v>
+      </c>
+      <c r="AK12" s="14">
+        <f t="shared" si="2"/>
+        <v>16238019.49</v>
+      </c>
+      <c r="AL12" s="14">
+        <f t="shared" si="3"/>
+        <v>6569530.8799999999</v>
+      </c>
+      <c r="AM12" s="14">
+        <f t="shared" si="4"/>
+        <v>789759.22</v>
+      </c>
+      <c r="AN12" s="14">
+        <f t="shared" si="5"/>
+        <v>5472280.5999999996</v>
+      </c>
+      <c r="AO12" s="14">
+        <f t="shared" si="6"/>
+        <v>4979380</v>
+      </c>
+      <c r="AP12" s="14">
+        <f t="shared" si="9"/>
+        <v>7049078</v>
+      </c>
+      <c r="AT12" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="AU12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV12" s="18">
+        <v>-0.85119440000000002</v>
+      </c>
+      <c r="AW12" s="17">
+        <v>367.51769999999999</v>
+      </c>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="14"/>
+      <c r="BG12" s="14"/>
+      <c r="BH12" s="14"/>
+      <c r="BI12" s="14"/>
+      <c r="BK12" s="14"/>
+      <c r="BL12" s="14"/>
+      <c r="BM12" s="14"/>
+      <c r="BO12" s="14"/>
+      <c r="BP12" s="14"/>
+      <c r="BQ12" s="14"/>
+      <c r="BS12" s="14"/>
+      <c r="BT12" s="14"/>
+      <c r="BU12" s="14"/>
+    </row>
+    <row r="13" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="15">
+        <v>-1.2333866</v>
+      </c>
+      <c r="D13" s="14">
+        <v>268838.75</v>
+      </c>
+      <c r="E13" s="15">
+        <v>-0.79529260000000002</v>
+      </c>
+      <c r="F13" s="14">
+        <v>241033.57</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>GGM</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J13" s="33">
+        <v>-1.2637936999999999</v>
+      </c>
+      <c r="K13" s="14">
+        <v>270662.7</v>
+      </c>
+      <c r="L13" s="14">
+        <f t="shared" si="8"/>
+        <v>29629.130000000005</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="O13" s="33">
+        <v>-1933.2909870000001</v>
+      </c>
+      <c r="P13" s="14">
+        <v>7179580</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S13" s="33">
+        <v>-1935.788642</v>
+      </c>
+      <c r="T13" s="14">
+        <v>7184214</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="W13" s="33">
+        <v>-179.7974595</v>
+      </c>
+      <c r="X13" s="14">
+        <v>2418834.08</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA13" s="33">
+        <v>-29.274857999999998</v>
+      </c>
+      <c r="AB13" s="14">
+        <v>989808</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE13" s="33">
+        <v>0.103008</v>
+      </c>
+      <c r="AF13" s="14">
+        <v>170374.3</v>
+      </c>
+      <c r="AH13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI13" s="14">
+        <f t="shared" si="0"/>
+        <v>7179580</v>
+      </c>
+      <c r="AJ13" s="14">
+        <f t="shared" si="1"/>
+        <v>7184214</v>
+      </c>
+      <c r="AK13" s="14">
+        <f t="shared" si="2"/>
+        <v>268838.75</v>
+      </c>
+      <c r="AL13" s="14">
+        <f t="shared" si="3"/>
+        <v>241033.57</v>
+      </c>
+      <c r="AM13" s="14">
+        <f t="shared" si="4"/>
+        <v>2418834.08</v>
+      </c>
+      <c r="AN13" s="14">
+        <f t="shared" si="5"/>
+        <v>270662.7</v>
+      </c>
+      <c r="AO13" s="14">
+        <f t="shared" si="6"/>
+        <v>989808</v>
+      </c>
+      <c r="AP13" s="14">
+        <f t="shared" si="9"/>
+        <v>170374.3</v>
+      </c>
+      <c r="AT13" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="AU13" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AV13" s="12">
+        <v>-31.850383799999999</v>
+      </c>
+      <c r="AW13" s="14">
+        <v>786390.35939999996</v>
+      </c>
+      <c r="BC13" s="14"/>
+      <c r="BD13" s="14"/>
+      <c r="BE13" s="14"/>
+      <c r="BG13" s="14"/>
+      <c r="BH13" s="14"/>
+      <c r="BI13" s="14"/>
+      <c r="BK13" s="14"/>
+      <c r="BL13" s="14"/>
+      <c r="BM13" s="14"/>
+      <c r="BO13" s="14"/>
+      <c r="BP13" s="14"/>
+      <c r="BQ13" s="14"/>
+      <c r="BS13" s="14"/>
+      <c r="BT13" s="14"/>
+      <c r="BU13" s="14"/>
+    </row>
+    <row r="14" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="16">
+        <v>-91.031581299999999</v>
+      </c>
+      <c r="D14" s="17">
+        <v>238687.29</v>
+      </c>
+      <c r="E14" s="16">
+        <v>-96.181229700000003</v>
+      </c>
+      <c r="F14" s="17">
+        <v>245274.3</v>
+      </c>
+      <c r="G14" s="6" t="str">
+        <f t="shared" si="7"/>
+        <v>BM</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J14" s="34">
+        <v>-89.237210300000001</v>
+      </c>
+      <c r="K14" s="17">
+        <v>236349</v>
+      </c>
+      <c r="L14" s="17">
+        <f t="shared" si="8"/>
+        <v>-8925.2999999999884</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="O14" s="34">
+        <v>-1799.8141330000001</v>
+      </c>
+      <c r="P14" s="17">
+        <v>996737.1</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="S14" s="34">
+        <v>-1795.435129</v>
+      </c>
+      <c r="T14" s="17">
+        <v>995524.5</v>
+      </c>
+      <c r="V14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="W14" s="34">
+        <v>-5.0710414999999998</v>
+      </c>
+      <c r="X14" s="17">
+        <v>61304.51</v>
+      </c>
+      <c r="Z14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AA14" s="34">
+        <v>-83.509297000000004</v>
+      </c>
+      <c r="AB14" s="17">
+        <v>228724.7</v>
+      </c>
+      <c r="AD14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AE14" s="34">
+        <v>-0.475381</v>
+      </c>
+      <c r="AF14" s="17">
+        <v>30221.29</v>
+      </c>
+      <c r="AH14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AI14" s="14">
+        <f t="shared" si="0"/>
+        <v>996737.1</v>
+      </c>
+      <c r="AJ14" s="14">
+        <f t="shared" si="1"/>
+        <v>995524.5</v>
+      </c>
+      <c r="AK14" s="14">
+        <f t="shared" si="2"/>
+        <v>238687.29</v>
+      </c>
+      <c r="AL14" s="14">
+        <f t="shared" si="3"/>
+        <v>245274.3</v>
+      </c>
+      <c r="AM14" s="14">
+        <f t="shared" si="4"/>
+        <v>61304.51</v>
+      </c>
+      <c r="AN14" s="14">
+        <f t="shared" si="5"/>
+        <v>236349</v>
+      </c>
+      <c r="AO14" s="14">
+        <f t="shared" si="6"/>
+        <v>228724.7</v>
+      </c>
+      <c r="AP14" s="14">
+        <f t="shared" si="9"/>
+        <v>30221.29</v>
+      </c>
+      <c r="AT14" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AU14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV14" s="18">
+        <v>-0.82254159999999998</v>
+      </c>
+      <c r="AW14" s="17">
+        <v>185228.0214</v>
+      </c>
+      <c r="BC14" s="14"/>
+      <c r="BD14" s="14"/>
+      <c r="BE14" s="14"/>
+      <c r="BG14" s="14"/>
+      <c r="BH14" s="14"/>
+      <c r="BI14" s="14"/>
+      <c r="BK14" s="14"/>
+      <c r="BL14" s="14"/>
+      <c r="BM14" s="14"/>
+      <c r="BO14" s="14"/>
+      <c r="BP14" s="14"/>
+      <c r="BQ14" s="14"/>
+      <c r="BS14" s="14"/>
+      <c r="BT14" s="14"/>
+      <c r="BU14" s="14"/>
+    </row>
+    <row r="15" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" s="15">
+        <v>-56.708334700000002</v>
+      </c>
+      <c r="D15" s="14">
+        <v>166922.54</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-103.01634919999999</v>
+      </c>
+      <c r="F15" s="14">
+        <v>224102.41</v>
+      </c>
+      <c r="G15" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>BM</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J15" s="33">
+        <v>-12.7604203</v>
+      </c>
+      <c r="K15" s="14">
+        <v>13084624.699999999</v>
+      </c>
+      <c r="L15" s="14">
+        <f t="shared" si="8"/>
+        <v>12860522.289999999</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="O15" s="33">
+        <v>-779.10362199999997</v>
+      </c>
+      <c r="P15" s="14">
+        <v>98519360</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S15" s="33">
+        <v>-779.06910800000003</v>
+      </c>
+      <c r="T15" s="14">
+        <v>98517180</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="W15" s="33">
+        <v>0.20104150000000001</v>
+      </c>
+      <c r="X15" s="14">
+        <v>3152880.72</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA15" s="33">
+        <v>-25.673124000000001</v>
+      </c>
+      <c r="AB15" s="14">
+        <v>18217230</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE15" s="33">
+        <v>0.66067100000000001</v>
+      </c>
+      <c r="AF15" s="14">
+        <v>2054735</v>
+      </c>
+      <c r="AH15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AI15" s="14">
+        <f t="shared" si="0"/>
+        <v>98519360</v>
+      </c>
+      <c r="AJ15" s="14">
+        <f t="shared" si="1"/>
+        <v>98517180</v>
+      </c>
+      <c r="AK15" s="14">
+        <f t="shared" si="2"/>
+        <v>14385138.210000001</v>
+      </c>
+      <c r="AL15" s="14">
+        <f t="shared" si="3"/>
+        <v>13084619.300000001</v>
+      </c>
+      <c r="AM15" s="14">
+        <f t="shared" si="4"/>
+        <v>3152880.72</v>
+      </c>
+      <c r="AN15" s="14">
+        <f t="shared" si="5"/>
+        <v>13084624.699999999</v>
+      </c>
+      <c r="AO15" s="14">
+        <f t="shared" si="6"/>
+        <v>18217230</v>
+      </c>
+      <c r="AP15" s="14">
+        <f t="shared" si="9"/>
+        <v>2054735</v>
+      </c>
+      <c r="BC15" s="14"/>
+      <c r="BD15" s="14"/>
+      <c r="BE15" s="14"/>
+      <c r="BG15" s="14"/>
+      <c r="BH15" s="14"/>
+      <c r="BI15" s="14"/>
+      <c r="BK15" s="14"/>
+      <c r="BL15" s="14"/>
+      <c r="BM15" s="14"/>
+      <c r="BO15" s="14"/>
+      <c r="BP15" s="14"/>
+      <c r="BQ15" s="14"/>
+      <c r="BS15" s="14"/>
+      <c r="BT15" s="14"/>
+      <c r="BU15" s="14"/>
+      <c r="CA15" s="13"/>
+      <c r="CB15" s="13"/>
+    </row>
+    <row r="16" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="16">
+        <v>-15.631722699999999</v>
+      </c>
+      <c r="D16" s="17">
+        <v>14385138.210000001</v>
+      </c>
+      <c r="E16" s="16">
+        <v>-12.7604089</v>
+      </c>
+      <c r="F16" s="17">
+        <v>13084619.300000001</v>
+      </c>
+      <c r="G16" s="6" t="str">
+        <f t="shared" si="7"/>
+        <v>GGM</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="J16" s="34">
+        <v>-86.961009899999993</v>
+      </c>
+      <c r="K16" s="17">
+        <v>206082.4</v>
+      </c>
+      <c r="L16" s="17">
+        <f t="shared" si="8"/>
+        <v>-12878536.9</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="O16" s="34">
+        <v>-2140.578501</v>
+      </c>
+      <c r="P16" s="17">
+        <v>1000999</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="S16" s="34">
+        <v>-2138.2510229999998</v>
+      </c>
+      <c r="T16" s="17">
+        <v>1000455</v>
+      </c>
+      <c r="V16" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="W16" s="34">
+        <v>0.41362320000000002</v>
+      </c>
+      <c r="X16" s="17">
+        <v>16826.12</v>
+      </c>
+      <c r="Z16" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AA16" s="34">
+        <v>-77.961535999999995</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>195255.6</v>
+      </c>
+      <c r="AD16" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE16" s="34">
+        <v>0.882351</v>
+      </c>
+      <c r="AF16" s="17">
+        <v>7536.8639999999996</v>
+      </c>
+      <c r="AH16" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI16" s="14">
+        <f t="shared" si="0"/>
+        <v>1000999</v>
+      </c>
+      <c r="AJ16" s="14">
+        <f t="shared" si="1"/>
+        <v>1000455</v>
+      </c>
+      <c r="AK16" s="14">
+        <f t="shared" si="2"/>
+        <v>166922.54</v>
+      </c>
+      <c r="AL16" s="14">
+        <f t="shared" si="3"/>
+        <v>224102.41</v>
+      </c>
+      <c r="AM16" s="14">
+        <f t="shared" si="4"/>
+        <v>16826.12</v>
+      </c>
+      <c r="AN16" s="14">
+        <f t="shared" si="5"/>
+        <v>206082.4</v>
+      </c>
+      <c r="AO16" s="14">
+        <f t="shared" si="6"/>
+        <v>195255.6</v>
+      </c>
+      <c r="AP16" s="14">
+        <f t="shared" si="9"/>
+        <v>7536.8639999999996</v>
+      </c>
+      <c r="BC16" s="14"/>
+      <c r="BD16" s="14"/>
+      <c r="BE16" s="14"/>
+      <c r="BG16" s="14"/>
+      <c r="BH16" s="14"/>
+      <c r="BI16" s="14"/>
+      <c r="BK16" s="14"/>
+      <c r="BL16" s="14"/>
+      <c r="BM16" s="14"/>
+      <c r="BO16" s="14"/>
+      <c r="BP16" s="14"/>
+      <c r="BQ16" s="14"/>
+      <c r="BS16" s="14"/>
+      <c r="BT16" s="14"/>
+      <c r="BU16" s="14"/>
+      <c r="CA16" s="13"/>
+      <c r="CB16" s="13"/>
+    </row>
+    <row r="17" spans="55:80" x14ac:dyDescent="0.3">
+      <c r="CA17" s="13"/>
+      <c r="CB17" s="13"/>
+    </row>
+    <row r="18" spans="55:80" x14ac:dyDescent="0.3">
+      <c r="CA18" s="13"/>
+      <c r="CB18" s="13"/>
+    </row>
+    <row r="19" spans="55:80" x14ac:dyDescent="0.3">
+      <c r="BW19" s="19"/>
+      <c r="BX19" s="19"/>
+      <c r="BY19" s="19"/>
+      <c r="BZ19" s="13"/>
+      <c r="CA19" s="13"/>
+      <c r="CB19" s="13"/>
+    </row>
+    <row r="20" spans="55:80" x14ac:dyDescent="0.3">
+      <c r="BW20" s="19"/>
+      <c r="BX20" s="19"/>
+      <c r="BY20" s="19"/>
+      <c r="BZ20" s="13"/>
+      <c r="CA20" s="13"/>
+      <c r="CB20" s="13"/>
+    </row>
+    <row r="21" spans="55:80" x14ac:dyDescent="0.3">
+      <c r="BW21" s="13"/>
+      <c r="BX21" s="13"/>
+      <c r="BY21" s="13"/>
+      <c r="BZ21" s="13"/>
+      <c r="CA21" s="13"/>
+      <c r="CB21" s="13"/>
+    </row>
+    <row r="22" spans="55:80" x14ac:dyDescent="0.3">
+      <c r="BW22" s="13"/>
+      <c r="BX22" s="13"/>
+      <c r="BY22" s="13"/>
+      <c r="BZ22" s="13"/>
+      <c r="CA22" s="13"/>
+      <c r="CB22" s="13"/>
+    </row>
+    <row r="23" spans="55:80" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="BC23" s="27"/>
+      <c r="BD23" s="27"/>
+      <c r="BE23" s="27"/>
+      <c r="BG23" s="27"/>
+      <c r="BH23" s="27"/>
+      <c r="BI23" s="27"/>
+      <c r="BK23" s="27"/>
+      <c r="BL23" s="27"/>
+      <c r="BO23" s="27"/>
+      <c r="BP23" s="27"/>
+      <c r="BQ23" s="27"/>
+      <c r="BS23" s="27"/>
+      <c r="BT23" s="27"/>
+      <c r="BU23" s="27"/>
+    </row>
+    <row r="24" spans="55:80" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="BC24" s="27"/>
+      <c r="BD24" s="28"/>
+      <c r="BE24" s="28"/>
+      <c r="BG24" s="28"/>
+      <c r="BH24" s="28"/>
+      <c r="BI24" s="28"/>
+      <c r="BK24" s="28"/>
+      <c r="BL24" s="28"/>
+      <c r="BM24" s="28"/>
+      <c r="BO24" s="28"/>
+      <c r="BP24" s="28"/>
+      <c r="BQ24" s="28"/>
+      <c r="BS24" s="28"/>
+      <c r="BT24" s="28"/>
+      <c r="BU24" s="28"/>
+    </row>
+    <row r="25" spans="55:80" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="BC25" s="27"/>
+      <c r="BD25" s="28"/>
+      <c r="BE25" s="28"/>
+      <c r="BG25" s="28"/>
+      <c r="BH25" s="28"/>
+      <c r="BI25" s="28"/>
+      <c r="BK25" s="28"/>
+      <c r="BL25" s="28"/>
+      <c r="BM25" s="28"/>
+      <c r="BO25" s="28"/>
+      <c r="BP25" s="28"/>
+      <c r="BQ25" s="28"/>
+      <c r="BS25" s="28"/>
+      <c r="BT25" s="28"/>
+      <c r="BU25" s="28"/>
+    </row>
+    <row r="26" spans="55:80" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="BC26" s="27"/>
+      <c r="BD26" s="28"/>
+      <c r="BE26" s="28"/>
+      <c r="BG26" s="28"/>
+      <c r="BH26" s="28"/>
+      <c r="BI26" s="28"/>
+      <c r="BK26" s="28"/>
+      <c r="BL26" s="28"/>
+      <c r="BM26" s="28"/>
+      <c r="BO26" s="28"/>
+      <c r="BP26" s="28"/>
+      <c r="BQ26" s="28"/>
+      <c r="BS26" s="28"/>
+      <c r="BT26" s="28"/>
+      <c r="BU26" s="28"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="BC13:BE16 BG13:BI16 BK13:BM16 BO13:BQ16">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BS13:BU16">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI7:AI16">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AJ16">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK7:AK16">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL7:AL16">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM7:AM16">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN7:AN16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO7:AO16">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP7:AP16">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI7:AP7">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI8:AP8">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI9:AP9">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI10:AP10">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI11:AP11">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI12:AP12">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI13:AP13">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI14:AP14">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI15:AP15">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI16:AP16">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX7:CE7">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX8:CE8">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX9:CE9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX10:CE10">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE21AE24-7B23-4499-8D22-C9A70AD3E5F9}">
   <dimension ref="B1:C40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6703,7 +9806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCC3A30-8DEB-4A80-AC0D-2CC25A9FC432}">
   <dimension ref="B1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6750,38 +9853,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5625718-4007-43A2-8FA5-6282944FC450}">
-  <dimension ref="B1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="B1" s="10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B3" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC0E92A-92C9-4E3F-8BE9-F4C0DC8654B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6240DCC-66AD-408A-B7CA-CD84D1FF5B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="300">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -562,9 +562,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Results</t>
-  </si>
-  <si>
     <t>Country</t>
   </si>
   <si>
@@ -950,6 +947,24 @@
   </si>
   <si>
     <t>Chicungunya</t>
+  </si>
+  <si>
+    <t>ElasticNet</t>
+  </si>
+  <si>
+    <t>GradientBoosting</t>
+  </si>
+  <si>
+    <t>Lasso</t>
+  </si>
+  <si>
+    <t>LinearRegression</t>
+  </si>
+  <si>
+    <t>RandomForest</t>
+  </si>
+  <si>
+    <t>Ridge</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1145,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1177,6 +1192,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1846,13 +1863,13 @@
         <v>22</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
@@ -1860,16 +1877,16 @@
         <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
@@ -1877,19 +1894,19 @@
         <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -2203,39 +2220,39 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -2296,16 +2313,16 @@
         <v>164</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N4" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="R4" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
@@ -2322,10 +2339,10 @@
         <v>139</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
@@ -2339,13 +2356,13 @@
         <v>137</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
@@ -2359,13 +2376,13 @@
         <v>137</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q7" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
@@ -2379,20 +2396,20 @@
         <v>149</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G8" s="12"/>
       <c r="M8" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
@@ -2406,19 +2423,19 @@
         <v>149</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M9" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="Q9" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
@@ -2432,13 +2449,13 @@
         <v>137</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
@@ -2452,13 +2469,13 @@
         <v>137</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
@@ -2466,19 +2483,19 @@
         <v>150</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>137</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
@@ -2486,19 +2503,19 @@
         <v>150</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>137</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
@@ -2512,13 +2529,13 @@
         <v>149</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
@@ -2532,13 +2549,13 @@
         <v>149</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
@@ -2552,13 +2569,13 @@
         <v>137</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
@@ -2572,13 +2589,13 @@
         <v>149</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
@@ -2592,10 +2609,10 @@
         <v>149</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.3">
@@ -2609,10 +2626,10 @@
         <v>149</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.3">
@@ -2626,10 +2643,10 @@
         <v>149</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.3">
@@ -2643,10 +2660,10 @@
         <v>149</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
@@ -2660,10 +2677,10 @@
         <v>149</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
@@ -2677,10 +2694,10 @@
         <v>149</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
@@ -2699,7 +2716,7 @@
         <v>151</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>137</v>
@@ -2710,7 +2727,7 @@
         <v>151</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>149</v>
@@ -2842,7 +2859,7 @@
         <v>152</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>137</v>
@@ -2853,7 +2870,7 @@
         <v>152</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>137</v>
@@ -2985,7 +3002,7 @@
         <v>153</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>149</v>
@@ -2996,7 +3013,7 @@
         <v>153</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>149</v>
@@ -3065,7 +3082,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2EA5AC-0586-4893-B88A-0F9AA6E9FD44}">
-  <dimension ref="B1:BR46"/>
+  <dimension ref="B1:BU46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -3098,40 +3115,46 @@
     <col min="35" max="35" width="9.109375" style="1" customWidth="1"/>
     <col min="36" max="36" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="12.109375" style="1" customWidth="1"/>
-    <col min="38" max="38" width="2" style="20" customWidth="1"/>
-    <col min="39" max="39" width="15.109375" style="1" customWidth="1"/>
-    <col min="40" max="42" width="8.88671875" style="1"/>
-    <col min="43" max="43" width="2" style="20" customWidth="1"/>
-    <col min="44" max="46" width="8.88671875" style="1"/>
-    <col min="47" max="47" width="2" style="20" customWidth="1"/>
-    <col min="48" max="50" width="12.109375" style="1" customWidth="1"/>
-    <col min="51" max="51" width="2" style="20" customWidth="1"/>
-    <col min="52" max="54" width="12.109375" style="1" customWidth="1"/>
-    <col min="55" max="55" width="2" style="20" customWidth="1"/>
-    <col min="56" max="58" width="12.109375" style="1" customWidth="1"/>
-    <col min="59" max="59" width="2" style="20" customWidth="1"/>
-    <col min="60" max="62" width="12.109375" style="1" customWidth="1"/>
-    <col min="63" max="63" width="2" style="20" customWidth="1"/>
-    <col min="64" max="64" width="11.88671875" style="1" customWidth="1"/>
-    <col min="65" max="68" width="8.88671875" style="1"/>
-    <col min="69" max="69" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="16384" width="8.88671875" style="1"/>
+    <col min="38" max="38" width="2" style="36" customWidth="1"/>
+    <col min="39" max="39" width="2" style="35" customWidth="1"/>
+    <col min="40" max="40" width="2" style="36" customWidth="1"/>
+    <col min="41" max="41" width="15.109375" style="1" customWidth="1"/>
+    <col min="42" max="44" width="8.88671875" style="1"/>
+    <col min="45" max="45" width="2" style="20" customWidth="1"/>
+    <col min="46" max="46" width="10.21875" style="1" customWidth="1"/>
+    <col min="47" max="48" width="8.88671875" style="1"/>
+    <col min="49" max="49" width="2" style="20" customWidth="1"/>
+    <col min="50" max="52" width="12.109375" style="1" customWidth="1"/>
+    <col min="53" max="53" width="2" style="20" customWidth="1"/>
+    <col min="54" max="56" width="12.109375" style="1" customWidth="1"/>
+    <col min="57" max="57" width="2" style="20" customWidth="1"/>
+    <col min="58" max="60" width="12.109375" style="1" customWidth="1"/>
+    <col min="61" max="61" width="2" style="20" customWidth="1"/>
+    <col min="62" max="64" width="12.109375" style="1" customWidth="1"/>
+    <col min="65" max="65" width="2" style="20" customWidth="1"/>
+    <col min="66" max="66" width="11.88671875" style="1" customWidth="1"/>
+    <col min="67" max="71" width="8.88671875" style="1"/>
+    <col min="72" max="72" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:70" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:73" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>165</v>
+        <v>290</v>
       </c>
       <c r="AC1" s="20" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="2" spans="2:70" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+      <c r="AO1" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="2" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N2" s="19" t="s">
         <v>138</v>
@@ -3141,154 +3164,154 @@
       </c>
       <c r="S2" s="19"/>
       <c r="V2" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W2" s="19"/>
       <c r="Z2" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AD2" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AE2" s="19"/>
       <c r="AF2" s="19"/>
-      <c r="AM2" s="19" t="s">
+      <c r="AO2" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AT2" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="AR2" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="AV2" s="19" t="s">
+      <c r="AX2" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="AZ2" s="19" t="s">
+      <c r="BB2" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="BD2" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="BH2" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="BL2" s="19" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BF2" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="BJ2" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="BN2" s="19" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V4" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z4" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AD4" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AE4" s="13"/>
       <c r="AF4" s="13"/>
-      <c r="AM4" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="AR4" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="AV4" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="AZ4" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="BD4" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="BH4" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="BL4" s="13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="6" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="AO4" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="AT4" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="AX4" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="BB4" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="BF4" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="BJ4" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="BN4" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>170</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="L6" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="P6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="P6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="R6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="T6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="T6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="V6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="X6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="X6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="Z6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AB6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="AD6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AE6" s="9" t="s">
         <v>138</v>
@@ -3297,100 +3320,105 @@
         <v>139</v>
       </c>
       <c r="AG6" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AH6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AI6" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ6" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="AK6" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="AO6" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="AK6" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="AM6" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="AN6" s="9" t="s">
+      <c r="AP6" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="AO6" s="9" t="s">
+      <c r="AQ6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="AR6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AP6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="AR6" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="AS6" s="9" t="s">
+      <c r="AT6" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="AU6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="AV6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AT6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="AV6" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="AW6" s="9" t="s">
+      <c r="AX6" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="AY6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="AZ6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AX6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="AZ6" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="BA6" s="9" t="s">
+      <c r="BB6" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="BC6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BD6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BB6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="BD6" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="BE6" s="9" t="s">
+      <c r="BF6" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="BG6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BH6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BF6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="BH6" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="BI6" s="9" t="s">
+      <c r="BJ6" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="BK6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BL6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BJ6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="BL6" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="BM6" s="9" t="s">
+      <c r="BN6" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="BO6" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="BN6" s="9" t="s">
+      <c r="BP6" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="BO6" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="BP6" s="9" t="s">
+      <c r="BQ6" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="BR6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="BQ6" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="BR6" s="9"/>
-    </row>
-    <row r="7" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BS6" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="BT6" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="BU6" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C7" s="15">
         <v>7.6682159999999999E-2</v>
@@ -3409,7 +3437,7 @@
         <v>GGM</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J7" s="12">
         <v>0.99999850000000001</v>
@@ -3422,7 +3450,7 @@
         <v>-1513833.6548000001</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O7" s="12">
         <v>-0.39370899999999998</v>
@@ -3431,7 +3459,7 @@
         <v>15217290</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S7" s="12">
         <v>-9.8227999999999996E-2</v>
@@ -3440,7 +3468,7 @@
         <v>13264390</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="W7" s="31">
         <v>0.99999800000000005</v>
@@ -3449,7 +3477,7 @@
         <v>15940.183487</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AA7" s="31">
         <v>0.99995000000000001</v>
@@ -3458,7 +3486,7 @@
         <v>91507.114184000005</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AE7" s="14">
         <f>+_xlfn.XLOOKUP($AD7,N$7:N$16,P$7:P$16)</f>
@@ -3488,90 +3516,98 @@
         <f>+_xlfn.XLOOKUP(AD7,$Z$7:$Z$16,$AB$7:$AB$16)</f>
         <v>91507.114184000005</v>
       </c>
-      <c r="AM7" s="1" t="s">
+      <c r="AO7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AQ7" s="12">
+        <v>-0.25174930000000001</v>
+      </c>
+      <c r="AR7" s="14">
+        <v>210875.2597</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="AU7" s="23">
+        <v>0.99999979999999999</v>
+      </c>
+      <c r="AV7" s="25">
+        <v>91.979789999999994</v>
+      </c>
+      <c r="AX7" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AN7" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AO7" s="12">
-        <v>-0.25174930000000001</v>
-      </c>
-      <c r="AP7" s="14">
+      <c r="AY7" s="12">
+        <v>0.94224399999999997</v>
+      </c>
+      <c r="AZ7" s="14">
+        <v>4703.6260300000004</v>
+      </c>
+      <c r="BB7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="BC7" s="12">
+        <v>0.91772100000000001</v>
+      </c>
+      <c r="BD7" s="14">
+        <v>5614.0714690000004</v>
+      </c>
+      <c r="BF7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="BG7" s="12">
+        <v>0.99995330000000004</v>
+      </c>
+      <c r="BH7" s="14">
+        <v>133.75837000000001</v>
+      </c>
+      <c r="BJ7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="BK7" s="12">
+        <v>0.98349299999999995</v>
+      </c>
+      <c r="BL7" s="14">
+        <v>2514.5705710000002</v>
+      </c>
+      <c r="BN7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="BO7" s="38">
+        <f>+_xlfn.XLOOKUP($BN7,$AX$7:$AX$10,$AZ$7:$AZ$10)</f>
+        <v>22520.654823000001</v>
+      </c>
+      <c r="BP7" s="14">
+        <f>+_xlfn.XLOOKUP(BN7,$BB$7:$BB$10,$BD$7:$BD$10)</f>
+        <v>16596.507481000001</v>
+      </c>
+      <c r="BQ7" s="14">
+        <f>+AR7</f>
         <v>210875.2597</v>
       </c>
-      <c r="AR7" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="AS7" s="23">
-        <v>0.99999979999999999</v>
-      </c>
-      <c r="AT7" s="25">
+      <c r="BR7" s="14">
+        <f>+AR8</f>
+        <v>15764.5885</v>
+      </c>
+      <c r="BS7" s="14">
+        <f>+_xlfn.XLOOKUP(BN7,$BF$7:$BF$10,$BH$7:$BH$10)</f>
+        <v>89.78492</v>
+      </c>
+      <c r="BT7" s="14">
+        <f>+AV7</f>
         <v>91.979789999999994</v>
       </c>
-      <c r="AV7" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="AW7" s="12">
-        <v>0.94224399999999997</v>
-      </c>
-      <c r="AX7" s="14">
-        <v>4703.6260300000004</v>
-      </c>
-      <c r="AZ7" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="BA7" s="12">
-        <v>0.91772100000000001</v>
-      </c>
-      <c r="BB7" s="14">
-        <v>5614.0714690000004</v>
-      </c>
-      <c r="BD7" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="BE7" s="12">
-        <v>0.91772100000000001</v>
-      </c>
-      <c r="BF7" s="14">
-        <v>5614.0714690000004</v>
-      </c>
-      <c r="BH7" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="BI7" s="12">
-        <v>0.91772100000000001</v>
-      </c>
-      <c r="BJ7" s="14">
-        <v>5614.0714690000004</v>
-      </c>
-      <c r="BL7" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="BM7" s="14">
-        <f>+_xlfn.XLOOKUP($BL7,$AV$7:$AV$9,$AX$7:$AX$9)</f>
-        <v>22520.654823000001</v>
-      </c>
-      <c r="BN7" s="14">
-        <f>+_xlfn.XLOOKUP(BL7,$AZ$7:$AZ$9,$BB$7:$BB$9)</f>
-        <v>16596.507481000001</v>
-      </c>
-      <c r="BO7" s="14">
-        <f>+AP7</f>
-        <v>210875.2597</v>
-      </c>
-      <c r="BP7" s="14">
-        <f>+AP8</f>
-        <v>15764.5885</v>
-      </c>
-      <c r="BQ7" s="14">
-        <f>+AT7</f>
-        <v>91.979789999999994</v>
-      </c>
-    </row>
-    <row r="8" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BU7" s="14">
+        <f>+_xlfn.XLOOKUP(BN7,$BJ$7:$BJ$10,$BL$7:$BL$10)</f>
+        <v>6828.2612090000002</v>
+      </c>
+    </row>
+    <row r="8" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C8" s="16">
         <v>-0.13819318</v>
@@ -3590,7 +3626,7 @@
         <v>GGM</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J8" s="18">
         <v>0.99999919999999998</v>
@@ -3603,7 +3639,7 @@
         <v>-843842.2267</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O8" s="18">
         <v>0.44333400000000001</v>
@@ -3612,7 +3648,7 @@
         <v>1304208</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S8" s="18">
         <v>0.91093299999999999</v>
@@ -3621,7 +3657,7 @@
         <v>518469</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="W8" s="32">
         <v>0.99999899999999997</v>
@@ -3630,7 +3666,7 @@
         <v>1580.191648</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA8" s="32">
         <v>0.999973</v>
@@ -3639,7 +3675,7 @@
         <v>9120.9211990000003</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AE8" s="14">
         <f t="shared" ref="AE8:AE16" si="3">+_xlfn.XLOOKUP($AD8,N$7:N$16,P$7:P$16)</f>
@@ -3669,90 +3705,98 @@
         <f t="shared" ref="AK8:AK16" si="8">+_xlfn.XLOOKUP(AD8,$Z$7:$Z$16,$AB$7:$AB$16)</f>
         <v>9120.9211990000003</v>
       </c>
-      <c r="AM8" s="6" t="s">
+      <c r="AO8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="AP8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ8" s="18">
+        <v>0.99300429999999995</v>
+      </c>
+      <c r="AR8" s="17">
+        <v>15764.5885</v>
+      </c>
+      <c r="AT8" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="AN8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO8" s="18">
-        <v>0.99300429999999995</v>
-      </c>
-      <c r="AP8" s="17">
-        <v>15764.5885</v>
-      </c>
-      <c r="AR8" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="AS8" s="24">
+      <c r="AU8" s="24">
         <v>0.99997420000000004</v>
       </c>
-      <c r="AT8" s="26">
+      <c r="AV8" s="26">
         <v>99.435940000000002</v>
       </c>
-      <c r="AV8" s="6" t="s">
+      <c r="AX8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="AY8" s="18">
+        <v>0.98572300000000002</v>
+      </c>
+      <c r="AZ8" s="17">
+        <v>22520.654823000001</v>
+      </c>
+      <c r="BB8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="BC8" s="18">
+        <v>0.99224599999999996</v>
+      </c>
+      <c r="BD8" s="17">
+        <v>16596.507481000001</v>
+      </c>
+      <c r="BF8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="BG8" s="18">
+        <v>0.99999979999999999</v>
+      </c>
+      <c r="BH8" s="17">
+        <v>89.78492</v>
+      </c>
+      <c r="BJ8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="BK8" s="18">
+        <v>0.99868800000000002</v>
+      </c>
+      <c r="BL8" s="17">
+        <v>6828.2612090000002</v>
+      </c>
+      <c r="BN8" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="AW8" s="18">
-        <v>0.98572300000000002</v>
-      </c>
-      <c r="AX8" s="17">
-        <v>22520.654823000001</v>
-      </c>
-      <c r="AZ8" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="BA8" s="18">
-        <v>0.99224599999999996</v>
-      </c>
-      <c r="BB8" s="17">
-        <v>16596.507481000001</v>
-      </c>
-      <c r="BD8" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="BE8" s="18">
-        <v>0.99224599999999996</v>
-      </c>
-      <c r="BF8" s="17">
-        <v>16596.507481000001</v>
-      </c>
-      <c r="BH8" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="BI8" s="18">
-        <v>0.99224599999999996</v>
-      </c>
-      <c r="BJ8" s="17">
-        <v>16596.507481000001</v>
-      </c>
-      <c r="BL8" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="BM8" s="17">
-        <f t="shared" ref="BM8:BM9" si="9">+_xlfn.XLOOKUP(BL8,$AV$7:$AV$9,$AX$7:$AX$9)</f>
+      <c r="BO8" s="39">
+        <f t="shared" ref="BO8:BO10" si="9">+_xlfn.XLOOKUP($BN8,$AX$7:$AX$10,$AZ$7:$AZ$10)</f>
         <v>4703.6260300000004</v>
       </c>
-      <c r="BN8" s="17">
-        <f t="shared" ref="BN8:BN9" si="10">+_xlfn.XLOOKUP(BL8,$AZ$7:$AZ$9,$BB$7:$BB$9)</f>
+      <c r="BP8" s="17">
+        <f t="shared" ref="BP8:BP10" si="10">+_xlfn.XLOOKUP(BN8,$BB$7:$BB$10,$BD$7:$BD$10)</f>
         <v>5614.0714690000004</v>
       </c>
-      <c r="BO8" s="17">
-        <f>+AP9</f>
+      <c r="BQ8" s="17">
+        <f>+AR9</f>
         <v>1100.5509999999999</v>
       </c>
-      <c r="BP8" s="17">
-        <f>+AP10</f>
+      <c r="BR8" s="17">
+        <f>+AR10</f>
         <v>756.05920000000003</v>
       </c>
-      <c r="BQ8" s="17">
-        <f>+AT8</f>
+      <c r="BS8" s="17">
+        <f t="shared" ref="BS8:BS10" si="11">+_xlfn.XLOOKUP(BN8,$BF$7:$BF$10,$BH$7:$BH$10)</f>
+        <v>133.75837000000001</v>
+      </c>
+      <c r="BT8" s="17">
+        <f>+AV8</f>
         <v>99.435940000000002</v>
       </c>
-    </row>
-    <row r="9" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BU8" s="17">
+        <f t="shared" ref="BU8:BU10" si="12">+_xlfn.XLOOKUP(BN8,$BJ$7:$BJ$10,$BL$7:$BL$10)</f>
+        <v>2514.5705710000002</v>
+      </c>
+    </row>
+    <row r="9" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C9" s="15">
         <v>0.99484592000000005</v>
@@ -3771,7 +3815,7 @@
         <v>GGM</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J9" s="12">
         <v>0.99526269999999994</v>
@@ -3784,7 +3828,7 @@
         <v>-589.51029999999446</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O9" s="12">
         <v>-0.84969700000000004</v>
@@ -3793,7 +3837,7 @@
         <v>3356209</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S9" s="12">
         <v>-0.18831400000000001</v>
@@ -3802,7 +3846,7 @@
         <v>2617900</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W9" s="31">
         <v>0.99999899999999997</v>
@@ -3811,7 +3855,7 @@
         <v>2142.2691100000002</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AA9" s="31">
         <v>0.99992800000000004</v>
@@ -3820,7 +3864,7 @@
         <v>20962.221375000001</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AE9" s="14">
         <f t="shared" si="3"/>
@@ -3850,90 +3894,98 @@
         <f t="shared" si="8"/>
         <v>20962.221375000001</v>
       </c>
-      <c r="AM9" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="AN9" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AO9" s="12">
+      <c r="AO9" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AQ9" s="12">
         <v>0.99683809999999995</v>
       </c>
-      <c r="AP9" s="14">
+      <c r="AR9" s="14">
         <v>1100.5509999999999</v>
       </c>
-      <c r="AR9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AS9" s="23">
+      <c r="AT9" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="AU9" s="23">
         <v>0.9999806</v>
       </c>
-      <c r="AT9" s="25">
+      <c r="AV9" s="25">
         <v>88.003110000000007</v>
       </c>
-      <c r="AV9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AW9" s="12">
+      <c r="AX9" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AY9" s="12">
         <v>0.98843700000000001</v>
       </c>
-      <c r="AX9" s="14">
+      <c r="AZ9" s="14">
         <v>2148.462321</v>
       </c>
-      <c r="AZ9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BA9" s="12">
+      <c r="BB9" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="BC9" s="12">
         <v>0.97706400000000004</v>
       </c>
-      <c r="BB9" s="14">
+      <c r="BD9" s="14">
         <v>3025.804118</v>
       </c>
-      <c r="BD9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BE9" s="12">
-        <v>0.97706400000000004</v>
-      </c>
-      <c r="BF9" s="14">
-        <v>3025.804118</v>
-      </c>
-      <c r="BH9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BI9" s="12">
-        <v>0.97706400000000004</v>
-      </c>
-      <c r="BJ9" s="14">
-        <v>3025.804118</v>
-      </c>
-      <c r="BL9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BM9" s="14">
+      <c r="BF9" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="BG9" s="12">
+        <v>0.999977</v>
+      </c>
+      <c r="BH9" s="14">
+        <v>95.776430000000005</v>
+      </c>
+      <c r="BJ9" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="BK9" s="12">
+        <v>0.99990800000000002</v>
+      </c>
+      <c r="BL9" s="14">
+        <v>192.12411499999999</v>
+      </c>
+      <c r="BN9" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="BO9" s="38">
         <f t="shared" si="9"/>
         <v>2148.462321</v>
       </c>
-      <c r="BN9" s="14">
+      <c r="BP9" s="14">
         <f t="shared" si="10"/>
         <v>3025.804118</v>
       </c>
-      <c r="BO9" s="14">
-        <f>+AP11</f>
+      <c r="BQ9" s="14">
+        <f>+AR11</f>
         <v>1976.5089</v>
       </c>
-      <c r="BP9" s="14">
-        <f>+AP12</f>
+      <c r="BR9" s="14">
+        <f>+AR12</f>
         <v>902.76419999999996</v>
       </c>
-      <c r="BQ9" s="14">
-        <f>+AT9</f>
+      <c r="BS9" s="14">
+        <f t="shared" si="11"/>
+        <v>95.776430000000005</v>
+      </c>
+      <c r="BT9" s="14">
+        <f>+AV9</f>
         <v>88.003110000000007</v>
       </c>
-    </row>
-    <row r="10" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BU9" s="14">
+        <f t="shared" si="12"/>
+        <v>192.12411499999999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C10" s="16">
         <v>0.98982815000000002</v>
@@ -3952,7 +4004,7 @@
         <v>GGM</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J10" s="18">
         <v>0.99999669999999996</v>
@@ -3965,7 +4017,7 @@
         <v>-19827.444499999998</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O10" s="18">
         <v>-0.70091599999999998</v>
@@ -3974,7 +4026,7 @@
         <v>305803.09999999998</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S10" s="18">
         <v>3.9317999999999999E-2</v>
@@ -3983,7 +4035,7 @@
         <v>224458</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="W10" s="32">
         <v>0.99999700000000002</v>
@@ -3992,7 +4044,7 @@
         <v>433.14919800000001</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AA10" s="32">
         <v>0.99969300000000005</v>
@@ -4001,7 +4053,7 @@
         <v>4105.2196100000001</v>
       </c>
       <c r="AD10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AE10" s="14">
         <f t="shared" si="3"/>
@@ -4031,58 +4083,98 @@
         <f t="shared" si="8"/>
         <v>4105.2196100000001</v>
       </c>
-      <c r="AM10" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="AN10" s="6" t="s">
+      <c r="AO10" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AP10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AO10" s="18">
+      <c r="AQ10" s="18">
         <v>0.9985077</v>
       </c>
-      <c r="AP10" s="17">
+      <c r="AR10" s="17">
         <v>756.05920000000003</v>
       </c>
-      <c r="AV10" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="AW10" s="18">
+      <c r="AT10" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="AU10" s="24">
+        <v>0.99999979999999999</v>
+      </c>
+      <c r="AV10" s="26">
+        <v>163.67088000000001</v>
+      </c>
+      <c r="AX10" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="AY10" s="18">
         <v>0.98303399999999996</v>
       </c>
-      <c r="AX10" s="17">
+      <c r="AZ10" s="17">
         <v>53755.513460000002</v>
       </c>
-      <c r="AZ10" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="BA10" s="18">
+      <c r="BB10" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="BC10" s="18">
         <v>0.99701899999999999</v>
       </c>
-      <c r="BB10" s="17">
+      <c r="BD10" s="17">
         <v>22532.557326999999</v>
       </c>
-      <c r="BD10" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="BE10" s="18">
-        <v>0.99701899999999999</v>
-      </c>
-      <c r="BF10" s="17">
+      <c r="BF10" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="BG10" s="18">
+        <v>0.99999990000000005</v>
+      </c>
+      <c r="BH10" s="17">
+        <v>157.38897</v>
+      </c>
+      <c r="BJ10" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="BK10" s="18">
+        <v>0.99997000000000003</v>
+      </c>
+      <c r="BL10" s="17">
+        <v>2248.9489680000001</v>
+      </c>
+      <c r="BN10" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO10" s="39">
+        <f t="shared" si="9"/>
+        <v>53755.513460000002</v>
+      </c>
+      <c r="BP10" s="17">
+        <f t="shared" si="10"/>
         <v>22532.557326999999</v>
       </c>
-      <c r="BH10" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="BI10" s="18">
-        <v>0.99701899999999999</v>
-      </c>
-      <c r="BJ10" s="17">
-        <v>22532.557326999999</v>
-      </c>
-    </row>
-    <row r="11" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BQ10" s="17">
+        <f>+AR13</f>
+        <v>12493.0429</v>
+      </c>
+      <c r="BR10" s="17">
+        <f>+AR14</f>
+        <v>8614.8230000000003</v>
+      </c>
+      <c r="BS10" s="17">
+        <f t="shared" si="11"/>
+        <v>157.38897</v>
+      </c>
+      <c r="BT10" s="17">
+        <f>+AV10</f>
+        <v>163.67088000000001</v>
+      </c>
+      <c r="BU10" s="17">
+        <f t="shared" si="12"/>
+        <v>2248.9489680000001</v>
+      </c>
+    </row>
+    <row r="11" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C11" s="15">
         <v>0.99039379999999999</v>
@@ -4101,7 +4193,7 @@
         <v>GGM</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J11" s="12">
         <v>0.99999199999999999</v>
@@ -4114,7 +4206,7 @@
         <v>-1231603.5988</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O11" s="12">
         <v>0.97311099999999995</v>
@@ -4123,7 +4215,7 @@
         <v>2287439</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S11" s="12">
         <v>0.98591399999999996</v>
@@ -4132,7 +4224,7 @@
         <v>1656545</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="W11" s="31">
         <v>0.99999499999999997</v>
@@ -4141,7 +4233,7 @@
         <v>30356.430119000001</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AA11" s="31">
         <v>0.99996600000000002</v>
@@ -4150,7 +4242,7 @@
         <v>81396.828680000006</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AE11" s="14">
         <f t="shared" si="3"/>
@@ -4180,33 +4272,33 @@
         <f t="shared" si="8"/>
         <v>81396.828680000006</v>
       </c>
-      <c r="AM11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="AN11" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AO11" s="12">
+      <c r="AO11" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AP11" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AQ11" s="12">
         <v>0.99021340000000002</v>
       </c>
-      <c r="AP11" s="14">
+      <c r="AR11" s="14">
         <v>1976.5089</v>
       </c>
-      <c r="AW11" s="12"/>
-      <c r="AX11" s="14"/>
+      <c r="AY11" s="12"/>
       <c r="AZ11" s="14"/>
-      <c r="BA11" s="14"/>
       <c r="BB11" s="14"/>
+      <c r="BC11" s="14"/>
       <c r="BD11" s="14"/>
-      <c r="BE11" s="14"/>
       <c r="BF11" s="14"/>
+      <c r="BG11" s="14"/>
       <c r="BH11" s="14"/>
-      <c r="BI11" s="14"/>
       <c r="BJ11" s="14"/>
-    </row>
-    <row r="12" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BK11" s="14"/>
+      <c r="BL11" s="14"/>
+    </row>
+    <row r="12" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C12" s="16">
         <v>0.98519310000000004</v>
@@ -4225,7 +4317,7 @@
         <v>GGM</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J12" s="18">
         <v>0.99999669999999996</v>
@@ -4238,7 +4330,7 @@
         <v>-947126.18190000008</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O12" s="18">
         <v>0.90446300000000002</v>
@@ -4247,7 +4339,7 @@
         <v>2800556</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S12" s="18">
         <v>0.96489400000000003</v>
@@ -4256,7 +4348,7 @@
         <v>1697944</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W12" s="32">
         <v>0.99999700000000002</v>
@@ -4265,7 +4357,7 @@
         <v>16474.693931999998</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AA12" s="32">
         <v>0.99982899999999997</v>
@@ -4274,7 +4366,7 @@
         <v>118520.743653</v>
       </c>
       <c r="AD12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AE12" s="14">
         <f t="shared" si="3"/>
@@ -4304,36 +4396,36 @@
         <f t="shared" si="8"/>
         <v>118520.743653</v>
       </c>
-      <c r="AM12" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="AN12" s="6" t="s">
+      <c r="AO12" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AP12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AO12" s="18">
+      <c r="AQ12" s="18">
         <v>0.99795840000000002</v>
       </c>
-      <c r="AP12" s="17">
+      <c r="AR12" s="17">
         <v>902.76419999999996</v>
       </c>
-      <c r="AW12" s="12"/>
-      <c r="AX12" s="14"/>
+      <c r="AY12" s="12"/>
       <c r="AZ12" s="14"/>
-      <c r="BA12" s="14"/>
       <c r="BB12" s="14"/>
+      <c r="BC12" s="14"/>
       <c r="BD12" s="14"/>
-      <c r="BE12" s="14"/>
       <c r="BF12" s="14"/>
+      <c r="BG12" s="14"/>
       <c r="BH12" s="14"/>
-      <c r="BI12" s="14"/>
       <c r="BJ12" s="14"/>
-      <c r="BL12" s="19" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="13" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BK12" s="14"/>
+      <c r="BL12" s="14"/>
+      <c r="BN12" s="19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C13" s="15">
         <v>5.7728759999999997E-2</v>
@@ -4352,7 +4444,7 @@
         <v>GGM</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J13" s="12">
         <v>0.99991370000000002</v>
@@ -4365,7 +4457,7 @@
         <v>-176866.9877</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O13" s="12">
         <v>-327.19220100000001</v>
@@ -4374,7 +4466,7 @@
         <v>46909600</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S13" s="12">
         <v>-4.0384000000000003E-2</v>
@@ -4383,7 +4475,7 @@
         <v>2603995</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W13" s="31">
         <v>0.99999099999999996</v>
@@ -4392,7 +4484,7 @@
         <v>7591.1932999999999</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AA13" s="31">
         <v>0.99989799999999995</v>
@@ -4401,7 +4493,7 @@
         <v>26091.076145999999</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AE13" s="14">
         <f t="shared" si="3"/>
@@ -4431,34 +4523,34 @@
         <f t="shared" si="8"/>
         <v>26091.076145999999</v>
       </c>
-      <c r="AM13" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="AN13" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AO13" s="12">
+      <c r="AO13" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="AP13" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AQ13" s="12">
         <v>0.99908359999999996</v>
       </c>
-      <c r="AP13" s="14">
+      <c r="AR13" s="14">
         <v>12493.0429</v>
       </c>
-      <c r="AV13" s="14"/>
-      <c r="AW13" s="14"/>
       <c r="AX13" s="14"/>
+      <c r="AY13" s="14"/>
       <c r="AZ13" s="14"/>
-      <c r="BA13" s="14"/>
       <c r="BB13" s="14"/>
+      <c r="BC13" s="14"/>
       <c r="BD13" s="14"/>
-      <c r="BE13" s="14"/>
       <c r="BF13" s="14"/>
+      <c r="BG13" s="14"/>
       <c r="BH13" s="14"/>
-      <c r="BI13" s="14"/>
       <c r="BJ13" s="14"/>
-    </row>
-    <row r="14" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BK13" s="14"/>
+      <c r="BL13" s="14"/>
+    </row>
+    <row r="14" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C14" s="16">
         <v>1.795393E-2</v>
@@ -4477,7 +4569,7 @@
         <v>GGM</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J14" s="18">
         <v>0.99998960000000003</v>
@@ -4490,7 +4582,7 @@
         <v>-46880.9761</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O14" s="18">
         <v>2.6889E-2</v>
@@ -4499,7 +4591,7 @@
         <v>353453</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S14" s="18">
         <v>0.87112000000000001</v>
@@ -4508,7 +4600,7 @@
         <v>125949</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W14" s="32">
         <v>0.99999000000000005</v>
@@ -4517,7 +4609,7 @@
         <v>1140.2147070000001</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA14" s="32">
         <v>0.99961699999999998</v>
@@ -4526,7 +4618,7 @@
         <v>7011.0990389999997</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE14" s="14">
         <f t="shared" si="3"/>
@@ -4556,37 +4648,37 @@
         <f t="shared" si="8"/>
         <v>7011.0990389999997</v>
       </c>
-      <c r="AM14" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="AN14" s="6" t="s">
+      <c r="AO14" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="AP14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AO14" s="18">
+      <c r="AQ14" s="18">
         <v>0.99956429999999996</v>
       </c>
-      <c r="AP14" s="17">
+      <c r="AR14" s="17">
         <v>8614.8230000000003</v>
       </c>
-      <c r="AV14" s="14"/>
-      <c r="AW14" s="14"/>
       <c r="AX14" s="14"/>
+      <c r="AY14" s="14"/>
       <c r="AZ14" s="14"/>
-      <c r="BA14" s="14"/>
       <c r="BB14" s="14"/>
+      <c r="BC14" s="14"/>
       <c r="BD14" s="14"/>
-      <c r="BE14" s="14"/>
       <c r="BF14" s="14"/>
+      <c r="BG14" s="14"/>
       <c r="BH14" s="14"/>
-      <c r="BI14" s="14"/>
       <c r="BJ14" s="14"/>
-      <c r="BL14" s="13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BK14" s="14"/>
+      <c r="BL14" s="14"/>
+      <c r="BN14" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C15" s="15">
         <v>0.97698001999999995</v>
@@ -4605,7 +4697,7 @@
         <v>GGM</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J15" s="12">
         <v>0.99999769999999999</v>
@@ -4618,7 +4710,7 @@
         <v>-4022279.7900999999</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O15" s="12">
         <v>0.29647899999999999</v>
@@ -4627,7 +4719,7 @@
         <v>30580360</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S15" s="12">
         <v>0.833893</v>
@@ -4636,7 +4728,7 @@
         <v>14859300</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="W15" s="31">
         <v>0.99999800000000005</v>
@@ -4645,7 +4737,7 @@
         <v>47866.562242</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AA15" s="31">
         <v>0.99987199999999998</v>
@@ -4654,7 +4746,7 @@
         <v>412581.51297400001</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE15" s="14">
         <f t="shared" si="3"/>
@@ -4684,22 +4776,22 @@
         <f t="shared" si="8"/>
         <v>412581.51297400001</v>
       </c>
-      <c r="AV15" s="14"/>
-      <c r="AW15" s="14"/>
       <c r="AX15" s="14"/>
+      <c r="AY15" s="14"/>
       <c r="AZ15" s="14"/>
-      <c r="BA15" s="14"/>
       <c r="BB15" s="14"/>
+      <c r="BC15" s="14"/>
       <c r="BD15" s="14"/>
-      <c r="BE15" s="14"/>
       <c r="BF15" s="14"/>
+      <c r="BG15" s="14"/>
       <c r="BH15" s="14"/>
-      <c r="BI15" s="14"/>
       <c r="BJ15" s="14"/>
-    </row>
-    <row r="16" spans="2:70" x14ac:dyDescent="0.3">
+      <c r="BK15" s="14"/>
+      <c r="BL15" s="14"/>
+    </row>
+    <row r="16" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C16" s="16">
         <v>5.2056409999999997E-2</v>
@@ -4718,7 +4810,7 @@
         <v>GGM</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J16" s="18">
         <v>0.98195189999999999</v>
@@ -4731,7 +4823,7 @@
         <v>-188.91730000000098</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O16" s="18">
         <v>0.52243200000000001</v>
@@ -4740,7 +4832,7 @@
         <v>283382.09999999998</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="S16" s="18">
         <v>0.96743000000000001</v>
@@ -4749,7 +4841,7 @@
         <v>73683.27</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="W16" s="32">
         <v>0.999996</v>
@@ -4758,7 +4850,7 @@
         <v>829.90016600000001</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AA16" s="32">
         <v>0.99970099999999995</v>
@@ -4767,7 +4859,7 @@
         <v>7087.1279500000001</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AE16" s="14">
         <f t="shared" si="3"/>
@@ -4797,208 +4889,249 @@
         <f t="shared" si="8"/>
         <v>7087.1279500000001</v>
       </c>
-      <c r="AV16" s="14"/>
-      <c r="AW16" s="14"/>
       <c r="AX16" s="14"/>
+      <c r="AY16" s="14"/>
       <c r="AZ16" s="14"/>
-      <c r="BA16" s="14"/>
       <c r="BB16" s="14"/>
+      <c r="BC16" s="14"/>
       <c r="BD16" s="14"/>
-      <c r="BE16" s="14"/>
       <c r="BF16" s="14"/>
+      <c r="BG16" s="14"/>
       <c r="BH16" s="14"/>
-      <c r="BI16" s="14"/>
       <c r="BJ16" s="14"/>
-      <c r="BL16" s="9" t="s">
+      <c r="BK16" s="14"/>
+      <c r="BL16" s="14"/>
+      <c r="BN16" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="BO16" s="9" t="str">
+        <f>+BO6</f>
+        <v>SIR</v>
+      </c>
+      <c r="BP16" s="9" t="str">
+        <f t="shared" ref="BP16:BU16" si="13">+BP6</f>
+        <v>SEIR</v>
+      </c>
+      <c r="BQ16" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>BM</v>
+      </c>
+      <c r="BR16" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>GGM</v>
+      </c>
+      <c r="BS16" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>ARIMA</v>
+      </c>
+      <c r="BT16" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>GGM+Refinement</v>
+      </c>
+      <c r="BU16" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>Prophet</v>
+      </c>
+    </row>
+    <row r="17" spans="2:73" x14ac:dyDescent="0.3">
+      <c r="BJ17" s="14"/>
+      <c r="BK17" s="14"/>
+      <c r="BL17" s="14"/>
+      <c r="BN17" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="BM16" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN16" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="BO16" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="BP16" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BQ16" s="9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="17" spans="2:69" x14ac:dyDescent="0.3">
-      <c r="BL17" s="1" t="s">
+      <c r="BO17" s="12">
+        <f>+_xlfn.XLOOKUP($BN17,$AX$7:$AX$9,$AY$7:$AY$9)</f>
+        <v>0.98572300000000002</v>
+      </c>
+      <c r="BP17" s="12">
+        <f>+_xlfn.XLOOKUP(BN17,$BB$7:$BB$9,$BC$7:$BC$9)</f>
+        <v>0.99224599999999996</v>
+      </c>
+      <c r="BQ17" s="12">
+        <f>+AQ7</f>
+        <v>-0.25174930000000001</v>
+      </c>
+      <c r="BR17" s="12">
+        <f>+AQ8</f>
+        <v>0.99300429999999995</v>
+      </c>
+      <c r="BS17" s="12"/>
+      <c r="BT17" s="12">
+        <f>+AU7</f>
+        <v>0.99999979999999999</v>
+      </c>
+      <c r="BU17" s="12"/>
+    </row>
+    <row r="18" spans="2:73" x14ac:dyDescent="0.3">
+      <c r="BJ18" s="14"/>
+      <c r="BK18" s="14"/>
+      <c r="BL18" s="14"/>
+      <c r="BN18" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="BM17" s="12">
-        <f>+_xlfn.XLOOKUP($BL17,$AV$7:$AV$9,$AW$7:$AW$9)</f>
-        <v>0.98572300000000002</v>
-      </c>
-      <c r="BN17" s="12">
-        <f>+_xlfn.XLOOKUP(BL17,$AZ$7:$AZ$9,$BA$7:$BA$9)</f>
-        <v>0.99224599999999996</v>
-      </c>
-      <c r="BO17" s="12">
-        <f>+AO7</f>
-        <v>-0.25174930000000001</v>
-      </c>
-      <c r="BP17" s="12">
-        <f>+AO8</f>
-        <v>0.99300429999999995</v>
-      </c>
-      <c r="BQ17" s="12">
-        <f>+AS7</f>
-        <v>0.99999979999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="2:69" x14ac:dyDescent="0.3">
-      <c r="BL18" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="BM18" s="18">
-        <f>+_xlfn.XLOOKUP($BL18,$AV$7:$AV$9,$AW$7:$AW$9)</f>
+      <c r="BO18" s="18">
+        <f>+_xlfn.XLOOKUP($BN18,$AX$7:$AX$9,$AY$7:$AY$9)</f>
         <v>0.94224399999999997</v>
       </c>
-      <c r="BN18" s="18">
-        <f t="shared" ref="BN18:BN19" si="11">+_xlfn.XLOOKUP(BL18,$AZ$7:$AZ$9,$BA$7:$BA$9)</f>
+      <c r="BP18" s="18">
+        <f t="shared" ref="BP18:BP19" si="14">+_xlfn.XLOOKUP(BN18,$BB$7:$BB$9,$BC$7:$BC$9)</f>
         <v>0.91772100000000001</v>
       </c>
-      <c r="BO18" s="18">
-        <f>+AO9</f>
+      <c r="BQ18" s="18">
+        <f>+AQ9</f>
         <v>0.99683809999999995</v>
       </c>
-      <c r="BP18" s="18">
-        <f>+AO10</f>
+      <c r="BR18" s="18">
+        <f>+AQ10</f>
         <v>0.9985077</v>
       </c>
-      <c r="BQ18" s="18">
-        <f>+AS8</f>
+      <c r="BS18" s="18"/>
+      <c r="BT18" s="18">
+        <f>+AU8</f>
         <v>0.99997420000000004</v>
       </c>
-    </row>
-    <row r="19" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="BU18" s="18"/>
+    </row>
+    <row r="19" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T19" s="21"/>
       <c r="V19" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
-      <c r="BL19" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BM19" s="12">
-        <f>+_xlfn.XLOOKUP($BL19,$AV$7:$AV$9,$AW$7:$AW$9)</f>
+      <c r="BJ19" s="14"/>
+      <c r="BK19" s="14"/>
+      <c r="BL19" s="14"/>
+      <c r="BN19" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="BO19" s="12">
+        <f>+_xlfn.XLOOKUP($BN19,$AX$7:$AX$9,$AY$7:$AY$9)</f>
         <v>0.98843700000000001</v>
       </c>
-      <c r="BN19" s="12">
-        <f t="shared" si="11"/>
+      <c r="BP19" s="12">
+        <f t="shared" si="14"/>
         <v>0.97706400000000004</v>
       </c>
-      <c r="BO19" s="12">
-        <f>+AO11</f>
+      <c r="BQ19" s="12">
+        <f>+AQ11</f>
         <v>0.99021340000000002</v>
       </c>
-      <c r="BP19" s="12">
-        <f>+AO12</f>
+      <c r="BR19" s="12">
+        <f>+AQ12</f>
         <v>0.99795840000000002</v>
       </c>
-      <c r="BQ19" s="12">
-        <f>+AS9</f>
+      <c r="BS19" s="12"/>
+      <c r="BT19" s="12">
+        <f>+AU9</f>
         <v>0.9999806</v>
       </c>
-    </row>
-    <row r="20" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="BU19" s="12"/>
+    </row>
+    <row r="20" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="T20" s="21"/>
-    </row>
-    <row r="21" spans="2:69" x14ac:dyDescent="0.3">
+      <c r="BJ20" s="14"/>
+      <c r="BK20" s="14"/>
+      <c r="BL20" s="14"/>
+      <c r="BN20" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO20" s="18"/>
+      <c r="BP20" s="18"/>
+      <c r="BQ20" s="18"/>
+      <c r="BR20" s="18"/>
+      <c r="BS20" s="18"/>
+      <c r="BT20" s="18"/>
+      <c r="BU20" s="18"/>
+    </row>
+    <row r="21" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B21" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="E21" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>170</v>
-      </c>
       <c r="G21" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J21" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="K21" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="K21" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="L21" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O21" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="P21" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="P21" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="R21" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S21" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="T21" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="T21" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="V21" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W21" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="X21" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="X21" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="Z21" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA21" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB21" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AB21" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="AD21" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AE21" s="9" t="s">
         <v>138</v>
@@ -5007,24 +5140,27 @@
         <v>139</v>
       </c>
       <c r="AG21" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AH21" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AI21" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ21" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AK21" s="9" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="22" spans="2:69" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+      <c r="BJ21" s="14"/>
+      <c r="BK21" s="14"/>
+      <c r="BL21" s="14"/>
+    </row>
+    <row r="22" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C22" s="15">
         <v>0.99309789999999998</v>
@@ -5043,7 +5179,7 @@
         <v>GGM</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J22" s="12">
         <v>0.99997320000000001</v>
@@ -5056,7 +5192,7 @@
         <v>-812345.71199999994</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O22" s="12">
         <v>0.82512600000000003</v>
@@ -5065,7 +5201,7 @@
         <v>5285818</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S22" s="12">
         <v>0.64468300000000001</v>
@@ -5074,7 +5210,7 @@
         <v>7558374</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="W22" s="31">
         <v>0.99996799999999997</v>
@@ -5083,7 +5219,7 @@
         <v>72886.599426000001</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AA22" s="31">
         <v>0.998919</v>
@@ -5092,7 +5228,7 @@
         <v>424624.7</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AE22" s="14">
         <f>+_xlfn.XLOOKUP($AD22,N$22:N$31,P$22:P$31)</f>
@@ -5123,9 +5259,9 @@
         <v>424624.7</v>
       </c>
     </row>
-    <row r="23" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C23" s="16">
         <v>0.98500410000000005</v>
@@ -5140,11 +5276,11 @@
         <v>191678.16</v>
       </c>
       <c r="G23" s="6" t="str">
-        <f t="shared" ref="G23:G31" si="12">+IF(F23&lt;D23,"GGM","BM")</f>
+        <f t="shared" ref="G23:G31" si="15">+IF(F23&lt;D23,"GGM","BM")</f>
         <v>GGM</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J23" s="18">
         <v>0.99997939999999996</v>
@@ -5153,11 +5289,11 @@
         <v>7970.5929999999998</v>
       </c>
       <c r="L23" s="17">
-        <f t="shared" ref="L23:L31" si="13">+K23-_xlfn.XLOOKUP(I23,B$22:B$31,F$22:F$31)</f>
+        <f t="shared" ref="L23:L31" si="16">+K23-_xlfn.XLOOKUP(I23,B$22:B$31,F$22:F$31)</f>
         <v>-183707.56700000001</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O23" s="18">
         <v>0.85929699999999998</v>
@@ -5166,7 +5302,7 @@
         <v>655919.19999999995</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S23" s="18">
         <v>0.86842799999999998</v>
@@ -5175,7 +5311,7 @@
         <v>634278.5</v>
       </c>
       <c r="V23" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="W23" s="32">
         <v>0.999977</v>
@@ -5184,7 +5320,7 @@
         <v>8395.1301469999999</v>
       </c>
       <c r="Z23" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA23" s="32">
         <v>0.99666699999999997</v>
@@ -5193,52 +5329,52 @@
         <v>101494.2</v>
       </c>
       <c r="AD23" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="AE23" s="14">
+        <f t="shared" ref="AE23:AE31" si="17">+_xlfn.XLOOKUP($AD23,N$22:N$31,P$22:P$31)</f>
+        <v>655919.19999999995</v>
+      </c>
+      <c r="AF23" s="14">
+        <f t="shared" ref="AF23:AF31" si="18">+_xlfn.XLOOKUP($AD23,R$22:R$31,T$22:T$31)</f>
+        <v>634278.5</v>
+      </c>
+      <c r="AG23" s="14">
+        <f t="shared" ref="AG23:AG31" si="19">+_xlfn.XLOOKUP($AD23,B$22:B$31,D$22:D$31)</f>
+        <v>215298.15</v>
+      </c>
+      <c r="AH23" s="14">
+        <f t="shared" ref="AH23:AH31" si="20">+_xlfn.XLOOKUP($AD23,B$22:B$31,F$22:F$31)</f>
+        <v>191678.16</v>
+      </c>
+      <c r="AI23" s="14">
+        <f t="shared" ref="AI23:AI31" si="21">+_xlfn.XLOOKUP($AD23,V$22:V$31,X$22:X$31)</f>
+        <v>8395.1301469999999</v>
+      </c>
+      <c r="AJ23" s="14">
+        <f t="shared" ref="AJ23:AJ31" si="22">+_xlfn.XLOOKUP($AD23,I$22:I$31,K$22:K$31)</f>
+        <v>7970.5929999999998</v>
+      </c>
+      <c r="AK23" s="14">
+        <f t="shared" ref="AK23:AK31" si="23">+_xlfn.XLOOKUP(AD23,$Z$22:$Z$31,$AB$22:$AB$31)</f>
+        <v>101494.2</v>
+      </c>
+      <c r="AX23" s="27"/>
+      <c r="AY23" s="27"/>
+      <c r="AZ23" s="27"/>
+      <c r="BB23" s="27"/>
+      <c r="BC23" s="27"/>
+      <c r="BD23" s="27"/>
+      <c r="BF23" s="27"/>
+      <c r="BG23" s="27"/>
+      <c r="BH23" s="27"/>
+      <c r="BJ23" s="27"/>
+      <c r="BK23" s="27"/>
+      <c r="BL23" s="27"/>
+    </row>
+    <row r="24" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="AE23" s="14">
-        <f t="shared" ref="AE23:AE31" si="14">+_xlfn.XLOOKUP($AD23,N$22:N$31,P$22:P$31)</f>
-        <v>655919.19999999995</v>
-      </c>
-      <c r="AF23" s="14">
-        <f t="shared" ref="AF23:AF31" si="15">+_xlfn.XLOOKUP($AD23,R$22:R$31,T$22:T$31)</f>
-        <v>634278.5</v>
-      </c>
-      <c r="AG23" s="14">
-        <f t="shared" ref="AG23:AG31" si="16">+_xlfn.XLOOKUP($AD23,B$22:B$31,D$22:D$31)</f>
-        <v>215298.15</v>
-      </c>
-      <c r="AH23" s="14">
-        <f t="shared" ref="AH23:AH31" si="17">+_xlfn.XLOOKUP($AD23,B$22:B$31,F$22:F$31)</f>
-        <v>191678.16</v>
-      </c>
-      <c r="AI23" s="14">
-        <f t="shared" ref="AI23:AI31" si="18">+_xlfn.XLOOKUP($AD23,V$22:V$31,X$22:X$31)</f>
-        <v>8395.1301469999999</v>
-      </c>
-      <c r="AJ23" s="14">
-        <f t="shared" ref="AJ23:AJ31" si="19">+_xlfn.XLOOKUP($AD23,I$22:I$31,K$22:K$31)</f>
-        <v>7970.5929999999998</v>
-      </c>
-      <c r="AK23" s="14">
-        <f t="shared" ref="AK23:AK31" si="20">+_xlfn.XLOOKUP(AD23,$Z$22:$Z$31,$AB$22:$AB$31)</f>
-        <v>101494.2</v>
-      </c>
-      <c r="AV23" s="27"/>
-      <c r="AW23" s="27"/>
-      <c r="AX23" s="27"/>
-      <c r="AZ23" s="27"/>
-      <c r="BA23" s="27"/>
-      <c r="BB23" s="27"/>
-      <c r="BD23" s="27"/>
-      <c r="BE23" s="27"/>
-      <c r="BF23" s="27"/>
-      <c r="BH23" s="27"/>
-      <c r="BI23" s="27"/>
-      <c r="BJ23" s="27"/>
-    </row>
-    <row r="24" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="C24" s="15">
         <v>0.99486560000000002</v>
@@ -5253,11 +5389,11 @@
         <v>170016.12</v>
       </c>
       <c r="G24" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J24" s="12">
         <v>0.9999827</v>
@@ -5266,11 +5402,11 @@
         <v>10259.941000000001</v>
       </c>
       <c r="L24" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-159756.179</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O24" s="12">
         <v>0.91229700000000002</v>
@@ -5279,7 +5415,7 @@
         <v>711743.3</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S24" s="12">
         <v>0.43064400000000003</v>
@@ -5288,7 +5424,7 @@
         <v>1813809</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W24" s="31">
         <v>0.99997899999999995</v>
@@ -5297,7 +5433,7 @@
         <v>11331.678796</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AA24" s="31">
         <v>0.99987199999999998</v>
@@ -5306,52 +5442,52 @@
         <v>27934.33</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AE24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>711743.3</v>
       </c>
       <c r="AF24" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1813809</v>
       </c>
       <c r="AG24" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>176803.48</v>
       </c>
       <c r="AH24" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>170016.12</v>
       </c>
       <c r="AI24" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>11331.678796</v>
       </c>
       <c r="AJ24" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>10259.941000000001</v>
       </c>
       <c r="AK24" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>27934.33</v>
       </c>
-      <c r="AV24" s="27"/>
-      <c r="AW24" s="28"/>
-      <c r="AX24" s="28"/>
+      <c r="AX24" s="27"/>
+      <c r="AY24" s="28"/>
       <c r="AZ24" s="28"/>
-      <c r="BA24" s="28"/>
       <c r="BB24" s="28"/>
+      <c r="BC24" s="28"/>
       <c r="BD24" s="28"/>
-      <c r="BE24" s="28"/>
       <c r="BF24" s="28"/>
+      <c r="BG24" s="28"/>
       <c r="BH24" s="28"/>
-      <c r="BI24" s="28"/>
       <c r="BJ24" s="28"/>
-    </row>
-    <row r="25" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="BK24" s="28"/>
+      <c r="BL24" s="28"/>
+    </row>
+    <row r="25" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="16">
         <v>0.98980849999999998</v>
@@ -5366,11 +5502,11 @@
         <v>20254.93</v>
       </c>
       <c r="G25" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J25" s="18">
         <v>0.99986940000000002</v>
@@ -5379,11 +5515,11 @@
         <v>2682.71</v>
       </c>
       <c r="L25" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-17572.22</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O25" s="18">
         <v>0.81773499999999999</v>
@@ -5392,7 +5528,7 @@
         <v>96842.15</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S25" s="18">
         <v>-0.70466200000000001</v>
@@ -5401,7 +5537,7 @@
         <v>300031.3</v>
       </c>
       <c r="V25" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="W25" s="32">
         <v>0.99985199999999996</v>
@@ -5410,7 +5546,7 @@
         <v>2856.3407999999999</v>
       </c>
       <c r="Z25" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AA25" s="32">
         <v>0.99764399999999998</v>
@@ -5419,52 +5555,52 @@
         <v>11391.69</v>
       </c>
       <c r="AD25" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AE25" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>96842.15</v>
       </c>
       <c r="AF25" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>300031.3</v>
       </c>
       <c r="AG25" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>23695.26</v>
       </c>
       <c r="AH25" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>20254.93</v>
       </c>
       <c r="AI25" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2856.3407999999999</v>
       </c>
       <c r="AJ25" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>2682.71</v>
       </c>
       <c r="AK25" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>11391.69</v>
       </c>
-      <c r="AV25" s="27"/>
-      <c r="AW25" s="28"/>
-      <c r="AX25" s="28"/>
+      <c r="AX25" s="27"/>
+      <c r="AY25" s="28"/>
       <c r="AZ25" s="28"/>
-      <c r="BA25" s="28"/>
       <c r="BB25" s="28"/>
+      <c r="BC25" s="28"/>
       <c r="BD25" s="28"/>
-      <c r="BE25" s="28"/>
       <c r="BF25" s="28"/>
+      <c r="BG25" s="28"/>
       <c r="BH25" s="28"/>
-      <c r="BI25" s="28"/>
       <c r="BJ25" s="28"/>
-    </row>
-    <row r="26" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="BK25" s="28"/>
+      <c r="BL25" s="28"/>
+    </row>
+    <row r="26" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C26" s="15">
         <v>0.99044909999999997</v>
@@ -5479,11 +5615,11 @@
         <v>1270365.45</v>
       </c>
       <c r="G26" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J26" s="12">
         <v>0.99998489999999995</v>
@@ -5492,11 +5628,11 @@
         <v>54571.813999999998</v>
       </c>
       <c r="L26" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-1215793.6359999999</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O26" s="12">
         <v>0.98488399999999998</v>
@@ -5505,7 +5641,7 @@
         <v>1726783</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S26" s="12">
         <v>0.98622900000000002</v>
@@ -5514,7 +5650,7 @@
         <v>1646926</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="W26" s="31">
         <v>0.99998200000000004</v>
@@ -5523,7 +5659,7 @@
         <v>59096.011952000001</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AA26" s="31">
         <v>0.99986600000000003</v>
@@ -5532,52 +5668,52 @@
         <v>162463.20000000001</v>
       </c>
       <c r="AD26" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="AE26" s="14">
+        <f t="shared" si="17"/>
+        <v>1726783</v>
+      </c>
+      <c r="AF26" s="14">
+        <f t="shared" si="18"/>
+        <v>1646926</v>
+      </c>
+      <c r="AG26" s="14">
+        <f t="shared" si="19"/>
+        <v>1370516.61</v>
+      </c>
+      <c r="AH26" s="14">
+        <f t="shared" si="20"/>
+        <v>1270365.45</v>
+      </c>
+      <c r="AI26" s="14">
+        <f t="shared" si="21"/>
+        <v>59096.011952000001</v>
+      </c>
+      <c r="AJ26" s="14">
+        <f t="shared" si="22"/>
+        <v>54571.813999999998</v>
+      </c>
+      <c r="AK26" s="14">
+        <f t="shared" si="23"/>
+        <v>162463.20000000001</v>
+      </c>
+      <c r="AX26" s="27"/>
+      <c r="AY26" s="28"/>
+      <c r="AZ26" s="28"/>
+      <c r="BB26" s="28"/>
+      <c r="BC26" s="28"/>
+      <c r="BD26" s="28"/>
+      <c r="BF26" s="28"/>
+      <c r="BG26" s="28"/>
+      <c r="BH26" s="28"/>
+      <c r="BJ26" s="28"/>
+      <c r="BK26" s="28"/>
+      <c r="BL26" s="28"/>
+    </row>
+    <row r="27" spans="2:73" x14ac:dyDescent="0.3">
+      <c r="B27" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="AE26" s="14">
-        <f t="shared" si="14"/>
-        <v>1726783</v>
-      </c>
-      <c r="AF26" s="14">
-        <f t="shared" si="15"/>
-        <v>1646926</v>
-      </c>
-      <c r="AG26" s="14">
-        <f t="shared" si="16"/>
-        <v>1370516.61</v>
-      </c>
-      <c r="AH26" s="14">
-        <f t="shared" si="17"/>
-        <v>1270365.45</v>
-      </c>
-      <c r="AI26" s="14">
-        <f t="shared" si="18"/>
-        <v>59096.011952000001</v>
-      </c>
-      <c r="AJ26" s="14">
-        <f t="shared" si="19"/>
-        <v>54571.813999999998</v>
-      </c>
-      <c r="AK26" s="14">
-        <f t="shared" si="20"/>
-        <v>162463.20000000001</v>
-      </c>
-      <c r="AV26" s="27"/>
-      <c r="AW26" s="28"/>
-      <c r="AX26" s="28"/>
-      <c r="AZ26" s="28"/>
-      <c r="BA26" s="28"/>
-      <c r="BB26" s="28"/>
-      <c r="BD26" s="28"/>
-      <c r="BE26" s="28"/>
-      <c r="BF26" s="28"/>
-      <c r="BH26" s="28"/>
-      <c r="BI26" s="28"/>
-      <c r="BJ26" s="28"/>
-    </row>
-    <row r="27" spans="2:69" x14ac:dyDescent="0.3">
-      <c r="B27" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C27" s="16">
         <v>0.98537799999999998</v>
@@ -5592,11 +5728,11 @@
         <v>962242.14</v>
       </c>
       <c r="G27" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J27" s="18">
         <v>0.99998299999999996</v>
@@ -5605,11 +5741,11 @@
         <v>37554.368000000002</v>
       </c>
       <c r="L27" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-924687.772</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O27" s="18">
         <v>0.94516</v>
@@ -5618,7 +5754,7 @@
         <v>2120841</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S27" s="18">
         <v>0.94915899999999997</v>
@@ -5627,7 +5763,7 @@
         <v>2056768</v>
       </c>
       <c r="V27" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W27" s="32">
         <v>0.99997999999999998</v>
@@ -5636,7 +5772,7 @@
         <v>40276.492481000001</v>
       </c>
       <c r="Z27" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AA27" s="32">
         <v>0.99753099999999995</v>
@@ -5645,40 +5781,40 @@
         <v>453190.5</v>
       </c>
       <c r="AD27" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="AE27" s="14">
+        <f t="shared" si="17"/>
+        <v>2120841</v>
+      </c>
+      <c r="AF27" s="14">
+        <f t="shared" si="18"/>
+        <v>2056768</v>
+      </c>
+      <c r="AG27" s="14">
+        <f t="shared" si="19"/>
+        <v>1102885.5</v>
+      </c>
+      <c r="AH27" s="14">
+        <f t="shared" si="20"/>
+        <v>962242.14</v>
+      </c>
+      <c r="AI27" s="14">
+        <f t="shared" si="21"/>
+        <v>40276.492481000001</v>
+      </c>
+      <c r="AJ27" s="14">
+        <f t="shared" si="22"/>
+        <v>37554.368000000002</v>
+      </c>
+      <c r="AK27" s="14">
+        <f t="shared" si="23"/>
+        <v>453190.5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:73" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="AE27" s="14">
-        <f t="shared" si="14"/>
-        <v>2120841</v>
-      </c>
-      <c r="AF27" s="14">
-        <f t="shared" si="15"/>
-        <v>2056768</v>
-      </c>
-      <c r="AG27" s="14">
-        <f t="shared" si="16"/>
-        <v>1102885.5</v>
-      </c>
-      <c r="AH27" s="14">
-        <f t="shared" si="17"/>
-        <v>962242.14</v>
-      </c>
-      <c r="AI27" s="14">
-        <f t="shared" si="18"/>
-        <v>40276.492481000001</v>
-      </c>
-      <c r="AJ27" s="14">
-        <f t="shared" si="19"/>
-        <v>37554.368000000002</v>
-      </c>
-      <c r="AK27" s="14">
-        <f t="shared" si="20"/>
-        <v>453190.5</v>
-      </c>
-    </row>
-    <row r="28" spans="2:69" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="C28" s="15">
         <v>0.99328240000000001</v>
@@ -5693,11 +5829,11 @@
         <v>177553.42</v>
       </c>
       <c r="G28" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J28" s="12">
         <v>0.99995199999999995</v>
@@ -5706,11 +5842,11 @@
         <v>18001.951000000001</v>
       </c>
       <c r="L28" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-159551.46900000001</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O28" s="12">
         <v>0.84834900000000002</v>
@@ -5719,7 +5855,7 @@
         <v>999266.5</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S28" s="12">
         <v>-0.34762500000000002</v>
@@ -5728,7 +5864,7 @@
         <v>2976087</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W28" s="31">
         <v>0.99994000000000005</v>
@@ -5737,7 +5873,7 @@
         <v>20204.683582000001</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AA28" s="31">
         <v>0.99860599999999999</v>
@@ -5746,40 +5882,40 @@
         <v>97029.98</v>
       </c>
       <c r="AD28" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE28" s="14">
+        <f t="shared" si="17"/>
+        <v>999266.5</v>
+      </c>
+      <c r="AF28" s="14">
+        <f t="shared" si="18"/>
+        <v>2976087</v>
+      </c>
+      <c r="AG28" s="14">
+        <f t="shared" si="19"/>
+        <v>212970.27</v>
+      </c>
+      <c r="AH28" s="14">
+        <f t="shared" si="20"/>
+        <v>177553.42</v>
+      </c>
+      <c r="AI28" s="14">
+        <f t="shared" si="21"/>
+        <v>20204.683582000001</v>
+      </c>
+      <c r="AJ28" s="14">
+        <f t="shared" si="22"/>
+        <v>18001.951000000001</v>
+      </c>
+      <c r="AK28" s="14">
+        <f t="shared" si="23"/>
+        <v>97029.98</v>
+      </c>
+    </row>
+    <row r="29" spans="2:73" x14ac:dyDescent="0.3">
+      <c r="B29" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="AE28" s="14">
-        <f t="shared" si="14"/>
-        <v>999266.5</v>
-      </c>
-      <c r="AF28" s="14">
-        <f t="shared" si="15"/>
-        <v>2976087</v>
-      </c>
-      <c r="AG28" s="14">
-        <f t="shared" si="16"/>
-        <v>212970.27</v>
-      </c>
-      <c r="AH28" s="14">
-        <f t="shared" si="17"/>
-        <v>177553.42</v>
-      </c>
-      <c r="AI28" s="14">
-        <f t="shared" si="18"/>
-        <v>20204.683582000001</v>
-      </c>
-      <c r="AJ28" s="14">
-        <f t="shared" si="19"/>
-        <v>18001.951000000001</v>
-      </c>
-      <c r="AK28" s="14">
-        <f t="shared" si="20"/>
-        <v>97029.98</v>
-      </c>
-    </row>
-    <row r="29" spans="2:69" x14ac:dyDescent="0.3">
-      <c r="B29" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="C29" s="16">
         <v>0.98214460000000003</v>
@@ -5794,11 +5930,11 @@
         <v>41689.589999999997</v>
       </c>
       <c r="G29" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J29" s="18">
         <v>0.9999439</v>
@@ -5807,11 +5943,11 @@
         <v>2688.72</v>
       </c>
       <c r="L29" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-39000.869999999995</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O29" s="18">
         <v>0.83975299999999997</v>
@@ -5820,7 +5956,7 @@
         <v>140633.70000000001</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S29" s="18">
         <v>0.86644399999999999</v>
@@ -5829,7 +5965,7 @@
         <v>128388.6</v>
       </c>
       <c r="V29" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W29" s="32">
         <v>0.99993799999999999</v>
@@ -5838,7 +5974,7 @@
         <v>2835.1556179999998</v>
       </c>
       <c r="Z29" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA29" s="32">
         <v>0.99784799999999996</v>
@@ -5847,40 +5983,40 @@
         <v>16657.2</v>
       </c>
       <c r="AD29" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE29" s="14">
+        <f t="shared" si="17"/>
+        <v>140633.70000000001</v>
+      </c>
+      <c r="AF29" s="14">
+        <f t="shared" si="18"/>
+        <v>128388.6</v>
+      </c>
+      <c r="AG29" s="14">
+        <f t="shared" si="19"/>
+        <v>47981.11</v>
+      </c>
+      <c r="AH29" s="14">
+        <f t="shared" si="20"/>
+        <v>41689.589999999997</v>
+      </c>
+      <c r="AI29" s="14">
+        <f t="shared" si="21"/>
+        <v>2835.1556179999998</v>
+      </c>
+      <c r="AJ29" s="14">
+        <f t="shared" si="22"/>
+        <v>2688.72</v>
+      </c>
+      <c r="AK29" s="14">
+        <f t="shared" si="23"/>
+        <v>16657.2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:73" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="AE29" s="14">
-        <f t="shared" si="14"/>
-        <v>140633.70000000001</v>
-      </c>
-      <c r="AF29" s="14">
-        <f t="shared" si="15"/>
-        <v>128388.6</v>
-      </c>
-      <c r="AG29" s="14">
-        <f t="shared" si="16"/>
-        <v>47981.11</v>
-      </c>
-      <c r="AH29" s="14">
-        <f t="shared" si="17"/>
-        <v>41689.589999999997</v>
-      </c>
-      <c r="AI29" s="14">
-        <f t="shared" si="18"/>
-        <v>2835.1556179999998</v>
-      </c>
-      <c r="AJ29" s="14">
-        <f t="shared" si="19"/>
-        <v>2688.72</v>
-      </c>
-      <c r="AK29" s="14">
-        <f t="shared" si="20"/>
-        <v>16657.2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:69" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="C30" s="15">
         <v>0.97719889999999998</v>
@@ -5895,11 +6031,11 @@
         <v>55105.7</v>
       </c>
       <c r="G30" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J30" s="12">
         <v>0.99001130000000004</v>
@@ -5908,11 +6044,11 @@
         <v>3653520.236</v>
       </c>
       <c r="L30" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-4.0000001899898052E-3</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O30" s="12">
         <v>0.83721299999999998</v>
@@ -5921,7 +6057,7 @@
         <v>14749160</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S30" s="12">
         <v>0.84466699999999995</v>
@@ -5930,7 +6066,7 @@
         <v>14407510</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="W30" s="31">
         <v>0.999973</v>
@@ -5939,7 +6075,7 @@
         <v>189197.220477</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AA30" s="31">
         <v>0.99802000000000002</v>
@@ -5948,40 +6084,40 @@
         <v>1626782</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE30" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>14749160</v>
       </c>
       <c r="AF30" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>14407510</v>
       </c>
       <c r="AG30" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>4160546.94</v>
       </c>
       <c r="AH30" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>3653520.24</v>
       </c>
       <c r="AI30" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>189197.220477</v>
       </c>
       <c r="AJ30" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>3653520.236</v>
       </c>
       <c r="AK30" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>1626782</v>
       </c>
     </row>
-    <row r="31" spans="2:69" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C31" s="16">
         <v>0.98704650000000005</v>
@@ -5996,11 +6132,11 @@
         <v>3653520.24</v>
       </c>
       <c r="G31" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>GGM</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J31" s="18">
         <v>0.99996839999999998</v>
@@ -6009,11 +6145,11 @@
         <v>2309.4769999999999</v>
       </c>
       <c r="L31" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-52796.222999999998</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O31" s="18">
         <v>0.94254700000000002</v>
@@ -6022,7 +6158,7 @@
         <v>97667.94</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="S31" s="18">
         <v>0.95194400000000001</v>
@@ -6031,7 +6167,7 @@
         <v>89659.199999999997</v>
       </c>
       <c r="V31" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="W31" s="32">
         <v>0.99996499999999999</v>
@@ -6040,7 +6176,7 @@
         <v>2423.543439</v>
       </c>
       <c r="Z31" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AA31" s="32">
         <v>0.98897800000000002</v>
@@ -6049,97 +6185,97 @@
         <v>43128.99</v>
       </c>
       <c r="AD31" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AE31" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>97667.94</v>
       </c>
       <c r="AF31" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>89659.199999999997</v>
       </c>
       <c r="AG31" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>62031.38</v>
       </c>
       <c r="AH31" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>55105.7</v>
       </c>
       <c r="AI31" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2423.543439</v>
       </c>
       <c r="AJ31" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>2309.4769999999999</v>
       </c>
       <c r="AK31" s="14">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>43128.99</v>
       </c>
     </row>
-    <row r="32" spans="2:69" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AD32" s="22"/>
       <c r="AE32" s="22"/>
       <c r="AF32" s="22"/>
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V34" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B36" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="F36" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>170</v>
-      </c>
       <c r="G36" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J36" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="K36" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="K36" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="L36" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V36" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W36" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="X36" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="X36" s="9" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="37" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C37" s="15">
         <v>0.99347419999999997</v>
@@ -6158,7 +6294,7 @@
         <v>GGM</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J37" s="12">
         <v>0.99883089999999997</v>
@@ -6171,7 +6307,7 @@
         <v>-416743.97</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="W37" s="31">
         <v>0.99801799999999996</v>
@@ -6182,7 +6318,7 @@
     </row>
     <row r="38" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C38" s="16">
         <v>0.9861259</v>
@@ -6197,11 +6333,11 @@
         <v>211942.1</v>
       </c>
       <c r="G38" s="6" t="str">
-        <f t="shared" ref="G38:G46" si="21">+IF(F38&lt;D38,"GGM","BM")</f>
+        <f t="shared" ref="G38:G46" si="24">+IF(F38&lt;D38,"GGM","BM")</f>
         <v>GGM</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J38" s="18">
         <v>0.99688900000000003</v>
@@ -6210,11 +6346,11 @@
         <v>100789.75999999999</v>
       </c>
       <c r="L38" s="17">
-        <f t="shared" ref="L38:L46" si="22">+K38-_xlfn.XLOOKUP(I38,B$37:B$46,F$37:F$46)</f>
+        <f t="shared" ref="L38:L46" si="25">+K38-_xlfn.XLOOKUP(I38,B$37:B$46,F$37:F$46)</f>
         <v>-111152.34000000001</v>
       </c>
       <c r="V38" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="W38" s="32">
         <v>0.99567000000000005</v>
@@ -6225,7 +6361,7 @@
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C39" s="15">
         <v>0.99485219999999996</v>
@@ -6240,11 +6376,11 @@
         <v>174775.12</v>
       </c>
       <c r="G39" s="1" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J39" s="12">
         <v>0.99764529999999996</v>
@@ -6253,11 +6389,11 @@
         <v>120410.38</v>
       </c>
       <c r="L39" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>-54364.739999999991</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W39" s="31">
         <v>0.99534699999999998</v>
@@ -6268,7 +6404,7 @@
     </row>
     <row r="40" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C40" s="16">
         <v>0.98931369999999996</v>
@@ -6283,11 +6419,11 @@
         <v>23030.65</v>
       </c>
       <c r="G40" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J40" s="18">
         <v>0.99412920000000005</v>
@@ -6296,11 +6432,11 @@
         <v>18214.75</v>
       </c>
       <c r="L40" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>-4815.9000000000015</v>
       </c>
       <c r="V40" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="W40" s="32">
         <v>0.99124800000000002</v>
@@ -6311,7 +6447,7 @@
     </row>
     <row r="41" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C41" s="15">
         <v>0.9914906</v>
@@ -6326,11 +6462,11 @@
         <v>1236195.68</v>
       </c>
       <c r="G41" s="1" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J41" s="12">
         <v>0.99875570000000002</v>
@@ -6339,11 +6475,11 @@
         <v>510440.15</v>
       </c>
       <c r="L41" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>-725755.52999999991</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="W41" s="31">
         <v>0.99727699999999997</v>
@@ -6354,7 +6490,7 @@
     </row>
     <row r="42" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C42" s="16">
         <v>0.98630370000000001</v>
@@ -6369,11 +6505,11 @@
         <v>1098061.48</v>
       </c>
       <c r="G42" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J42" s="18">
         <v>0.9954769</v>
@@ -6382,11 +6518,11 @@
         <v>631028.31999999995</v>
       </c>
       <c r="L42" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>-467033.16000000003</v>
       </c>
       <c r="V42" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W42" s="32">
         <v>0.99294800000000005</v>
@@ -6397,7 +6533,7 @@
     </row>
     <row r="43" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C43" s="15">
         <v>0.99346559999999995</v>
@@ -6412,11 +6548,11 @@
         <v>198641.06</v>
       </c>
       <c r="G43" s="1" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J43" s="12">
         <v>0.99769969999999997</v>
@@ -6425,11 +6561,11 @@
         <v>126978.78</v>
       </c>
       <c r="L43" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>-71662.28</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W43" s="31">
         <v>0.99575800000000003</v>
@@ -6440,7 +6576,7 @@
     </row>
     <row r="44" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C44" s="16">
         <v>0.98240799999999995</v>
@@ -6455,11 +6591,11 @@
         <v>46165.85</v>
       </c>
       <c r="G44" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J44" s="18">
         <v>0.99363820000000003</v>
@@ -6468,11 +6604,11 @@
         <v>29197.63</v>
       </c>
       <c r="L44" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>-16968.219999999998</v>
       </c>
       <c r="V44" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W44" s="32">
         <v>0.99148400000000003</v>
@@ -6483,7 +6619,7 @@
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C45" s="15">
         <v>0.97879510000000003</v>
@@ -6498,11 +6634,11 @@
         <v>53945.74</v>
       </c>
       <c r="G45" s="1" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J45" s="12">
         <v>0.98804809999999998</v>
@@ -6511,11 +6647,11 @@
         <v>4077694.45</v>
       </c>
       <c r="L45" s="14">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="W45" s="31">
         <v>0.993228</v>
@@ -6526,7 +6662,7 @@
     </row>
     <row r="46" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B46" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C46" s="16">
         <v>0.98749869999999995</v>
@@ -6541,11 +6677,11 @@
         <v>4077694.45</v>
       </c>
       <c r="G46" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>GGM</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J46" s="18">
         <v>0.99455020000000005</v>
@@ -6554,11 +6690,11 @@
         <v>30806.880000000001</v>
       </c>
       <c r="L46" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>-23138.859999999997</v>
       </c>
       <c r="V46" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="W46" s="32">
         <v>0.99019000000000001</v>
@@ -6568,8 +6704,8 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AV13:AX16 AZ13:BB16 BD13:BF16 BH13:BJ16">
-    <cfRule type="colorScale" priority="46">
+  <conditionalFormatting sqref="AE7:AE16">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6580,7 +6716,331 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE7:AE16">
+  <conditionalFormatting sqref="AE22:AE31">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AK7">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE8:AK8">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE9:AK9">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE10:AK10">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE11:AK11">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE12:AK12">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE13:AK13">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE14:AK14">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE15:AK15">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE16:AK16">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE22:AK22">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE23:AK23">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE24:AK24">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE25:AK25">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE26:AK26">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE27:AK27">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE28:AK28">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE29:AK29">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE30:AK30">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE31:AK31">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF7:AF16">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF22:AF31">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG7:AG16">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG22:AG31">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH7:AH16">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH22:AH31">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI7:AI16">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -6592,7 +7052,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF7:AF16">
+  <conditionalFormatting sqref="AI22:AI31">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AJ16">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -6604,7 +7076,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG7:AG16">
+  <conditionalFormatting sqref="AJ22:AJ31">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK7:AK16">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
@@ -6616,199 +7100,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH7:AH16">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI7:AI16">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ7:AJ16">
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK7:AK16">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE7:AK7">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE8:AK8">
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE9:AK9">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE10:AK10">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE11:AK11">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE12:AK12">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE13:AK13">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE14:AK14">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE15:AK15">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE16:AK16">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE22:AE31">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF22:AF31">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG22:AG31">
+  <conditionalFormatting sqref="AK22:AK31">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -6820,8 +7112,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH22:AH31">
-    <cfRule type="colorScale" priority="15">
+  <conditionalFormatting sqref="AX13:AZ16 BB13:BD16 BF13:BH16 BJ13:BL21">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6832,115 +7124,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI22:AI31">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ22:AJ31">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK22:AK31">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE22:AK22">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE23:AK23">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE24:AK24">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE25:AK25">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE26:AK26">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE27:AK27">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE28:AK28">
+  <conditionalFormatting sqref="BO7:BU7">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6952,7 +7136,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE29:AK29">
+  <conditionalFormatting sqref="BO8:BU8">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6964,7 +7148,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE30:AK30">
+  <conditionalFormatting sqref="BO9:BU9">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6976,7 +7160,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE31:AK31">
+  <conditionalFormatting sqref="BO10:BU10">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7025,8 +7209,10 @@
     <col min="30" max="32" width="10.109375" style="1" customWidth="1"/>
     <col min="33" max="33" width="2" style="20" customWidth="1"/>
     <col min="34" max="34" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="38" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="9.109375" style="1" customWidth="1"/>
+    <col min="35" max="35" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="41" max="42" width="12.109375" style="1" customWidth="1"/>
     <col min="43" max="43" width="2" style="36" customWidth="1"/>
@@ -7059,27 +7245,27 @@
   <sheetData>
     <row r="1" spans="2:83" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AC1" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG1" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AT1" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AX1" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="2:83" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="I2" s="19" t="s">
         <v>292</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>293</v>
       </c>
       <c r="N2" s="19" t="s">
         <v>138</v>
@@ -7089,25 +7275,25 @@
       </c>
       <c r="S2" s="19"/>
       <c r="V2" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W2" s="19"/>
       <c r="Z2" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AD2" s="19" t="s">
         <v>145</v>
       </c>
       <c r="AH2" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI2" s="19"/>
       <c r="AJ2" s="19"/>
       <c r="AT2" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AY2" s="19" t="s">
         <v>199</v>
-      </c>
-      <c r="AY2" s="19" t="s">
-        <v>200</v>
       </c>
       <c r="BC2" s="19" t="s">
         <v>138</v>
@@ -7116,16 +7302,16 @@
         <v>139</v>
       </c>
       <c r="BK2" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BO2" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BS2" s="19" t="s">
         <v>145</v>
       </c>
       <c r="BW2" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="2:83" x14ac:dyDescent="0.3">
@@ -7146,55 +7332,55 @@
     </row>
     <row r="4" spans="2:83" ht="16.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T4" s="21"/>
       <c r="V4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AD4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AH4" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AI4" s="13"/>
       <c r="AJ4" s="13"/>
       <c r="AT4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AY4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BC4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BG4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BK4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BO4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BS4" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BW4" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="2:83" ht="16.8" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -7202,82 +7388,82 @@
     </row>
     <row r="6" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>170</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="L6" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="P6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="P6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="R6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="T6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="T6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="V6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="X6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="X6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="Z6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AB6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="AD6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AE6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="AF6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AF6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="AH6" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AI6" s="9" t="s">
         <v>138</v>
@@ -7286,91 +7472,91 @@
         <v>139</v>
       </c>
       <c r="AK6" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AM6" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AN6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AO6" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AP6" s="9" t="s">
         <v>145</v>
       </c>
       <c r="AT6" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AU6" s="9" t="s">
         <v>134</v>
       </c>
       <c r="AV6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="AW6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AW6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="AY6" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AZ6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BA6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BA6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="BC6" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BD6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BE6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BE6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="BG6" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BH6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BI6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BI6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="BK6" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BL6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BM6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BM6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="BO6" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BP6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BQ6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BQ6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="BS6" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BT6" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="BU6" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BU6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="BW6" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BX6" s="9" t="s">
         <v>138</v>
@@ -7379,19 +7565,19 @@
         <v>139</v>
       </c>
       <c r="BZ6" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="CA6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="CB6" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="CC6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="CD6" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="CE6" s="9" t="s">
         <v>145</v>
@@ -7399,7 +7585,7 @@
     </row>
     <row r="7" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C7" s="15">
         <v>-0.88045949999999995</v>
@@ -7418,7 +7604,7 @@
         <v>BM</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J7" s="33">
         <v>-18.442921699999999</v>
@@ -7431,7 +7617,7 @@
         <v>-33376.900000000373</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O7" s="33">
         <v>-1167.2323490000001</v>
@@ -7440,7 +7626,7 @@
         <v>35518040</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S7" s="33">
         <v>-1167.7180880000001</v>
@@ -7449,7 +7635,7 @@
         <v>35525420</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="W7" s="33">
         <v>-6.5581474999999996</v>
@@ -7458,7 +7644,7 @@
         <v>2922129.51</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AA7" s="33">
         <v>-5.1333900000000003</v>
@@ -7467,7 +7653,7 @@
         <v>2632341</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AE7" s="33">
         <v>0.15242800000000001</v>
@@ -7476,7 +7662,7 @@
         <v>978543.1</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AI7" s="14">
         <f t="shared" ref="AI7:AI16" si="0">+_xlfn.XLOOKUP($AH7,N$7:N$16,P$7:P$16)</f>
@@ -7511,10 +7697,10 @@
         <v>978543.1</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AV7" s="12">
         <v>-5.7474112999999996</v>
@@ -7523,7 +7709,7 @@
         <v>269246.39079999999</v>
       </c>
       <c r="AY7" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AZ7" s="15">
         <v>-2.6609845999999999</v>
@@ -7532,7 +7718,7 @@
         <v>62.22701</v>
       </c>
       <c r="BC7" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BD7" s="33">
         <v>-1556969</v>
@@ -7541,7 +7727,7 @@
         <v>40580.75</v>
       </c>
       <c r="BG7" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BH7" s="33">
         <v>-1466067</v>
@@ -7550,7 +7736,7 @@
         <v>39378.31</v>
       </c>
       <c r="BK7" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BL7" s="33">
         <v>0.45879575</v>
@@ -7559,7 +7745,7 @@
         <v>23.92548</v>
       </c>
       <c r="BO7" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BP7" s="33">
         <v>-71.902986999999996</v>
@@ -7568,7 +7754,7 @@
         <v>1366.269454</v>
       </c>
       <c r="BS7" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BT7" s="33">
         <v>0.95831999999999995</v>
@@ -7577,7 +7763,7 @@
         <v>6.6396439999999997</v>
       </c>
       <c r="BW7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BX7" s="14">
         <f>+_xlfn.XLOOKUP($BW7,$BC$7:$BC$10,$BE$7:$BE$10)</f>
@@ -7614,7 +7800,7 @@
     </row>
     <row r="8" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C8" s="16">
         <v>-28.473542599999998</v>
@@ -7633,7 +7819,7 @@
         <v>BM</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J8" s="34">
         <v>-39.417364499999998</v>
@@ -7646,7 +7832,7 @@
         <v>-106032.52000000002</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O8" s="34">
         <v>-342.44675999999998</v>
@@ -7655,7 +7841,7 @@
         <v>4850543</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S8" s="34">
         <v>-342.43093699999997</v>
@@ -7664,7 +7850,7 @@
         <v>4850431</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="W8" s="34">
         <v>-0.14459959999999999</v>
@@ -7673,7 +7859,7 @@
         <v>297053.53000000003</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA8" s="34">
         <v>-3.654674</v>
@@ -7682,7 +7868,7 @@
         <v>599035.5</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AE8" s="34">
         <v>0.90742500000000004</v>
@@ -7691,7 +7877,7 @@
         <v>84480.34</v>
       </c>
       <c r="AH8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AI8" s="14">
         <f t="shared" si="0"/>
@@ -7726,7 +7912,7 @@
         <v>84480.34</v>
       </c>
       <c r="AT8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AU8" s="6" t="s">
         <v>33</v>
@@ -7738,7 +7924,7 @@
         <v>367562.62449999998</v>
       </c>
       <c r="AY8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AZ8" s="16">
         <v>0.59136739999999999</v>
@@ -7747,7 +7933,7 @@
         <v>33522.334649999997</v>
       </c>
       <c r="BC8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BD8" s="34">
         <v>-96.224559999999997</v>
@@ -7756,7 +7942,7 @@
         <v>517077.6</v>
       </c>
       <c r="BG8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BH8" s="34">
         <v>-93.707589999999996</v>
@@ -7765,7 +7951,7 @@
         <v>510340.6</v>
       </c>
       <c r="BK8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BL8" s="34">
         <v>-0.12438572000000001</v>
@@ -7774,7 +7960,7 @@
         <v>55606.478790000001</v>
       </c>
       <c r="BO8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BP8" s="34">
         <v>0.70949499999999999</v>
@@ -7783,7 +7969,7 @@
         <v>55867.376609999999</v>
       </c>
       <c r="BS8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BT8" s="34">
         <v>0.56132400000000005</v>
@@ -7792,7 +7978,7 @@
         <v>34732.780121999996</v>
       </c>
       <c r="BW8" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BX8" s="17">
         <f t="shared" ref="BX8:BX10" si="10">+_xlfn.XLOOKUP($BW8,$BC$7:$BC$10,$BE$7:$BE$10)</f>
@@ -7829,7 +8015,7 @@
     </row>
     <row r="9" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C9" s="15">
         <v>-14.8750605</v>
@@ -7848,7 +8034,7 @@
         <v>BM</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J9" s="33">
         <v>-101.5126727</v>
@@ -7861,7 +8047,7 @@
         <v>888.47000000000116</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O9" s="33">
         <v>-74322.225143000003</v>
@@ -7870,7 +8056,7 @@
         <v>6319862</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S9" s="33">
         <v>-74373.441279000006</v>
@@ -7879,7 +8065,7 @@
         <v>6322039</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W9" s="33">
         <v>-844.09909029999994</v>
@@ -7888,7 +8074,7 @@
         <v>720988.16000000003</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AA9" s="33">
         <v>-527.98294699999997</v>
@@ -7897,7 +8083,7 @@
         <v>570420.5</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AE9" s="33">
         <v>0.85376200000000002</v>
@@ -7906,7 +8092,7 @@
         <v>9484.2870000000003</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AI9" s="14">
         <f t="shared" si="0"/>
@@ -7941,10 +8127,10 @@
         <v>9484.2870000000003</v>
       </c>
       <c r="AT9" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AU9" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AV9" s="12">
         <v>-87.875995500000002</v>
@@ -7953,7 +8139,7 @@
         <v>1508.5369000000001</v>
       </c>
       <c r="AY9" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AZ9" s="15">
         <v>-54.161358200000002</v>
@@ -7962,7 +8148,7 @@
         <v>326.82960000000003</v>
       </c>
       <c r="BC9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BD9" s="33">
         <v>-1116797</v>
@@ -7971,7 +8157,7 @@
         <v>46504.1</v>
       </c>
       <c r="BG9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BH9" s="33">
         <v>-1057560</v>
@@ -7980,7 +8166,7 @@
         <v>45253.96</v>
       </c>
       <c r="BK9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BL9" s="33">
         <v>0.43556107999999999</v>
@@ -7989,7 +8175,7 @@
         <v>33.06073</v>
       </c>
       <c r="BO9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BP9" s="33">
         <v>-16.475088</v>
@@ -7998,7 +8184,7 @@
         <v>1129.176692</v>
       </c>
       <c r="BS9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BT9" s="33">
         <v>-2.6274600000000001</v>
@@ -8007,7 +8193,7 @@
         <v>83.811807000000002</v>
       </c>
       <c r="BW9" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BX9" s="14">
         <f t="shared" si="10"/>
@@ -8044,7 +8230,7 @@
     </row>
     <row r="10" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C10" s="16">
         <v>-45.222719599999998</v>
@@ -8063,7 +8249,7 @@
         <v>GGM</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J10" s="34">
         <v>-36.981007400000003</v>
@@ -8076,7 +8262,7 @@
         <v>-4312.989999999998</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O10" s="34">
         <v>-5849.742776</v>
@@ -8085,7 +8271,7 @@
         <v>648975</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S10" s="34">
         <v>-5872.4790750000002</v>
@@ -8094,7 +8280,7 @@
         <v>650234.80000000005</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="W10" s="34">
         <v>-39.938344000000001</v>
@@ -8103,7 +8289,7 @@
         <v>58675.03</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AA10" s="34">
         <v>-164.294004</v>
@@ -8112,7 +8298,7 @@
         <v>117900.8</v>
       </c>
       <c r="AD10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AE10" s="34">
         <v>0.70942099999999997</v>
@@ -8121,7 +8307,7 @@
         <v>4943.3419999999996</v>
       </c>
       <c r="AH10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI10" s="14">
         <f t="shared" si="0"/>
@@ -8156,7 +8342,7 @@
         <v>4943.3419999999996</v>
       </c>
       <c r="AT10" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AU10" s="6" t="s">
         <v>33</v>
@@ -8168,7 +8354,7 @@
         <v>1273.9808</v>
       </c>
       <c r="AY10" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AZ10" s="16">
         <v>-7.8432873000000001</v>
@@ -8177,7 +8363,7 @@
         <v>63829.462</v>
       </c>
       <c r="BC10" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BD10" s="34">
         <v>-2694.8380000000002</v>
@@ -8186,7 +8372,7 @@
         <v>1114452</v>
       </c>
       <c r="BG10" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BH10" s="34">
         <v>-2581.6080000000002</v>
@@ -8195,7 +8381,7 @@
         <v>1090796</v>
       </c>
       <c r="BK10" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BL10" s="34">
         <v>1.256618E-2</v>
@@ -8204,7 +8390,7 @@
         <v>21328.893110000001</v>
       </c>
       <c r="BO10" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BP10" s="34">
         <v>-1.0690390000000001</v>
@@ -8213,7 +8399,7 @@
         <v>197356.89684900001</v>
       </c>
       <c r="BS10" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BT10" s="34">
         <v>0.74929500000000004</v>
@@ -8222,7 +8408,7 @@
         <v>10747.212681999999</v>
       </c>
       <c r="BW10" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BX10" s="17">
         <f t="shared" si="10"/>
@@ -8259,7 +8445,7 @@
     </row>
     <row r="11" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C11" s="15">
         <v>-11.4324584</v>
@@ -8278,7 +8464,7 @@
         <v>GGM</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J11" s="33">
         <v>0.7672158</v>
@@ -8291,7 +8477,7 @@
         <v>-29986.589999999851</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O11" s="33">
         <v>-210.45065</v>
@@ -8300,7 +8486,7 @@
         <v>35465050</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S11" s="33">
         <v>-210.44169099999999</v>
@@ -8309,7 +8495,7 @@
         <v>35464300</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="W11" s="33">
         <v>-10.440305199999999</v>
@@ -8318,7 +8504,7 @@
         <v>8249258.3600000003</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AA11" s="33">
         <v>-22.354537000000001</v>
@@ -8327,7 +8513,7 @@
         <v>11786420</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AE11" s="33">
         <v>0.96534200000000003</v>
@@ -8336,7 +8522,7 @@
         <v>454043.1</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AI11" s="14">
         <f t="shared" si="0"/>
@@ -8371,10 +8557,10 @@
         <v>454043.1</v>
       </c>
       <c r="AT11" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AU11" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AV11" s="12">
         <v>-62.730387200000003</v>
@@ -8399,7 +8585,7 @@
     </row>
     <row r="12" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C12" s="16">
         <v>-111.9174616</v>
@@ -8418,7 +8604,7 @@
         <v>GGM</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J12" s="34">
         <v>-11.824242099999999</v>
@@ -8431,7 +8617,7 @@
         <v>-1097250.2800000003</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O12" s="34">
         <v>-242.90492599999999</v>
@@ -8440,7 +8626,7 @@
         <v>23865070</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S12" s="34">
         <v>-242.90095299999999</v>
@@ -8449,7 +8635,7 @@
         <v>23864880</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W12" s="34">
         <v>0.73289349999999998</v>
@@ -8458,7 +8644,7 @@
         <v>789759.22</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AA12" s="34">
         <v>-9.6180679999999992</v>
@@ -8467,7 +8653,7 @@
         <v>4979380</v>
       </c>
       <c r="AD12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AE12" s="34">
         <v>-20.279411</v>
@@ -8476,7 +8662,7 @@
         <v>7049078</v>
       </c>
       <c r="AH12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AI12" s="14">
         <f t="shared" si="0"/>
@@ -8511,7 +8697,7 @@
         <v>7049078</v>
       </c>
       <c r="AT12" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AU12" s="6" t="s">
         <v>33</v>
@@ -8539,7 +8725,7 @@
     </row>
     <row r="13" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C13" s="15">
         <v>-1.2333866</v>
@@ -8558,7 +8744,7 @@
         <v>GGM</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J13" s="33">
         <v>-1.2637936999999999</v>
@@ -8571,7 +8757,7 @@
         <v>29629.130000000005</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O13" s="33">
         <v>-1933.2909870000001</v>
@@ -8580,7 +8766,7 @@
         <v>7179580</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S13" s="33">
         <v>-1935.788642</v>
@@ -8589,7 +8775,7 @@
         <v>7184214</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W13" s="33">
         <v>-179.7974595</v>
@@ -8598,7 +8784,7 @@
         <v>2418834.08</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AA13" s="33">
         <v>-29.274857999999998</v>
@@ -8607,7 +8793,7 @@
         <v>989808</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AE13" s="33">
         <v>0.103008</v>
@@ -8616,7 +8802,7 @@
         <v>170374.3</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AI13" s="14">
         <f t="shared" si="0"/>
@@ -8651,10 +8837,10 @@
         <v>170374.3</v>
       </c>
       <c r="AT13" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AU13" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AV13" s="12">
         <v>-31.850383799999999</v>
@@ -8680,7 +8866,7 @@
     </row>
     <row r="14" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C14" s="16">
         <v>-91.031581299999999</v>
@@ -8699,7 +8885,7 @@
         <v>BM</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J14" s="34">
         <v>-89.237210300000001</v>
@@ -8712,7 +8898,7 @@
         <v>-8925.2999999999884</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O14" s="34">
         <v>-1799.8141330000001</v>
@@ -8721,7 +8907,7 @@
         <v>996737.1</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S14" s="34">
         <v>-1795.435129</v>
@@ -8730,7 +8916,7 @@
         <v>995524.5</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W14" s="34">
         <v>-5.0710414999999998</v>
@@ -8739,7 +8925,7 @@
         <v>61304.51</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA14" s="34">
         <v>-83.509297000000004</v>
@@ -8748,7 +8934,7 @@
         <v>228724.7</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE14" s="34">
         <v>-0.475381</v>
@@ -8757,7 +8943,7 @@
         <v>30221.29</v>
       </c>
       <c r="AH14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AI14" s="14">
         <f t="shared" si="0"/>
@@ -8792,7 +8978,7 @@
         <v>30221.29</v>
       </c>
       <c r="AT14" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AU14" s="6" t="s">
         <v>33</v>
@@ -8821,7 +9007,7 @@
     </row>
     <row r="15" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C15" s="15">
         <v>-56.708334700000002</v>
@@ -8840,7 +9026,7 @@
         <v>BM</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J15" s="33">
         <v>-12.7604203</v>
@@ -8853,7 +9039,7 @@
         <v>12860522.289999999</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O15" s="33">
         <v>-779.10362199999997</v>
@@ -8862,7 +9048,7 @@
         <v>98519360</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S15" s="33">
         <v>-779.06910800000003</v>
@@ -8871,7 +9057,7 @@
         <v>98517180</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="W15" s="33">
         <v>0.20104150000000001</v>
@@ -8880,7 +9066,7 @@
         <v>3152880.72</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AA15" s="33">
         <v>-25.673124000000001</v>
@@ -8889,7 +9075,7 @@
         <v>18217230</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE15" s="33">
         <v>0.66067100000000001</v>
@@ -8898,7 +9084,7 @@
         <v>2054735</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AI15" s="14">
         <f t="shared" si="0"/>
@@ -8952,7 +9138,7 @@
     </row>
     <row r="16" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C16" s="16">
         <v>-15.631722699999999</v>
@@ -8971,7 +9157,7 @@
         <v>GGM</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J16" s="34">
         <v>-86.961009899999993</v>
@@ -8984,7 +9170,7 @@
         <v>-12878536.9</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O16" s="34">
         <v>-2140.578501</v>
@@ -8993,7 +9179,7 @@
         <v>1000999</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="S16" s="34">
         <v>-2138.2510229999998</v>
@@ -9002,7 +9188,7 @@
         <v>1000455</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="W16" s="34">
         <v>0.41362320000000002</v>
@@ -9011,7 +9197,7 @@
         <v>16826.12</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AA16" s="34">
         <v>-77.961535999999995</v>
@@ -9020,7 +9206,7 @@
         <v>195255.6</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AE16" s="34">
         <v>0.882351</v>
@@ -9029,7 +9215,7 @@
         <v>7536.8639999999996</v>
       </c>
       <c r="AH16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AI16" s="14">
         <f t="shared" si="0"/>
@@ -9081,15 +9267,15 @@
       <c r="CA16" s="13"/>
       <c r="CB16" s="13"/>
     </row>
-    <row r="17" spans="55:80" x14ac:dyDescent="0.3">
+    <row r="17" spans="34:80" x14ac:dyDescent="0.3">
       <c r="CA17" s="13"/>
       <c r="CB17" s="13"/>
     </row>
-    <row r="18" spans="55:80" x14ac:dyDescent="0.3">
+    <row r="18" spans="34:80" x14ac:dyDescent="0.3">
       <c r="CA18" s="13"/>
       <c r="CB18" s="13"/>
     </row>
-    <row r="19" spans="55:80" x14ac:dyDescent="0.3">
+    <row r="19" spans="34:80" x14ac:dyDescent="0.3">
       <c r="BW19" s="19"/>
       <c r="BX19" s="19"/>
       <c r="BY19" s="19"/>
@@ -9097,7 +9283,7 @@
       <c r="CA19" s="13"/>
       <c r="CB19" s="13"/>
     </row>
-    <row r="20" spans="55:80" x14ac:dyDescent="0.3">
+    <row r="20" spans="34:80" x14ac:dyDescent="0.3">
       <c r="BW20" s="19"/>
       <c r="BX20" s="19"/>
       <c r="BY20" s="19"/>
@@ -9105,7 +9291,31 @@
       <c r="CA20" s="13"/>
       <c r="CB20" s="13"/>
     </row>
-    <row r="21" spans="55:80" x14ac:dyDescent="0.3">
+    <row r="21" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="AH21" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI21" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="AJ21" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="AK21" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="AL21" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="AM21" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="AN21" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO21" s="9" t="s">
+        <v>233</v>
+      </c>
       <c r="BW21" s="13"/>
       <c r="BX21" s="13"/>
       <c r="BY21" s="13"/>
@@ -9113,7 +9323,31 @@
       <c r="CA21" s="13"/>
       <c r="CB21" s="13"/>
     </row>
-    <row r="22" spans="55:80" x14ac:dyDescent="0.3">
+    <row r="22" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="AH22" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI22" s="14">
+        <v>7977465</v>
+      </c>
+      <c r="AJ22" s="14">
+        <v>6744284</v>
+      </c>
+      <c r="AK22" s="14">
+        <v>152178.4</v>
+      </c>
+      <c r="AL22" s="14">
+        <v>179231.8</v>
+      </c>
+      <c r="AM22" s="14">
+        <v>7386617</v>
+      </c>
+      <c r="AN22" s="14">
+        <v>908021.6</v>
+      </c>
+      <c r="AO22" s="14">
+        <v>22672170</v>
+      </c>
       <c r="BW22" s="13"/>
       <c r="BX22" s="13"/>
       <c r="BY22" s="13"/>
@@ -9121,7 +9355,31 @@
       <c r="CA22" s="13"/>
       <c r="CB22" s="13"/>
     </row>
-    <row r="23" spans="55:80" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="34:80" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AH23" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI23" s="14">
+        <v>3406131</v>
+      </c>
+      <c r="AJ23" s="14">
+        <v>1289262</v>
+      </c>
+      <c r="AK23" s="14">
+        <v>180850.8</v>
+      </c>
+      <c r="AL23" s="14">
+        <v>178724.6</v>
+      </c>
+      <c r="AM23" s="14">
+        <v>1464898</v>
+      </c>
+      <c r="AN23" s="14">
+        <v>3359250</v>
+      </c>
+      <c r="AO23" s="14">
+        <v>24316190</v>
+      </c>
       <c r="BC23" s="27"/>
       <c r="BD23" s="27"/>
       <c r="BE23" s="27"/>
@@ -9137,7 +9395,31 @@
       <c r="BT23" s="27"/>
       <c r="BU23" s="27"/>
     </row>
-    <row r="24" spans="55:80" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="34:80" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AH24" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AI24" s="14">
+        <v>41910400</v>
+      </c>
+      <c r="AJ24" s="14">
+        <v>39159000</v>
+      </c>
+      <c r="AK24" s="14">
+        <v>2336516</v>
+      </c>
+      <c r="AL24" s="14">
+        <v>2336694</v>
+      </c>
+      <c r="AM24" s="14">
+        <v>40142750</v>
+      </c>
+      <c r="AN24" s="14">
+        <v>4643869</v>
+      </c>
+      <c r="AO24" s="14">
+        <v>122159800</v>
+      </c>
       <c r="BC24" s="27"/>
       <c r="BD24" s="28"/>
       <c r="BE24" s="28"/>
@@ -9154,7 +9436,31 @@
       <c r="BT24" s="28"/>
       <c r="BU24" s="28"/>
     </row>
-    <row r="25" spans="55:80" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="34:80" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AH25" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI25" s="14">
+        <v>8240698</v>
+      </c>
+      <c r="AJ25" s="14">
+        <v>9073383</v>
+      </c>
+      <c r="AK25" s="14">
+        <v>357059.1</v>
+      </c>
+      <c r="AL25" s="14">
+        <v>406927.1</v>
+      </c>
+      <c r="AM25" s="14">
+        <v>8918761</v>
+      </c>
+      <c r="AN25" s="14">
+        <v>1458045</v>
+      </c>
+      <c r="AO25" s="14">
+        <v>30861490</v>
+      </c>
       <c r="BC25" s="27"/>
       <c r="BD25" s="28"/>
       <c r="BE25" s="28"/>
@@ -9171,7 +9477,31 @@
       <c r="BT25" s="28"/>
       <c r="BU25" s="28"/>
     </row>
-    <row r="26" spans="55:80" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="34:80" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="AH26" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI26" s="14">
+        <v>76685160</v>
+      </c>
+      <c r="AJ26" s="14">
+        <v>87278960</v>
+      </c>
+      <c r="AK26" s="14">
+        <v>3562568</v>
+      </c>
+      <c r="AL26" s="14">
+        <v>3704493</v>
+      </c>
+      <c r="AM26" s="14">
+        <v>103207900</v>
+      </c>
+      <c r="AN26" s="14">
+        <v>18045810</v>
+      </c>
+      <c r="AO26" s="14">
+        <v>426086100</v>
+      </c>
       <c r="BC26" s="27"/>
       <c r="BD26" s="28"/>
       <c r="BE26" s="28"/>
@@ -9189,7 +9519,235 @@
       <c r="BU26" s="28"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="AI7:AI16">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI7:AP7">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI8:AP8">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI9:AP9">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI10:AP10">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI11:AP11">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI12:AP12">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI13:AP13">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI14:AP14">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI15:AP15">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI16:AP16">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AJ16">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK7:AK16">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL7:AL16">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM7:AM16">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN7:AN16">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO7:AO16">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP7:AP16">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BC13:BE16 BG13:BI16 BK13:BM16 BO13:BQ16">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BS13:BU16">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
@@ -9201,103 +9759,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BS13:BU16">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI7:AI16">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ7:AJ16">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK7:AK16">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL7:AL16">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM7:AM16">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN7:AN16">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO7:AO16">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP7:AP16">
+  <conditionalFormatting sqref="BX7:CE7">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -9309,7 +9771,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI7:AP7">
+  <conditionalFormatting sqref="BX8:CE8">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -9321,7 +9783,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI8:AP8">
+  <conditionalFormatting sqref="BX9:CE9">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -9333,7 +9795,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI9:AP9">
+  <conditionalFormatting sqref="BX10:CE10">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -9345,7 +9807,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI10:AP10">
+  <conditionalFormatting sqref="AI22:AI26">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -9357,7 +9819,79 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI11:AP11">
+  <conditionalFormatting sqref="AI22:AO22">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI23:AO23">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI24:AO24">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI25:AO25">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI26:AO26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ22:AJ26">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK22:AK26">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -9369,7 +9903,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI12:AP12">
+  <conditionalFormatting sqref="AL22:AL26">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -9381,7 +9915,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI13:AP13">
+  <conditionalFormatting sqref="AM22:AM26">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -9393,7 +9927,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI14:AP14">
+  <conditionalFormatting sqref="AN22:AN26">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -9405,68 +9939,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI15:AP15">
+  <conditionalFormatting sqref="AO22:AO26">
     <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI16:AP16">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX7:CE7">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX8:CE8">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX9:CE9">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX10:CE10">
-    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9694,7 +10168,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
@@ -9702,7 +10176,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
@@ -9710,7 +10184,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
@@ -9718,7 +10192,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
@@ -9726,7 +10200,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
@@ -9734,7 +10208,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -9742,7 +10216,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
@@ -9750,7 +10224,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
@@ -9758,7 +10232,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
@@ -9766,7 +10240,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
@@ -9774,7 +10248,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
@@ -9782,7 +10256,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
@@ -9790,7 +10264,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
@@ -9798,7 +10272,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -9817,37 +10291,37 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6240DCC-66AD-408A-B7CA-CD84D1FF5B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F599DCF-7B95-4525-837C-84C6E14C0BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="302">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -965,6 +965,12 @@
   </si>
   <si>
     <t>Ridge</t>
+  </si>
+  <si>
+    <t>Cases_t_1</t>
+  </si>
+  <si>
+    <t>Cases_t_4</t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1151,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1192,8 +1198,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3576,7 +3580,7 @@
       <c r="BN7" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="BO7" s="38">
+      <c r="BO7" s="14">
         <f>+_xlfn.XLOOKUP($BN7,$AX$7:$AX$10,$AZ$7:$AZ$10)</f>
         <v>22520.654823000001</v>
       </c>
@@ -3765,7 +3769,7 @@
       <c r="BN8" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="BO8" s="39">
+      <c r="BO8" s="17">
         <f t="shared" ref="BO8:BO10" si="9">+_xlfn.XLOOKUP($BN8,$AX$7:$AX$10,$AZ$7:$AZ$10)</f>
         <v>4703.6260300000004</v>
       </c>
@@ -3954,7 +3958,7 @@
       <c r="BN9" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="BO9" s="38">
+      <c r="BO9" s="14">
         <f t="shared" si="9"/>
         <v>2148.462321</v>
       </c>
@@ -4143,7 +4147,7 @@
       <c r="BN10" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="BO10" s="39">
+      <c r="BO10" s="17">
         <f t="shared" si="9"/>
         <v>53755.513460000002</v>
       </c>
@@ -7178,7 +7182,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93B5247-589C-44F9-8D52-5DE81A7C1480}">
-  <dimension ref="B1:CE26"/>
+  <dimension ref="B1:CE44"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -9284,6 +9288,9 @@
       <c r="CB19" s="13"/>
     </row>
     <row r="20" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="AH20" s="1" t="s">
+        <v>250</v>
+      </c>
       <c r="BW20" s="19"/>
       <c r="BX20" s="19"/>
       <c r="BY20" s="19"/>
@@ -9328,25 +9335,25 @@
         <v>171</v>
       </c>
       <c r="AI22" s="14">
-        <v>7977465</v>
+        <v>8358205</v>
       </c>
       <c r="AJ22" s="14">
-        <v>6744284</v>
+        <v>6472772</v>
       </c>
       <c r="AK22" s="14">
-        <v>152178.4</v>
+        <v>247333.9</v>
       </c>
       <c r="AL22" s="14">
-        <v>179231.8</v>
+        <v>247360.9</v>
       </c>
       <c r="AM22" s="14">
-        <v>7386617</v>
+        <v>7119606</v>
       </c>
       <c r="AN22" s="14">
-        <v>908021.6</v>
+        <v>739199.5</v>
       </c>
       <c r="AO22" s="14">
-        <v>22672170</v>
+        <v>22672160</v>
       </c>
       <c r="BW22" s="13"/>
       <c r="BX22" s="13"/>
@@ -9360,22 +9367,22 @@
         <v>172</v>
       </c>
       <c r="AI23" s="14">
-        <v>3406131</v>
+        <v>3756126</v>
       </c>
       <c r="AJ23" s="14">
-        <v>1289262</v>
+        <v>1272250</v>
       </c>
       <c r="AK23" s="14">
-        <v>180850.8</v>
+        <v>141937.60000000001</v>
       </c>
       <c r="AL23" s="14">
-        <v>178724.6</v>
+        <v>141957.6</v>
       </c>
       <c r="AM23" s="14">
-        <v>1464898</v>
+        <v>1460144</v>
       </c>
       <c r="AN23" s="14">
-        <v>3359250</v>
+        <v>3376700</v>
       </c>
       <c r="AO23" s="14">
         <v>24316190</v>
@@ -9400,22 +9407,22 @@
         <v>175</v>
       </c>
       <c r="AI24" s="14">
-        <v>41910400</v>
+        <v>42386480</v>
       </c>
       <c r="AJ24" s="14">
-        <v>39159000</v>
+        <v>37853330</v>
       </c>
       <c r="AK24" s="14">
-        <v>2336516</v>
+        <v>2035471</v>
       </c>
       <c r="AL24" s="14">
-        <v>2336694</v>
+        <v>2035450</v>
       </c>
       <c r="AM24" s="14">
-        <v>40142750</v>
+        <v>40214680</v>
       </c>
       <c r="AN24" s="14">
-        <v>4643869</v>
+        <v>1304844</v>
       </c>
       <c r="AO24" s="14">
         <v>122159800</v>
@@ -9441,22 +9448,22 @@
         <v>176</v>
       </c>
       <c r="AI25" s="14">
-        <v>8240698</v>
+        <v>8256902</v>
       </c>
       <c r="AJ25" s="14">
-        <v>9073383</v>
+        <v>8702138</v>
       </c>
       <c r="AK25" s="14">
-        <v>357059.1</v>
+        <v>400986.7</v>
       </c>
       <c r="AL25" s="14">
-        <v>406927.1</v>
+        <v>401188.3</v>
       </c>
       <c r="AM25" s="14">
-        <v>8918761</v>
+        <v>8497244</v>
       </c>
       <c r="AN25" s="14">
-        <v>1458045</v>
+        <v>2367122</v>
       </c>
       <c r="AO25" s="14">
         <v>30861490</v>
@@ -9482,22 +9489,22 @@
         <v>179</v>
       </c>
       <c r="AI26" s="14">
-        <v>76685160</v>
+        <v>87020490</v>
       </c>
       <c r="AJ26" s="14">
-        <v>87278960</v>
+        <v>87979830</v>
       </c>
       <c r="AK26" s="14">
-        <v>3562568</v>
+        <v>3994550</v>
       </c>
       <c r="AL26" s="14">
-        <v>3704493</v>
+        <v>3993905</v>
       </c>
       <c r="AM26" s="14">
-        <v>103207900</v>
+        <v>99369740</v>
       </c>
       <c r="AN26" s="14">
-        <v>18045810</v>
+        <v>18872380</v>
       </c>
       <c r="AO26" s="14">
         <v>426086100</v>
@@ -9518,8 +9525,546 @@
       <c r="BT26" s="28"/>
       <c r="BU26" s="28"/>
     </row>
+    <row r="29" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="AH29" s="29" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="AH30" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI30" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="AJ30" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="AK30" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="AL30" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="AM30" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="AN30" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO30" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="31" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="AH31" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI31" s="14">
+        <v>8448053</v>
+      </c>
+      <c r="AJ31" s="14">
+        <v>6780585</v>
+      </c>
+      <c r="AK31" s="14">
+        <v>65899.95</v>
+      </c>
+      <c r="AL31" s="14">
+        <v>59433.07</v>
+      </c>
+      <c r="AM31" s="14">
+        <v>7730858</v>
+      </c>
+      <c r="AN31" s="14">
+        <v>772883.5</v>
+      </c>
+      <c r="AO31" s="14">
+        <v>22698710</v>
+      </c>
+    </row>
+    <row r="32" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="AH32" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI32" s="14">
+        <v>3641375</v>
+      </c>
+      <c r="AJ32" s="14">
+        <v>1288990</v>
+      </c>
+      <c r="AK32" s="14">
+        <v>98367.06</v>
+      </c>
+      <c r="AL32" s="14">
+        <v>147808.5</v>
+      </c>
+      <c r="AM32" s="14">
+        <v>1442136</v>
+      </c>
+      <c r="AN32" s="14">
+        <v>3279935</v>
+      </c>
+      <c r="AO32" s="14">
+        <v>23558110</v>
+      </c>
+    </row>
+    <row r="33" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AH33" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AI33" s="14">
+        <v>44264800</v>
+      </c>
+      <c r="AJ33" s="14">
+        <v>39037660</v>
+      </c>
+      <c r="AK33" s="14">
+        <v>396822.9</v>
+      </c>
+      <c r="AL33" s="14">
+        <v>410083.2</v>
+      </c>
+      <c r="AM33" s="14">
+        <v>40922950</v>
+      </c>
+      <c r="AN33" s="14">
+        <v>2976958</v>
+      </c>
+      <c r="AO33" s="14">
+        <v>123353700</v>
+      </c>
+    </row>
+    <row r="34" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AH34" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI34" s="14">
+        <v>8295826</v>
+      </c>
+      <c r="AJ34" s="14">
+        <v>8770232</v>
+      </c>
+      <c r="AK34" s="14">
+        <v>236383.9</v>
+      </c>
+      <c r="AL34" s="14">
+        <v>268165.8</v>
+      </c>
+      <c r="AM34" s="14">
+        <v>8565617</v>
+      </c>
+      <c r="AN34" s="14">
+        <v>2513404</v>
+      </c>
+      <c r="AO34" s="14">
+        <v>31047740</v>
+      </c>
+    </row>
+    <row r="35" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AH35" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI35" s="14">
+        <v>88022780</v>
+      </c>
+      <c r="AJ35" s="14">
+        <v>81075680</v>
+      </c>
+      <c r="AK35" s="14">
+        <v>1296517</v>
+      </c>
+      <c r="AL35" s="14">
+        <v>1329986</v>
+      </c>
+      <c r="AM35" s="14">
+        <v>99065760</v>
+      </c>
+      <c r="AN35" s="14">
+        <v>19143400</v>
+      </c>
+      <c r="AO35" s="14">
+        <v>427453400</v>
+      </c>
+    </row>
+    <row r="38" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AH38" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="39" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AH39" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI39" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="AJ39" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="AK39" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="AL39" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="AM39" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="AN39" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO39" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AH40" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI40" s="14">
+        <v>8300763</v>
+      </c>
+      <c r="AJ40" s="14">
+        <v>7395443</v>
+      </c>
+      <c r="AK40" s="14">
+        <v>408375.8</v>
+      </c>
+      <c r="AL40" s="14">
+        <v>408305.3</v>
+      </c>
+      <c r="AM40" s="14">
+        <v>7755566</v>
+      </c>
+      <c r="AN40" s="14">
+        <v>1238832</v>
+      </c>
+      <c r="AO40" s="14">
+        <v>22730730</v>
+      </c>
+    </row>
+    <row r="41" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AH41" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI41" s="14">
+        <v>3779986</v>
+      </c>
+      <c r="AJ41" s="14">
+        <v>1261350</v>
+      </c>
+      <c r="AK41" s="14">
+        <v>2078308</v>
+      </c>
+      <c r="AL41" s="14">
+        <v>2078353</v>
+      </c>
+      <c r="AM41" s="14">
+        <v>1379444</v>
+      </c>
+      <c r="AN41" s="14">
+        <v>3793630</v>
+      </c>
+      <c r="AO41" s="14">
+        <v>21256790</v>
+      </c>
+    </row>
+    <row r="42" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AH42" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AI42" s="14">
+        <v>43990100</v>
+      </c>
+      <c r="AJ42" s="14">
+        <v>39106190</v>
+      </c>
+      <c r="AK42" s="14">
+        <v>3578022</v>
+      </c>
+      <c r="AL42" s="14">
+        <v>3578005</v>
+      </c>
+      <c r="AM42" s="14">
+        <v>44898540</v>
+      </c>
+      <c r="AN42" s="14">
+        <v>5110701</v>
+      </c>
+      <c r="AO42" s="14">
+        <v>127592700</v>
+      </c>
+    </row>
+    <row r="43" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AH43" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI43" s="14">
+        <v>8065792</v>
+      </c>
+      <c r="AJ43" s="14">
+        <v>8527451</v>
+      </c>
+      <c r="AK43" s="14">
+        <v>2342675</v>
+      </c>
+      <c r="AL43" s="14">
+        <v>2342966</v>
+      </c>
+      <c r="AM43" s="14">
+        <v>8968693</v>
+      </c>
+      <c r="AN43" s="14">
+        <v>3263058</v>
+      </c>
+      <c r="AO43" s="14">
+        <v>31673230</v>
+      </c>
+    </row>
+    <row r="44" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AH44" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI44" s="14">
+        <v>80946790</v>
+      </c>
+      <c r="AJ44" s="14">
+        <v>78253060</v>
+      </c>
+      <c r="AK44" s="14">
+        <v>16474180</v>
+      </c>
+      <c r="AL44" s="14">
+        <v>16476130</v>
+      </c>
+      <c r="AM44" s="14">
+        <v>91963430</v>
+      </c>
+      <c r="AN44" s="14">
+        <v>19756890</v>
+      </c>
+      <c r="AO44" s="14">
+        <v>433487500</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="AI7:AI16">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI22:AI26">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI22:AO22">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI23:AO23">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI24:AO24">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI25:AO25">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI26:AO26">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI7:AP7">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI8:AP8">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI9:AP9">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI10:AP10">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI11:AP11">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI12:AP12">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI13:AP13">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI14:AP14">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI15:AP15">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI16:AP16">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AJ16">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ22:AJ26">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -9531,8 +10076,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI7:AP7">
-    <cfRule type="colorScale" priority="27">
+  <conditionalFormatting sqref="AK7:AK16">
+    <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9543,8 +10088,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI8:AP8">
-    <cfRule type="colorScale" priority="26">
+  <conditionalFormatting sqref="AK22:AK26">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9555,8 +10100,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI9:AP9">
-    <cfRule type="colorScale" priority="25">
+  <conditionalFormatting sqref="AL7:AL16">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9567,7 +10112,175 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI10:AP10">
+  <conditionalFormatting sqref="AL22:AL26">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM7:AM16">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM22:AM26">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN7:AN16">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN22:AN26">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO7:AO16">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO22:AO26">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP7:AP16">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BC13:BE16 BG13:BI16 BK13:BM16 BO13:BQ16">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BS13:BU16">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX7:CE7">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX8:CE8">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX9:CE9">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX10:CE10">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI31:AI35">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -9579,7 +10292,79 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI11:AP11">
+  <conditionalFormatting sqref="AI31:AO31">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI32:AO32">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI33:AO33">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI34:AO34">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI35:AO35">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ31:AJ35">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK31:AK35">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
@@ -9591,7 +10376,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI12:AP12">
+  <conditionalFormatting sqref="AL31:AL35">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -9603,7 +10388,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI13:AP13">
+  <conditionalFormatting sqref="AM31:AM35">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -9615,7 +10400,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI14:AP14">
+  <conditionalFormatting sqref="AN31:AN35">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -9627,7 +10412,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI15:AP15">
+  <conditionalFormatting sqref="AO31:AO35">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -9639,175 +10424,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI16:AP16">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ7:AJ16">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK7:AK16">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL7:AL16">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM7:AM16">
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN7:AN16">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO7:AO16">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP7:AP16">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BC13:BE16 BG13:BI16 BK13:BM16 BO13:BQ16">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BS13:BU16">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX7:CE7">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX8:CE8">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX9:CE9">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX10:CE10">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI22:AI26">
+  <conditionalFormatting sqref="AI40:AI44">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -9819,7 +10436,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI22:AO22">
+  <conditionalFormatting sqref="AI40:AO40">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -9831,7 +10448,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI23:AO23">
+  <conditionalFormatting sqref="AI41:AO41">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -9843,7 +10460,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI24:AO24">
+  <conditionalFormatting sqref="AI42:AO42">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -9855,7 +10472,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI25:AO25">
+  <conditionalFormatting sqref="AI43:AO43">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -9867,7 +10484,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI26:AO26">
+  <conditionalFormatting sqref="AI44:AO44">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -9879,7 +10496,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ22:AJ26">
+  <conditionalFormatting sqref="AJ40:AJ44">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -9891,7 +10508,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK22:AK26">
+  <conditionalFormatting sqref="AK40:AK44">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -9903,7 +10520,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL22:AL26">
+  <conditionalFormatting sqref="AL40:AL44">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -9915,7 +10532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM22:AM26">
+  <conditionalFormatting sqref="AM40:AM44">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -9927,7 +10544,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN22:AN26">
+  <conditionalFormatting sqref="AN40:AN44">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -9939,7 +10556,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO22:AO26">
+  <conditionalFormatting sqref="AO40:AO44">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F599DCF-7B95-4525-837C-84C6E14C0BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B842F594-9C25-43B9-B9E6-900E327DED9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="323">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -971,6 +971,69 @@
   </si>
   <si>
     <t>Cases_t_4</t>
+  </si>
+  <si>
+    <t>const</t>
+  </si>
+  <si>
+    <t>L1.cases</t>
+  </si>
+  <si>
+    <t>L2.cases</t>
+  </si>
+  <si>
+    <t>L3.cases</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>L4.cases</t>
+  </si>
+  <si>
+    <t>L4.no2</t>
+  </si>
+  <si>
+    <t>L5.cases</t>
+  </si>
+  <si>
+    <t>VAR cases log</t>
+  </si>
+  <si>
+    <t>L1.o3</t>
+  </si>
+  <si>
+    <t>L2.Mean_distance_avg_14day_movavg</t>
+  </si>
+  <si>
+    <t>L3.no2</t>
+  </si>
+  <si>
+    <t>L4.o3</t>
+  </si>
+  <si>
+    <t>L5.o3</t>
+  </si>
+  <si>
+    <t>L3.o3</t>
+  </si>
+  <si>
+    <t>L4.Mean_distance_avg_14day_movavg</t>
+  </si>
+  <si>
+    <t>L5.Mean_distance_avg_14day_movavg</t>
+  </si>
+  <si>
+    <t>L1.pm25</t>
+  </si>
+  <si>
+    <t>L4.pm25</t>
+  </si>
+  <si>
+    <t>L5.pm25</t>
+  </si>
+  <si>
+    <t>VAR</t>
   </si>
 </sst>
 </file>
@@ -7182,7 +7245,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93B5247-589C-44F9-8D52-5DE81A7C1480}">
-  <dimension ref="B1:CE44"/>
+  <dimension ref="B1:CE60"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -9555,6 +9618,9 @@
       <c r="AO30" s="9" t="s">
         <v>233</v>
       </c>
+      <c r="AP30" s="9" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="31" spans="34:80" x14ac:dyDescent="0.3">
       <c r="AH31" s="1" t="s">
@@ -9581,6 +9647,9 @@
       <c r="AO31" s="14">
         <v>22698710</v>
       </c>
+      <c r="AP31" s="14">
+        <v>4344672</v>
+      </c>
     </row>
     <row r="32" spans="34:80" x14ac:dyDescent="0.3">
       <c r="AH32" s="6" t="s">
@@ -9607,8 +9676,11 @@
       <c r="AO32" s="14">
         <v>23558110</v>
       </c>
-    </row>
-    <row r="33" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AP32" s="14">
+        <v>2015265</v>
+      </c>
+    </row>
+    <row r="33" spans="34:42" x14ac:dyDescent="0.3">
       <c r="AH33" s="1" t="s">
         <v>175</v>
       </c>
@@ -9633,8 +9705,11 @@
       <c r="AO33" s="14">
         <v>123353700</v>
       </c>
-    </row>
-    <row r="34" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AP33" s="14">
+        <v>152331600</v>
+      </c>
+    </row>
+    <row r="34" spans="34:42" x14ac:dyDescent="0.3">
       <c r="AH34" s="6" t="s">
         <v>176</v>
       </c>
@@ -9659,8 +9734,11 @@
       <c r="AO34" s="14">
         <v>31047740</v>
       </c>
-    </row>
-    <row r="35" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AP34" s="14">
+        <v>3783188</v>
+      </c>
+    </row>
+    <row r="35" spans="34:42" x14ac:dyDescent="0.3">
       <c r="AH35" s="1" t="s">
         <v>179</v>
       </c>
@@ -9685,13 +9763,16 @@
       <c r="AO35" s="14">
         <v>427453400</v>
       </c>
-    </row>
-    <row r="38" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AP35" s="14">
+        <v>228807800</v>
+      </c>
+    </row>
+    <row r="38" spans="34:42" x14ac:dyDescent="0.3">
       <c r="AH38" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="39" spans="34:41" x14ac:dyDescent="0.3">
+    <row r="39" spans="34:42" x14ac:dyDescent="0.3">
       <c r="AH39" s="9" t="s">
         <v>165</v>
       </c>
@@ -9717,7 +9798,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="40" spans="34:41" x14ac:dyDescent="0.3">
+    <row r="40" spans="34:42" x14ac:dyDescent="0.3">
       <c r="AH40" s="1" t="s">
         <v>171</v>
       </c>
@@ -9742,8 +9823,9 @@
       <c r="AO40" s="14">
         <v>22730730</v>
       </c>
-    </row>
-    <row r="41" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AP40" s="14"/>
+    </row>
+    <row r="41" spans="34:42" x14ac:dyDescent="0.3">
       <c r="AH41" s="6" t="s">
         <v>172</v>
       </c>
@@ -9768,8 +9850,9 @@
       <c r="AO41" s="14">
         <v>21256790</v>
       </c>
-    </row>
-    <row r="42" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AP41" s="14"/>
+    </row>
+    <row r="42" spans="34:42" x14ac:dyDescent="0.3">
       <c r="AH42" s="1" t="s">
         <v>175</v>
       </c>
@@ -9794,8 +9877,9 @@
       <c r="AO42" s="14">
         <v>127592700</v>
       </c>
-    </row>
-    <row r="43" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AP42" s="14"/>
+    </row>
+    <row r="43" spans="34:42" x14ac:dyDescent="0.3">
       <c r="AH43" s="6" t="s">
         <v>176</v>
       </c>
@@ -9820,8 +9904,9 @@
       <c r="AO43" s="14">
         <v>31673230</v>
       </c>
-    </row>
-    <row r="44" spans="34:41" x14ac:dyDescent="0.3">
+      <c r="AP43" s="14"/>
+    </row>
+    <row r="44" spans="34:42" x14ac:dyDescent="0.3">
       <c r="AH44" s="1" t="s">
         <v>179</v>
       </c>
@@ -9846,9 +9931,526 @@
       <c r="AO44" s="14">
         <v>433487500</v>
       </c>
+      <c r="AP44" s="14"/>
+    </row>
+    <row r="49" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH49" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="50" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH50" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI50" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ50" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="AK50" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL50" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH51" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="AI51" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="AJ51" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="AK51" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="AL51" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="52" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH52" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI52" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="AJ52" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="AK52" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="AL52" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="53" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH53" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AI53" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="AJ53" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="AK53" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AL53" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="54" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH54" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="AI54" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="AJ54" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="AK54" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="AL54" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="55" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH55" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="AI55" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="AJ55" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AK55" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AL55" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="56" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH56" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI56" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="AJ56" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="AK56" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="AL56" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="57" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH57" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="AI57" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AJ57" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AK57" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AL57" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="58" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH58" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="AI58" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="AJ58" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="AK58" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="AL58" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="59" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH59" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AI59" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="AJ59" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AK59" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AL59" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="60" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH60" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="AI60" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="AJ60" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="AK60" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="AL60" s="6" t="s">
+        <v>306</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="AI7:AI16">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI22:AI26">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI31:AI35">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI40:AI44">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI22:AO22">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI23:AO23">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI24:AO24">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI25:AO25">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI26:AO26">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI31:AO31">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI32:AO32">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI33:AO33">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI34:AO34">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI35:AO35">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI40:AP40">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI41:AP41">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI42:AP42">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI43:AP43">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI44:AP44">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI7:AP7">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI8:AP8">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI9:AP9">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI10:AP10">
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI11:AP11">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI12:AP12">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI13:AP13">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI14:AP14">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI15:AP15">
     <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
@@ -9860,7 +10462,235 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI22:AI26">
+  <conditionalFormatting sqref="AI16:AP16">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AJ16">
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ22:AJ26">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ31:AJ35">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ40:AJ44">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK7:AK16">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK22:AK26">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK31:AK35">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK40:AK44">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL7:AL16">
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL22:AL26">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL31:AL35">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL40:AL44">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM7:AM16">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM22:AM26">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM31:AM35">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM40:AM44">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN7:AN16">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN22:AN26">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN31:AN35">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -9872,8 +10702,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI22:AO22">
-    <cfRule type="colorScale" priority="29">
+  <conditionalFormatting sqref="AN40:AN44">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9884,8 +10714,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI23:AO23">
-    <cfRule type="colorScale" priority="28">
+  <conditionalFormatting sqref="AO7:AO16">
+    <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9896,8 +10726,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI24:AO24">
-    <cfRule type="colorScale" priority="27">
+  <conditionalFormatting sqref="AO22:AO26">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9908,163 +10738,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI25:AO25">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI26:AO26">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI7:AP7">
-    <cfRule type="colorScale" priority="51">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI8:AP8">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI9:AP9">
-    <cfRule type="colorScale" priority="49">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI10:AP10">
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI11:AP11">
-    <cfRule type="colorScale" priority="46">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI12:AP12">
-    <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI13:AP13">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI14:AP14">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI15:AP15">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI16:AP16">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ7:AJ16">
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ22:AJ26">
+  <conditionalFormatting sqref="AO31:AO35">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -10076,7 +10750,55 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK7:AK16">
+  <conditionalFormatting sqref="AO40:AO44">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP7:AP16">
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BC13:BE16 BG13:BI16 BK13:BM16 BO13:BQ16">
+    <cfRule type="colorScale" priority="91">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BS13:BU16">
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX7:CE7">
     <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
@@ -10088,19 +10810,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK22:AK26">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL7:AL16">
+  <conditionalFormatting sqref="BX8:CE8">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
@@ -10112,19 +10822,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL22:AL26">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM7:AM16">
+  <conditionalFormatting sqref="BX9:CE9">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -10136,19 +10834,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM22:AM26">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN7:AN16">
+  <conditionalFormatting sqref="BX10:CE10">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
@@ -10160,139 +10846,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN22:AN26">
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO7:AO16">
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO22:AO26">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP7:AP16">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BC13:BE16 BG13:BI16 BK13:BM16 BO13:BQ16">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BS13:BU16">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX7:CE7">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX8:CE8">
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX9:CE9">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX10:CE10">
-    <cfRule type="colorScale" priority="37">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI31:AI35">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI31:AO31">
+  <conditionalFormatting sqref="AP40:AP44">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -10304,8 +10858,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI32:AO32">
-    <cfRule type="colorScale" priority="16">
+  <conditionalFormatting sqref="AP31">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10316,8 +10870,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI33:AO33">
-    <cfRule type="colorScale" priority="15">
+  <conditionalFormatting sqref="AP32">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10328,8 +10882,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI34:AO34">
-    <cfRule type="colorScale" priority="14">
+  <conditionalFormatting sqref="AP33">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10340,8 +10894,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI35:AO35">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="AP34">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10352,8 +10906,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ31:AJ35">
-    <cfRule type="colorScale" priority="23">
+  <conditionalFormatting sqref="AP35">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10364,8 +10918,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK31:AK35">
-    <cfRule type="colorScale" priority="22">
+  <conditionalFormatting sqref="AP31:AP35">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10376,67 +10930,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL31:AL35">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM31:AM35">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN31:AN35">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO31:AO35">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI40:AI44">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI40:AO40">
+  <conditionalFormatting sqref="AI31:AP31">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -10448,7 +10942,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI41:AO41">
+  <conditionalFormatting sqref="AI32:AP32">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -10460,7 +10954,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI42:AO42">
+  <conditionalFormatting sqref="AI33:AP33">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10472,7 +10966,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI43:AO43">
+  <conditionalFormatting sqref="AI34:AP34">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10484,80 +10978,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI44:AO44">
+  <conditionalFormatting sqref="AI35:AP35">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ40:AJ44">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK40:AK44">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL40:AL44">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM40:AM44">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN40:AN44">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO40:AO44">
-    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B842F594-9C25-43B9-B9E6-900E327DED9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22D20B1-DF2F-4E22-9997-41AC0C1ACD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
   <sheets>
     <sheet name="literature review" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="325">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -1034,6 +1034,12 @@
   </si>
   <si>
     <t>VAR</t>
+  </si>
+  <si>
+    <t>https://meteostat.net/en/place/co/medellin?s=80110&amp;t=2021-10-31/2024-11-16</t>
+  </si>
+  <si>
+    <t>meteo colombia</t>
   </si>
 </sst>
 </file>
@@ -2141,7 +2147,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA430712-2AF2-46BC-B2A9-A9F8B8AAD612}">
-  <dimension ref="B1:E23"/>
+  <dimension ref="B1:E24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -2320,6 +2326,14 @@
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -2343,6 +2357,7 @@
     <hyperlink ref="B21" r:id="rId17" xr:uid="{076631A6-3276-4BBE-A1D5-B4C566BE8922}"/>
     <hyperlink ref="B22" r:id="rId18" xr:uid="{9A099B35-5ED8-4261-8DF9-3E66B98A53E9}"/>
     <hyperlink ref="B23" r:id="rId19" xr:uid="{147E40C6-D2E1-46D8-854B-3827BE9D5F5D}"/>
+    <hyperlink ref="B24" r:id="rId20" xr:uid="{072E2C55-83F5-4678-A782-C260562B8B6B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10294,66 +10309,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI40:AP40">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI41:AP41">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI42:AP42">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI43:AP43">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI44:AP44">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AI7:AP7">
     <cfRule type="colorScale" priority="68">
       <colorScale>
@@ -10464,6 +10419,126 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="AI16:AP16">
     <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI31:AP31">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI32:AP32">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI33:AP33">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI34:AP34">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI35:AP35">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI40:AP40">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI41:AP41">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI42:AP42">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI43:AP43">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI44:AP44">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10774,6 +10849,90 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AP31">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP31:AP35">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP32">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP33">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP34">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP35">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP40:AP44">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="BC13:BE16 BG13:BI16 BK13:BM16 BO13:BQ16">
     <cfRule type="colorScale" priority="91">
       <colorScale>
@@ -10846,150 +11005,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AP40:AP44">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP31">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP32">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP33">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP34">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP35">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP31:AP35">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI31:AP31">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI32:AP32">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI33:AP33">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI34:AP34">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI35:AP35">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22D20B1-DF2F-4E22-9997-41AC0C1ACD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD79D47-8CD5-4D63-8AAC-D8024168CC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="327">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -1040,6 +1040,12 @@
   </si>
   <si>
     <t>meteo colombia</t>
+  </si>
+  <si>
+    <t>https://trends.google.it/trends/explore?date=2020-01-01%202023-12-31&amp;geo=UY&amp;q=%2Fm%2F05t4q,%2Fm%2F0hpnr,%2Fm%2F01rfps,%2Fm%2F01b_06&amp;hl=en-GB</t>
+  </si>
+  <si>
+    <t>query google trends</t>
   </si>
 </sst>
 </file>
@@ -2147,7 +2153,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA430712-2AF2-46BC-B2A9-A9F8B8AAD612}">
-  <dimension ref="B1:E24"/>
+  <dimension ref="B1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -2334,6 +2340,14 @@
       </c>
       <c r="C24" s="1" t="s">
         <v>324</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -2358,6 +2372,7 @@
     <hyperlink ref="B22" r:id="rId18" xr:uid="{9A099B35-5ED8-4261-8DF9-3E66B98A53E9}"/>
     <hyperlink ref="B23" r:id="rId19" xr:uid="{147E40C6-D2E1-46D8-854B-3827BE9D5F5D}"/>
     <hyperlink ref="B24" r:id="rId20" xr:uid="{072E2C55-83F5-4678-A782-C260562B8B6B}"/>
+    <hyperlink ref="B25" r:id="rId21" xr:uid="{0B637547-4E97-4EC3-B314-56A41CE2A5A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD79D47-8CD5-4D63-8AAC-D8024168CC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6BE1B1-5845-454B-97B9-1E604E698293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
   <sheets>
     <sheet name="literature review" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="330">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -985,42 +985,21 @@
     <t>L3.cases</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>L4.cases</t>
   </si>
   <si>
-    <t>L4.no2</t>
-  </si>
-  <si>
     <t>L5.cases</t>
   </si>
   <si>
     <t>VAR cases log</t>
   </si>
   <si>
-    <t>L1.o3</t>
-  </si>
-  <si>
-    <t>L2.Mean_distance_avg_14day_movavg</t>
-  </si>
-  <si>
-    <t>L3.no2</t>
-  </si>
-  <si>
     <t>L4.o3</t>
   </si>
   <si>
     <t>L5.o3</t>
   </si>
   <si>
-    <t>L3.o3</t>
-  </si>
-  <si>
-    <t>L4.Mean_distance_avg_14day_movavg</t>
-  </si>
-  <si>
     <t>L5.Mean_distance_avg_14day_movavg</t>
   </si>
   <si>
@@ -1046,6 +1025,36 @@
   </si>
   <si>
     <t>query google trends</t>
+  </si>
+  <si>
+    <t>L1.google_symptom</t>
+  </si>
+  <si>
+    <t>L1.google_hospital</t>
+  </si>
+  <si>
+    <t>L1.StringencyIndex_Average</t>
+  </si>
+  <si>
+    <t>L3.google_symptom</t>
+  </si>
+  <si>
+    <t>L2.pm25</t>
+  </si>
+  <si>
+    <t>L2.google_symptom</t>
+  </si>
+  <si>
+    <t>L5.no2</t>
+  </si>
+  <si>
+    <t>L5.google_symptom</t>
+  </si>
+  <si>
+    <t>L3.pm25</t>
+  </si>
+  <si>
+    <t>L4.google_symptom</t>
   </si>
 </sst>
 </file>
@@ -2336,18 +2345,18 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -7275,7 +7284,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93B5247-589C-44F9-8D52-5DE81A7C1480}">
-  <dimension ref="B1:CE60"/>
+  <dimension ref="B1:CE63"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -9428,25 +9437,25 @@
         <v>171</v>
       </c>
       <c r="AI22" s="14">
-        <v>8358205</v>
+        <v>8441809</v>
       </c>
       <c r="AJ22" s="14">
-        <v>6472772</v>
+        <v>6741888</v>
       </c>
       <c r="AK22" s="14">
-        <v>247333.9</v>
+        <v>217327.9</v>
       </c>
       <c r="AL22" s="14">
-        <v>247360.9</v>
+        <v>217397.7</v>
       </c>
       <c r="AM22" s="14">
-        <v>7119606</v>
+        <v>7258473</v>
       </c>
       <c r="AN22" s="14">
-        <v>739199.5</v>
+        <v>923421.7</v>
       </c>
       <c r="AO22" s="14">
-        <v>22672160</v>
+        <v>22672170</v>
       </c>
       <c r="BW22" s="13"/>
       <c r="BX22" s="13"/>
@@ -9460,22 +9469,22 @@
         <v>172</v>
       </c>
       <c r="AI23" s="14">
-        <v>3756126</v>
+        <v>4189569</v>
       </c>
       <c r="AJ23" s="14">
-        <v>1272250</v>
+        <v>1319308</v>
       </c>
       <c r="AK23" s="14">
-        <v>141937.60000000001</v>
+        <v>122447.2</v>
       </c>
       <c r="AL23" s="14">
-        <v>141957.6</v>
+        <v>122322.1</v>
       </c>
       <c r="AM23" s="14">
-        <v>1460144</v>
+        <v>1430908</v>
       </c>
       <c r="AN23" s="14">
-        <v>3376700</v>
+        <v>3468436</v>
       </c>
       <c r="AO23" s="14">
         <v>24316190</v>
@@ -9500,22 +9509,22 @@
         <v>175</v>
       </c>
       <c r="AI24" s="14">
-        <v>42386480</v>
+        <v>43852750</v>
       </c>
       <c r="AJ24" s="14">
-        <v>37853330</v>
+        <v>39165530</v>
       </c>
       <c r="AK24" s="14">
-        <v>2035471</v>
+        <v>2108284</v>
       </c>
       <c r="AL24" s="14">
-        <v>2035450</v>
+        <v>2108237</v>
       </c>
       <c r="AM24" s="14">
-        <v>40214680</v>
+        <v>41151780</v>
       </c>
       <c r="AN24" s="14">
-        <v>1304844</v>
+        <v>2839716</v>
       </c>
       <c r="AO24" s="14">
         <v>122159800</v>
@@ -9541,22 +9550,22 @@
         <v>176</v>
       </c>
       <c r="AI25" s="14">
-        <v>8256902</v>
+        <v>8964942</v>
       </c>
       <c r="AJ25" s="14">
-        <v>8702138</v>
+        <v>8945718</v>
       </c>
       <c r="AK25" s="14">
-        <v>400986.7</v>
+        <v>369454.8</v>
       </c>
       <c r="AL25" s="14">
-        <v>401188.3</v>
+        <v>368821.8</v>
       </c>
       <c r="AM25" s="14">
-        <v>8497244</v>
+        <v>8818598</v>
       </c>
       <c r="AN25" s="14">
-        <v>2367122</v>
+        <v>2741323</v>
       </c>
       <c r="AO25" s="14">
         <v>30861490</v>
@@ -9582,25 +9591,25 @@
         <v>179</v>
       </c>
       <c r="AI26" s="14">
-        <v>87020490</v>
+        <v>97036170</v>
       </c>
       <c r="AJ26" s="14">
-        <v>87979830</v>
+        <v>91167670</v>
       </c>
       <c r="AK26" s="14">
-        <v>3994550</v>
+        <v>2541037</v>
       </c>
       <c r="AL26" s="14">
-        <v>3993905</v>
+        <v>2547046</v>
       </c>
       <c r="AM26" s="14">
-        <v>99369740</v>
+        <v>104857300</v>
       </c>
       <c r="AN26" s="14">
-        <v>18872380</v>
+        <v>16466860</v>
       </c>
       <c r="AO26" s="14">
-        <v>426086100</v>
+        <v>426086200</v>
       </c>
       <c r="BC26" s="27"/>
       <c r="BD26" s="28"/>
@@ -9649,7 +9658,7 @@
         <v>233</v>
       </c>
       <c r="AP30" s="9" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="34:80" x14ac:dyDescent="0.3">
@@ -9657,28 +9666,28 @@
         <v>171</v>
       </c>
       <c r="AI31" s="14">
-        <v>8448053</v>
+        <v>8545518</v>
       </c>
       <c r="AJ31" s="14">
-        <v>6780585</v>
+        <v>7276467</v>
       </c>
       <c r="AK31" s="14">
-        <v>65899.95</v>
+        <v>45099.8</v>
       </c>
       <c r="AL31" s="14">
-        <v>59433.07</v>
+        <v>40432.839999999997</v>
       </c>
       <c r="AM31" s="14">
-        <v>7730858</v>
+        <v>7678303</v>
       </c>
       <c r="AN31" s="14">
-        <v>772883.5</v>
+        <v>963486.9</v>
       </c>
       <c r="AO31" s="14">
         <v>22698710</v>
       </c>
       <c r="AP31" s="14">
-        <v>4344672</v>
+        <v>7268706</v>
       </c>
     </row>
     <row r="32" spans="34:80" x14ac:dyDescent="0.3">
@@ -9686,28 +9695,28 @@
         <v>172</v>
       </c>
       <c r="AI32" s="14">
-        <v>3641375</v>
+        <v>3983888</v>
       </c>
       <c r="AJ32" s="14">
-        <v>1288990</v>
+        <v>1321752</v>
       </c>
       <c r="AK32" s="14">
-        <v>98367.06</v>
+        <v>114767.7</v>
       </c>
       <c r="AL32" s="14">
-        <v>147808.5</v>
+        <v>148072.1</v>
       </c>
       <c r="AM32" s="14">
-        <v>1442136</v>
+        <v>1455460</v>
       </c>
       <c r="AN32" s="14">
-        <v>3279935</v>
+        <v>3324201</v>
       </c>
       <c r="AO32" s="14">
         <v>23558110</v>
       </c>
       <c r="AP32" s="14">
-        <v>2015265</v>
+        <v>1387276</v>
       </c>
     </row>
     <row r="33" spans="34:42" x14ac:dyDescent="0.3">
@@ -9715,28 +9724,28 @@
         <v>175</v>
       </c>
       <c r="AI33" s="14">
-        <v>44264800</v>
+        <v>45450350</v>
       </c>
       <c r="AJ33" s="14">
-        <v>39037660</v>
+        <v>36017980</v>
       </c>
       <c r="AK33" s="14">
-        <v>396822.9</v>
+        <v>328257.59999999998</v>
       </c>
       <c r="AL33" s="14">
-        <v>410083.2</v>
+        <v>327651.09999999998</v>
       </c>
       <c r="AM33" s="14">
-        <v>40922950</v>
+        <v>39467590</v>
       </c>
       <c r="AN33" s="14">
-        <v>2976958</v>
+        <v>4967453</v>
       </c>
       <c r="AO33" s="14">
         <v>123353700</v>
       </c>
       <c r="AP33" s="14">
-        <v>152331600</v>
+        <v>86397360</v>
       </c>
     </row>
     <row r="34" spans="34:42" x14ac:dyDescent="0.3">
@@ -9744,28 +9753,28 @@
         <v>176</v>
       </c>
       <c r="AI34" s="14">
-        <v>8295826</v>
+        <v>9150194</v>
       </c>
       <c r="AJ34" s="14">
-        <v>8770232</v>
+        <v>9187983</v>
       </c>
       <c r="AK34" s="14">
-        <v>236383.9</v>
+        <v>143265.1</v>
       </c>
       <c r="AL34" s="14">
-        <v>268165.8</v>
+        <v>160340.1</v>
       </c>
       <c r="AM34" s="14">
-        <v>8565617</v>
+        <v>8707002</v>
       </c>
       <c r="AN34" s="14">
-        <v>2513404</v>
+        <v>2793362</v>
       </c>
       <c r="AO34" s="14">
         <v>31047740</v>
       </c>
       <c r="AP34" s="14">
-        <v>3783188</v>
+        <v>6536393</v>
       </c>
     </row>
     <row r="35" spans="34:42" x14ac:dyDescent="0.3">
@@ -9773,28 +9782,28 @@
         <v>179</v>
       </c>
       <c r="AI35" s="14">
-        <v>88022780</v>
+        <v>97801220</v>
       </c>
       <c r="AJ35" s="14">
-        <v>81075680</v>
+        <v>88807950</v>
       </c>
       <c r="AK35" s="14">
-        <v>1296517</v>
+        <v>1981908</v>
       </c>
       <c r="AL35" s="14">
-        <v>1329986</v>
+        <v>1751053</v>
       </c>
       <c r="AM35" s="14">
-        <v>99065760</v>
+        <v>102744800</v>
       </c>
       <c r="AN35" s="14">
-        <v>19143400</v>
+        <v>15589460</v>
       </c>
       <c r="AO35" s="14">
         <v>427453400</v>
       </c>
       <c r="AP35" s="14">
-        <v>228807800</v>
+        <v>259778200</v>
       </c>
     </row>
     <row r="38" spans="34:42" x14ac:dyDescent="0.3">
@@ -9833,22 +9842,22 @@
         <v>171</v>
       </c>
       <c r="AI40" s="14">
-        <v>8300763</v>
+        <v>8333632</v>
       </c>
       <c r="AJ40" s="14">
-        <v>7395443</v>
+        <v>7639386</v>
       </c>
       <c r="AK40" s="14">
-        <v>408375.8</v>
+        <v>318639</v>
       </c>
       <c r="AL40" s="14">
-        <v>408305.3</v>
+        <v>318678.2</v>
       </c>
       <c r="AM40" s="14">
-        <v>7755566</v>
+        <v>7553660</v>
       </c>
       <c r="AN40" s="14">
-        <v>1238832</v>
+        <v>1062718</v>
       </c>
       <c r="AO40" s="14">
         <v>22730730</v>
@@ -9860,25 +9869,25 @@
         <v>172</v>
       </c>
       <c r="AI41" s="14">
-        <v>3779986</v>
+        <v>4180177</v>
       </c>
       <c r="AJ41" s="14">
-        <v>1261350</v>
+        <v>1297426</v>
       </c>
       <c r="AK41" s="14">
-        <v>2078308</v>
+        <v>1861296</v>
       </c>
       <c r="AL41" s="14">
-        <v>2078353</v>
+        <v>1861223</v>
       </c>
       <c r="AM41" s="14">
-        <v>1379444</v>
+        <v>1367516</v>
       </c>
       <c r="AN41" s="14">
-        <v>3793630</v>
+        <v>3854216</v>
       </c>
       <c r="AO41" s="14">
-        <v>21256790</v>
+        <v>21256800</v>
       </c>
       <c r="AP41" s="14"/>
     </row>
@@ -9887,22 +9896,22 @@
         <v>175</v>
       </c>
       <c r="AI42" s="14">
-        <v>43990100</v>
+        <v>45846120</v>
       </c>
       <c r="AJ42" s="14">
-        <v>39106190</v>
+        <v>39437130</v>
       </c>
       <c r="AK42" s="14">
-        <v>3578022</v>
+        <v>3234668</v>
       </c>
       <c r="AL42" s="14">
-        <v>3578005</v>
+        <v>3234677</v>
       </c>
       <c r="AM42" s="14">
-        <v>44898540</v>
+        <v>43241250</v>
       </c>
       <c r="AN42" s="14">
-        <v>5110701</v>
+        <v>5947889</v>
       </c>
       <c r="AO42" s="14">
         <v>127592700</v>
@@ -9914,22 +9923,22 @@
         <v>176</v>
       </c>
       <c r="AI43" s="14">
-        <v>8065792</v>
+        <v>8779838</v>
       </c>
       <c r="AJ43" s="14">
-        <v>8527451</v>
+        <v>8789270</v>
       </c>
       <c r="AK43" s="14">
-        <v>2342675</v>
+        <v>1096361</v>
       </c>
       <c r="AL43" s="14">
-        <v>2342966</v>
+        <v>1097970</v>
       </c>
       <c r="AM43" s="14">
-        <v>8968693</v>
+        <v>8932713</v>
       </c>
       <c r="AN43" s="14">
-        <v>3263058</v>
+        <v>2712343</v>
       </c>
       <c r="AO43" s="14">
         <v>31673230</v>
@@ -9941,22 +9950,22 @@
         <v>179</v>
       </c>
       <c r="AI44" s="14">
-        <v>80946790</v>
+        <v>84855730</v>
       </c>
       <c r="AJ44" s="14">
-        <v>78253060</v>
+        <v>76684460</v>
       </c>
       <c r="AK44" s="14">
-        <v>16474180</v>
+        <v>21991510</v>
       </c>
       <c r="AL44" s="14">
-        <v>16476130</v>
+        <v>22016230</v>
       </c>
       <c r="AM44" s="14">
-        <v>91963430</v>
+        <v>93464800</v>
       </c>
       <c r="AN44" s="14">
-        <v>19756890</v>
+        <v>16716870</v>
       </c>
       <c r="AO44" s="14">
         <v>433487500</v>
@@ -9965,7 +9974,7 @@
     </row>
     <row r="49" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH49" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="34:38" x14ac:dyDescent="0.3">
@@ -10007,157 +10016,138 @@
         <v>303</v>
       </c>
       <c r="AI52" s="6" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="AJ52" s="6" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="AK52" s="6" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="AL52" s="6" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH53" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="AI53" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="AJ53" s="1" t="s">
         <v>304</v>
       </c>
       <c r="AK53" s="1" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="AL53" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="54" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH54" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AI54" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AJ54" s="6" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="AK54" s="6" t="s">
         <v>306</v>
       </c>
       <c r="AL54" s="6" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH55" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AI55" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="AJ55" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="AK55" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="AJ55" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="AK55" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="AL55" s="1" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH56" s="6" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="AI56" s="6" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="AJ56" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="AK56" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="AL56" s="6" t="s">
-        <v>306</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="AK56" s="6"/>
+      <c r="AL56" s="6"/>
     </row>
     <row r="57" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH57" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="AI57" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AJ57" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="58" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH58" s="6"/>
+      <c r="AI58" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="AJ58" s="6"/>
+      <c r="AK58" s="6"/>
+      <c r="AL58" s="6"/>
+    </row>
+    <row r="59" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AI59" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="AI57" s="1" t="s">
+    </row>
+    <row r="60" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH60" s="6"/>
+      <c r="AI60" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="AJ60" s="6"/>
+      <c r="AK60" s="6"/>
+      <c r="AL60" s="6"/>
+    </row>
+    <row r="61" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AI61" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="62" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AH62" s="6"/>
+      <c r="AI62" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="AJ57" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="AK57" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="AL57" s="1" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="58" spans="34:38" x14ac:dyDescent="0.3">
-      <c r="AH58" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="AI58" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="AJ58" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="AK58" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="AL58" s="6" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="59" spans="34:38" x14ac:dyDescent="0.3">
-      <c r="AH59" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="AI59" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="AJ59" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="AK59" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="AL59" s="1" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="60" spans="34:38" x14ac:dyDescent="0.3">
-      <c r="AH60" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="AI60" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="AJ60" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="AK60" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="AL60" s="6" t="s">
-        <v>306</v>
+      <c r="AJ62" s="6"/>
+      <c r="AK62" s="6"/>
+      <c r="AL62" s="6"/>
+    </row>
+    <row r="63" spans="34:38" x14ac:dyDescent="0.3">
+      <c r="AI63" s="1" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="AI7:AI16">
-    <cfRule type="colorScale" priority="76">
+    <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10169,7 +10159,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI22:AI26">
-    <cfRule type="colorScale" priority="53">
+    <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10181,7 +10171,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI31:AI35">
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10193,7 +10183,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI40:AI44">
-    <cfRule type="colorScale" priority="29">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10205,7 +10195,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI22:AO22">
-    <cfRule type="colorScale" priority="46">
+    <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10217,7 +10207,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI23:AO23">
-    <cfRule type="colorScale" priority="45">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10229,7 +10219,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI24:AO24">
-    <cfRule type="colorScale" priority="44">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10241,7 +10231,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI25:AO25">
-    <cfRule type="colorScale" priority="43">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10253,7 +10243,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI26:AO26">
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10265,7 +10255,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI31:AO31">
-    <cfRule type="colorScale" priority="34">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10277,7 +10267,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI32:AO32">
-    <cfRule type="colorScale" priority="33">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10289,7 +10279,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI33:AO33">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10301,7 +10291,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI34:AO34">
-    <cfRule type="colorScale" priority="31">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10313,7 +10303,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI35:AO35">
-    <cfRule type="colorScale" priority="30">
+    <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10325,6 +10315,54 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI7:AP7">
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI8:AP8">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI9:AP9">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI10:AP10">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI11:AP11">
     <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="min"/>
@@ -10336,7 +10374,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI8:AP8">
+  <conditionalFormatting sqref="AI12:AP12">
     <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="min"/>
@@ -10348,7 +10386,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI9:AP9">
+  <conditionalFormatting sqref="AI13:AP13">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
@@ -10360,7 +10398,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI10:AP10">
+  <conditionalFormatting sqref="AI14:AP14">
     <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
@@ -10372,56 +10410,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI11:AP11">
-    <cfRule type="colorScale" priority="63">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI12:AP12">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI13:AP13">
-    <cfRule type="colorScale" priority="61">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI14:AP14">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AI15:AP15">
-    <cfRule type="colorScale" priority="59">
+    <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10433,7 +10423,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI16:AP16">
-    <cfRule type="colorScale" priority="58">
+    <cfRule type="colorScale" priority="63">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10505,6 +10495,378 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI40:AP40">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI41:AP41">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI42:AP42">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI43:AP43">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI44:AP44">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AJ16">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ22:AJ26">
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ31:AJ35">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ40:AJ44">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK7:AK16">
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK22:AK26">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK31:AK35">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK40:AK44">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL7:AL16">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL22:AL26">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL31:AL35">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL40:AL44">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM7:AM16">
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM22:AM26">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM31:AM35">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM40:AM44">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN7:AN16">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN22:AN26">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN31:AN35">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN40:AN44">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO7:AO16">
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO22:AO26">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO31:AO35">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO40:AO44">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP7:AP16">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP31">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP31:AP35">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -10516,19 +10878,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI41:AP41">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI42:AP42">
+  <conditionalFormatting sqref="AP32">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -10540,7 +10890,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI43:AP43">
+  <conditionalFormatting sqref="AP33">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -10552,7 +10902,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI44:AP44">
+  <conditionalFormatting sqref="AP34">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -10564,319 +10914,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ7:AJ16">
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ22:AJ26">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ31:AJ35">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ40:AJ44">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK7:AK16">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK22:AK26">
-    <cfRule type="colorScale" priority="51">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK31:AK35">
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK40:AK44">
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL7:AL16">
-    <cfRule type="colorScale" priority="73">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL22:AL26">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL31:AL35">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL40:AL44">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM7:AM16">
-    <cfRule type="colorScale" priority="72">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM22:AM26">
-    <cfRule type="colorScale" priority="49">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM31:AM35">
-    <cfRule type="colorScale" priority="37">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM40:AM44">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN7:AN16">
-    <cfRule type="colorScale" priority="71">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN22:AN26">
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN31:AN35">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN40:AN44">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO7:AO16">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO22:AO26">
-    <cfRule type="colorScale" priority="47">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO31:AO35">
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO40:AO44">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP7:AP16">
-    <cfRule type="colorScale" priority="69">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP31">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP31:AP35">
+  <conditionalFormatting sqref="AP35">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -10888,56 +10926,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AP32">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP33">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP34">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP35">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AP40:AP44">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10949,7 +10939,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC13:BE16 BG13:BI16 BK13:BM16 BO13:BQ16">
-    <cfRule type="colorScale" priority="91">
+    <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10961,7 +10951,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS13:BU16">
-    <cfRule type="colorScale" priority="79">
+    <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10973,7 +10963,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BX7:CE7">
-    <cfRule type="colorScale" priority="57">
+    <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10985,7 +10975,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BX8:CE8">
-    <cfRule type="colorScale" priority="56">
+    <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10997,7 +10987,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BX9:CE9">
-    <cfRule type="colorScale" priority="55">
+    <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11009,7 +10999,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BX10:CE10">
-    <cfRule type="colorScale" priority="54">
+    <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6BE1B1-5845-454B-97B9-1E604E698293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95322EF9-6CD9-4F00-A53B-602DC4A4A41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="352">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -1055,6 +1055,72 @@
   </si>
   <si>
     <t>L4.google_symptom</t>
+  </si>
+  <si>
+    <t>Epidemic</t>
+  </si>
+  <si>
+    <t>Chikungunya</t>
+  </si>
+  <si>
+    <t>Chickenpox</t>
+  </si>
+  <si>
+    <t>L1.zika_cumulative</t>
+  </si>
+  <si>
+    <t>L1.dengue_cumulative</t>
+  </si>
+  <si>
+    <t>L1.prcp</t>
+  </si>
+  <si>
+    <t>L2.pres</t>
+  </si>
+  <si>
+    <t>L1.var_cumulative</t>
+  </si>
+  <si>
+    <t>L2.dengue_cumulative</t>
+  </si>
+  <si>
+    <t>L2.zika_cumulative</t>
+  </si>
+  <si>
+    <t>L3.chik_cumulative</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>L3.pres</t>
+  </si>
+  <si>
+    <t>L4.chik_cumulative</t>
+  </si>
+  <si>
+    <t>L5.tavg</t>
+  </si>
+  <si>
+    <t>L2.google_pharmacy</t>
+  </si>
+  <si>
+    <t>L5.chik_cumulative</t>
+  </si>
+  <si>
+    <t>L3.zika_cumulative</t>
+  </si>
+  <si>
+    <t>L3.tavg</t>
+  </si>
+  <si>
+    <t>L4.zika_cumulative</t>
+  </si>
+  <si>
+    <t>L4.tavg</t>
+  </si>
+  <si>
+    <t>t+1</t>
   </si>
 </sst>
 </file>
@@ -9110,6 +9176,9 @@
       <c r="BS14" s="14"/>
       <c r="BT14" s="14"/>
       <c r="BU14" s="14"/>
+      <c r="BW14" s="1" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="15" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
@@ -9239,8 +9308,33 @@
       <c r="BS15" s="14"/>
       <c r="BT15" s="14"/>
       <c r="BU15" s="14"/>
-      <c r="CA15" s="13"/>
-      <c r="CB15" s="13"/>
+      <c r="BW15" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="BX15" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="BY15" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="BZ15" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="CA15" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="CB15" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="CC15" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="CD15" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="CE15" s="9" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="16" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
@@ -9370,26 +9464,122 @@
       <c r="BS16" s="14"/>
       <c r="BT16" s="14"/>
       <c r="BU16" s="14"/>
-      <c r="CA16" s="13"/>
-      <c r="CB16" s="13"/>
-    </row>
-    <row r="17" spans="34:80" x14ac:dyDescent="0.3">
-      <c r="CA17" s="13"/>
-      <c r="CB17" s="13"/>
-    </row>
-    <row r="18" spans="34:80" x14ac:dyDescent="0.3">
-      <c r="CA18" s="13"/>
-      <c r="CB18" s="13"/>
-    </row>
-    <row r="19" spans="34:80" x14ac:dyDescent="0.3">
-      <c r="BW19" s="19"/>
-      <c r="BX19" s="19"/>
-      <c r="BY19" s="19"/>
-      <c r="BZ19" s="13"/>
-      <c r="CA19" s="13"/>
-      <c r="CB19" s="13"/>
-    </row>
-    <row r="20" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="BW16" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="BX16" s="14">
+        <v>7.3023619999999996</v>
+      </c>
+      <c r="BY16" s="14">
+        <v>23.153338999999999</v>
+      </c>
+      <c r="BZ16" s="14">
+        <v>1.312649</v>
+      </c>
+      <c r="CA16" s="14">
+        <v>1.6906680000000001</v>
+      </c>
+      <c r="CB16" s="14">
+        <v>24.156554</v>
+      </c>
+      <c r="CC16" s="14">
+        <v>9.6223559999999999</v>
+      </c>
+      <c r="CD16" s="14">
+        <v>107.470157</v>
+      </c>
+      <c r="CE16" s="14">
+        <v>31.725518000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="34:83" x14ac:dyDescent="0.3">
+      <c r="BW17" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="BX17" s="17">
+        <v>27784.75676</v>
+      </c>
+      <c r="BY17" s="17">
+        <v>45692.435870000001</v>
+      </c>
+      <c r="BZ17" s="17">
+        <v>831.05332099999998</v>
+      </c>
+      <c r="CA17" s="17">
+        <v>349.12991</v>
+      </c>
+      <c r="CB17" s="17">
+        <v>47565.684982999999</v>
+      </c>
+      <c r="CC17" s="17">
+        <v>13343.920405000001</v>
+      </c>
+      <c r="CD17" s="17">
+        <v>121114.350896</v>
+      </c>
+      <c r="CE17" s="17">
+        <v>6894.8666080000003</v>
+      </c>
+    </row>
+    <row r="18" spans="34:83" x14ac:dyDescent="0.3">
+      <c r="BW18" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="BX18" s="14">
+        <v>6912.7279230000004</v>
+      </c>
+      <c r="BY18" s="14">
+        <v>16731.626419</v>
+      </c>
+      <c r="BZ18" s="14">
+        <v>1236.609516</v>
+      </c>
+      <c r="CA18" s="14">
+        <v>66.889324000000002</v>
+      </c>
+      <c r="CB18" s="14">
+        <v>17334.479093000002</v>
+      </c>
+      <c r="CC18" s="14">
+        <v>657.88363900000002</v>
+      </c>
+      <c r="CD18" s="14">
+        <v>48215.132081999996</v>
+      </c>
+      <c r="CE18" s="14">
+        <v>8147.0878750000002</v>
+      </c>
+    </row>
+    <row r="19" spans="34:83" x14ac:dyDescent="0.3">
+      <c r="BW19" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="BX19" s="17">
+        <v>12.758763999999999</v>
+      </c>
+      <c r="BY19" s="17">
+        <v>11.847369</v>
+      </c>
+      <c r="BZ19" s="17">
+        <v>1.5559229999999999</v>
+      </c>
+      <c r="CA19" s="17">
+        <v>1.591691</v>
+      </c>
+      <c r="CB19" s="17">
+        <v>12.320406999999999</v>
+      </c>
+      <c r="CC19" s="17">
+        <v>8.3875679999999999</v>
+      </c>
+      <c r="CD19" s="17">
+        <v>67.611076999999995</v>
+      </c>
+      <c r="CE19" s="17">
+        <v>25.013144</v>
+      </c>
+    </row>
+    <row r="20" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH20" s="1" t="s">
         <v>250</v>
       </c>
@@ -9400,7 +9590,7 @@
       <c r="CA20" s="13"/>
       <c r="CB20" s="13"/>
     </row>
-    <row r="21" spans="34:80" x14ac:dyDescent="0.3">
+    <row r="21" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH21" s="9" t="s">
         <v>165</v>
       </c>
@@ -9432,7 +9622,7 @@
       <c r="CA21" s="13"/>
       <c r="CB21" s="13"/>
     </row>
-    <row r="22" spans="34:80" x14ac:dyDescent="0.3">
+    <row r="22" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH22" s="1" t="s">
         <v>171</v>
       </c>
@@ -9464,7 +9654,7 @@
       <c r="CA22" s="13"/>
       <c r="CB22" s="13"/>
     </row>
-    <row r="23" spans="34:80" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH23" s="6" t="s">
         <v>172</v>
       </c>
@@ -9504,7 +9694,7 @@
       <c r="BT23" s="27"/>
       <c r="BU23" s="27"/>
     </row>
-    <row r="24" spans="34:80" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH24" s="1" t="s">
         <v>175</v>
       </c>
@@ -9545,7 +9735,7 @@
       <c r="BT24" s="28"/>
       <c r="BU24" s="28"/>
     </row>
-    <row r="25" spans="34:80" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH25" s="6" t="s">
         <v>176</v>
       </c>
@@ -9585,8 +9775,11 @@
       <c r="BS25" s="28"/>
       <c r="BT25" s="28"/>
       <c r="BU25" s="28"/>
-    </row>
-    <row r="26" spans="34:80" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="BX25" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="26" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH26" s="1" t="s">
         <v>179</v>
       </c>
@@ -9626,13 +9819,65 @@
       <c r="BS26" s="28"/>
       <c r="BT26" s="28"/>
       <c r="BU26" s="28"/>
-    </row>
-    <row r="29" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="BX26" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="BY26" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="BZ26" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="CA26" s="9" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="27" spans="34:83" x14ac:dyDescent="0.3">
+      <c r="BX27" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="BY27" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="BZ27" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="CA27" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="28" spans="34:83" x14ac:dyDescent="0.3">
+      <c r="BX28" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="BY28" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="BZ28" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="CA28" s="6" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="29" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH29" s="29" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="30" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="BX29" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="BY29" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="BZ29" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="CA29" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="30" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH30" s="9" t="s">
         <v>165</v>
       </c>
@@ -9660,8 +9905,20 @@
       <c r="AP30" s="9" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="31" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="BX30" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="BY30" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="BZ30" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="CA30" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="31" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH31" s="1" t="s">
         <v>171</v>
       </c>
@@ -9689,8 +9946,20 @@
       <c r="AP31" s="14">
         <v>7268706</v>
       </c>
-    </row>
-    <row r="32" spans="34:80" x14ac:dyDescent="0.3">
+      <c r="BX31" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="BY31" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="BZ31" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="CA31" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="32" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH32" s="6" t="s">
         <v>172</v>
       </c>
@@ -9718,8 +9987,20 @@
       <c r="AP32" s="14">
         <v>1387276</v>
       </c>
-    </row>
-    <row r="33" spans="34:42" x14ac:dyDescent="0.3">
+      <c r="BX32" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="BY32" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="BZ32" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="CA32" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="33" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH33" s="1" t="s">
         <v>175</v>
       </c>
@@ -9747,8 +10028,20 @@
       <c r="AP33" s="14">
         <v>86397360</v>
       </c>
-    </row>
-    <row r="34" spans="34:42" x14ac:dyDescent="0.3">
+      <c r="BX33" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="BY33" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="BZ33" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="CA33" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="34" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH34" s="6" t="s">
         <v>176</v>
       </c>
@@ -9776,8 +10069,20 @@
       <c r="AP34" s="14">
         <v>6536393</v>
       </c>
-    </row>
-    <row r="35" spans="34:42" x14ac:dyDescent="0.3">
+      <c r="BX34" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="BY34" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="BZ34" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="CA34" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="35" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH35" s="1" t="s">
         <v>179</v>
       </c>
@@ -9805,13 +10110,25 @@
       <c r="AP35" s="14">
         <v>259778200</v>
       </c>
-    </row>
-    <row r="38" spans="34:42" x14ac:dyDescent="0.3">
+      <c r="BX35" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="BY35" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="BZ35" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="CA35" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="38" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH38" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="39" spans="34:42" x14ac:dyDescent="0.3">
+    <row r="39" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH39" s="9" t="s">
         <v>165</v>
       </c>
@@ -9837,7 +10154,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="40" spans="34:42" x14ac:dyDescent="0.3">
+    <row r="40" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH40" s="1" t="s">
         <v>171</v>
       </c>
@@ -9864,7 +10181,7 @@
       </c>
       <c r="AP40" s="14"/>
     </row>
-    <row r="41" spans="34:42" x14ac:dyDescent="0.3">
+    <row r="41" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH41" s="6" t="s">
         <v>172</v>
       </c>
@@ -9891,7 +10208,7 @@
       </c>
       <c r="AP41" s="14"/>
     </row>
-    <row r="42" spans="34:42" x14ac:dyDescent="0.3">
+    <row r="42" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH42" s="1" t="s">
         <v>175</v>
       </c>
@@ -9918,7 +10235,7 @@
       </c>
       <c r="AP42" s="14"/>
     </row>
-    <row r="43" spans="34:42" x14ac:dyDescent="0.3">
+    <row r="43" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH43" s="6" t="s">
         <v>176</v>
       </c>
@@ -9945,7 +10262,7 @@
       </c>
       <c r="AP43" s="14"/>
     </row>
-    <row r="44" spans="34:42" x14ac:dyDescent="0.3">
+    <row r="44" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH44" s="1" t="s">
         <v>179</v>
       </c>
@@ -10147,6 +10464,558 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="AI7:AI16">
+    <cfRule type="colorScale" priority="85">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI22:AI26">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI31:AI35">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI40:AI44">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI22:AO22">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI23:AO23">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI24:AO24">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI25:AO25">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI26:AO26">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI31:AO31">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI32:AO32">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI33:AO33">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI34:AO34">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI35:AO35">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI7:AP7">
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI8:AP8">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI9:AP9">
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI10:AP10">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI11:AP11">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI12:AP12">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI13:AP13">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI14:AP14">
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI15:AP15">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI16:AP16">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI31:AP31">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI32:AP32">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI33:AP33">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI34:AP34">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI35:AP35">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI40:AP40">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI41:AP41">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI42:AP42">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI43:AP43">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI44:AP44">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AJ16">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ22:AJ26">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ31:AJ35">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ40:AJ44">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK7:AK16">
+    <cfRule type="colorScale" priority="83">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK22:AK26">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK31:AK35">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK40:AK44">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL7:AL16">
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL22:AL26">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL31:AL35">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL40:AL44">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AM7:AM16">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -10158,7 +11027,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI22:AI26">
+  <conditionalFormatting sqref="AM22:AM26">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min"/>
@@ -10170,7 +11039,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI31:AI35">
+  <conditionalFormatting sqref="AM31:AM35">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
@@ -10182,7 +11051,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI40:AI44">
+  <conditionalFormatting sqref="AM40:AM44">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
@@ -10194,8 +11063,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI22:AO22">
-    <cfRule type="colorScale" priority="51">
+  <conditionalFormatting sqref="AN7:AN16">
+    <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10206,8 +11075,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI23:AO23">
-    <cfRule type="colorScale" priority="50">
+  <conditionalFormatting sqref="AN22:AN26">
+    <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10218,8 +11087,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI24:AO24">
-    <cfRule type="colorScale" priority="49">
+  <conditionalFormatting sqref="AN31:AN35">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10230,8 +11099,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI25:AO25">
-    <cfRule type="colorScale" priority="48">
+  <conditionalFormatting sqref="AN40:AN44">
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10242,8 +11111,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI26:AO26">
-    <cfRule type="colorScale" priority="47">
+  <conditionalFormatting sqref="AO7:AO16">
+    <cfRule type="colorScale" priority="79">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10254,8 +11123,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI31:AO31">
-    <cfRule type="colorScale" priority="39">
+  <conditionalFormatting sqref="AO22:AO26">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10266,8 +11135,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI32:AO32">
-    <cfRule type="colorScale" priority="38">
+  <conditionalFormatting sqref="AO31:AO35">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10278,8 +11147,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI33:AO33">
-    <cfRule type="colorScale" priority="37">
+  <conditionalFormatting sqref="AO40:AO44">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10290,8 +11159,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI34:AO34">
-    <cfRule type="colorScale" priority="36">
+  <conditionalFormatting sqref="AP7:AP16">
+    <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10302,8 +11171,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI35:AO35">
-    <cfRule type="colorScale" priority="35">
+  <conditionalFormatting sqref="AP31">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10314,8 +11183,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI7:AP7">
-    <cfRule type="colorScale" priority="73">
+  <conditionalFormatting sqref="AP31:AP35">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10326,8 +11195,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI8:AP8">
-    <cfRule type="colorScale" priority="72">
+  <conditionalFormatting sqref="AP32">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10338,8 +11207,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI9:AP9">
-    <cfRule type="colorScale" priority="71">
+  <conditionalFormatting sqref="AP33">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10350,8 +11219,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI10:AP10">
-    <cfRule type="colorScale" priority="70">
+  <conditionalFormatting sqref="AP34">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10362,8 +11231,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI11:AP11">
-    <cfRule type="colorScale" priority="68">
+  <conditionalFormatting sqref="AP35">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10374,8 +11243,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI12:AP12">
-    <cfRule type="colorScale" priority="67">
+  <conditionalFormatting sqref="AP40:AP44">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10386,7 +11255,31 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI13:AP13">
+  <conditionalFormatting sqref="BC13:BE16 BG13:BI16 BK13:BM16 BO13:BQ16">
+    <cfRule type="colorScale" priority="100">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BS13:BU16">
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX7:CE7">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
@@ -10398,7 +11291,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI14:AP14">
+  <conditionalFormatting sqref="BX8:CE8">
     <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
@@ -10410,7 +11303,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI15:AP15">
+  <conditionalFormatting sqref="BX9:CE9">
     <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="min"/>
@@ -10422,7 +11315,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI16:AP16">
+  <conditionalFormatting sqref="BX10:CE10">
     <cfRule type="colorScale" priority="63">
       <colorScale>
         <cfvo type="min"/>
@@ -10434,19 +11327,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI31:AP31">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI32:AP32">
+  <conditionalFormatting sqref="BX16:CE16">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -10458,7 +11339,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI33:AP33">
+  <conditionalFormatting sqref="BX17:CE17">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10470,7 +11351,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI34:AP34">
+  <conditionalFormatting sqref="BX18:CE18">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10482,524 +11363,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI35:AP35">
+  <conditionalFormatting sqref="BX19:CE19">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI40:AP40">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI41:AP41">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI42:AP42">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI43:AP43">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI44:AP44">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ7:AJ16">
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ22:AJ26">
-    <cfRule type="colorScale" priority="57">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ31:AJ35">
-    <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ40:AJ44">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK7:AK16">
-    <cfRule type="colorScale" priority="79">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK22:AK26">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK31:AK35">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK40:AK44">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL7:AL16">
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL22:AL26">
-    <cfRule type="colorScale" priority="55">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL31:AL35">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL40:AL44">
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM7:AM16">
-    <cfRule type="colorScale" priority="77">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM22:AM26">
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM31:AM35">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AM40:AM44">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN7:AN16">
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN22:AN26">
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN31:AN35">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN40:AN44">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO7:AO16">
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO22:AO26">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO31:AO35">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO40:AO44">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP7:AP16">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP31">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP31:AP35">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP32">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP33">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP34">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP35">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP40:AP44">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BC13:BE16 BG13:BI16 BK13:BM16 BO13:BQ16">
-    <cfRule type="colorScale" priority="96">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BS13:BU16">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX7:CE7">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX8:CE8">
-    <cfRule type="colorScale" priority="61">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX9:CE9">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BX10:CE10">
-    <cfRule type="colorScale" priority="59">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95322EF9-6CD9-4F00-A53B-602DC4A4A41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAC58CD-0470-4196-97D5-0434328969E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="354">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -1090,15 +1090,9 @@
     <t>L3.chik_cumulative</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>L3.pres</t>
   </si>
   <si>
-    <t>L4.chik_cumulative</t>
-  </si>
-  <si>
     <t>L5.tavg</t>
   </si>
   <si>
@@ -1111,16 +1105,28 @@
     <t>L3.zika_cumulative</t>
   </si>
   <si>
-    <t>L3.tavg</t>
-  </si>
-  <si>
     <t>L4.zika_cumulative</t>
   </si>
   <si>
-    <t>L4.tavg</t>
-  </si>
-  <si>
     <t>t+1</t>
+  </si>
+  <si>
+    <t>L1.pm10</t>
+  </si>
+  <si>
+    <t>L1.pres</t>
+  </si>
+  <si>
+    <t>L3.google_hospital</t>
+  </si>
+  <si>
+    <t>L3.pm10</t>
+  </si>
+  <si>
+    <t>L5.humidity</t>
+  </si>
+  <si>
+    <t>L3.so2</t>
   </si>
 </sst>
 </file>
@@ -9177,7 +9183,7 @@
       <c r="BT14" s="14"/>
       <c r="BU14" s="14"/>
       <c r="BW14" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -9468,25 +9474,25 @@
         <v>331</v>
       </c>
       <c r="BX16" s="14">
-        <v>7.3023619999999996</v>
+        <v>6.5000390000000001</v>
       </c>
       <c r="BY16" s="14">
-        <v>23.153338999999999</v>
+        <v>23.705583000000001</v>
       </c>
       <c r="BZ16" s="14">
-        <v>1.312649</v>
+        <v>1.312819</v>
       </c>
       <c r="CA16" s="14">
-        <v>1.6906680000000001</v>
+        <v>1.3858550000000001</v>
       </c>
       <c r="CB16" s="14">
-        <v>24.156554</v>
+        <v>24.441410999999999</v>
       </c>
       <c r="CC16" s="14">
-        <v>9.6223559999999999</v>
+        <v>9.3939389999999996</v>
       </c>
       <c r="CD16" s="14">
-        <v>107.470157</v>
+        <v>109.669701</v>
       </c>
       <c r="CE16" s="14">
         <v>31.725518000000001</v>
@@ -9497,28 +9503,28 @@
         <v>195</v>
       </c>
       <c r="BX17" s="17">
-        <v>27784.75676</v>
+        <v>28631.619245999998</v>
       </c>
       <c r="BY17" s="17">
-        <v>45692.435870000001</v>
+        <v>45811.162887999999</v>
       </c>
       <c r="BZ17" s="17">
-        <v>831.05332099999998</v>
+        <v>937.95254799999998</v>
       </c>
       <c r="CA17" s="17">
-        <v>349.12991</v>
+        <v>450.39849199999998</v>
       </c>
       <c r="CB17" s="17">
-        <v>47565.684982999999</v>
+        <v>47791.344292000002</v>
       </c>
       <c r="CC17" s="17">
-        <v>13343.920405000001</v>
+        <v>14177.064490999999</v>
       </c>
       <c r="CD17" s="17">
-        <v>121114.350896</v>
+        <v>121112.837029</v>
       </c>
       <c r="CE17" s="17">
-        <v>6894.8666080000003</v>
+        <v>5855.042743</v>
       </c>
     </row>
     <row r="18" spans="34:83" x14ac:dyDescent="0.3">
@@ -9526,28 +9532,28 @@
         <v>332</v>
       </c>
       <c r="BX18" s="14">
-        <v>6912.7279230000004</v>
+        <v>7253.7510709999997</v>
       </c>
       <c r="BY18" s="14">
-        <v>16731.626419</v>
+        <v>16866.313760000001</v>
       </c>
       <c r="BZ18" s="14">
-        <v>1236.609516</v>
+        <v>2231.3267719999999</v>
       </c>
       <c r="CA18" s="14">
-        <v>66.889324000000002</v>
+        <v>57.783405999999999</v>
       </c>
       <c r="CB18" s="14">
-        <v>17334.479093000002</v>
+        <v>17332.664193000001</v>
       </c>
       <c r="CC18" s="14">
-        <v>657.88363900000002</v>
+        <v>928.31180199999994</v>
       </c>
       <c r="CD18" s="14">
-        <v>48215.132081999996</v>
+        <v>48213.643342000003</v>
       </c>
       <c r="CE18" s="14">
-        <v>8147.0878750000002</v>
+        <v>8510.9496409999992</v>
       </c>
     </row>
     <row r="19" spans="34:83" x14ac:dyDescent="0.3">
@@ -9555,28 +9561,28 @@
         <v>196</v>
       </c>
       <c r="BX19" s="17">
-        <v>12.758763999999999</v>
+        <v>11.312836000000001</v>
       </c>
       <c r="BY19" s="17">
-        <v>11.847369</v>
+        <v>11.884532</v>
       </c>
       <c r="BZ19" s="17">
-        <v>1.5559229999999999</v>
+        <v>1.5555490000000001</v>
       </c>
       <c r="CA19" s="17">
-        <v>1.591691</v>
+        <v>1.3179190000000001</v>
       </c>
       <c r="CB19" s="17">
-        <v>12.320406999999999</v>
+        <v>12.5166</v>
       </c>
       <c r="CC19" s="17">
-        <v>8.3875679999999999</v>
+        <v>9.2154480000000003</v>
       </c>
       <c r="CD19" s="17">
-        <v>67.611076999999995</v>
+        <v>70.252651999999998</v>
       </c>
       <c r="CE19" s="17">
-        <v>25.013144</v>
+        <v>16.767234999999999</v>
       </c>
     </row>
     <row r="20" spans="34:83" x14ac:dyDescent="0.3">
@@ -9837,7 +9843,7 @@
         <v>302</v>
       </c>
       <c r="BY27" s="1" t="s">
-        <v>333</v>
+        <v>302</v>
       </c>
       <c r="BZ27" s="1" t="s">
         <v>302</v>
@@ -9851,7 +9857,7 @@
         <v>334</v>
       </c>
       <c r="BY28" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="BZ28" s="6" t="s">
         <v>336</v>
@@ -9868,13 +9874,13 @@
         <v>338</v>
       </c>
       <c r="BY29" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="BZ29" s="1" t="s">
         <v>340</v>
       </c>
       <c r="CA29" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="34:83" x14ac:dyDescent="0.3">
@@ -9906,16 +9912,16 @@
         <v>315</v>
       </c>
       <c r="BX30" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="BY30" s="6" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="BZ30" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="CA30" s="6" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="34:83" x14ac:dyDescent="0.3">
@@ -9947,16 +9953,13 @@
         <v>7268706</v>
       </c>
       <c r="BX31" s="1" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="BY31" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="BZ31" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="CA31" s="1" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="34:83" x14ac:dyDescent="0.3">
@@ -9988,16 +9991,14 @@
         <v>1387276</v>
       </c>
       <c r="BX32" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="BY32" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="BZ32" s="6" t="s">
-        <v>341</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="BZ32" s="6"/>
       <c r="CA32" s="6" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="33" spans="34:79" x14ac:dyDescent="0.3">
@@ -10029,16 +10030,13 @@
         <v>86397360</v>
       </c>
       <c r="BX33" s="1" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="BY33" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="BZ33" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="CA33" s="1" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="34:79" x14ac:dyDescent="0.3">
@@ -10069,18 +10067,12 @@
       <c r="AP34" s="14">
         <v>6536393</v>
       </c>
-      <c r="BX34" s="6" t="s">
-        <v>341</v>
-      </c>
+      <c r="BX34" s="6"/>
       <c r="BY34" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="BZ34" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="CA34" s="6" t="s">
-        <v>341</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="BZ34" s="6"/>
+      <c r="CA34" s="6"/>
     </row>
     <row r="35" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH35" s="1" t="s">
@@ -10110,17 +10102,21 @@
       <c r="AP35" s="14">
         <v>259778200</v>
       </c>
-      <c r="BX35" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="BY35" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="BZ35" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="CA35" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="36" spans="34:79" x14ac:dyDescent="0.3">
+      <c r="BX36" s="6"/>
+      <c r="BY36" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="BZ36" s="6"/>
+      <c r="CA36" s="6"/>
+    </row>
+    <row r="37" spans="34:79" x14ac:dyDescent="0.3">
+      <c r="BY37" s="1" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="38" spans="34:79" x14ac:dyDescent="0.3">

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAC58CD-0470-4196-97D5-0434328969E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A62940-E3B9-4B34-AA4E-106DC0C3C68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
   <sheets>
     <sheet name="literature review" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="358">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -1127,6 +1127,18 @@
   </si>
   <si>
     <t>L3.so2</t>
+  </si>
+  <si>
+    <t>https://origin.cpc.ncep.noaa.gov/products/analysis_monitoring/ensostuff/ONI_v5.php</t>
+  </si>
+  <si>
+    <t>el nino</t>
+  </si>
+  <si>
+    <t>build an index using the variables with highest effect on risk of propagation</t>
+  </si>
+  <si>
+    <t>The index is just the probability scores of cases going beyond 1std</t>
   </si>
 </sst>
 </file>
@@ -2234,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA430712-2AF2-46BC-B2A9-A9F8B8AAD612}">
-  <dimension ref="B1:E25"/>
+  <dimension ref="B1:E26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -2429,6 +2441,14 @@
       </c>
       <c r="C25" s="1" t="s">
         <v>319</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -2454,6 +2474,7 @@
     <hyperlink ref="B23" r:id="rId19" xr:uid="{147E40C6-D2E1-46D8-854B-3827BE9D5F5D}"/>
     <hyperlink ref="B24" r:id="rId20" xr:uid="{072E2C55-83F5-4678-A782-C260562B8B6B}"/>
     <hyperlink ref="B25" r:id="rId21" xr:uid="{0B637547-4E97-4EC3-B314-56A41CE2A5A5}"/>
+    <hyperlink ref="B26" r:id="rId22" xr:uid="{74940AD8-16FA-4D19-8C89-A6E8C43ECBF9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2693,7 +2714,7 @@
         <v>258</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
@@ -2713,7 +2734,7 @@
         <v>259</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
@@ -2841,7 +2862,7 @@
         <v>266</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
@@ -11377,7 +11398,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE21AE24-7B23-4499-8D22-C9A70AD3E5F9}">
-  <dimension ref="B1:C40"/>
+  <dimension ref="B1:C42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -11693,6 +11714,22 @@
       </c>
       <c r="C40" s="29" t="s">
         <v>279</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B41" s="1">
+        <v>38</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B42" s="1">
+        <v>39</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A62940-E3B9-4B34-AA4E-106DC0C3C68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44DA836-95C6-4C71-8E33-4C0918930F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
   <sheets>
     <sheet name="literature review" sheetId="1" r:id="rId1"/>
@@ -457,9 +457,6 @@
     <t>https://portalsivigila.ins.gov.co/Paginas/Buscador.aspx</t>
   </si>
   <si>
-    <t>Access to epidemic data colombia (is broken)</t>
-  </si>
-  <si>
     <t>Medellin Data Sivigila / dengue, zika,…2019-2025</t>
   </si>
   <si>
@@ -1139,6 +1136,9 @@
   </si>
   <si>
     <t>The index is just the probability scores of cases going beyond 1std</t>
+  </si>
+  <si>
+    <t>Access to epidemic data colombia</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1247,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1296,6 +1296,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1319,7 +1325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1366,6 +1372,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2007,13 +2014,13 @@
         <v>20</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
@@ -2021,13 +2028,13 @@
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="E24" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
@@ -2035,13 +2042,13 @@
         <v>22</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
@@ -2049,16 +2056,16 @@
         <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
@@ -2066,19 +2073,19 @@
         <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -2124,22 +2131,22 @@
   <sheetData>
     <row r="1" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2371,84 +2378,84 @@
         <v>128</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="38" t="s">
         <v>129</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>130</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -2495,771 +2502,771 @@
   <sheetData>
     <row r="1" spans="2:18" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>135</v>
-      </c>
       <c r="E4" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N4" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="R4" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="M5" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q7" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G8" s="12"/>
       <c r="M8" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M9" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="Q9" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3339,285 +3346,285 @@
   <sheetData>
     <row r="1" spans="2:73" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AC1" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AO1" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N2" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="R2" s="19" t="s">
         <v>138</v>
-      </c>
-      <c r="R2" s="19" t="s">
-        <v>139</v>
       </c>
       <c r="S2" s="19"/>
       <c r="V2" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W2" s="19"/>
       <c r="Z2" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AD2" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AE2" s="19"/>
       <c r="AF2" s="19"/>
       <c r="AO2" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="AT2" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="AT2" s="19" t="s">
-        <v>199</v>
-      </c>
       <c r="AX2" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BB2" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="BB2" s="19" t="s">
-        <v>139</v>
-      </c>
       <c r="BF2" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BJ2" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="BN2" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="V4" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Z4" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AD4" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE4" s="13"/>
       <c r="AF4" s="13"/>
       <c r="AO4" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AT4" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AX4" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BB4" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BF4" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BJ4" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BN4" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>169</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="L6" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="P6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="P6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="R6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="T6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="T6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="V6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="X6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="X6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="Z6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="AB6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="AD6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF6" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="AF6" s="9" t="s">
-        <v>139</v>
-      </c>
       <c r="AG6" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AH6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AI6" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AJ6" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="AK6" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="AO6" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="AK6" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="AO6" s="9" t="s">
-        <v>194</v>
-      </c>
       <c r="AP6" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AQ6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AR6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="AR6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="AT6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AU6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AV6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="AV6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="AX6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AY6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AZ6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="AZ6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="BB6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BC6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BD6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BD6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="BF6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BG6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BH6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BH6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="BJ6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BK6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BL6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BL6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="BN6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BO6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="BP6" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="BP6" s="9" t="s">
-        <v>139</v>
-      </c>
       <c r="BQ6" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BR6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="BS6" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BT6" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BU6" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C7" s="15">
         <v>7.6682159999999999E-2</v>
@@ -3636,7 +3643,7 @@
         <v>GGM</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J7" s="12">
         <v>0.99999850000000001</v>
@@ -3649,7 +3656,7 @@
         <v>-1513833.6548000001</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O7" s="12">
         <v>-0.39370899999999998</v>
@@ -3658,7 +3665,7 @@
         <v>15217290</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S7" s="12">
         <v>-9.8227999999999996E-2</v>
@@ -3667,7 +3674,7 @@
         <v>13264390</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W7" s="31">
         <v>0.99999800000000005</v>
@@ -3676,7 +3683,7 @@
         <v>15940.183487</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA7" s="31">
         <v>0.99995000000000001</v>
@@ -3685,7 +3692,7 @@
         <v>91507.114184000005</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AE7" s="14">
         <f>+_xlfn.XLOOKUP($AD7,N$7:N$16,P$7:P$16)</f>
@@ -3716,10 +3723,10 @@
         <v>91507.114184000005</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AQ7" s="12">
         <v>-0.25174930000000001</v>
@@ -3728,7 +3735,7 @@
         <v>210875.2597</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AU7" s="23">
         <v>0.99999979999999999</v>
@@ -3737,7 +3744,7 @@
         <v>91.979789999999994</v>
       </c>
       <c r="AX7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY7" s="12">
         <v>0.94224399999999997</v>
@@ -3746,7 +3753,7 @@
         <v>4703.6260300000004</v>
       </c>
       <c r="BB7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BC7" s="12">
         <v>0.91772100000000001</v>
@@ -3755,7 +3762,7 @@
         <v>5614.0714690000004</v>
       </c>
       <c r="BF7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BG7" s="12">
         <v>0.99995330000000004</v>
@@ -3764,7 +3771,7 @@
         <v>133.75837000000001</v>
       </c>
       <c r="BJ7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BK7" s="12">
         <v>0.98349299999999995</v>
@@ -3773,7 +3780,7 @@
         <v>2514.5705710000002</v>
       </c>
       <c r="BN7" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BO7" s="14">
         <f>+_xlfn.XLOOKUP($BN7,$AX$7:$AX$10,$AZ$7:$AZ$10)</f>
@@ -3806,7 +3813,7 @@
     </row>
     <row r="8" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C8" s="16">
         <v>-0.13819318</v>
@@ -3825,7 +3832,7 @@
         <v>GGM</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J8" s="18">
         <v>0.99999919999999998</v>
@@ -3838,7 +3845,7 @@
         <v>-843842.2267</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O8" s="18">
         <v>0.44333400000000001</v>
@@ -3847,7 +3854,7 @@
         <v>1304208</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S8" s="18">
         <v>0.91093299999999999</v>
@@ -3856,7 +3863,7 @@
         <v>518469</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="W8" s="32">
         <v>0.99999899999999997</v>
@@ -3865,7 +3872,7 @@
         <v>1580.191648</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AA8" s="32">
         <v>0.999973</v>
@@ -3874,7 +3881,7 @@
         <v>9120.9211990000003</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AE8" s="14">
         <f t="shared" ref="AE8:AE16" si="3">+_xlfn.XLOOKUP($AD8,N$7:N$16,P$7:P$16)</f>
@@ -3905,7 +3912,7 @@
         <v>9120.9211990000003</v>
       </c>
       <c r="AO8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AP8" s="6" t="s">
         <v>33</v>
@@ -3917,7 +3924,7 @@
         <v>15764.5885</v>
       </c>
       <c r="AT8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AU8" s="24">
         <v>0.99997420000000004</v>
@@ -3926,7 +3933,7 @@
         <v>99.435940000000002</v>
       </c>
       <c r="AX8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY8" s="18">
         <v>0.98572300000000002</v>
@@ -3935,7 +3942,7 @@
         <v>22520.654823000001</v>
       </c>
       <c r="BB8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BC8" s="18">
         <v>0.99224599999999996</v>
@@ -3944,7 +3951,7 @@
         <v>16596.507481000001</v>
       </c>
       <c r="BF8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BG8" s="18">
         <v>0.99999979999999999</v>
@@ -3953,7 +3960,7 @@
         <v>89.78492</v>
       </c>
       <c r="BJ8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BK8" s="18">
         <v>0.99868800000000002</v>
@@ -3962,7 +3969,7 @@
         <v>6828.2612090000002</v>
       </c>
       <c r="BN8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BO8" s="17">
         <f t="shared" ref="BO8:BO10" si="9">+_xlfn.XLOOKUP($BN8,$AX$7:$AX$10,$AZ$7:$AZ$10)</f>
@@ -3995,7 +4002,7 @@
     </row>
     <row r="9" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C9" s="15">
         <v>0.99484592000000005</v>
@@ -4014,7 +4021,7 @@
         <v>GGM</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J9" s="12">
         <v>0.99526269999999994</v>
@@ -4027,7 +4034,7 @@
         <v>-589.51029999999446</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O9" s="12">
         <v>-0.84969700000000004</v>
@@ -4036,7 +4043,7 @@
         <v>3356209</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S9" s="12">
         <v>-0.18831400000000001</v>
@@ -4045,7 +4052,7 @@
         <v>2617900</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="W9" s="31">
         <v>0.99999899999999997</v>
@@ -4054,7 +4061,7 @@
         <v>2142.2691100000002</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA9" s="31">
         <v>0.99992800000000004</v>
@@ -4063,7 +4070,7 @@
         <v>20962.221375000001</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AE9" s="14">
         <f t="shared" si="3"/>
@@ -4094,10 +4101,10 @@
         <v>20962.221375000001</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AP9" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AQ9" s="12">
         <v>0.99683809999999995</v>
@@ -4106,7 +4113,7 @@
         <v>1100.5509999999999</v>
       </c>
       <c r="AT9" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AU9" s="23">
         <v>0.9999806</v>
@@ -4115,7 +4122,7 @@
         <v>88.003110000000007</v>
       </c>
       <c r="AX9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AY9" s="12">
         <v>0.98843700000000001</v>
@@ -4124,7 +4131,7 @@
         <v>2148.462321</v>
       </c>
       <c r="BB9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BC9" s="12">
         <v>0.97706400000000004</v>
@@ -4133,7 +4140,7 @@
         <v>3025.804118</v>
       </c>
       <c r="BF9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BG9" s="12">
         <v>0.999977</v>
@@ -4142,7 +4149,7 @@
         <v>95.776430000000005</v>
       </c>
       <c r="BJ9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BK9" s="12">
         <v>0.99990800000000002</v>
@@ -4151,7 +4158,7 @@
         <v>192.12411499999999</v>
       </c>
       <c r="BN9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BO9" s="14">
         <f t="shared" si="9"/>
@@ -4184,7 +4191,7 @@
     </row>
     <row r="10" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C10" s="16">
         <v>0.98982815000000002</v>
@@ -4203,7 +4210,7 @@
         <v>GGM</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J10" s="18">
         <v>0.99999669999999996</v>
@@ -4216,7 +4223,7 @@
         <v>-19827.444499999998</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O10" s="18">
         <v>-0.70091599999999998</v>
@@ -4225,7 +4232,7 @@
         <v>305803.09999999998</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S10" s="18">
         <v>3.9317999999999999E-2</v>
@@ -4234,7 +4241,7 @@
         <v>224458</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W10" s="32">
         <v>0.99999700000000002</v>
@@ -4243,7 +4250,7 @@
         <v>433.14919800000001</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AA10" s="32">
         <v>0.99969300000000005</v>
@@ -4252,7 +4259,7 @@
         <v>4105.2196100000001</v>
       </c>
       <c r="AD10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AE10" s="14">
         <f t="shared" si="3"/>
@@ -4283,7 +4290,7 @@
         <v>4105.2196100000001</v>
       </c>
       <c r="AO10" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AP10" s="6" t="s">
         <v>33</v>
@@ -4295,7 +4302,7 @@
         <v>756.05920000000003</v>
       </c>
       <c r="AT10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AU10" s="24">
         <v>0.99999979999999999</v>
@@ -4304,7 +4311,7 @@
         <v>163.67088000000001</v>
       </c>
       <c r="AX10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AY10" s="18">
         <v>0.98303399999999996</v>
@@ -4313,7 +4320,7 @@
         <v>53755.513460000002</v>
       </c>
       <c r="BB10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BC10" s="18">
         <v>0.99701899999999999</v>
@@ -4322,7 +4329,7 @@
         <v>22532.557326999999</v>
       </c>
       <c r="BF10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BG10" s="18">
         <v>0.99999990000000005</v>
@@ -4331,7 +4338,7 @@
         <v>157.38897</v>
       </c>
       <c r="BJ10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BK10" s="18">
         <v>0.99997000000000003</v>
@@ -4340,7 +4347,7 @@
         <v>2248.9489680000001</v>
       </c>
       <c r="BN10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BO10" s="17">
         <f t="shared" si="9"/>
@@ -4373,7 +4380,7 @@
     </row>
     <row r="11" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C11" s="15">
         <v>0.99039379999999999</v>
@@ -4392,7 +4399,7 @@
         <v>GGM</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J11" s="12">
         <v>0.99999199999999999</v>
@@ -4405,7 +4412,7 @@
         <v>-1231603.5988</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O11" s="12">
         <v>0.97311099999999995</v>
@@ -4414,7 +4421,7 @@
         <v>2287439</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="S11" s="12">
         <v>0.98591399999999996</v>
@@ -4423,7 +4430,7 @@
         <v>1656545</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="W11" s="31">
         <v>0.99999499999999997</v>
@@ -4432,7 +4439,7 @@
         <v>30356.430119000001</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA11" s="31">
         <v>0.99996600000000002</v>
@@ -4441,7 +4448,7 @@
         <v>81396.828680000006</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AE11" s="14">
         <f t="shared" si="3"/>
@@ -4472,10 +4479,10 @@
         <v>81396.828680000006</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AP11" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AQ11" s="12">
         <v>0.99021340000000002</v>
@@ -4497,7 +4504,7 @@
     </row>
     <row r="12" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C12" s="16">
         <v>0.98519310000000004</v>
@@ -4516,7 +4523,7 @@
         <v>GGM</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J12" s="18">
         <v>0.99999669999999996</v>
@@ -4529,7 +4536,7 @@
         <v>-947126.18190000008</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O12" s="18">
         <v>0.90446300000000002</v>
@@ -4538,7 +4545,7 @@
         <v>2800556</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S12" s="18">
         <v>0.96489400000000003</v>
@@ -4547,7 +4554,7 @@
         <v>1697944</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="W12" s="32">
         <v>0.99999700000000002</v>
@@ -4556,7 +4563,7 @@
         <v>16474.693931999998</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AA12" s="32">
         <v>0.99982899999999997</v>
@@ -4565,7 +4572,7 @@
         <v>118520.743653</v>
       </c>
       <c r="AD12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AE12" s="14">
         <f t="shared" si="3"/>
@@ -4596,7 +4603,7 @@
         <v>118520.743653</v>
       </c>
       <c r="AO12" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AP12" s="6" t="s">
         <v>33</v>
@@ -4619,12 +4626,12 @@
       <c r="BK12" s="14"/>
       <c r="BL12" s="14"/>
       <c r="BN12" s="19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C13" s="15">
         <v>5.7728759999999997E-2</v>
@@ -4643,7 +4650,7 @@
         <v>GGM</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J13" s="12">
         <v>0.99991370000000002</v>
@@ -4656,7 +4663,7 @@
         <v>-176866.9877</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O13" s="12">
         <v>-327.19220100000001</v>
@@ -4665,7 +4672,7 @@
         <v>46909600</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S13" s="12">
         <v>-4.0384000000000003E-2</v>
@@ -4674,7 +4681,7 @@
         <v>2603995</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W13" s="31">
         <v>0.99999099999999996</v>
@@ -4683,7 +4690,7 @@
         <v>7591.1932999999999</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AA13" s="31">
         <v>0.99989799999999995</v>
@@ -4692,7 +4699,7 @@
         <v>26091.076145999999</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AE13" s="14">
         <f t="shared" si="3"/>
@@ -4723,10 +4730,10 @@
         <v>26091.076145999999</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AP13" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AQ13" s="12">
         <v>0.99908359999999996</v>
@@ -4749,7 +4756,7 @@
     </row>
     <row r="14" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C14" s="16">
         <v>1.795393E-2</v>
@@ -4768,7 +4775,7 @@
         <v>GGM</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J14" s="18">
         <v>0.99998960000000003</v>
@@ -4781,7 +4788,7 @@
         <v>-46880.9761</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O14" s="18">
         <v>2.6889E-2</v>
@@ -4790,7 +4797,7 @@
         <v>353453</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S14" s="18">
         <v>0.87112000000000001</v>
@@ -4799,7 +4806,7 @@
         <v>125949</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W14" s="32">
         <v>0.99999000000000005</v>
@@ -4808,7 +4815,7 @@
         <v>1140.2147070000001</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AA14" s="32">
         <v>0.99961699999999998</v>
@@ -4817,7 +4824,7 @@
         <v>7011.0990389999997</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AE14" s="14">
         <f t="shared" si="3"/>
@@ -4848,7 +4855,7 @@
         <v>7011.0990389999997</v>
       </c>
       <c r="AO14" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AP14" s="6" t="s">
         <v>33</v>
@@ -4872,12 +4879,12 @@
       <c r="BK14" s="14"/>
       <c r="BL14" s="14"/>
       <c r="BN14" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C15" s="15">
         <v>0.97698001999999995</v>
@@ -4896,7 +4903,7 @@
         <v>GGM</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J15" s="12">
         <v>0.99999769999999999</v>
@@ -4909,7 +4916,7 @@
         <v>-4022279.7900999999</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O15" s="12">
         <v>0.29647899999999999</v>
@@ -4918,7 +4925,7 @@
         <v>30580360</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="S15" s="12">
         <v>0.833893</v>
@@ -4927,7 +4934,7 @@
         <v>14859300</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="W15" s="31">
         <v>0.99999800000000005</v>
@@ -4936,7 +4943,7 @@
         <v>47866.562242</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AA15" s="31">
         <v>0.99987199999999998</v>
@@ -4945,7 +4952,7 @@
         <v>412581.51297400001</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AE15" s="14">
         <f t="shared" si="3"/>
@@ -4990,7 +4997,7 @@
     </row>
     <row r="16" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16" s="16">
         <v>5.2056409999999997E-2</v>
@@ -5009,7 +5016,7 @@
         <v>GGM</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J16" s="18">
         <v>0.98195189999999999</v>
@@ -5022,7 +5029,7 @@
         <v>-188.91730000000098</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O16" s="18">
         <v>0.52243200000000001</v>
@@ -5031,7 +5038,7 @@
         <v>283382.09999999998</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S16" s="18">
         <v>0.96743000000000001</v>
@@ -5040,7 +5047,7 @@
         <v>73683.27</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W16" s="32">
         <v>0.999996</v>
@@ -5049,7 +5056,7 @@
         <v>829.90016600000001</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA16" s="32">
         <v>0.99970099999999995</v>
@@ -5058,7 +5065,7 @@
         <v>7087.1279500000001</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE16" s="14">
         <f t="shared" si="3"/>
@@ -5101,7 +5108,7 @@
       <c r="BK16" s="14"/>
       <c r="BL16" s="14"/>
       <c r="BN16" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BO16" s="9" t="str">
         <f>+BO6</f>
@@ -5137,7 +5144,7 @@
       <c r="BK17" s="14"/>
       <c r="BL17" s="14"/>
       <c r="BN17" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BO17" s="12">
         <f>+_xlfn.XLOOKUP($BN17,$AX$7:$AX$9,$AY$7:$AY$9)</f>
@@ -5167,7 +5174,7 @@
       <c r="BK18" s="14"/>
       <c r="BL18" s="14"/>
       <c r="BN18" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BO18" s="18">
         <f>+_xlfn.XLOOKUP($BN18,$AX$7:$AX$9,$AY$7:$AY$9)</f>
@@ -5194,26 +5201,26 @@
     </row>
     <row r="19" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="T19" s="21"/>
       <c r="V19" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
@@ -5221,7 +5228,7 @@
       <c r="BK19" s="14"/>
       <c r="BL19" s="14"/>
       <c r="BN19" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BO19" s="12">
         <f>+_xlfn.XLOOKUP($BN19,$AX$7:$AX$9,$AY$7:$AY$9)</f>
@@ -5252,7 +5259,7 @@
       <c r="BK20" s="14"/>
       <c r="BL20" s="14"/>
       <c r="BN20" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BO20" s="18"/>
       <c r="BP20" s="18"/>
@@ -5264,94 +5271,94 @@
     </row>
     <row r="21" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B21" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="E21" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>169</v>
-      </c>
       <c r="G21" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J21" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K21" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="K21" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="L21" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O21" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="P21" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="P21" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="R21" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S21" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="T21" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="T21" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="V21" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W21" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="X21" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="X21" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="Z21" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA21" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB21" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="AB21" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="AD21" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE21" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF21" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="AF21" s="9" t="s">
-        <v>139</v>
-      </c>
       <c r="AG21" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AH21" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AI21" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AJ21" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AK21" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="BJ21" s="14"/>
       <c r="BK21" s="14"/>
@@ -5359,7 +5366,7 @@
     </row>
     <row r="22" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C22" s="15">
         <v>0.99309789999999998</v>
@@ -5378,7 +5385,7 @@
         <v>GGM</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J22" s="12">
         <v>0.99997320000000001</v>
@@ -5391,7 +5398,7 @@
         <v>-812345.71199999994</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O22" s="12">
         <v>0.82512600000000003</v>
@@ -5400,7 +5407,7 @@
         <v>5285818</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S22" s="12">
         <v>0.64468300000000001</v>
@@ -5409,7 +5416,7 @@
         <v>7558374</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W22" s="31">
         <v>0.99996799999999997</v>
@@ -5418,7 +5425,7 @@
         <v>72886.599426000001</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA22" s="31">
         <v>0.998919</v>
@@ -5427,7 +5434,7 @@
         <v>424624.7</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AE22" s="14">
         <f>+_xlfn.XLOOKUP($AD22,N$22:N$31,P$22:P$31)</f>
@@ -5460,7 +5467,7 @@
     </row>
     <row r="23" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C23" s="16">
         <v>0.98500410000000005</v>
@@ -5479,7 +5486,7 @@
         <v>GGM</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J23" s="18">
         <v>0.99997939999999996</v>
@@ -5492,7 +5499,7 @@
         <v>-183707.56700000001</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O23" s="18">
         <v>0.85929699999999998</v>
@@ -5501,7 +5508,7 @@
         <v>655919.19999999995</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S23" s="18">
         <v>0.86842799999999998</v>
@@ -5510,7 +5517,7 @@
         <v>634278.5</v>
       </c>
       <c r="V23" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="W23" s="32">
         <v>0.999977</v>
@@ -5519,7 +5526,7 @@
         <v>8395.1301469999999</v>
       </c>
       <c r="Z23" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AA23" s="32">
         <v>0.99666699999999997</v>
@@ -5528,7 +5535,7 @@
         <v>101494.2</v>
       </c>
       <c r="AD23" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AE23" s="14">
         <f t="shared" ref="AE23:AE31" si="17">+_xlfn.XLOOKUP($AD23,N$22:N$31,P$22:P$31)</f>
@@ -5573,7 +5580,7 @@
     </row>
     <row r="24" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="15">
         <v>0.99486560000000002</v>
@@ -5592,7 +5599,7 @@
         <v>GGM</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J24" s="12">
         <v>0.9999827</v>
@@ -5605,7 +5612,7 @@
         <v>-159756.179</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O24" s="12">
         <v>0.91229700000000002</v>
@@ -5614,7 +5621,7 @@
         <v>711743.3</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S24" s="12">
         <v>0.43064400000000003</v>
@@ -5623,7 +5630,7 @@
         <v>1813809</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="W24" s="31">
         <v>0.99997899999999995</v>
@@ -5632,7 +5639,7 @@
         <v>11331.678796</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA24" s="31">
         <v>0.99987199999999998</v>
@@ -5641,7 +5648,7 @@
         <v>27934.33</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AE24" s="14">
         <f t="shared" si="17"/>
@@ -5686,7 +5693,7 @@
     </row>
     <row r="25" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="16">
         <v>0.98980849999999998</v>
@@ -5705,7 +5712,7 @@
         <v>GGM</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J25" s="18">
         <v>0.99986940000000002</v>
@@ -5718,7 +5725,7 @@
         <v>-17572.22</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O25" s="18">
         <v>0.81773499999999999</v>
@@ -5727,7 +5734,7 @@
         <v>96842.15</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S25" s="18">
         <v>-0.70466200000000001</v>
@@ -5736,7 +5743,7 @@
         <v>300031.3</v>
       </c>
       <c r="V25" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W25" s="32">
         <v>0.99985199999999996</v>
@@ -5745,7 +5752,7 @@
         <v>2856.3407999999999</v>
       </c>
       <c r="Z25" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AA25" s="32">
         <v>0.99764399999999998</v>
@@ -5754,7 +5761,7 @@
         <v>11391.69</v>
       </c>
       <c r="AD25" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AE25" s="14">
         <f t="shared" si="17"/>
@@ -5799,7 +5806,7 @@
     </row>
     <row r="26" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C26" s="15">
         <v>0.99044909999999997</v>
@@ -5818,7 +5825,7 @@
         <v>GGM</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J26" s="12">
         <v>0.99998489999999995</v>
@@ -5831,7 +5838,7 @@
         <v>-1215793.6359999999</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O26" s="12">
         <v>0.98488399999999998</v>
@@ -5840,7 +5847,7 @@
         <v>1726783</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="S26" s="12">
         <v>0.98622900000000002</v>
@@ -5849,7 +5856,7 @@
         <v>1646926</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="W26" s="31">
         <v>0.99998200000000004</v>
@@ -5858,7 +5865,7 @@
         <v>59096.011952000001</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA26" s="31">
         <v>0.99986600000000003</v>
@@ -5867,7 +5874,7 @@
         <v>162463.20000000001</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AE26" s="14">
         <f t="shared" si="17"/>
@@ -5912,7 +5919,7 @@
     </row>
     <row r="27" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27" s="16">
         <v>0.98537799999999998</v>
@@ -5931,7 +5938,7 @@
         <v>GGM</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J27" s="18">
         <v>0.99998299999999996</v>
@@ -5944,7 +5951,7 @@
         <v>-924687.772</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O27" s="18">
         <v>0.94516</v>
@@ -5953,7 +5960,7 @@
         <v>2120841</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S27" s="18">
         <v>0.94915899999999997</v>
@@ -5962,7 +5969,7 @@
         <v>2056768</v>
       </c>
       <c r="V27" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="W27" s="32">
         <v>0.99997999999999998</v>
@@ -5971,7 +5978,7 @@
         <v>40276.492481000001</v>
       </c>
       <c r="Z27" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AA27" s="32">
         <v>0.99753099999999995</v>
@@ -5980,7 +5987,7 @@
         <v>453190.5</v>
       </c>
       <c r="AD27" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AE27" s="14">
         <f t="shared" si="17"/>
@@ -6013,7 +6020,7 @@
     </row>
     <row r="28" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C28" s="15">
         <v>0.99328240000000001</v>
@@ -6032,7 +6039,7 @@
         <v>GGM</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J28" s="12">
         <v>0.99995199999999995</v>
@@ -6045,7 +6052,7 @@
         <v>-159551.46900000001</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O28" s="12">
         <v>0.84834900000000002</v>
@@ -6054,7 +6061,7 @@
         <v>999266.5</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S28" s="12">
         <v>-0.34762500000000002</v>
@@ -6063,7 +6070,7 @@
         <v>2976087</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W28" s="31">
         <v>0.99994000000000005</v>
@@ -6072,7 +6079,7 @@
         <v>20204.683582000001</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AA28" s="31">
         <v>0.99860599999999999</v>
@@ -6081,7 +6088,7 @@
         <v>97029.98</v>
       </c>
       <c r="AD28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AE28" s="14">
         <f t="shared" si="17"/>
@@ -6114,7 +6121,7 @@
     </row>
     <row r="29" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C29" s="16">
         <v>0.98214460000000003</v>
@@ -6133,7 +6140,7 @@
         <v>GGM</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J29" s="18">
         <v>0.9999439</v>
@@ -6146,7 +6153,7 @@
         <v>-39000.869999999995</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O29" s="18">
         <v>0.83975299999999997</v>
@@ -6155,7 +6162,7 @@
         <v>140633.70000000001</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S29" s="18">
         <v>0.86644399999999999</v>
@@ -6164,7 +6171,7 @@
         <v>128388.6</v>
       </c>
       <c r="V29" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W29" s="32">
         <v>0.99993799999999999</v>
@@ -6173,7 +6180,7 @@
         <v>2835.1556179999998</v>
       </c>
       <c r="Z29" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AA29" s="32">
         <v>0.99784799999999996</v>
@@ -6182,7 +6189,7 @@
         <v>16657.2</v>
       </c>
       <c r="AD29" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AE29" s="14">
         <f t="shared" si="17"/>
@@ -6215,7 +6222,7 @@
     </row>
     <row r="30" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C30" s="15">
         <v>0.97719889999999998</v>
@@ -6234,7 +6241,7 @@
         <v>GGM</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J30" s="12">
         <v>0.99001130000000004</v>
@@ -6247,7 +6254,7 @@
         <v>-4.0000001899898052E-3</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O30" s="12">
         <v>0.83721299999999998</v>
@@ -6256,7 +6263,7 @@
         <v>14749160</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="S30" s="12">
         <v>0.84466699999999995</v>
@@ -6265,7 +6272,7 @@
         <v>14407510</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="W30" s="31">
         <v>0.999973</v>
@@ -6274,7 +6281,7 @@
         <v>189197.220477</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AA30" s="31">
         <v>0.99802000000000002</v>
@@ -6283,7 +6290,7 @@
         <v>1626782</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AE30" s="14">
         <f t="shared" si="17"/>
@@ -6316,7 +6323,7 @@
     </row>
     <row r="31" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C31" s="16">
         <v>0.98704650000000005</v>
@@ -6335,7 +6342,7 @@
         <v>GGM</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J31" s="18">
         <v>0.99996839999999998</v>
@@ -6348,7 +6355,7 @@
         <v>-52796.222999999998</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O31" s="18">
         <v>0.94254700000000002</v>
@@ -6357,7 +6364,7 @@
         <v>97667.94</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S31" s="18">
         <v>0.95194400000000001</v>
@@ -6366,7 +6373,7 @@
         <v>89659.199999999997</v>
       </c>
       <c r="V31" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W31" s="32">
         <v>0.99996499999999999</v>
@@ -6375,7 +6382,7 @@
         <v>2423.543439</v>
       </c>
       <c r="Z31" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA31" s="32">
         <v>0.98897800000000002</v>
@@ -6384,7 +6391,7 @@
         <v>43128.99</v>
       </c>
       <c r="AD31" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE31" s="14">
         <f t="shared" si="17"/>
@@ -6422,59 +6429,59 @@
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V34" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B36" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="F36" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>169</v>
-      </c>
       <c r="G36" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J36" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K36" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="K36" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="L36" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V36" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W36" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="X36" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="X36" s="9" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="37" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C37" s="15">
         <v>0.99347419999999997</v>
@@ -6493,7 +6500,7 @@
         <v>GGM</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J37" s="12">
         <v>0.99883089999999997</v>
@@ -6506,7 +6513,7 @@
         <v>-416743.97</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W37" s="31">
         <v>0.99801799999999996</v>
@@ -6517,7 +6524,7 @@
     </row>
     <row r="38" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C38" s="16">
         <v>0.9861259</v>
@@ -6536,7 +6543,7 @@
         <v>GGM</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J38" s="18">
         <v>0.99688900000000003</v>
@@ -6549,7 +6556,7 @@
         <v>-111152.34000000001</v>
       </c>
       <c r="V38" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="W38" s="32">
         <v>0.99567000000000005</v>
@@ -6560,7 +6567,7 @@
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C39" s="15">
         <v>0.99485219999999996</v>
@@ -6579,7 +6586,7 @@
         <v>GGM</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J39" s="12">
         <v>0.99764529999999996</v>
@@ -6592,7 +6599,7 @@
         <v>-54364.739999999991</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="W39" s="31">
         <v>0.99534699999999998</v>
@@ -6603,7 +6610,7 @@
     </row>
     <row r="40" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40" s="16">
         <v>0.98931369999999996</v>
@@ -6622,7 +6629,7 @@
         <v>GGM</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J40" s="18">
         <v>0.99412920000000005</v>
@@ -6635,7 +6642,7 @@
         <v>-4815.9000000000015</v>
       </c>
       <c r="V40" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W40" s="32">
         <v>0.99124800000000002</v>
@@ -6646,7 +6653,7 @@
     </row>
     <row r="41" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C41" s="15">
         <v>0.9914906</v>
@@ -6665,7 +6672,7 @@
         <v>GGM</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J41" s="12">
         <v>0.99875570000000002</v>
@@ -6678,7 +6685,7 @@
         <v>-725755.52999999991</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="W41" s="31">
         <v>0.99727699999999997</v>
@@ -6689,7 +6696,7 @@
     </row>
     <row r="42" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C42" s="16">
         <v>0.98630370000000001</v>
@@ -6708,7 +6715,7 @@
         <v>GGM</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J42" s="18">
         <v>0.9954769</v>
@@ -6721,7 +6728,7 @@
         <v>-467033.16000000003</v>
       </c>
       <c r="V42" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="W42" s="32">
         <v>0.99294800000000005</v>
@@ -6732,7 +6739,7 @@
     </row>
     <row r="43" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C43" s="15">
         <v>0.99346559999999995</v>
@@ -6751,7 +6758,7 @@
         <v>GGM</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J43" s="12">
         <v>0.99769969999999997</v>
@@ -6764,7 +6771,7 @@
         <v>-71662.28</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W43" s="31">
         <v>0.99575800000000003</v>
@@ -6775,7 +6782,7 @@
     </row>
     <row r="44" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C44" s="16">
         <v>0.98240799999999995</v>
@@ -6794,7 +6801,7 @@
         <v>GGM</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J44" s="18">
         <v>0.99363820000000003</v>
@@ -6807,7 +6814,7 @@
         <v>-16968.219999999998</v>
       </c>
       <c r="V44" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W44" s="32">
         <v>0.99148400000000003</v>
@@ -6818,7 +6825,7 @@
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C45" s="15">
         <v>0.97879510000000003</v>
@@ -6837,7 +6844,7 @@
         <v>GGM</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J45" s="12">
         <v>0.98804809999999998</v>
@@ -6850,7 +6857,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="W45" s="31">
         <v>0.993228</v>
@@ -6861,7 +6868,7 @@
     </row>
     <row r="46" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B46" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C46" s="16">
         <v>0.98749869999999995</v>
@@ -6880,7 +6887,7 @@
         <v>GGM</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J46" s="18">
         <v>0.99455020000000005</v>
@@ -6893,7 +6900,7 @@
         <v>-23138.859999999997</v>
       </c>
       <c r="V46" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W46" s="32">
         <v>0.99019000000000001</v>
@@ -7444,73 +7451,73 @@
   <sheetData>
     <row r="1" spans="2:83" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AC1" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG1" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AT1" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AX1" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="2:83" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="I2" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="19" t="s">
-        <v>292</v>
-      </c>
       <c r="N2" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="R2" s="19" t="s">
         <v>138</v>
-      </c>
-      <c r="R2" s="19" t="s">
-        <v>139</v>
       </c>
       <c r="S2" s="19"/>
       <c r="V2" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W2" s="19"/>
       <c r="Z2" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AD2" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH2" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI2" s="19"/>
       <c r="AJ2" s="19"/>
       <c r="AT2" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="AY2" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="AY2" s="19" t="s">
-        <v>199</v>
-      </c>
       <c r="BC2" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="BG2" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="BG2" s="19" t="s">
-        <v>139</v>
-      </c>
       <c r="BK2" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BO2" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="BS2" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BW2" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="2:83" x14ac:dyDescent="0.3">
@@ -7531,55 +7538,55 @@
     </row>
     <row r="4" spans="2:83" ht="16.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="T4" s="21"/>
       <c r="V4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AD4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AH4" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AI4" s="13"/>
       <c r="AJ4" s="13"/>
       <c r="AT4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AY4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BC4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BG4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BK4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BO4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BS4" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BW4" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="2:83" ht="16.8" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -7587,204 +7594,204 @@
     </row>
     <row r="6" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>169</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="L6" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="P6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="P6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="R6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="T6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="T6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="V6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="X6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="X6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="Z6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="AB6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="AD6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AF6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="AF6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="AH6" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="AJ6" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="AJ6" s="9" t="s">
-        <v>139</v>
-      </c>
       <c r="AK6" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AL6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AM6" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AN6" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="AO6" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="AP6" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT6" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="AO6" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="AP6" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="AT6" s="9" t="s">
-        <v>194</v>
-      </c>
       <c r="AU6" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AV6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AW6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="AW6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="AY6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AZ6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BA6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BA6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="BC6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BD6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BE6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BE6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="BG6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BH6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BI6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BI6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="BK6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BL6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BM6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BM6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="BO6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BP6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BQ6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BQ6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="BS6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BT6" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BU6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BU6" s="9" t="s">
-        <v>187</v>
-      </c>
       <c r="BW6" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BX6" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="BY6" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="BY6" s="9" t="s">
-        <v>139</v>
-      </c>
       <c r="BZ6" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="CA6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="CB6" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CC6" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="CD6" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="CE6" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C7" s="15">
         <v>-0.88045949999999995</v>
@@ -7803,7 +7810,7 @@
         <v>BM</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J7" s="33">
         <v>-18.442921699999999</v>
@@ -7816,7 +7823,7 @@
         <v>-33376.900000000373</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O7" s="33">
         <v>-1167.2323490000001</v>
@@ -7825,7 +7832,7 @@
         <v>35518040</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S7" s="33">
         <v>-1167.7180880000001</v>
@@ -7834,7 +7841,7 @@
         <v>35525420</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="W7" s="33">
         <v>-6.5581474999999996</v>
@@ -7843,7 +7850,7 @@
         <v>2922129.51</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA7" s="33">
         <v>-5.1333900000000003</v>
@@ -7852,7 +7859,7 @@
         <v>2632341</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AE7" s="33">
         <v>0.15242800000000001</v>
@@ -7861,7 +7868,7 @@
         <v>978543.1</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AI7" s="14">
         <f t="shared" ref="AI7:AI16" si="0">+_xlfn.XLOOKUP($AH7,N$7:N$16,P$7:P$16)</f>
@@ -7896,10 +7903,10 @@
         <v>978543.1</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AV7" s="12">
         <v>-5.7474112999999996</v>
@@ -7908,7 +7915,7 @@
         <v>269246.39079999999</v>
       </c>
       <c r="AY7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AZ7" s="15">
         <v>-2.6609845999999999</v>
@@ -7917,7 +7924,7 @@
         <v>62.22701</v>
       </c>
       <c r="BC7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BD7" s="33">
         <v>-1556969</v>
@@ -7926,7 +7933,7 @@
         <v>40580.75</v>
       </c>
       <c r="BG7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BH7" s="33">
         <v>-1466067</v>
@@ -7935,7 +7942,7 @@
         <v>39378.31</v>
       </c>
       <c r="BK7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BL7" s="33">
         <v>0.45879575</v>
@@ -7944,7 +7951,7 @@
         <v>23.92548</v>
       </c>
       <c r="BO7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BP7" s="33">
         <v>-71.902986999999996</v>
@@ -7953,7 +7960,7 @@
         <v>1366.269454</v>
       </c>
       <c r="BS7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BT7" s="33">
         <v>0.95831999999999995</v>
@@ -7962,7 +7969,7 @@
         <v>6.6396439999999997</v>
       </c>
       <c r="BW7" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BX7" s="14">
         <f>+_xlfn.XLOOKUP($BW7,$BC$7:$BC$10,$BE$7:$BE$10)</f>
@@ -7999,7 +8006,7 @@
     </row>
     <row r="8" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C8" s="16">
         <v>-28.473542599999998</v>
@@ -8018,7 +8025,7 @@
         <v>BM</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J8" s="34">
         <v>-39.417364499999998</v>
@@ -8031,7 +8038,7 @@
         <v>-106032.52000000002</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O8" s="34">
         <v>-342.44675999999998</v>
@@ -8040,7 +8047,7 @@
         <v>4850543</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S8" s="34">
         <v>-342.43093699999997</v>
@@ -8049,7 +8056,7 @@
         <v>4850431</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="W8" s="34">
         <v>-0.14459959999999999</v>
@@ -8058,7 +8065,7 @@
         <v>297053.53000000003</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AA8" s="34">
         <v>-3.654674</v>
@@ -8067,7 +8074,7 @@
         <v>599035.5</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AE8" s="34">
         <v>0.90742500000000004</v>
@@ -8076,7 +8083,7 @@
         <v>84480.34</v>
       </c>
       <c r="AH8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AI8" s="14">
         <f t="shared" si="0"/>
@@ -8111,7 +8118,7 @@
         <v>84480.34</v>
       </c>
       <c r="AT8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AU8" s="6" t="s">
         <v>33</v>
@@ -8123,7 +8130,7 @@
         <v>367562.62449999998</v>
       </c>
       <c r="AY8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AZ8" s="16">
         <v>0.59136739999999999</v>
@@ -8132,7 +8139,7 @@
         <v>33522.334649999997</v>
       </c>
       <c r="BC8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BD8" s="34">
         <v>-96.224559999999997</v>
@@ -8141,7 +8148,7 @@
         <v>517077.6</v>
       </c>
       <c r="BG8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BH8" s="34">
         <v>-93.707589999999996</v>
@@ -8150,7 +8157,7 @@
         <v>510340.6</v>
       </c>
       <c r="BK8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BL8" s="34">
         <v>-0.12438572000000001</v>
@@ -8159,7 +8166,7 @@
         <v>55606.478790000001</v>
       </c>
       <c r="BO8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BP8" s="34">
         <v>0.70949499999999999</v>
@@ -8168,7 +8175,7 @@
         <v>55867.376609999999</v>
       </c>
       <c r="BS8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BT8" s="34">
         <v>0.56132400000000005</v>
@@ -8177,7 +8184,7 @@
         <v>34732.780121999996</v>
       </c>
       <c r="BW8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BX8" s="17">
         <f t="shared" ref="BX8:BX10" si="10">+_xlfn.XLOOKUP($BW8,$BC$7:$BC$10,$BE$7:$BE$10)</f>
@@ -8214,7 +8221,7 @@
     </row>
     <row r="9" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C9" s="15">
         <v>-14.8750605</v>
@@ -8233,7 +8240,7 @@
         <v>BM</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J9" s="33">
         <v>-101.5126727</v>
@@ -8246,7 +8253,7 @@
         <v>888.47000000000116</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O9" s="33">
         <v>-74322.225143000003</v>
@@ -8255,7 +8262,7 @@
         <v>6319862</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S9" s="33">
         <v>-74373.441279000006</v>
@@ -8264,7 +8271,7 @@
         <v>6322039</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="W9" s="33">
         <v>-844.09909029999994</v>
@@ -8273,7 +8280,7 @@
         <v>720988.16000000003</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA9" s="33">
         <v>-527.98294699999997</v>
@@ -8282,7 +8289,7 @@
         <v>570420.5</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AE9" s="33">
         <v>0.85376200000000002</v>
@@ -8291,7 +8298,7 @@
         <v>9484.2870000000003</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AI9" s="14">
         <f t="shared" si="0"/>
@@ -8326,10 +8333,10 @@
         <v>9484.2870000000003</v>
       </c>
       <c r="AT9" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AU9" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AV9" s="12">
         <v>-87.875995500000002</v>
@@ -8338,7 +8345,7 @@
         <v>1508.5369000000001</v>
       </c>
       <c r="AY9" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AZ9" s="15">
         <v>-54.161358200000002</v>
@@ -8347,7 +8354,7 @@
         <v>326.82960000000003</v>
       </c>
       <c r="BC9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BD9" s="33">
         <v>-1116797</v>
@@ -8356,7 +8363,7 @@
         <v>46504.1</v>
       </c>
       <c r="BG9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BH9" s="33">
         <v>-1057560</v>
@@ -8365,7 +8372,7 @@
         <v>45253.96</v>
       </c>
       <c r="BK9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BL9" s="33">
         <v>0.43556107999999999</v>
@@ -8374,7 +8381,7 @@
         <v>33.06073</v>
       </c>
       <c r="BO9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BP9" s="33">
         <v>-16.475088</v>
@@ -8383,7 +8390,7 @@
         <v>1129.176692</v>
       </c>
       <c r="BS9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BT9" s="33">
         <v>-2.6274600000000001</v>
@@ -8392,7 +8399,7 @@
         <v>83.811807000000002</v>
       </c>
       <c r="BW9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BX9" s="14">
         <f t="shared" si="10"/>
@@ -8429,7 +8436,7 @@
     </row>
     <row r="10" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C10" s="16">
         <v>-45.222719599999998</v>
@@ -8448,7 +8455,7 @@
         <v>GGM</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J10" s="34">
         <v>-36.981007400000003</v>
@@ -8461,7 +8468,7 @@
         <v>-4312.989999999998</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O10" s="34">
         <v>-5849.742776</v>
@@ -8470,7 +8477,7 @@
         <v>648975</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S10" s="34">
         <v>-5872.4790750000002</v>
@@ -8479,7 +8486,7 @@
         <v>650234.80000000005</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W10" s="34">
         <v>-39.938344000000001</v>
@@ -8488,7 +8495,7 @@
         <v>58675.03</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AA10" s="34">
         <v>-164.294004</v>
@@ -8497,7 +8504,7 @@
         <v>117900.8</v>
       </c>
       <c r="AD10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AE10" s="34">
         <v>0.70942099999999997</v>
@@ -8506,7 +8513,7 @@
         <v>4943.3419999999996</v>
       </c>
       <c r="AH10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AI10" s="14">
         <f t="shared" si="0"/>
@@ -8541,7 +8548,7 @@
         <v>4943.3419999999996</v>
       </c>
       <c r="AT10" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AU10" s="6" t="s">
         <v>33</v>
@@ -8553,7 +8560,7 @@
         <v>1273.9808</v>
       </c>
       <c r="AY10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AZ10" s="16">
         <v>-7.8432873000000001</v>
@@ -8562,7 +8569,7 @@
         <v>63829.462</v>
       </c>
       <c r="BC10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BD10" s="34">
         <v>-2694.8380000000002</v>
@@ -8571,7 +8578,7 @@
         <v>1114452</v>
       </c>
       <c r="BG10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BH10" s="34">
         <v>-2581.6080000000002</v>
@@ -8580,7 +8587,7 @@
         <v>1090796</v>
       </c>
       <c r="BK10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BL10" s="34">
         <v>1.256618E-2</v>
@@ -8589,7 +8596,7 @@
         <v>21328.893110000001</v>
       </c>
       <c r="BO10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BP10" s="34">
         <v>-1.0690390000000001</v>
@@ -8598,7 +8605,7 @@
         <v>197356.89684900001</v>
       </c>
       <c r="BS10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BT10" s="34">
         <v>0.74929500000000004</v>
@@ -8607,7 +8614,7 @@
         <v>10747.212681999999</v>
       </c>
       <c r="BW10" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BX10" s="17">
         <f t="shared" si="10"/>
@@ -8644,7 +8651,7 @@
     </row>
     <row r="11" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C11" s="15">
         <v>-11.4324584</v>
@@ -8663,7 +8670,7 @@
         <v>GGM</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J11" s="33">
         <v>0.7672158</v>
@@ -8676,7 +8683,7 @@
         <v>-29986.589999999851</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O11" s="33">
         <v>-210.45065</v>
@@ -8685,7 +8692,7 @@
         <v>35465050</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="S11" s="33">
         <v>-210.44169099999999</v>
@@ -8694,7 +8701,7 @@
         <v>35464300</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="W11" s="33">
         <v>-10.440305199999999</v>
@@ -8703,7 +8710,7 @@
         <v>8249258.3600000003</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA11" s="33">
         <v>-22.354537000000001</v>
@@ -8712,7 +8719,7 @@
         <v>11786420</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AE11" s="33">
         <v>0.96534200000000003</v>
@@ -8721,7 +8728,7 @@
         <v>454043.1</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AI11" s="14">
         <f t="shared" si="0"/>
@@ -8756,10 +8763,10 @@
         <v>454043.1</v>
       </c>
       <c r="AT11" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AU11" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AV11" s="12">
         <v>-62.730387200000003</v>
@@ -8784,7 +8791,7 @@
     </row>
     <row r="12" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C12" s="16">
         <v>-111.9174616</v>
@@ -8803,7 +8810,7 @@
         <v>GGM</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J12" s="34">
         <v>-11.824242099999999</v>
@@ -8816,7 +8823,7 @@
         <v>-1097250.2800000003</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O12" s="34">
         <v>-242.90492599999999</v>
@@ -8825,7 +8832,7 @@
         <v>23865070</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S12" s="34">
         <v>-242.90095299999999</v>
@@ -8834,7 +8841,7 @@
         <v>23864880</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="W12" s="34">
         <v>0.73289349999999998</v>
@@ -8843,7 +8850,7 @@
         <v>789759.22</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AA12" s="34">
         <v>-9.6180679999999992</v>
@@ -8852,7 +8859,7 @@
         <v>4979380</v>
       </c>
       <c r="AD12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AE12" s="34">
         <v>-20.279411</v>
@@ -8861,7 +8868,7 @@
         <v>7049078</v>
       </c>
       <c r="AH12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AI12" s="14">
         <f t="shared" si="0"/>
@@ -8896,7 +8903,7 @@
         <v>7049078</v>
       </c>
       <c r="AT12" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AU12" s="6" t="s">
         <v>33</v>
@@ -8924,7 +8931,7 @@
     </row>
     <row r="13" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C13" s="15">
         <v>-1.2333866</v>
@@ -8943,7 +8950,7 @@
         <v>GGM</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J13" s="33">
         <v>-1.2637936999999999</v>
@@ -8956,7 +8963,7 @@
         <v>29629.130000000005</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O13" s="33">
         <v>-1933.2909870000001</v>
@@ -8965,7 +8972,7 @@
         <v>7179580</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S13" s="33">
         <v>-1935.788642</v>
@@ -8974,7 +8981,7 @@
         <v>7184214</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W13" s="33">
         <v>-179.7974595</v>
@@ -8983,7 +8990,7 @@
         <v>2418834.08</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AA13" s="33">
         <v>-29.274857999999998</v>
@@ -8992,7 +8999,7 @@
         <v>989808</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AE13" s="33">
         <v>0.103008</v>
@@ -9001,7 +9008,7 @@
         <v>170374.3</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AI13" s="14">
         <f t="shared" si="0"/>
@@ -9036,10 +9043,10 @@
         <v>170374.3</v>
       </c>
       <c r="AT13" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AU13" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AV13" s="12">
         <v>-31.850383799999999</v>
@@ -9065,7 +9072,7 @@
     </row>
     <row r="14" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C14" s="16">
         <v>-91.031581299999999</v>
@@ -9084,7 +9091,7 @@
         <v>BM</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J14" s="34">
         <v>-89.237210300000001</v>
@@ -9097,7 +9104,7 @@
         <v>-8925.2999999999884</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O14" s="34">
         <v>-1799.8141330000001</v>
@@ -9106,7 +9113,7 @@
         <v>996737.1</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S14" s="34">
         <v>-1795.435129</v>
@@ -9115,7 +9122,7 @@
         <v>995524.5</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W14" s="34">
         <v>-5.0710414999999998</v>
@@ -9124,7 +9131,7 @@
         <v>61304.51</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AA14" s="34">
         <v>-83.509297000000004</v>
@@ -9133,7 +9140,7 @@
         <v>228724.7</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AE14" s="34">
         <v>-0.475381</v>
@@ -9142,7 +9149,7 @@
         <v>30221.29</v>
       </c>
       <c r="AH14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AI14" s="14">
         <f t="shared" si="0"/>
@@ -9177,7 +9184,7 @@
         <v>30221.29</v>
       </c>
       <c r="AT14" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AU14" s="6" t="s">
         <v>33</v>
@@ -9204,12 +9211,12 @@
       <c r="BT14" s="14"/>
       <c r="BU14" s="14"/>
       <c r="BW14" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C15" s="15">
         <v>-56.708334700000002</v>
@@ -9228,7 +9235,7 @@
         <v>BM</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J15" s="33">
         <v>-12.7604203</v>
@@ -9241,7 +9248,7 @@
         <v>12860522.289999999</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O15" s="33">
         <v>-779.10362199999997</v>
@@ -9250,7 +9257,7 @@
         <v>98519360</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="S15" s="33">
         <v>-779.06910800000003</v>
@@ -9259,7 +9266,7 @@
         <v>98517180</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="W15" s="33">
         <v>0.20104150000000001</v>
@@ -9268,7 +9275,7 @@
         <v>3152880.72</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AA15" s="33">
         <v>-25.673124000000001</v>
@@ -9277,7 +9284,7 @@
         <v>18217230</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AE15" s="33">
         <v>0.66067100000000001</v>
@@ -9286,7 +9293,7 @@
         <v>2054735</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AI15" s="14">
         <f t="shared" si="0"/>
@@ -9336,36 +9343,36 @@
       <c r="BT15" s="14"/>
       <c r="BU15" s="14"/>
       <c r="BW15" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BX15" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="BY15" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="BY15" s="9" t="s">
+      <c r="BZ15" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="BZ15" s="9" t="s">
+      <c r="CA15" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="CA15" s="9" t="s">
+      <c r="CB15" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="CB15" s="9" t="s">
+      <c r="CC15" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="CC15" s="9" t="s">
-        <v>299</v>
-      </c>
       <c r="CD15" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="CE15" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16" s="16">
         <v>-15.631722699999999</v>
@@ -9384,7 +9391,7 @@
         <v>GGM</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J16" s="34">
         <v>-86.961009899999993</v>
@@ -9397,7 +9404,7 @@
         <v>-12878536.9</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O16" s="34">
         <v>-2140.578501</v>
@@ -9406,7 +9413,7 @@
         <v>1000999</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S16" s="34">
         <v>-2138.2510229999998</v>
@@ -9415,7 +9422,7 @@
         <v>1000455</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W16" s="34">
         <v>0.41362320000000002</v>
@@ -9424,7 +9431,7 @@
         <v>16826.12</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA16" s="34">
         <v>-77.961535999999995</v>
@@ -9433,7 +9440,7 @@
         <v>195255.6</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE16" s="34">
         <v>0.882351</v>
@@ -9442,7 +9449,7 @@
         <v>7536.8639999999996</v>
       </c>
       <c r="AH16" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AI16" s="14">
         <f t="shared" si="0"/>
@@ -9492,7 +9499,7 @@
       <c r="BT16" s="14"/>
       <c r="BU16" s="14"/>
       <c r="BW16" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="BX16" s="14">
         <v>6.5000390000000001</v>
@@ -9521,7 +9528,7 @@
     </row>
     <row r="17" spans="34:83" x14ac:dyDescent="0.3">
       <c r="BW17" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BX17" s="17">
         <v>28631.619245999998</v>
@@ -9550,7 +9557,7 @@
     </row>
     <row r="18" spans="34:83" x14ac:dyDescent="0.3">
       <c r="BW18" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BX18" s="14">
         <v>7253.7510709999997</v>
@@ -9579,7 +9586,7 @@
     </row>
     <row r="19" spans="34:83" x14ac:dyDescent="0.3">
       <c r="BW19" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BX19" s="17">
         <v>11.312836000000001</v>
@@ -9608,7 +9615,7 @@
     </row>
     <row r="20" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH20" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="BW20" s="19"/>
       <c r="BX20" s="19"/>
@@ -9619,28 +9626,28 @@
     </row>
     <row r="21" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH21" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI21" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="AJ21" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="AJ21" s="9" t="s">
+      <c r="AK21" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="AK21" s="9" t="s">
+      <c r="AL21" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="AL21" s="9" t="s">
+      <c r="AM21" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="AM21" s="9" t="s">
+      <c r="AN21" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="AN21" s="9" t="s">
-        <v>299</v>
-      </c>
       <c r="AO21" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BW21" s="13"/>
       <c r="BX21" s="13"/>
@@ -9651,7 +9658,7 @@
     </row>
     <row r="22" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH22" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AI22" s="14">
         <v>8441809</v>
@@ -9683,7 +9690,7 @@
     </row>
     <row r="23" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH23" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AI23" s="14">
         <v>4189569</v>
@@ -9723,7 +9730,7 @@
     </row>
     <row r="24" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH24" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AI24" s="14">
         <v>43852750</v>
@@ -9764,7 +9771,7 @@
     </row>
     <row r="25" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH25" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AI25" s="14">
         <v>8964942</v>
@@ -9803,12 +9810,12 @@
       <c r="BT25" s="28"/>
       <c r="BU25" s="28"/>
       <c r="BX25" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH26" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AI26" s="14">
         <v>97036170</v>
@@ -9847,107 +9854,107 @@
       <c r="BT26" s="28"/>
       <c r="BU26" s="28"/>
       <c r="BX26" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="BY26" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="BY26" s="9" t="s">
-        <v>196</v>
-      </c>
       <c r="BZ26" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="CA26" s="9" t="s">
         <v>331</v>
-      </c>
-      <c r="CA26" s="9" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="27" spans="34:83" x14ac:dyDescent="0.3">
       <c r="BX27" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="BY27" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="BZ27" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="CA27" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="28" spans="34:83" x14ac:dyDescent="0.3">
       <c r="BX28" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BY28" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BZ28" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="CA28" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="CA28" s="6" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="29" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH29" s="29" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BX29" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="BY29" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BZ29" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="CA29" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH30" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI30" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="AJ30" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="AJ30" s="9" t="s">
+      <c r="AK30" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="AK30" s="9" t="s">
+      <c r="AL30" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="AL30" s="9" t="s">
+      <c r="AM30" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="AM30" s="9" t="s">
+      <c r="AN30" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="AN30" s="9" t="s">
-        <v>299</v>
-      </c>
       <c r="AO30" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AP30" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="BX30" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="BY30" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="BZ30" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="CA30" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="31" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH31" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AI31" s="14">
         <v>8545518</v>
@@ -9974,18 +9981,18 @@
         <v>7268706</v>
       </c>
       <c r="BX31" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="BY31" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="CA31" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="BY31" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="CA31" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="32" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH32" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AI32" s="14">
         <v>3983888</v>
@@ -10012,19 +10019,19 @@
         <v>1387276</v>
       </c>
       <c r="BX32" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="BY32" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="BZ32" s="6"/>
       <c r="CA32" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH33" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AI33" s="14">
         <v>45450350</v>
@@ -10051,18 +10058,18 @@
         <v>86397360</v>
       </c>
       <c r="BX33" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="BY33" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="CA33" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="34" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH34" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AI34" s="14">
         <v>9150194</v>
@@ -10090,14 +10097,14 @@
       </c>
       <c r="BX34" s="6"/>
       <c r="BY34" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BZ34" s="6"/>
       <c r="CA34" s="6"/>
     </row>
     <row r="35" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH35" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AI35" s="14">
         <v>97801220</v>
@@ -10124,56 +10131,56 @@
         <v>259778200</v>
       </c>
       <c r="BY35" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="34:79" x14ac:dyDescent="0.3">
       <c r="BX36" s="6"/>
       <c r="BY36" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="BZ36" s="6"/>
       <c r="CA36" s="6"/>
     </row>
     <row r="37" spans="34:79" x14ac:dyDescent="0.3">
       <c r="BY37" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH38" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH39" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI39" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="AJ39" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="AJ39" s="9" t="s">
+      <c r="AK39" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="AK39" s="9" t="s">
+      <c r="AL39" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="AL39" s="9" t="s">
+      <c r="AM39" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="AM39" s="9" t="s">
+      <c r="AN39" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="AN39" s="9" t="s">
-        <v>299</v>
-      </c>
       <c r="AO39" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH40" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AI40" s="14">
         <v>8333632</v>
@@ -10200,7 +10207,7 @@
     </row>
     <row r="41" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH41" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AI41" s="14">
         <v>4180177</v>
@@ -10227,7 +10234,7 @@
     </row>
     <row r="42" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH42" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AI42" s="14">
         <v>45846120</v>
@@ -10254,7 +10261,7 @@
     </row>
     <row r="43" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH43" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AI43" s="14">
         <v>8779838</v>
@@ -10281,7 +10288,7 @@
     </row>
     <row r="44" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH44" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AI44" s="14">
         <v>84855730</v>
@@ -10308,139 +10315,139 @@
     </row>
     <row r="49" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH49" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="50" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH50" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AI50" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="AI50" s="9" t="s">
-        <v>172</v>
-      </c>
       <c r="AJ50" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="AK50" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="AK50" s="9" t="s">
-        <v>176</v>
-      </c>
       <c r="AL50" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH51" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="AI51" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="AI51" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="AJ51" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AK51" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AL51" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="52" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH52" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AI52" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AJ52" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="AK52" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="AL52" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="AK52" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="AL52" s="6" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="53" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH53" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AI53" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="AJ53" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="AK53" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="AJ53" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="AK53" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="AL53" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="54" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH54" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AI54" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AJ54" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AK54" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AL54" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH55" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AI55" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="AJ55" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="AK55" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AL55" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="AJ55" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="AK55" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="AL55" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="56" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH56" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AI56" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AJ56" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AK56" s="6"/>
       <c r="AL56" s="6"/>
     </row>
     <row r="57" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH57" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="AI57" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="AJ57" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="AI57" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="AJ57" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="58" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH58" s="6"/>
       <c r="AI58" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AJ58" s="6"/>
       <c r="AK58" s="6"/>
@@ -10448,13 +10455,13 @@
     </row>
     <row r="59" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AI59" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="60" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH60" s="6"/>
       <c r="AI60" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ60" s="6"/>
       <c r="AK60" s="6"/>
@@ -10462,13 +10469,13 @@
     </row>
     <row r="61" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AI61" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="62" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH62" s="6"/>
       <c r="AI62" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AJ62" s="6"/>
       <c r="AK62" s="6"/>
@@ -10476,7 +10483,7 @@
     </row>
     <row r="63" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AI63" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -11593,7 +11600,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
@@ -11601,7 +11608,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
@@ -11609,7 +11616,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
@@ -11617,7 +11624,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
@@ -11625,7 +11632,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
@@ -11633,7 +11640,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
@@ -11641,7 +11648,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
@@ -11649,7 +11656,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -11657,7 +11664,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
@@ -11665,7 +11672,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
@@ -11673,7 +11680,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
@@ -11681,7 +11688,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
@@ -11689,7 +11696,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
@@ -11697,7 +11704,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
@@ -11705,7 +11712,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
@@ -11713,7 +11720,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
@@ -11721,7 +11728,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
@@ -11729,7 +11736,7 @@
         <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -11748,37 +11755,37 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44DA836-95C6-4C71-8E33-4C0918930F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E06B48-0C17-4BF3-9C7E-7F5AEC324B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E06B48-0C17-4BF3-9C7E-7F5AEC324B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51007C25-6365-4EF8-B51A-773694D017B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
   <sheets>
     <sheet name="literature review" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="357">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -279,12 +279,6 @@
   </si>
   <si>
     <t>An effective drift-diffusion model for pandemic propagation and uncertainty prediction</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2302.13361</t>
-  </si>
-  <si>
-    <t>A simplified drift-diffusion model for pandemic propagation</t>
   </si>
   <si>
     <t>SIR, SIR + uncertainty</t>
@@ -919,9 +913,6 @@
     <t>Check tweets, reddits, etc with LLM to see if frequency of symptoms is on the rise, then fit a GGM on top of it</t>
   </si>
   <si>
-    <t xml:space="preserve">Use brandwatch or reddit </t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -1139,6 +1130,12 @@
   </si>
   <si>
     <t>Access to epidemic data colombia</t>
+  </si>
+  <si>
+    <t>Writen on text</t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1148,7 @@
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1246,6 +1243,13 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Wingdings 2"/>
+      <family val="1"/>
+      <charset val="2"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1325,7 +1329,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1373,6 +1377,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1708,7 +1715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{354077A2-E602-4D9A-90DA-98AD5E623913}">
-  <dimension ref="B1:Q27"/>
+  <dimension ref="B1:Q26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -1719,12 +1726,12 @@
     <col min="18" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1737,8 +1744,14 @@
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -1751,8 +1764,11 @@
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
         <v>2</v>
       </c>
@@ -1765,8 +1781,11 @@
       <c r="E5" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>3</v>
       </c>
@@ -1779,8 +1798,11 @@
       <c r="E6" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>4</v>
       </c>
@@ -1793,8 +1815,11 @@
       <c r="E7" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>5</v>
       </c>
@@ -1807,8 +1832,11 @@
       <c r="E8" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>6</v>
       </c>
@@ -1821,8 +1849,11 @@
       <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G9" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>7</v>
       </c>
@@ -1835,8 +1866,11 @@
       <c r="E10" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="6">
         <v>8</v>
       </c>
@@ -1849,8 +1883,11 @@
       <c r="E11" s="7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G11" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>9</v>
       </c>
@@ -1866,8 +1903,11 @@
       <c r="F12" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="6">
         <v>10</v>
       </c>
@@ -1880,8 +1920,11 @@
       <c r="E13" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>11</v>
       </c>
@@ -1895,10 +1938,13 @@
         <v>43</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="6">
         <v>12</v>
       </c>
@@ -1911,8 +1957,11 @@
       <c r="E15" s="7" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>13</v>
       </c>
@@ -1924,6 +1973,9 @@
       </c>
       <c r="E16" s="4" t="s">
         <v>49</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
@@ -1934,10 +1986,13 @@
         <v>77</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>76</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.3">
@@ -1945,42 +2000,48 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>78</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q18" s="30"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="6">
         <v>16</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="Q19" s="30"/>
+      <c r="G19" s="39" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>85</v>
+        <v>108</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
@@ -1988,11 +2049,16 @@
         <v>18</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="6"/>
+        <v>123</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="E21" s="7" t="s">
-        <v>110</v>
+        <v>121</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
@@ -2000,13 +2066,16 @@
         <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>123</v>
+        <v>154</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
@@ -2017,10 +2086,13 @@
         <v>158</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>156</v>
+      <c r="G23" s="39" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
@@ -2028,13 +2100,16 @@
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>159</v>
+        <v>208</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
@@ -2042,13 +2117,19 @@
         <v>22</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>210</v>
+        <v>223</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G25" s="39" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
@@ -2056,36 +2137,19 @@
         <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>227</v>
+        <v>280</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="1">
-        <v>24</v>
-      </c>
-      <c r="C27" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>284</v>
+      <c r="G26" s="39" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -2104,17 +2168,16 @@
     <hyperlink ref="E15" r:id="rId12" xr:uid="{35FC94A4-52D8-488B-A301-CBAEE2798622}"/>
     <hyperlink ref="E16" r:id="rId13" xr:uid="{DFD6A570-7736-4FD6-85BA-79E740F48BEE}"/>
     <hyperlink ref="E17" r:id="rId14" xr:uid="{2EF7F835-3B5D-4681-A018-340019AAD385}"/>
-    <hyperlink ref="E18" r:id="rId15" xr:uid="{B597D65C-B2E3-416D-AC8E-047791932DB6}"/>
-    <hyperlink ref="F14" r:id="rId16" location=":~:text=The%20diffusion%20models%20we%20use,%2C%20and%20Chapman%2DRichards%20models." xr:uid="{7D08B040-2F5C-47CF-9FA0-75C5CA1D0A69}"/>
-    <hyperlink ref="E19" r:id="rId17" xr:uid="{AB0ECB57-EE9E-4AC6-8D22-1CD28E351F18}"/>
-    <hyperlink ref="E20" r:id="rId18" xr:uid="{329731CB-DF4B-4585-9EF3-AFC1FF4697B1}"/>
-    <hyperlink ref="E21" r:id="rId19" xr:uid="{8BF97103-8B1D-479D-A092-E129DB45FC39}"/>
-    <hyperlink ref="E22" r:id="rId20" xr:uid="{94F4A7D7-3F55-4643-9FD0-A11EF159A4C1}"/>
-    <hyperlink ref="E23" r:id="rId21" xr:uid="{3D99AF48-A732-4ADA-B469-518D1E1C4F59}"/>
-    <hyperlink ref="E24" r:id="rId22" xr:uid="{EAAB6CA0-E60C-4CCA-9A60-6D6314C9AA39}"/>
-    <hyperlink ref="E25" r:id="rId23" xr:uid="{4730B165-77B9-44CC-96F1-5D46B06A3B46}"/>
-    <hyperlink ref="E26" r:id="rId24" xr:uid="{27F3ABE4-E9A8-4610-B13D-775FBB8CFAA5}"/>
-    <hyperlink ref="E27" r:id="rId25" xr:uid="{9C94BE50-1EBB-4A1E-992C-64AF15F3BEC8}"/>
+    <hyperlink ref="F14" r:id="rId15" location=":~:text=The%20diffusion%20models%20we%20use,%2C%20and%20Chapman%2DRichards%20models." xr:uid="{7D08B040-2F5C-47CF-9FA0-75C5CA1D0A69}"/>
+    <hyperlink ref="E18" r:id="rId16" xr:uid="{AB0ECB57-EE9E-4AC6-8D22-1CD28E351F18}"/>
+    <hyperlink ref="E19" r:id="rId17" xr:uid="{329731CB-DF4B-4585-9EF3-AFC1FF4697B1}"/>
+    <hyperlink ref="E20" r:id="rId18" xr:uid="{8BF97103-8B1D-479D-A092-E129DB45FC39}"/>
+    <hyperlink ref="E21" r:id="rId19" xr:uid="{94F4A7D7-3F55-4643-9FD0-A11EF159A4C1}"/>
+    <hyperlink ref="E22" r:id="rId20" xr:uid="{3D99AF48-A732-4ADA-B469-518D1E1C4F59}"/>
+    <hyperlink ref="E23" r:id="rId21" xr:uid="{EAAB6CA0-E60C-4CCA-9A60-6D6314C9AA39}"/>
+    <hyperlink ref="E24" r:id="rId22" xr:uid="{4730B165-77B9-44CC-96F1-5D46B06A3B46}"/>
+    <hyperlink ref="E25" r:id="rId23" xr:uid="{27F3ABE4-E9A8-4610-B13D-775FBB8CFAA5}"/>
+    <hyperlink ref="E26" r:id="rId24" xr:uid="{9C94BE50-1EBB-4A1E-992C-64AF15F3BEC8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2131,22 +2194,22 @@
   <sheetData>
     <row r="1" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2276,7 +2339,7 @@
         <v>69</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -2329,133 +2392,133 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -2502,771 +2565,771 @@
   <sheetData>
     <row r="1" spans="2:18" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>134</v>
-      </c>
       <c r="E4" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="Q4" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="Q5" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G8" s="12"/>
       <c r="M8" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -3346,285 +3409,285 @@
   <sheetData>
     <row r="1" spans="2:73" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AC1" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="AO1" s="10" t="s">
         <v>285</v>
-      </c>
-      <c r="AO1" s="10" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="2" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N2" s="19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R2" s="19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S2" s="19"/>
       <c r="V2" s="19" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="W2" s="19"/>
       <c r="Z2" s="19" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AD2" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AE2" s="19"/>
       <c r="AF2" s="19"/>
       <c r="AO2" s="19" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AT2" s="19" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AX2" s="19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BB2" s="19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="BF2" s="19" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="BJ2" s="19" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="BN2" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="V4" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Z4" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AD4" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AE4" s="13"/>
       <c r="AF4" s="13"/>
       <c r="AO4" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AT4" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AX4" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="BB4" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="BF4" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="BJ4" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="BN4" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>168</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K6" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="L6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="L6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="N6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="S6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="W6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AA6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AB6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AD6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AE6" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF6" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG6" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AH6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AI6" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AJ6" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AK6" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AO6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AP6" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AQ6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AR6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AT6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AU6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AV6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AX6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AY6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AZ6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BB6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BC6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BD6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BF6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BG6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BH6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BK6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BL6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BN6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BO6" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BP6" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="BQ6" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="BR6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="BS6" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="BT6" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="BU6" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" s="15">
         <v>7.6682159999999999E-2</v>
@@ -3643,7 +3706,7 @@
         <v>GGM</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J7" s="12">
         <v>0.99999850000000001</v>
@@ -3656,7 +3719,7 @@
         <v>-1513833.6548000001</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O7" s="12">
         <v>-0.39370899999999998</v>
@@ -3665,7 +3728,7 @@
         <v>15217290</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="S7" s="12">
         <v>-9.8227999999999996E-2</v>
@@ -3674,7 +3737,7 @@
         <v>13264390</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W7" s="31">
         <v>0.99999800000000005</v>
@@ -3683,7 +3746,7 @@
         <v>15940.183487</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AA7" s="31">
         <v>0.99995000000000001</v>
@@ -3692,7 +3755,7 @@
         <v>91507.114184000005</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AE7" s="14">
         <f>+_xlfn.XLOOKUP($AD7,N$7:N$16,P$7:P$16)</f>
@@ -3723,10 +3786,10 @@
         <v>91507.114184000005</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AQ7" s="12">
         <v>-0.25174930000000001</v>
@@ -3735,7 +3798,7 @@
         <v>210875.2597</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AU7" s="23">
         <v>0.99999979999999999</v>
@@ -3744,7 +3807,7 @@
         <v>91.979789999999994</v>
       </c>
       <c r="AX7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AY7" s="12">
         <v>0.94224399999999997</v>
@@ -3753,7 +3816,7 @@
         <v>4703.6260300000004</v>
       </c>
       <c r="BB7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BC7" s="12">
         <v>0.91772100000000001</v>
@@ -3762,7 +3825,7 @@
         <v>5614.0714690000004</v>
       </c>
       <c r="BF7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BG7" s="12">
         <v>0.99995330000000004</v>
@@ -3771,7 +3834,7 @@
         <v>133.75837000000001</v>
       </c>
       <c r="BJ7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BK7" s="12">
         <v>0.98349299999999995</v>
@@ -3780,7 +3843,7 @@
         <v>2514.5705710000002</v>
       </c>
       <c r="BN7" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BO7" s="14">
         <f>+_xlfn.XLOOKUP($BN7,$AX$7:$AX$10,$AZ$7:$AZ$10)</f>
@@ -3813,7 +3876,7 @@
     </row>
     <row r="8" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C8" s="16">
         <v>-0.13819318</v>
@@ -3832,7 +3895,7 @@
         <v>GGM</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J8" s="18">
         <v>0.99999919999999998</v>
@@ -3845,7 +3908,7 @@
         <v>-843842.2267</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O8" s="18">
         <v>0.44333400000000001</v>
@@ -3854,7 +3917,7 @@
         <v>1304208</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S8" s="18">
         <v>0.91093299999999999</v>
@@ -3863,7 +3926,7 @@
         <v>518469</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="W8" s="32">
         <v>0.99999899999999997</v>
@@ -3872,7 +3935,7 @@
         <v>1580.191648</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AA8" s="32">
         <v>0.999973</v>
@@ -3881,7 +3944,7 @@
         <v>9120.9211990000003</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AE8" s="14">
         <f t="shared" ref="AE8:AE16" si="3">+_xlfn.XLOOKUP($AD8,N$7:N$16,P$7:P$16)</f>
@@ -3912,7 +3975,7 @@
         <v>9120.9211990000003</v>
       </c>
       <c r="AO8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AP8" s="6" t="s">
         <v>33</v>
@@ -3924,7 +3987,7 @@
         <v>15764.5885</v>
       </c>
       <c r="AT8" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AU8" s="24">
         <v>0.99997420000000004</v>
@@ -3933,7 +3996,7 @@
         <v>99.435940000000002</v>
       </c>
       <c r="AX8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AY8" s="18">
         <v>0.98572300000000002</v>
@@ -3942,7 +4005,7 @@
         <v>22520.654823000001</v>
       </c>
       <c r="BB8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BC8" s="18">
         <v>0.99224599999999996</v>
@@ -3951,7 +4014,7 @@
         <v>16596.507481000001</v>
       </c>
       <c r="BF8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BG8" s="18">
         <v>0.99999979999999999</v>
@@ -3960,7 +4023,7 @@
         <v>89.78492</v>
       </c>
       <c r="BJ8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BK8" s="18">
         <v>0.99868800000000002</v>
@@ -3969,7 +4032,7 @@
         <v>6828.2612090000002</v>
       </c>
       <c r="BN8" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BO8" s="17">
         <f t="shared" ref="BO8:BO10" si="9">+_xlfn.XLOOKUP($BN8,$AX$7:$AX$10,$AZ$7:$AZ$10)</f>
@@ -4002,7 +4065,7 @@
     </row>
     <row r="9" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C9" s="15">
         <v>0.99484592000000005</v>
@@ -4021,7 +4084,7 @@
         <v>GGM</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J9" s="12">
         <v>0.99526269999999994</v>
@@ -4034,7 +4097,7 @@
         <v>-589.51029999999446</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O9" s="12">
         <v>-0.84969700000000004</v>
@@ -4043,7 +4106,7 @@
         <v>3356209</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S9" s="12">
         <v>-0.18831400000000001</v>
@@ -4052,7 +4115,7 @@
         <v>2617900</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W9" s="31">
         <v>0.99999899999999997</v>
@@ -4061,7 +4124,7 @@
         <v>2142.2691100000002</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AA9" s="31">
         <v>0.99992800000000004</v>
@@ -4070,7 +4133,7 @@
         <v>20962.221375000001</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AE9" s="14">
         <f t="shared" si="3"/>
@@ -4101,10 +4164,10 @@
         <v>20962.221375000001</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AP9" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AQ9" s="12">
         <v>0.99683809999999995</v>
@@ -4113,7 +4176,7 @@
         <v>1100.5509999999999</v>
       </c>
       <c r="AT9" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AU9" s="23">
         <v>0.9999806</v>
@@ -4122,7 +4185,7 @@
         <v>88.003110000000007</v>
       </c>
       <c r="AX9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AY9" s="12">
         <v>0.98843700000000001</v>
@@ -4131,7 +4194,7 @@
         <v>2148.462321</v>
       </c>
       <c r="BB9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BC9" s="12">
         <v>0.97706400000000004</v>
@@ -4140,7 +4203,7 @@
         <v>3025.804118</v>
       </c>
       <c r="BF9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BG9" s="12">
         <v>0.999977</v>
@@ -4149,7 +4212,7 @@
         <v>95.776430000000005</v>
       </c>
       <c r="BJ9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BK9" s="12">
         <v>0.99990800000000002</v>
@@ -4158,7 +4221,7 @@
         <v>192.12411499999999</v>
       </c>
       <c r="BN9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BO9" s="14">
         <f t="shared" si="9"/>
@@ -4191,7 +4254,7 @@
     </row>
     <row r="10" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C10" s="16">
         <v>0.98982815000000002</v>
@@ -4210,7 +4273,7 @@
         <v>GGM</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J10" s="18">
         <v>0.99999669999999996</v>
@@ -4223,7 +4286,7 @@
         <v>-19827.444499999998</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O10" s="18">
         <v>-0.70091599999999998</v>
@@ -4232,7 +4295,7 @@
         <v>305803.09999999998</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="S10" s="18">
         <v>3.9317999999999999E-2</v>
@@ -4241,7 +4304,7 @@
         <v>224458</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="W10" s="32">
         <v>0.99999700000000002</v>
@@ -4250,7 +4313,7 @@
         <v>433.14919800000001</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AA10" s="32">
         <v>0.99969300000000005</v>
@@ -4259,7 +4322,7 @@
         <v>4105.2196100000001</v>
       </c>
       <c r="AD10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AE10" s="14">
         <f t="shared" si="3"/>
@@ -4290,7 +4353,7 @@
         <v>4105.2196100000001</v>
       </c>
       <c r="AO10" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AP10" s="6" t="s">
         <v>33</v>
@@ -4302,7 +4365,7 @@
         <v>756.05920000000003</v>
       </c>
       <c r="AT10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AU10" s="24">
         <v>0.99999979999999999</v>
@@ -4311,7 +4374,7 @@
         <v>163.67088000000001</v>
       </c>
       <c r="AX10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AY10" s="18">
         <v>0.98303399999999996</v>
@@ -4320,7 +4383,7 @@
         <v>53755.513460000002</v>
       </c>
       <c r="BB10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BC10" s="18">
         <v>0.99701899999999999</v>
@@ -4329,7 +4392,7 @@
         <v>22532.557326999999</v>
       </c>
       <c r="BF10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BG10" s="18">
         <v>0.99999990000000005</v>
@@ -4338,7 +4401,7 @@
         <v>157.38897</v>
       </c>
       <c r="BJ10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BK10" s="18">
         <v>0.99997000000000003</v>
@@ -4347,7 +4410,7 @@
         <v>2248.9489680000001</v>
       </c>
       <c r="BN10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BO10" s="17">
         <f t="shared" si="9"/>
@@ -4380,7 +4443,7 @@
     </row>
     <row r="11" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C11" s="15">
         <v>0.99039379999999999</v>
@@ -4399,7 +4462,7 @@
         <v>GGM</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J11" s="12">
         <v>0.99999199999999999</v>
@@ -4412,7 +4475,7 @@
         <v>-1231603.5988</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O11" s="12">
         <v>0.97311099999999995</v>
@@ -4421,7 +4484,7 @@
         <v>2287439</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S11" s="12">
         <v>0.98591399999999996</v>
@@ -4430,7 +4493,7 @@
         <v>1656545</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W11" s="31">
         <v>0.99999499999999997</v>
@@ -4439,7 +4502,7 @@
         <v>30356.430119000001</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA11" s="31">
         <v>0.99996600000000002</v>
@@ -4448,7 +4511,7 @@
         <v>81396.828680000006</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AE11" s="14">
         <f t="shared" si="3"/>
@@ -4479,10 +4542,10 @@
         <v>81396.828680000006</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AP11" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AQ11" s="12">
         <v>0.99021340000000002</v>
@@ -4504,7 +4567,7 @@
     </row>
     <row r="12" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C12" s="16">
         <v>0.98519310000000004</v>
@@ -4523,7 +4586,7 @@
         <v>GGM</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J12" s="18">
         <v>0.99999669999999996</v>
@@ -4536,7 +4599,7 @@
         <v>-947126.18190000008</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O12" s="18">
         <v>0.90446300000000002</v>
@@ -4545,7 +4608,7 @@
         <v>2800556</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S12" s="18">
         <v>0.96489400000000003</v>
@@ -4554,7 +4617,7 @@
         <v>1697944</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="W12" s="32">
         <v>0.99999700000000002</v>
@@ -4563,7 +4626,7 @@
         <v>16474.693931999998</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AA12" s="32">
         <v>0.99982899999999997</v>
@@ -4572,7 +4635,7 @@
         <v>118520.743653</v>
       </c>
       <c r="AD12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AE12" s="14">
         <f t="shared" si="3"/>
@@ -4603,7 +4666,7 @@
         <v>118520.743653</v>
       </c>
       <c r="AO12" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AP12" s="6" t="s">
         <v>33</v>
@@ -4626,12 +4689,12 @@
       <c r="BK12" s="14"/>
       <c r="BL12" s="14"/>
       <c r="BN12" s="19" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C13" s="15">
         <v>5.7728759999999997E-2</v>
@@ -4650,7 +4713,7 @@
         <v>GGM</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J13" s="12">
         <v>0.99991370000000002</v>
@@ -4663,7 +4726,7 @@
         <v>-176866.9877</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O13" s="12">
         <v>-327.19220100000001</v>
@@ -4672,7 +4735,7 @@
         <v>46909600</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S13" s="12">
         <v>-4.0384000000000003E-2</v>
@@ -4681,7 +4744,7 @@
         <v>2603995</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="W13" s="31">
         <v>0.99999099999999996</v>
@@ -4690,7 +4753,7 @@
         <v>7591.1932999999999</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AA13" s="31">
         <v>0.99989799999999995</v>
@@ -4699,7 +4762,7 @@
         <v>26091.076145999999</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AE13" s="14">
         <f t="shared" si="3"/>
@@ -4730,10 +4793,10 @@
         <v>26091.076145999999</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AP13" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AQ13" s="12">
         <v>0.99908359999999996</v>
@@ -4756,7 +4819,7 @@
     </row>
     <row r="14" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C14" s="16">
         <v>1.795393E-2</v>
@@ -4775,7 +4838,7 @@
         <v>GGM</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J14" s="18">
         <v>0.99998960000000003</v>
@@ -4788,7 +4851,7 @@
         <v>-46880.9761</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O14" s="18">
         <v>2.6889E-2</v>
@@ -4797,7 +4860,7 @@
         <v>353453</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="S14" s="18">
         <v>0.87112000000000001</v>
@@ -4806,7 +4869,7 @@
         <v>125949</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="W14" s="32">
         <v>0.99999000000000005</v>
@@ -4815,7 +4878,7 @@
         <v>1140.2147070000001</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AA14" s="32">
         <v>0.99961699999999998</v>
@@ -4824,7 +4887,7 @@
         <v>7011.0990389999997</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AE14" s="14">
         <f t="shared" si="3"/>
@@ -4855,7 +4918,7 @@
         <v>7011.0990389999997</v>
       </c>
       <c r="AO14" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AP14" s="6" t="s">
         <v>33</v>
@@ -4879,12 +4942,12 @@
       <c r="BK14" s="14"/>
       <c r="BL14" s="14"/>
       <c r="BN14" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C15" s="15">
         <v>0.97698001999999995</v>
@@ -4903,7 +4966,7 @@
         <v>GGM</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J15" s="12">
         <v>0.99999769999999999</v>
@@ -4916,7 +4979,7 @@
         <v>-4022279.7900999999</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O15" s="12">
         <v>0.29647899999999999</v>
@@ -4925,7 +4988,7 @@
         <v>30580360</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="S15" s="12">
         <v>0.833893</v>
@@ -4934,7 +4997,7 @@
         <v>14859300</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="W15" s="31">
         <v>0.99999800000000005</v>
@@ -4943,7 +5006,7 @@
         <v>47866.562242</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AA15" s="31">
         <v>0.99987199999999998</v>
@@ -4952,7 +5015,7 @@
         <v>412581.51297400001</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AE15" s="14">
         <f t="shared" si="3"/>
@@ -4997,7 +5060,7 @@
     </row>
     <row r="16" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C16" s="16">
         <v>5.2056409999999997E-2</v>
@@ -5016,7 +5079,7 @@
         <v>GGM</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J16" s="18">
         <v>0.98195189999999999</v>
@@ -5029,7 +5092,7 @@
         <v>-188.91730000000098</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O16" s="18">
         <v>0.52243200000000001</v>
@@ -5038,7 +5101,7 @@
         <v>283382.09999999998</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S16" s="18">
         <v>0.96743000000000001</v>
@@ -5047,7 +5110,7 @@
         <v>73683.27</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W16" s="32">
         <v>0.999996</v>
@@ -5056,7 +5119,7 @@
         <v>829.90016600000001</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AA16" s="32">
         <v>0.99970099999999995</v>
@@ -5065,7 +5128,7 @@
         <v>7087.1279500000001</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AE16" s="14">
         <f t="shared" si="3"/>
@@ -5108,7 +5171,7 @@
       <c r="BK16" s="14"/>
       <c r="BL16" s="14"/>
       <c r="BN16" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BO16" s="9" t="str">
         <f>+BO6</f>
@@ -5144,7 +5207,7 @@
       <c r="BK17" s="14"/>
       <c r="BL17" s="14"/>
       <c r="BN17" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BO17" s="12">
         <f>+_xlfn.XLOOKUP($BN17,$AX$7:$AX$9,$AY$7:$AY$9)</f>
@@ -5174,7 +5237,7 @@
       <c r="BK18" s="14"/>
       <c r="BL18" s="14"/>
       <c r="BN18" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BO18" s="18">
         <f>+_xlfn.XLOOKUP($BN18,$AX$7:$AX$9,$AY$7:$AY$9)</f>
@@ -5201,26 +5264,26 @@
     </row>
     <row r="19" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="T19" s="21"/>
       <c r="V19" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
@@ -5228,7 +5291,7 @@
       <c r="BK19" s="14"/>
       <c r="BL19" s="14"/>
       <c r="BN19" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BO19" s="12">
         <f>+_xlfn.XLOOKUP($BN19,$AX$7:$AX$9,$AY$7:$AY$9)</f>
@@ -5259,7 +5322,7 @@
       <c r="BK20" s="14"/>
       <c r="BL20" s="14"/>
       <c r="BN20" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BO20" s="18"/>
       <c r="BP20" s="18"/>
@@ -5271,94 +5334,94 @@
     </row>
     <row r="21" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B21" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="E21" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="F21" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>168</v>
-      </c>
       <c r="G21" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K21" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="L21" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="L21" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="N21" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R21" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="V21" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="W21" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Z21" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AA21" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AB21" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AD21" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AE21" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AF21" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG21" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AH21" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AI21" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AJ21" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AK21" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="BJ21" s="14"/>
       <c r="BK21" s="14"/>
@@ -5366,7 +5429,7 @@
     </row>
     <row r="22" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C22" s="15">
         <v>0.99309789999999998</v>
@@ -5385,7 +5448,7 @@
         <v>GGM</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J22" s="12">
         <v>0.99997320000000001</v>
@@ -5398,7 +5461,7 @@
         <v>-812345.71199999994</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O22" s="12">
         <v>0.82512600000000003</v>
@@ -5407,7 +5470,7 @@
         <v>5285818</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="S22" s="12">
         <v>0.64468300000000001</v>
@@ -5416,7 +5479,7 @@
         <v>7558374</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W22" s="31">
         <v>0.99996799999999997</v>
@@ -5425,7 +5488,7 @@
         <v>72886.599426000001</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AA22" s="31">
         <v>0.998919</v>
@@ -5434,7 +5497,7 @@
         <v>424624.7</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AE22" s="14">
         <f>+_xlfn.XLOOKUP($AD22,N$22:N$31,P$22:P$31)</f>
@@ -5467,7 +5530,7 @@
     </row>
     <row r="23" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C23" s="16">
         <v>0.98500410000000005</v>
@@ -5486,7 +5549,7 @@
         <v>GGM</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J23" s="18">
         <v>0.99997939999999996</v>
@@ -5499,7 +5562,7 @@
         <v>-183707.56700000001</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O23" s="18">
         <v>0.85929699999999998</v>
@@ -5508,7 +5571,7 @@
         <v>655919.19999999995</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S23" s="18">
         <v>0.86842799999999998</v>
@@ -5517,7 +5580,7 @@
         <v>634278.5</v>
       </c>
       <c r="V23" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="W23" s="32">
         <v>0.999977</v>
@@ -5526,7 +5589,7 @@
         <v>8395.1301469999999</v>
       </c>
       <c r="Z23" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AA23" s="32">
         <v>0.99666699999999997</v>
@@ -5535,7 +5598,7 @@
         <v>101494.2</v>
       </c>
       <c r="AD23" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AE23" s="14">
         <f t="shared" ref="AE23:AE31" si="17">+_xlfn.XLOOKUP($AD23,N$22:N$31,P$22:P$31)</f>
@@ -5580,7 +5643,7 @@
     </row>
     <row r="24" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C24" s="15">
         <v>0.99486560000000002</v>
@@ -5599,7 +5662,7 @@
         <v>GGM</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J24" s="12">
         <v>0.9999827</v>
@@ -5612,7 +5675,7 @@
         <v>-159756.179</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O24" s="12">
         <v>0.91229700000000002</v>
@@ -5621,7 +5684,7 @@
         <v>711743.3</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S24" s="12">
         <v>0.43064400000000003</v>
@@ -5630,7 +5693,7 @@
         <v>1813809</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W24" s="31">
         <v>0.99997899999999995</v>
@@ -5639,7 +5702,7 @@
         <v>11331.678796</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AA24" s="31">
         <v>0.99987199999999998</v>
@@ -5648,7 +5711,7 @@
         <v>27934.33</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AE24" s="14">
         <f t="shared" si="17"/>
@@ -5693,7 +5756,7 @@
     </row>
     <row r="25" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C25" s="16">
         <v>0.98980849999999998</v>
@@ -5712,7 +5775,7 @@
         <v>GGM</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J25" s="18">
         <v>0.99986940000000002</v>
@@ -5725,7 +5788,7 @@
         <v>-17572.22</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O25" s="18">
         <v>0.81773499999999999</v>
@@ -5734,7 +5797,7 @@
         <v>96842.15</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="S25" s="18">
         <v>-0.70466200000000001</v>
@@ -5743,7 +5806,7 @@
         <v>300031.3</v>
       </c>
       <c r="V25" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="W25" s="32">
         <v>0.99985199999999996</v>
@@ -5752,7 +5815,7 @@
         <v>2856.3407999999999</v>
       </c>
       <c r="Z25" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AA25" s="32">
         <v>0.99764399999999998</v>
@@ -5761,7 +5824,7 @@
         <v>11391.69</v>
       </c>
       <c r="AD25" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AE25" s="14">
         <f t="shared" si="17"/>
@@ -5806,7 +5869,7 @@
     </row>
     <row r="26" spans="2:73" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C26" s="15">
         <v>0.99044909999999997</v>
@@ -5825,7 +5888,7 @@
         <v>GGM</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J26" s="12">
         <v>0.99998489999999995</v>
@@ -5838,7 +5901,7 @@
         <v>-1215793.6359999999</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O26" s="12">
         <v>0.98488399999999998</v>
@@ -5847,7 +5910,7 @@
         <v>1726783</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S26" s="12">
         <v>0.98622900000000002</v>
@@ -5856,7 +5919,7 @@
         <v>1646926</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W26" s="31">
         <v>0.99998200000000004</v>
@@ -5865,7 +5928,7 @@
         <v>59096.011952000001</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA26" s="31">
         <v>0.99986600000000003</v>
@@ -5874,7 +5937,7 @@
         <v>162463.20000000001</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AE26" s="14">
         <f t="shared" si="17"/>
@@ -5919,7 +5982,7 @@
     </row>
     <row r="27" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C27" s="16">
         <v>0.98537799999999998</v>
@@ -5938,7 +6001,7 @@
         <v>GGM</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J27" s="18">
         <v>0.99998299999999996</v>
@@ -5951,7 +6014,7 @@
         <v>-924687.772</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O27" s="18">
         <v>0.94516</v>
@@ -5960,7 +6023,7 @@
         <v>2120841</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S27" s="18">
         <v>0.94915899999999997</v>
@@ -5969,7 +6032,7 @@
         <v>2056768</v>
       </c>
       <c r="V27" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="W27" s="32">
         <v>0.99997999999999998</v>
@@ -5978,7 +6041,7 @@
         <v>40276.492481000001</v>
       </c>
       <c r="Z27" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AA27" s="32">
         <v>0.99753099999999995</v>
@@ -5987,7 +6050,7 @@
         <v>453190.5</v>
       </c>
       <c r="AD27" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AE27" s="14">
         <f t="shared" si="17"/>
@@ -6020,7 +6083,7 @@
     </row>
     <row r="28" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C28" s="15">
         <v>0.99328240000000001</v>
@@ -6039,7 +6102,7 @@
         <v>GGM</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J28" s="12">
         <v>0.99995199999999995</v>
@@ -6052,7 +6115,7 @@
         <v>-159551.46900000001</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O28" s="12">
         <v>0.84834900000000002</v>
@@ -6061,7 +6124,7 @@
         <v>999266.5</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S28" s="12">
         <v>-0.34762500000000002</v>
@@ -6070,7 +6133,7 @@
         <v>2976087</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="W28" s="31">
         <v>0.99994000000000005</v>
@@ -6079,7 +6142,7 @@
         <v>20204.683582000001</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AA28" s="31">
         <v>0.99860599999999999</v>
@@ -6088,7 +6151,7 @@
         <v>97029.98</v>
       </c>
       <c r="AD28" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AE28" s="14">
         <f t="shared" si="17"/>
@@ -6121,7 +6184,7 @@
     </row>
     <row r="29" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C29" s="16">
         <v>0.98214460000000003</v>
@@ -6140,7 +6203,7 @@
         <v>GGM</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J29" s="18">
         <v>0.9999439</v>
@@ -6153,7 +6216,7 @@
         <v>-39000.869999999995</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O29" s="18">
         <v>0.83975299999999997</v>
@@ -6162,7 +6225,7 @@
         <v>140633.70000000001</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="S29" s="18">
         <v>0.86644399999999999</v>
@@ -6171,7 +6234,7 @@
         <v>128388.6</v>
       </c>
       <c r="V29" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="W29" s="32">
         <v>0.99993799999999999</v>
@@ -6180,7 +6243,7 @@
         <v>2835.1556179999998</v>
       </c>
       <c r="Z29" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AA29" s="32">
         <v>0.99784799999999996</v>
@@ -6189,7 +6252,7 @@
         <v>16657.2</v>
       </c>
       <c r="AD29" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AE29" s="14">
         <f t="shared" si="17"/>
@@ -6222,7 +6285,7 @@
     </row>
     <row r="30" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C30" s="15">
         <v>0.97719889999999998</v>
@@ -6241,7 +6304,7 @@
         <v>GGM</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J30" s="12">
         <v>0.99001130000000004</v>
@@ -6254,7 +6317,7 @@
         <v>-4.0000001899898052E-3</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O30" s="12">
         <v>0.83721299999999998</v>
@@ -6263,7 +6326,7 @@
         <v>14749160</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="S30" s="12">
         <v>0.84466699999999995</v>
@@ -6272,7 +6335,7 @@
         <v>14407510</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="W30" s="31">
         <v>0.999973</v>
@@ -6281,7 +6344,7 @@
         <v>189197.220477</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AA30" s="31">
         <v>0.99802000000000002</v>
@@ -6290,7 +6353,7 @@
         <v>1626782</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AE30" s="14">
         <f t="shared" si="17"/>
@@ -6323,7 +6386,7 @@
     </row>
     <row r="31" spans="2:73" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C31" s="16">
         <v>0.98704650000000005</v>
@@ -6342,7 +6405,7 @@
         <v>GGM</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J31" s="18">
         <v>0.99996839999999998</v>
@@ -6355,7 +6418,7 @@
         <v>-52796.222999999998</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O31" s="18">
         <v>0.94254700000000002</v>
@@ -6364,7 +6427,7 @@
         <v>97667.94</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S31" s="18">
         <v>0.95194400000000001</v>
@@ -6373,7 +6436,7 @@
         <v>89659.199999999997</v>
       </c>
       <c r="V31" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W31" s="32">
         <v>0.99996499999999999</v>
@@ -6382,7 +6445,7 @@
         <v>2423.543439</v>
       </c>
       <c r="Z31" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AA31" s="32">
         <v>0.98897800000000002</v>
@@ -6391,7 +6454,7 @@
         <v>43128.99</v>
       </c>
       <c r="AD31" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AE31" s="14">
         <f t="shared" si="17"/>
@@ -6429,59 +6492,59 @@
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="V34" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B36" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="F36" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E36" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>168</v>
-      </c>
       <c r="G36" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K36" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="L36" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="L36" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="V36" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="W36" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C37" s="15">
         <v>0.99347419999999997</v>
@@ -6500,7 +6563,7 @@
         <v>GGM</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J37" s="12">
         <v>0.99883089999999997</v>
@@ -6513,7 +6576,7 @@
         <v>-416743.97</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W37" s="31">
         <v>0.99801799999999996</v>
@@ -6524,7 +6587,7 @@
     </row>
     <row r="38" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C38" s="16">
         <v>0.9861259</v>
@@ -6543,7 +6606,7 @@
         <v>GGM</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J38" s="18">
         <v>0.99688900000000003</v>
@@ -6556,7 +6619,7 @@
         <v>-111152.34000000001</v>
       </c>
       <c r="V38" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="W38" s="32">
         <v>0.99567000000000005</v>
@@ -6567,7 +6630,7 @@
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C39" s="15">
         <v>0.99485219999999996</v>
@@ -6586,7 +6649,7 @@
         <v>GGM</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J39" s="12">
         <v>0.99764529999999996</v>
@@ -6599,7 +6662,7 @@
         <v>-54364.739999999991</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W39" s="31">
         <v>0.99534699999999998</v>
@@ -6610,7 +6673,7 @@
     </row>
     <row r="40" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C40" s="16">
         <v>0.98931369999999996</v>
@@ -6629,7 +6692,7 @@
         <v>GGM</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J40" s="18">
         <v>0.99412920000000005</v>
@@ -6642,7 +6705,7 @@
         <v>-4815.9000000000015</v>
       </c>
       <c r="V40" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="W40" s="32">
         <v>0.99124800000000002</v>
@@ -6653,7 +6716,7 @@
     </row>
     <row r="41" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C41" s="15">
         <v>0.9914906</v>
@@ -6672,7 +6735,7 @@
         <v>GGM</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J41" s="12">
         <v>0.99875570000000002</v>
@@ -6685,7 +6748,7 @@
         <v>-725755.52999999991</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W41" s="31">
         <v>0.99727699999999997</v>
@@ -6696,7 +6759,7 @@
     </row>
     <row r="42" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C42" s="16">
         <v>0.98630370000000001</v>
@@ -6715,7 +6778,7 @@
         <v>GGM</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J42" s="18">
         <v>0.9954769</v>
@@ -6728,7 +6791,7 @@
         <v>-467033.16000000003</v>
       </c>
       <c r="V42" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="W42" s="32">
         <v>0.99294800000000005</v>
@@ -6739,7 +6802,7 @@
     </row>
     <row r="43" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C43" s="15">
         <v>0.99346559999999995</v>
@@ -6758,7 +6821,7 @@
         <v>GGM</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J43" s="12">
         <v>0.99769969999999997</v>
@@ -6771,7 +6834,7 @@
         <v>-71662.28</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="W43" s="31">
         <v>0.99575800000000003</v>
@@ -6782,7 +6845,7 @@
     </row>
     <row r="44" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C44" s="16">
         <v>0.98240799999999995</v>
@@ -6801,7 +6864,7 @@
         <v>GGM</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J44" s="18">
         <v>0.99363820000000003</v>
@@ -6814,7 +6877,7 @@
         <v>-16968.219999999998</v>
       </c>
       <c r="V44" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="W44" s="32">
         <v>0.99148400000000003</v>
@@ -6825,7 +6888,7 @@
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C45" s="15">
         <v>0.97879510000000003</v>
@@ -6844,7 +6907,7 @@
         <v>GGM</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J45" s="12">
         <v>0.98804809999999998</v>
@@ -6857,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="W45" s="31">
         <v>0.993228</v>
@@ -6868,7 +6931,7 @@
     </row>
     <row r="46" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B46" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C46" s="16">
         <v>0.98749869999999995</v>
@@ -6887,7 +6950,7 @@
         <v>GGM</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J46" s="18">
         <v>0.99455020000000005</v>
@@ -6900,7 +6963,7 @@
         <v>-23138.859999999997</v>
       </c>
       <c r="V46" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W46" s="32">
         <v>0.99019000000000001</v>
@@ -7451,73 +7514,73 @@
   <sheetData>
     <row r="1" spans="2:83" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AC1" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="AG1" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="AT1" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="AG1" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="AT1" s="10" t="s">
-        <v>288</v>
-      </c>
       <c r="AX1" s="20" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="2:83" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="N2" s="19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R2" s="19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S2" s="19"/>
       <c r="V2" s="19" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="W2" s="19"/>
       <c r="Z2" s="19" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AD2" s="19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AH2" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AI2" s="19"/>
       <c r="AJ2" s="19"/>
       <c r="AT2" s="19" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AY2" s="19" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="BC2" s="19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BG2" s="19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="BK2" s="19" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="BO2" s="19" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="BS2" s="19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="BW2" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="2:83" x14ac:dyDescent="0.3">
@@ -7538,55 +7601,55 @@
     </row>
     <row r="4" spans="2:83" ht="16.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="T4" s="21"/>
       <c r="V4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AD4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AH4" s="13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AI4" s="13"/>
       <c r="AJ4" s="13"/>
       <c r="AT4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AY4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="BC4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="BG4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="BK4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="BO4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="BS4" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="BW4" s="13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="2:83" ht="16.8" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -7594,204 +7657,204 @@
     </row>
     <row r="6" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>168</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K6" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="L6" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="L6" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="N6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="S6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="W6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AA6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AB6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AD6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AE6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AF6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AH6" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AI6" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AJ6" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK6" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AM6" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AN6" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AO6" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AP6" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AT6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AU6" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AV6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AW6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AY6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AZ6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BA6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BC6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BD6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BE6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BG6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BH6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BI6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BK6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BL6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BM6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BO6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BP6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BQ6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BS6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BT6" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BU6" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BW6" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BX6" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BY6" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="BZ6" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="CA6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="CB6" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="CC6" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="CD6" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="CE6" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" s="15">
         <v>-0.88045949999999995</v>
@@ -7810,7 +7873,7 @@
         <v>BM</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J7" s="33">
         <v>-18.442921699999999</v>
@@ -7823,7 +7886,7 @@
         <v>-33376.900000000373</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="O7" s="33">
         <v>-1167.2323490000001</v>
@@ -7832,7 +7895,7 @@
         <v>35518040</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="S7" s="33">
         <v>-1167.7180880000001</v>
@@ -7841,7 +7904,7 @@
         <v>35525420</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W7" s="33">
         <v>-6.5581474999999996</v>
@@ -7850,7 +7913,7 @@
         <v>2922129.51</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AA7" s="33">
         <v>-5.1333900000000003</v>
@@ -7859,7 +7922,7 @@
         <v>2632341</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AE7" s="33">
         <v>0.15242800000000001</v>
@@ -7868,7 +7931,7 @@
         <v>978543.1</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AI7" s="14">
         <f t="shared" ref="AI7:AI16" si="0">+_xlfn.XLOOKUP($AH7,N$7:N$16,P$7:P$16)</f>
@@ -7903,10 +7966,10 @@
         <v>978543.1</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AV7" s="12">
         <v>-5.7474112999999996</v>
@@ -7915,7 +7978,7 @@
         <v>269246.39079999999</v>
       </c>
       <c r="AY7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AZ7" s="15">
         <v>-2.6609845999999999</v>
@@ -7924,7 +7987,7 @@
         <v>62.22701</v>
       </c>
       <c r="BC7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BD7" s="33">
         <v>-1556969</v>
@@ -7933,7 +7996,7 @@
         <v>40580.75</v>
       </c>
       <c r="BG7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BH7" s="33">
         <v>-1466067</v>
@@ -7942,7 +8005,7 @@
         <v>39378.31</v>
       </c>
       <c r="BK7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BL7" s="33">
         <v>0.45879575</v>
@@ -7951,7 +8014,7 @@
         <v>23.92548</v>
       </c>
       <c r="BO7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BP7" s="33">
         <v>-71.902986999999996</v>
@@ -7960,7 +8023,7 @@
         <v>1366.269454</v>
       </c>
       <c r="BS7" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BT7" s="33">
         <v>0.95831999999999995</v>
@@ -7969,7 +8032,7 @@
         <v>6.6396439999999997</v>
       </c>
       <c r="BW7" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BX7" s="14">
         <f>+_xlfn.XLOOKUP($BW7,$BC$7:$BC$10,$BE$7:$BE$10)</f>
@@ -8006,7 +8069,7 @@
     </row>
     <row r="8" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C8" s="16">
         <v>-28.473542599999998</v>
@@ -8025,7 +8088,7 @@
         <v>BM</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J8" s="34">
         <v>-39.417364499999998</v>
@@ -8038,7 +8101,7 @@
         <v>-106032.52000000002</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O8" s="34">
         <v>-342.44675999999998</v>
@@ -8047,7 +8110,7 @@
         <v>4850543</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S8" s="34">
         <v>-342.43093699999997</v>
@@ -8056,7 +8119,7 @@
         <v>4850431</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="W8" s="34">
         <v>-0.14459959999999999</v>
@@ -8065,7 +8128,7 @@
         <v>297053.53000000003</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AA8" s="34">
         <v>-3.654674</v>
@@ -8074,7 +8137,7 @@
         <v>599035.5</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AE8" s="34">
         <v>0.90742500000000004</v>
@@ -8083,7 +8146,7 @@
         <v>84480.34</v>
       </c>
       <c r="AH8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AI8" s="14">
         <f t="shared" si="0"/>
@@ -8118,7 +8181,7 @@
         <v>84480.34</v>
       </c>
       <c r="AT8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AU8" s="6" t="s">
         <v>33</v>
@@ -8130,7 +8193,7 @@
         <v>367562.62449999998</v>
       </c>
       <c r="AY8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AZ8" s="16">
         <v>0.59136739999999999</v>
@@ -8139,7 +8202,7 @@
         <v>33522.334649999997</v>
       </c>
       <c r="BC8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BD8" s="34">
         <v>-96.224559999999997</v>
@@ -8148,7 +8211,7 @@
         <v>517077.6</v>
       </c>
       <c r="BG8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BH8" s="34">
         <v>-93.707589999999996</v>
@@ -8157,7 +8220,7 @@
         <v>510340.6</v>
       </c>
       <c r="BK8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BL8" s="34">
         <v>-0.12438572000000001</v>
@@ -8166,7 +8229,7 @@
         <v>55606.478790000001</v>
       </c>
       <c r="BO8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BP8" s="34">
         <v>0.70949499999999999</v>
@@ -8175,7 +8238,7 @@
         <v>55867.376609999999</v>
       </c>
       <c r="BS8" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BT8" s="34">
         <v>0.56132400000000005</v>
@@ -8184,7 +8247,7 @@
         <v>34732.780121999996</v>
       </c>
       <c r="BW8" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BX8" s="17">
         <f t="shared" ref="BX8:BX10" si="10">+_xlfn.XLOOKUP($BW8,$BC$7:$BC$10,$BE$7:$BE$10)</f>
@@ -8221,7 +8284,7 @@
     </row>
     <row r="9" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C9" s="15">
         <v>-14.8750605</v>
@@ -8240,7 +8303,7 @@
         <v>BM</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J9" s="33">
         <v>-101.5126727</v>
@@ -8253,7 +8316,7 @@
         <v>888.47000000000116</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O9" s="33">
         <v>-74322.225143000003</v>
@@ -8262,7 +8325,7 @@
         <v>6319862</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S9" s="33">
         <v>-74373.441279000006</v>
@@ -8271,7 +8334,7 @@
         <v>6322039</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W9" s="33">
         <v>-844.09909029999994</v>
@@ -8280,7 +8343,7 @@
         <v>720988.16000000003</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AA9" s="33">
         <v>-527.98294699999997</v>
@@ -8289,7 +8352,7 @@
         <v>570420.5</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AE9" s="33">
         <v>0.85376200000000002</v>
@@ -8298,7 +8361,7 @@
         <v>9484.2870000000003</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AI9" s="14">
         <f t="shared" si="0"/>
@@ -8333,10 +8396,10 @@
         <v>9484.2870000000003</v>
       </c>
       <c r="AT9" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AU9" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AV9" s="12">
         <v>-87.875995500000002</v>
@@ -8345,7 +8408,7 @@
         <v>1508.5369000000001</v>
       </c>
       <c r="AY9" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AZ9" s="15">
         <v>-54.161358200000002</v>
@@ -8354,7 +8417,7 @@
         <v>326.82960000000003</v>
       </c>
       <c r="BC9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BD9" s="33">
         <v>-1116797</v>
@@ -8363,7 +8426,7 @@
         <v>46504.1</v>
       </c>
       <c r="BG9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BH9" s="33">
         <v>-1057560</v>
@@ -8372,7 +8435,7 @@
         <v>45253.96</v>
       </c>
       <c r="BK9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BL9" s="33">
         <v>0.43556107999999999</v>
@@ -8381,7 +8444,7 @@
         <v>33.06073</v>
       </c>
       <c r="BO9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BP9" s="33">
         <v>-16.475088</v>
@@ -8390,7 +8453,7 @@
         <v>1129.176692</v>
       </c>
       <c r="BS9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BT9" s="33">
         <v>-2.6274600000000001</v>
@@ -8399,7 +8462,7 @@
         <v>83.811807000000002</v>
       </c>
       <c r="BW9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BX9" s="14">
         <f t="shared" si="10"/>
@@ -8436,7 +8499,7 @@
     </row>
     <row r="10" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C10" s="16">
         <v>-45.222719599999998</v>
@@ -8455,7 +8518,7 @@
         <v>GGM</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J10" s="34">
         <v>-36.981007400000003</v>
@@ -8468,7 +8531,7 @@
         <v>-4312.989999999998</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O10" s="34">
         <v>-5849.742776</v>
@@ -8477,7 +8540,7 @@
         <v>648975</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="S10" s="34">
         <v>-5872.4790750000002</v>
@@ -8486,7 +8549,7 @@
         <v>650234.80000000005</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="W10" s="34">
         <v>-39.938344000000001</v>
@@ -8495,7 +8558,7 @@
         <v>58675.03</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AA10" s="34">
         <v>-164.294004</v>
@@ -8504,7 +8567,7 @@
         <v>117900.8</v>
       </c>
       <c r="AD10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AE10" s="34">
         <v>0.70942099999999997</v>
@@ -8513,7 +8576,7 @@
         <v>4943.3419999999996</v>
       </c>
       <c r="AH10" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AI10" s="14">
         <f t="shared" si="0"/>
@@ -8548,7 +8611,7 @@
         <v>4943.3419999999996</v>
       </c>
       <c r="AT10" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AU10" s="6" t="s">
         <v>33</v>
@@ -8560,7 +8623,7 @@
         <v>1273.9808</v>
       </c>
       <c r="AY10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AZ10" s="16">
         <v>-7.8432873000000001</v>
@@ -8569,7 +8632,7 @@
         <v>63829.462</v>
       </c>
       <c r="BC10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BD10" s="34">
         <v>-2694.8380000000002</v>
@@ -8578,7 +8641,7 @@
         <v>1114452</v>
       </c>
       <c r="BG10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BH10" s="34">
         <v>-2581.6080000000002</v>
@@ -8587,7 +8650,7 @@
         <v>1090796</v>
       </c>
       <c r="BK10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BL10" s="34">
         <v>1.256618E-2</v>
@@ -8596,7 +8659,7 @@
         <v>21328.893110000001</v>
       </c>
       <c r="BO10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BP10" s="34">
         <v>-1.0690390000000001</v>
@@ -8605,7 +8668,7 @@
         <v>197356.89684900001</v>
       </c>
       <c r="BS10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BT10" s="34">
         <v>0.74929500000000004</v>
@@ -8614,7 +8677,7 @@
         <v>10747.212681999999</v>
       </c>
       <c r="BW10" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BX10" s="17">
         <f t="shared" si="10"/>
@@ -8651,7 +8714,7 @@
     </row>
     <row r="11" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C11" s="15">
         <v>-11.4324584</v>
@@ -8670,7 +8733,7 @@
         <v>GGM</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J11" s="33">
         <v>0.7672158</v>
@@ -8683,7 +8746,7 @@
         <v>-29986.589999999851</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O11" s="33">
         <v>-210.45065</v>
@@ -8692,7 +8755,7 @@
         <v>35465050</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S11" s="33">
         <v>-210.44169099999999</v>
@@ -8701,7 +8764,7 @@
         <v>35464300</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W11" s="33">
         <v>-10.440305199999999</v>
@@ -8710,7 +8773,7 @@
         <v>8249258.3600000003</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA11" s="33">
         <v>-22.354537000000001</v>
@@ -8719,7 +8782,7 @@
         <v>11786420</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AE11" s="33">
         <v>0.96534200000000003</v>
@@ -8728,7 +8791,7 @@
         <v>454043.1</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AI11" s="14">
         <f t="shared" si="0"/>
@@ -8763,10 +8826,10 @@
         <v>454043.1</v>
       </c>
       <c r="AT11" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AU11" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AV11" s="12">
         <v>-62.730387200000003</v>
@@ -8791,7 +8854,7 @@
     </row>
     <row r="12" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C12" s="16">
         <v>-111.9174616</v>
@@ -8810,7 +8873,7 @@
         <v>GGM</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J12" s="34">
         <v>-11.824242099999999</v>
@@ -8823,7 +8886,7 @@
         <v>-1097250.2800000003</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O12" s="34">
         <v>-242.90492599999999</v>
@@ -8832,7 +8895,7 @@
         <v>23865070</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S12" s="34">
         <v>-242.90095299999999</v>
@@ -8841,7 +8904,7 @@
         <v>23864880</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="W12" s="34">
         <v>0.73289349999999998</v>
@@ -8850,7 +8913,7 @@
         <v>789759.22</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AA12" s="34">
         <v>-9.6180679999999992</v>
@@ -8859,7 +8922,7 @@
         <v>4979380</v>
       </c>
       <c r="AD12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AE12" s="34">
         <v>-20.279411</v>
@@ -8868,7 +8931,7 @@
         <v>7049078</v>
       </c>
       <c r="AH12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AI12" s="14">
         <f t="shared" si="0"/>
@@ -8903,7 +8966,7 @@
         <v>7049078</v>
       </c>
       <c r="AT12" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AU12" s="6" t="s">
         <v>33</v>
@@ -8931,7 +8994,7 @@
     </row>
     <row r="13" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C13" s="15">
         <v>-1.2333866</v>
@@ -8950,7 +9013,7 @@
         <v>GGM</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J13" s="33">
         <v>-1.2637936999999999</v>
@@ -8963,7 +9026,7 @@
         <v>29629.130000000005</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O13" s="33">
         <v>-1933.2909870000001</v>
@@ -8972,7 +9035,7 @@
         <v>7179580</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S13" s="33">
         <v>-1935.788642</v>
@@ -8981,7 +9044,7 @@
         <v>7184214</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="W13" s="33">
         <v>-179.7974595</v>
@@ -8990,7 +9053,7 @@
         <v>2418834.08</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AA13" s="33">
         <v>-29.274857999999998</v>
@@ -8999,7 +9062,7 @@
         <v>989808</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AE13" s="33">
         <v>0.103008</v>
@@ -9008,7 +9071,7 @@
         <v>170374.3</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AI13" s="14">
         <f t="shared" si="0"/>
@@ -9043,10 +9106,10 @@
         <v>170374.3</v>
       </c>
       <c r="AT13" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AU13" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AV13" s="12">
         <v>-31.850383799999999</v>
@@ -9072,7 +9135,7 @@
     </row>
     <row r="14" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C14" s="16">
         <v>-91.031581299999999</v>
@@ -9091,7 +9154,7 @@
         <v>BM</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J14" s="34">
         <v>-89.237210300000001</v>
@@ -9104,7 +9167,7 @@
         <v>-8925.2999999999884</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O14" s="34">
         <v>-1799.8141330000001</v>
@@ -9113,7 +9176,7 @@
         <v>996737.1</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="S14" s="34">
         <v>-1795.435129</v>
@@ -9122,7 +9185,7 @@
         <v>995524.5</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="W14" s="34">
         <v>-5.0710414999999998</v>
@@ -9131,7 +9194,7 @@
         <v>61304.51</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AA14" s="34">
         <v>-83.509297000000004</v>
@@ -9140,7 +9203,7 @@
         <v>228724.7</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AE14" s="34">
         <v>-0.475381</v>
@@ -9149,7 +9212,7 @@
         <v>30221.29</v>
       </c>
       <c r="AH14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AI14" s="14">
         <f t="shared" si="0"/>
@@ -9184,7 +9247,7 @@
         <v>30221.29</v>
       </c>
       <c r="AT14" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AU14" s="6" t="s">
         <v>33</v>
@@ -9211,12 +9274,12 @@
       <c r="BT14" s="14"/>
       <c r="BU14" s="14"/>
       <c r="BW14" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C15" s="15">
         <v>-56.708334700000002</v>
@@ -9235,7 +9298,7 @@
         <v>BM</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J15" s="33">
         <v>-12.7604203</v>
@@ -9248,7 +9311,7 @@
         <v>12860522.289999999</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O15" s="33">
         <v>-779.10362199999997</v>
@@ -9257,7 +9320,7 @@
         <v>98519360</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="S15" s="33">
         <v>-779.06910800000003</v>
@@ -9266,7 +9329,7 @@
         <v>98517180</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="W15" s="33">
         <v>0.20104150000000001</v>
@@ -9275,7 +9338,7 @@
         <v>3152880.72</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AA15" s="33">
         <v>-25.673124000000001</v>
@@ -9284,7 +9347,7 @@
         <v>18217230</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AE15" s="33">
         <v>0.66067100000000001</v>
@@ -9293,7 +9356,7 @@
         <v>2054735</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AI15" s="14">
         <f t="shared" si="0"/>
@@ -9343,36 +9406,36 @@
       <c r="BT15" s="14"/>
       <c r="BU15" s="14"/>
       <c r="BW15" s="9" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="BX15" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="BY15" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="BZ15" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="CA15" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="BY15" s="9" t="s">
+      <c r="CB15" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="BZ15" s="9" t="s">
+      <c r="CC15" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="CA15" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="CB15" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="CC15" s="9" t="s">
-        <v>298</v>
-      </c>
       <c r="CD15" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="CE15" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="2:83" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C16" s="16">
         <v>-15.631722699999999</v>
@@ -9391,7 +9454,7 @@
         <v>GGM</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J16" s="34">
         <v>-86.961009899999993</v>
@@ -9404,7 +9467,7 @@
         <v>-12878536.9</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O16" s="34">
         <v>-2140.578501</v>
@@ -9413,7 +9476,7 @@
         <v>1000999</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S16" s="34">
         <v>-2138.2510229999998</v>
@@ -9422,7 +9485,7 @@
         <v>1000455</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W16" s="34">
         <v>0.41362320000000002</v>
@@ -9431,7 +9494,7 @@
         <v>16826.12</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AA16" s="34">
         <v>-77.961535999999995</v>
@@ -9440,7 +9503,7 @@
         <v>195255.6</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AE16" s="34">
         <v>0.882351</v>
@@ -9449,7 +9512,7 @@
         <v>7536.8639999999996</v>
       </c>
       <c r="AH16" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AI16" s="14">
         <f t="shared" si="0"/>
@@ -9499,7 +9562,7 @@
       <c r="BT16" s="14"/>
       <c r="BU16" s="14"/>
       <c r="BW16" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="BX16" s="14">
         <v>6.5000390000000001</v>
@@ -9528,7 +9591,7 @@
     </row>
     <row r="17" spans="34:83" x14ac:dyDescent="0.3">
       <c r="BW17" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BX17" s="17">
         <v>28631.619245999998</v>
@@ -9557,7 +9620,7 @@
     </row>
     <row r="18" spans="34:83" x14ac:dyDescent="0.3">
       <c r="BW18" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="BX18" s="14">
         <v>7253.7510709999997</v>
@@ -9586,7 +9649,7 @@
     </row>
     <row r="19" spans="34:83" x14ac:dyDescent="0.3">
       <c r="BW19" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BX19" s="17">
         <v>11.312836000000001</v>
@@ -9615,7 +9678,7 @@
     </row>
     <row r="20" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH20" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="BW20" s="19"/>
       <c r="BX20" s="19"/>
@@ -9626,28 +9689,28 @@
     </row>
     <row r="21" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH21" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AI21" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="AJ21" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="AK21" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="AL21" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="AJ21" s="9" t="s">
+      <c r="AM21" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="AK21" s="9" t="s">
+      <c r="AN21" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="AL21" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="AM21" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="AN21" s="9" t="s">
-        <v>298</v>
-      </c>
       <c r="AO21" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="BW21" s="13"/>
       <c r="BX21" s="13"/>
@@ -9658,7 +9721,7 @@
     </row>
     <row r="22" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH22" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AI22" s="14">
         <v>8441809</v>
@@ -9690,7 +9753,7 @@
     </row>
     <row r="23" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH23" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AI23" s="14">
         <v>4189569</v>
@@ -9730,7 +9793,7 @@
     </row>
     <row r="24" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH24" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AI24" s="14">
         <v>43852750</v>
@@ -9771,7 +9834,7 @@
     </row>
     <row r="25" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH25" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AI25" s="14">
         <v>8964942</v>
@@ -9810,12 +9873,12 @@
       <c r="BT25" s="28"/>
       <c r="BU25" s="28"/>
       <c r="BX25" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="34:83" ht="16.8" x14ac:dyDescent="0.3">
       <c r="AH26" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AI26" s="14">
         <v>97036170</v>
@@ -9854,107 +9917,107 @@
       <c r="BT26" s="28"/>
       <c r="BU26" s="28"/>
       <c r="BX26" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="BY26" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BZ26" s="9" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="CA26" s="9" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="34:83" x14ac:dyDescent="0.3">
       <c r="BX27" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="BY27" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="BZ27" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="CA27" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="34:83" x14ac:dyDescent="0.3">
       <c r="BX28" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="BY28" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="BZ28" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="CA28" s="6" t="s">
         <v>333</v>
-      </c>
-      <c r="BY28" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="BZ28" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="CA28" s="6" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="29" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH29" s="29" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="BX29" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="BY29" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="BZ29" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="CA29" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH30" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AI30" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="AJ30" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="AK30" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="AL30" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="AJ30" s="9" t="s">
+      <c r="AM30" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="AK30" s="9" t="s">
+      <c r="AN30" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="AL30" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="AM30" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="AN30" s="9" t="s">
-        <v>298</v>
-      </c>
       <c r="AO30" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AP30" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="BX30" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="BY30" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="BZ30" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="BY30" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="BZ30" s="6" t="s">
-        <v>343</v>
-      </c>
       <c r="CA30" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="31" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH31" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AI31" s="14">
         <v>8545518</v>
@@ -9981,18 +10044,18 @@
         <v>7268706</v>
       </c>
       <c r="BX31" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="BY31" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="CA31" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="CA31" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="32" spans="34:83" x14ac:dyDescent="0.3">
       <c r="AH32" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AI32" s="14">
         <v>3983888</v>
@@ -10019,19 +10082,19 @@
         <v>1387276</v>
       </c>
       <c r="BX32" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="BY32" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="BZ32" s="6"/>
       <c r="CA32" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH33" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AI33" s="14">
         <v>45450350</v>
@@ -10058,18 +10121,18 @@
         <v>86397360</v>
       </c>
       <c r="BX33" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="BY33" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="CA33" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH34" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AI34" s="14">
         <v>9150194</v>
@@ -10097,14 +10160,14 @@
       </c>
       <c r="BX34" s="6"/>
       <c r="BY34" s="6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="BZ34" s="6"/>
       <c r="CA34" s="6"/>
     </row>
     <row r="35" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH35" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AI35" s="14">
         <v>97801220</v>
@@ -10131,56 +10194,56 @@
         <v>259778200</v>
       </c>
       <c r="BY35" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="36" spans="34:79" x14ac:dyDescent="0.3">
       <c r="BX36" s="6"/>
       <c r="BY36" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="BZ36" s="6"/>
       <c r="CA36" s="6"/>
     </row>
     <row r="37" spans="34:79" x14ac:dyDescent="0.3">
       <c r="BY37" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH38" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH39" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AI39" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="AJ39" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="AK39" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="AL39" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="AJ39" s="9" t="s">
+      <c r="AM39" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="AK39" s="9" t="s">
+      <c r="AN39" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="AL39" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="AM39" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="AN39" s="9" t="s">
-        <v>298</v>
-      </c>
       <c r="AO39" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH40" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AI40" s="14">
         <v>8333632</v>
@@ -10207,7 +10270,7 @@
     </row>
     <row r="41" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH41" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AI41" s="14">
         <v>4180177</v>
@@ -10234,7 +10297,7 @@
     </row>
     <row r="42" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH42" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AI42" s="14">
         <v>45846120</v>
@@ -10261,7 +10324,7 @@
     </row>
     <row r="43" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH43" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AI43" s="14">
         <v>8779838</v>
@@ -10288,7 +10351,7 @@
     </row>
     <row r="44" spans="34:79" x14ac:dyDescent="0.3">
       <c r="AH44" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AI44" s="14">
         <v>84855730</v>
@@ -10315,139 +10378,139 @@
     </row>
     <row r="49" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH49" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="50" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH50" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AI50" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AJ50" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AK50" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AL50" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH51" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AI51" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AJ51" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AK51" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AL51" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="52" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH52" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AI52" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AJ52" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AK52" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AL52" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH53" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="AI53" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="AJ53" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="AK53" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="AI53" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="AJ53" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="AK53" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="AL53" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="54" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH54" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AI54" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AJ54" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AK54" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AL54" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="55" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH55" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AI55" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AJ55" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AK55" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AL55" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH56" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AI56" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AJ56" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AK56" s="6"/>
       <c r="AL56" s="6"/>
     </row>
     <row r="57" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH57" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AI57" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AJ57" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH58" s="6"/>
       <c r="AI58" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AJ58" s="6"/>
       <c r="AK58" s="6"/>
@@ -10455,13 +10518,13 @@
     </row>
     <row r="59" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AI59" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="60" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH60" s="6"/>
       <c r="AI60" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AJ60" s="6"/>
       <c r="AK60" s="6"/>
@@ -10469,13 +10532,13 @@
     </row>
     <row r="61" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AI61" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="62" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AH62" s="6"/>
       <c r="AI62" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AJ62" s="6"/>
       <c r="AK62" s="6"/>
@@ -10483,7 +10546,7 @@
     </row>
     <row r="63" spans="34:38" x14ac:dyDescent="0.3">
       <c r="AI63" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -11416,7 +11479,7 @@
   <sheetData>
     <row r="1" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
@@ -11424,7 +11487,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
@@ -11432,7 +11495,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
@@ -11440,7 +11503,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
@@ -11448,7 +11511,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
@@ -11456,7 +11519,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
@@ -11464,7 +11527,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
@@ -11472,7 +11535,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
@@ -11480,7 +11543,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
@@ -11488,7 +11551,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
@@ -11496,7 +11559,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
@@ -11504,7 +11567,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
@@ -11512,7 +11575,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
@@ -11520,7 +11583,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
@@ -11528,7 +11591,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
@@ -11536,7 +11599,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
@@ -11544,7 +11607,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
@@ -11552,7 +11615,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
@@ -11560,7 +11623,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
@@ -11568,7 +11631,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
@@ -11576,7 +11639,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
@@ -11584,7 +11647,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
@@ -11592,7 +11655,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
@@ -11600,7 +11663,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
@@ -11608,7 +11671,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
@@ -11616,7 +11679,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
@@ -11624,7 +11687,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
@@ -11632,7 +11695,7 @@
         <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
@@ -11640,7 +11703,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
@@ -11648,7 +11711,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
@@ -11656,7 +11719,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -11664,7 +11727,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
@@ -11672,7 +11735,7 @@
         <v>32</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
@@ -11680,7 +11743,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
@@ -11688,7 +11751,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
@@ -11696,7 +11759,7 @@
         <v>35</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
@@ -11704,7 +11767,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
@@ -11712,7 +11775,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
@@ -11720,7 +11783,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
@@ -11728,7 +11791,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
@@ -11736,7 +11799,7 @@
         <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -11755,37 +11818,37 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B1" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51007C25-6365-4EF8-B51A-773694D017B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4CE30C-C5DC-4F46-84AE-9BE0C422B0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
   <sheets>
     <sheet name="literature review" sheetId="1" r:id="rId1"/>
@@ -2108,6 +2108,9 @@
       <c r="E24" s="4" t="s">
         <v>208</v>
       </c>
+      <c r="F24" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="G24" s="39" t="s">
         <v>356</v>
       </c>
@@ -2124,9 +2127,6 @@
       </c>
       <c r="E25" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="G25" s="39" t="s">
         <v>356</v>

--- a/administrative/main.xlsx
+++ b/administrative/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\thesis\administrative\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4CE30C-C5DC-4F46-84AE-9BE0C422B0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA7E228-652B-4B6F-AA70-9DF3A9D5DE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4AC8BB16-67F5-4941-86E8-7E194268DB8A}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="400">
   <si>
     <t>Pandemics &amp; Diffussion Models</t>
   </si>
@@ -1136,6 +1136,135 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s43762-024-00132-2</t>
+  </si>
+  <si>
+    <t>Impact of initial outbreak locations on transmission risk of infectious diseases in an intra-urban area</t>
+  </si>
+  <si>
+    <t>Effect of initial case on SIR (type) models: simulatio via networks</t>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10503727/</t>
+  </si>
+  <si>
+    <t>Latitude and longitude as drivers of COVID-19 waves’ behavior in Europe: A time-space perspective of the pandemic</t>
+  </si>
+  <si>
+    <t>Multivariate COX, Gam. Covid for centroids of countries: No effect on surge, but effect on instensity</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41597-022-01797-2</t>
+  </si>
+  <si>
+    <t>A global dataset of pandemic- and epidemic-prone disease outbreaks</t>
+  </si>
+  <si>
+    <t>Africa, America, Asia are hotspots for disease outbreaks, the data is created at country level</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/doi/10.1177/1176934321989695</t>
+  </si>
+  <si>
+    <t>Temperature and Latitude Correlate with SARS-CoV-2 Epidemiological Variables but not with Genomic Change Worldwide</t>
+  </si>
+  <si>
+    <t>Temp and latitude as covid predictors, longitude was not effective, Pearson correlation and p-value</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0269749120337866</t>
+  </si>
+  <si>
+    <t>The effect of latitude and PM2.5 on spreading of SARS-CoV-2 in tropical and temperate zone countries</t>
+  </si>
+  <si>
+    <t>Hot countries get 14x more covid, latitude, temp, air pollution, humidity among predictors of COVID: mainly correlation</t>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3121613/</t>
+  </si>
+  <si>
+    <t>The influence of geographic and climate factors on the timing of dengue epidemics in Perú, 1994-2008</t>
+  </si>
+  <si>
+    <t>Dengue with demographic and climate factors across geographic regions : Difference in jungle and coastal zone: data is aggregated by region (jungle, coast…)</t>
+  </si>
+  <si>
+    <t>https://research.pasteur.fr/en/publication/temperature-season-and-latitude-influence-development-related-phenotypes-of-philippine-aedes-aegypti-linnaeus-implications-for-dengue-control-amidst-global-warming/</t>
+  </si>
+  <si>
+    <t>Temperature, season, and latitude influence development-related phenotypes of Philippine Aedes aegypti (Linnaeus): Implications for dengue control amidst global warming.</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-024-56044-y</t>
+  </si>
+  <si>
+    <t>Climate change, thermal anomalies, and the recent progression of dengue in Brazil</t>
+  </si>
+  <si>
+    <t>identify climatic and demographic indicators that explain (2014–2020)dengue, high altitude was barrier, now is not</t>
+  </si>
+  <si>
+    <t>https://www.thelancet.com/journals/lanplh/article/PIIS2542-5196(20)30292-8/fulltext</t>
+  </si>
+  <si>
+    <t>Combined effects of hydrometeorological hazards and urbanisation on dengue risk in Brazil: a spatiotemporal modelling study</t>
+  </si>
+  <si>
+    <t>uses spatial autocorrelation inside the model</t>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7528758/</t>
+  </si>
+  <si>
+    <t>Geospatial analysis of dengue emergence in rural areas in the Southern Province of Sri Lanka</t>
+  </si>
+  <si>
+    <t>Spatial GAM using coordinates as covariates: coordinates had effect on dengue</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2212096322000365</t>
+  </si>
+  <si>
+    <t>Spatio-temporal detection for dengue outbreaks in the Central Region of Malaysia using climatic drivers at mesoscale and synoptic scale</t>
+  </si>
+  <si>
+    <t>GAM using weather and dummy for capital city. No coordinates, but spatial bc k regions and t times</t>
+  </si>
+  <si>
+    <t>https://www.pnas.org/doi/10.1073/pnas.2004978117</t>
+  </si>
+  <si>
+    <t>Spread and dynamics of the COVID-19 epidemic in Italy: Effects of emergency containment measures</t>
+  </si>
+  <si>
+    <t>Can do models on local scale because of granularity of data, quantify local effect of variables: is focused on SEIR on network</t>
+  </si>
+  <si>
+    <t>A joint spatial marked point process model for dengue and severe dengue in Medellin, Colombia</t>
+  </si>
+  <si>
+    <t>https://www.medrxiv.org/content/10.1101/2021.07.06.21260108v2.full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatial analysis using hierarchical Bayesian models: they find clusters </t>
+  </si>
+  <si>
+    <t>https://epiverse-trace.github.io/epimodelac/Sivirep-tutorial.html</t>
+  </si>
+  <si>
+    <t>Packete Sivigila</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-024-71807-3</t>
+  </si>
+  <si>
+    <t>Bayesian spatio-temporal analysis of dengue transmission in Lao PDR</t>
+  </si>
+  <si>
+    <t>Time series in 148 districts, include elevation and weather in all regions, Poisson regression</t>
   </si>
 </sst>
 </file>
@@ -1715,7 +1844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{354077A2-E602-4D9A-90DA-98AD5E623913}">
-  <dimension ref="B1:Q26"/>
+  <dimension ref="B1:Q41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -2150,6 +2279,204 @@
       </c>
       <c r="G26" s="39" t="s">
         <v>356</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B27" s="1">
+        <v>24</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="1">
+        <v>25</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B29" s="1">
+        <v>26</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B30" s="1">
+        <v>27</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B31" s="1">
+        <v>28</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B32" s="1">
+        <v>29</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="1">
+        <v>30</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="1">
+        <v>31</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="1">
+        <v>32</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="1">
+        <v>33</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="1">
+        <v>34</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B38" s="1">
+        <v>35</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="1">
+        <v>36</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="1">
+        <v>37</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="1">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2178,6 +2505,20 @@
     <hyperlink ref="E24" r:id="rId22" xr:uid="{4730B165-77B9-44CC-96F1-5D46B06A3B46}"/>
     <hyperlink ref="E25" r:id="rId23" xr:uid="{27F3ABE4-E9A8-4610-B13D-775FBB8CFAA5}"/>
     <hyperlink ref="E26" r:id="rId24" xr:uid="{9C94BE50-1EBB-4A1E-992C-64AF15F3BEC8}"/>
+    <hyperlink ref="E27" r:id="rId25" xr:uid="{63C4E218-DE76-4291-8915-8E79E7B9AEC1}"/>
+    <hyperlink ref="E28" r:id="rId26" xr:uid="{07877473-1316-4B0D-AC34-D30F2634C2A8}"/>
+    <hyperlink ref="E29" r:id="rId27" xr:uid="{F52E1B02-21BA-47C1-893E-2B59CB3DDF0C}"/>
+    <hyperlink ref="E30" r:id="rId28" xr:uid="{FBDB4828-B141-4E9A-AEC0-2B853A9EE2F0}"/>
+    <hyperlink ref="E31" r:id="rId29" xr:uid="{51F6BE93-C193-4782-A202-51C0DC26DD4A}"/>
+    <hyperlink ref="E32" r:id="rId30" xr:uid="{8E34C276-90B9-4788-8E6C-C1BC33721622}"/>
+    <hyperlink ref="E33" r:id="rId31" xr:uid="{F1A87C10-0685-4464-886A-0E8AF23ACC81}"/>
+    <hyperlink ref="E34" r:id="rId32" xr:uid="{B4D68C9C-A581-413C-921A-D4D8FCAF178B}"/>
+    <hyperlink ref="E35" r:id="rId33" xr:uid="{8C994E2F-6729-46A1-9F08-47FE809C312E}"/>
+    <hyperlink ref="E36" r:id="rId34" xr:uid="{BEC3ADD1-F4DD-4069-8A0E-8511649BF650}"/>
+    <hyperlink ref="E37" r:id="rId35" xr:uid="{E022F4DC-2BC4-4692-9ECF-731C2E359902}"/>
+    <hyperlink ref="E38" r:id="rId36" xr:uid="{A0E9EF5B-B1DA-481F-BA24-CE4583B2E18D}"/>
+    <hyperlink ref="E39" r:id="rId37" xr:uid="{B8098542-FD89-408B-9E12-0BFA9107DB90}"/>
+    <hyperlink ref="E40" r:id="rId38" xr:uid="{F737A6C6-04FF-4A90-8D59-5DA931CBE46E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2316,7 +2657,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA430712-2AF2-46BC-B2A9-A9F8B8AAD612}">
-  <dimension ref="B1:E26"/>
+  <dimension ref="B1:E27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -2519,6 +2860,14 @@
       </c>
       <c r="C26" s="1" t="s">
         <v>351</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -2545,6 +2894,7 @@
     <hyperlink ref="B24" r:id="rId20" xr:uid="{072E2C55-83F5-4678-A782-C260562B8B6B}"/>
     <hyperlink ref="B25" r:id="rId21" xr:uid="{0B637547-4E97-4EC3-B314-56A41CE2A5A5}"/>
     <hyperlink ref="B26" r:id="rId22" xr:uid="{74940AD8-16FA-4D19-8C89-A6E8C43ECBF9}"/>
+    <hyperlink ref="B27" r:id="rId23" xr:uid="{A7846FDF-CB73-40AC-9CCB-265DBBEC0AC2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
